--- a/data/sxbet/ligas/K2-League/trades.xlsx
+++ b/data/sxbet/ligas/K2-League/trades.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/data/sxbet/ligas/K2-League/trades.xlsx
+++ b/data/sxbet/ligas/K2-League/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V56"/>
+  <dimension ref="A1:V57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,31 +531,39 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x07b844c409deb0bc9c8e8dbda27c7c2b772aec07892356105db79f67ffb0e227</t>
+          <t>0x4da39049a709357f30ef968bfc90b4eec2da9d99090f3b99edf4ea11aeddd708</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6.39</t>
+          <t>32.79</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.5675</t>
+          <t>1.5488</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Hwaseong FC +0.5</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -563,27 +571,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC vs Yongin City</t>
+          <t>Hwaseong FC vs Daegu FC</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC</t>
+          <t>Hwaseong FC</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Daegu FC</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0xf73fcbba4baac94056070f4c2db509913d7317940066a6918ac1f13256f52327</t>
+          <t>0xbde5165c3a540b0c6dd64b3df320540fd10ecb173373b087359951e7f790f852</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19306783</t>
+          <t>L19382332</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -608,17 +616,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1785064787</t>
+          <t>1785527084</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1785061800</t>
+          <t>1785580200</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>11.259912</t>
+          <t>59.753986</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -635,28 +643,28 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0xf95f88d59f982dc2c9ca6387361b5a066ab48deeb7f9f6071274eb879ddabdd0</t>
+          <t>0x07b844c409deb0bc9c8e8dbda27c7c2b772aec07892356105db79f67ffb0e227</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>126.4351</t>
+          <t>6.39</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.815</t>
+          <t>1.5675</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
@@ -682,7 +690,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0x1482cd21984a144c2f6033821f76b4033b1aeaebbab5c85a758b2e86c0553134</t>
+          <t>0xf73fcbba4baac94056070f4c2db509913d7317940066a6918ac1f13256f52327</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -712,7 +720,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1785064732</t>
+          <t>1785064787</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -722,7 +730,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>155.135092</t>
+          <t>11.259912</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -739,39 +747,31 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0xe74ba88448233ab30d6e4b230046fe45bf1be0a6f71b8860703364abbbb40afe</t>
+          <t>0xf95f88d59f982dc2c9ca6387361b5a066ab48deeb7f9f6071274eb879ddabdd0</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>19.69</t>
+          <t>126.4351</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.5038</t>
+          <t>1.815</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Over 1.5</t>
-        </is>
-      </c>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -779,27 +779,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Paju Citizen vs Ansan Greeners</t>
+          <t>Gimpo Citizen FC vs Yongin City</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Gimpo Citizen FC</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0x6a23b140597c01b1670e03fdb996fc8e94424ec45a5e6e429b292ba1688dff5c</t>
+          <t>0x1482cd21984a144c2f6033821f76b4033b1aeaebbab5c85a758b2e86c0553134</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>L19306782</t>
+          <t>L19306783</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1785064111</t>
+          <t>1785064732</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>39.086849</t>
+          <t>155.135092</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -851,31 +851,39 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x02858e4fe5f076373faa42c17e9058ea19bff69a0b68493520c024b133c2ceed</t>
+          <t>0xe74ba88448233ab30d6e4b230046fe45bf1be0a6f71b8860703364abbbb40afe</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0x0C2DA7fC8702784d6f75c78Da25460783A6709a0</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>19.69</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.4975</t>
+          <t>1.5038</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Over 1.5</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -898,7 +906,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0x90106aa6ffeea165b450ea7a1094c65ae9db8d6fdde000ce479b4af5b3fa3072</t>
+          <t>0x6a23b140597c01b1670e03fdb996fc8e94424ec45a5e6e429b292ba1688dff5c</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -928,7 +936,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1785063804</t>
+          <t>1785064111</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -938,7 +946,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>6.030151</t>
+          <t>39.086849</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -955,39 +963,31 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0xd6b44cd45d93535a9c1b39fad13245ea6ef0e5cbff858b443a9d40a281cf422f</t>
+          <t>0x02858e4fe5f076373faa42c17e9058ea19bff69a0b68493520c024b133c2ceed</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x0C2DA7fC8702784d6f75c78Da25460783A6709a0</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>21.3</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.2988</t>
+          <t>1.4975</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Over 2.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -1010,7 +1010,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0x2d5eca3e665030fe8c7c2a84772b94d8fc59c9a6991fd216ba914d3b345ffe07</t>
+          <t>0x90106aa6ffeea165b450ea7a1094c65ae9db8d6fdde000ce479b4af5b3fa3072</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1785063590</t>
+          <t>1785063804</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1050,7 +1050,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>71.297071</t>
+          <t>6.030151</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1067,7 +1067,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0xc41eea20c9aa34da894372c77f23e0a6ee134568f117e95b14c294310b2dc1f7</t>
+          <t>0xd6b44cd45d93535a9c1b39fad13245ea6ef0e5cbff858b443a9d40a281cf422f</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1082,22 +1082,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>12.53</t>
+          <t>21.3</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.2037</t>
+          <t>1.2988</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Over 2.5</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1107,27 +1107,27 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC vs Yongin City</t>
+          <t>Paju Citizen vs Ansan Greeners</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0x520e073f044523b55003a1d70f752c30f91cd5ebae7e23b2f294ad6679b3ed58</t>
+          <t>0x2d5eca3e665030fe8c7c2a84772b94d8fc59c9a6991fd216ba914d3b345ffe07</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>L19306783</t>
+          <t>L19306782</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1785063530</t>
+          <t>1785063590</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>61.496933</t>
+          <t>71.297071</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1179,7 +1179,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0xe5a4265d3896fe621f44bfc6c8c9d2efe8a044ac121c6a5ec411dcd8ecbb22c9</t>
+          <t>0xc41eea20c9aa34da894372c77f23e0a6ee134568f117e95b14c294310b2dc1f7</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1194,12 +1194,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12.53</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.5162</t>
+          <t>1.2037</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1209,24 +1209,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
+          <t>Yongin City</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>K2-League</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen FC vs Yongin City</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>Gimpo Citizen FC</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>K2-League</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Gimpo Citizen FC vs Yongin City</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Gimpo Citizen FC</t>
-        </is>
-      </c>
       <c r="K8" t="inlineStr">
         <is>
           <t>Yongin City</t>
@@ -1234,7 +1234,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0x2725ecc350e6d5314ddee250cd3e445f586ab55a992fc73108db0913c5a41f24</t>
+          <t>0x520e073f044523b55003a1d70f752c30f91cd5ebae7e23b2f294ad6679b3ed58</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1785063352</t>
+          <t>1785063530</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1.937046</t>
+          <t>61.496933</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1291,7 +1291,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0x996289847910ea662fcd868b20c9fa48f68ab4d7334bac4351bc46b6d3f479df</t>
+          <t>0xe5a4265d3896fe621f44bfc6c8c9d2efe8a044ac121c6a5ec411dcd8ecbb22c9</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1376,7 +1376,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1785063326</t>
+          <t>1785063352</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1403,7 +1403,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0xed44d31e5a5b7071006924700a0078a2f8a3710d9bb8d24217652d198ffae7d7</t>
+          <t>0x996289847910ea662fcd868b20c9fa48f68ab4d7334bac4351bc46b6d3f479df</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>28.84</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1785063319</t>
+          <t>1785063326</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>55.864407</t>
+          <t>1.937046</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1515,7 +1515,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x2bcba69d716b343c190b4a215a8f323f4abe23b13cd57d716f1b386e77406d71</t>
+          <t>0xed44d31e5a5b7071006924700a0078a2f8a3710d9bb8d24217652d198ffae7d7</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1523,23 +1523,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>28.84</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.3912</t>
+          <t>1.5162</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen FC</t>
+        </is>
+      </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -1562,7 +1570,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0xf73fcbba4baac94056070f4c2db509913d7317940066a6918ac1f13256f52327</t>
+          <t>0x2725ecc350e6d5314ddee250cd3e445f586ab55a992fc73108db0913c5a41f24</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1602,7 +1610,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>6.696486</t>
+          <t>55.864407</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1619,7 +1627,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x74897816645fe410040b71368723e823f96b8b8ad1a8558a60563ea6a63c17b9</t>
+          <t>0x2bcba69d716b343c190b4a215a8f323f4abe23b13cd57d716f1b386e77406d71</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1627,31 +1635,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.5488</t>
+          <t>1.3912</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Paju Citizen</t>
-        </is>
-      </c>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -1659,27 +1659,27 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Paju Citizen vs Ansan Greeners</t>
+          <t>Gimpo Citizen FC vs Yongin City</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Gimpo Citizen FC</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0x90106aa6ffeea165b450ea7a1094c65ae9db8d6fdde000ce479b4af5b3fa3072</t>
+          <t>0xf73fcbba4baac94056070f4c2db509913d7317940066a6918ac1f13256f52327</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>L19306782</t>
+          <t>L19306783</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1785063283</t>
+          <t>1785063319</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>18.223235</t>
+          <t>6.696486</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1731,7 +1731,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0x6c9b96e6ea55e8d6386264e63d154ad9cdf850c8f9c18b5c088abdcfcc710e8d</t>
+          <t>0x74897816645fe410040b71368723e823f96b8b8ad1a8558a60563ea6a63c17b9</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1739,15 +1739,19 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1.74999</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.8313</t>
+          <t>1.5488</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1755,7 +1759,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Paju Citizen</t>
+        </is>
+      </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -1778,7 +1786,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0x6de105784818e175bb2cb50f54d4325a684a5693a05f8bd5b7f2b402aeb4bdfa</t>
+          <t>0x90106aa6ffeea165b450ea7a1094c65ae9db8d6fdde000ce479b4af5b3fa3072</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1808,7 +1816,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1785063278</t>
+          <t>1785063283</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1818,7 +1826,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2.105251</t>
+          <t>18.223235</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1835,7 +1843,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0x653ed25ca6aba498efe0c95f6d394f607985bf6c4ab830c3599772279631e8b1</t>
+          <t>0x6c9b96e6ea55e8d6386264e63d154ad9cdf850c8f9c18b5c088abdcfcc710e8d</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1846,12 +1854,12 @@
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>201.32998</t>
+          <t>1.74999</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.8213</t>
+          <t>1.8313</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1912,7 +1920,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1785063071</t>
+          <t>1785063278</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1922,7 +1930,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>245.150661</t>
+          <t>2.105251</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1939,23 +1947,23 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0xd7beeace3688b4d75f908058620cd47f10d9926e086901a2c83333dd169ec720</t>
+          <t>0x653ed25ca6aba498efe0c95f6d394f607985bf6c4ab830c3599772279631e8b1</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>48.03</t>
+          <t>201.32998</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.8213</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1971,27 +1979,27 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC vs Yongin City</t>
+          <t>Paju Citizen vs Ansan Greeners</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0x2725ecc350e6d5314ddee250cd3e445f586ab55a992fc73108db0913c5a41f24</t>
+          <t>0x6de105784818e175bb2cb50f54d4325a684a5693a05f8bd5b7f2b402aeb4bdfa</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>L19306783</t>
+          <t>L19306782</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2016,7 +2024,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1785062970</t>
+          <t>1785063071</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2026,7 +2034,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>98.020408</t>
+          <t>245.150661</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2043,23 +2051,23 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0x8940d52e7feb848f5ca44e42ecc2fed94e942961b918122bc87142ffbf346d4c</t>
+          <t>0xd7beeace3688b4d75f908058620cd47f10d9926e086901a2c83333dd169ec720</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>196.03997</t>
+          <t>48.03</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.8188</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2075,27 +2083,27 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Paju Citizen vs Ansan Greeners</t>
+          <t>Gimpo Citizen FC vs Yongin City</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Gimpo Citizen FC</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0x6de105784818e175bb2cb50f54d4325a684a5693a05f8bd5b7f2b402aeb4bdfa</t>
+          <t>0x2725ecc350e6d5314ddee250cd3e445f586ab55a992fc73108db0913c5a41f24</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>L19306782</t>
+          <t>L19306783</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2120,7 +2128,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1785062953</t>
+          <t>1785062970</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2130,7 +2138,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>239.438131</t>
+          <t>98.020408</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2147,7 +2155,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0x2b9441f7515eb95a00a5708be64644050b069886b2e84d77ecdeea72fe8e3da7</t>
+          <t>0x8940d52e7feb848f5ca44e42ecc2fed94e942961b918122bc87142ffbf346d4c</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2155,19 +2163,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>12.06</t>
+          <t>196.03997</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.1975</t>
+          <t>1.8188</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2175,11 +2179,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Yongin City</t>
-        </is>
-      </c>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -2187,27 +2187,27 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC vs Yongin City</t>
+          <t>Paju Citizen vs Ansan Greeners</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0x520e073f044523b55003a1d70f752c30f91cd5ebae7e23b2f294ad6679b3ed58</t>
+          <t>0x6de105784818e175bb2cb50f54d4325a684a5693a05f8bd5b7f2b402aeb4bdfa</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>L19306783</t>
+          <t>L19306782</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1785062934</t>
+          <t>1785062953</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2242,7 +2242,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>61.063291</t>
+          <t>239.438131</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2259,7 +2259,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0x17ea9fc34d8d08859197baf8694510eafd385c5cb30d1bccaf4135418710a4ee</t>
+          <t>0x2b9441f7515eb95a00a5708be64644050b069886b2e84d77ecdeea72fe8e3da7</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2274,22 +2274,22 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12.06</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.3862</t>
+          <t>1.1975</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Over 2.5</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2299,27 +2299,27 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Paju Citizen vs Ansan Greeners</t>
+          <t>Gimpo Citizen FC vs Yongin City</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Gimpo Citizen FC</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0x2d5eca3e665030fe8c7c2a84772b94d8fc59c9a6991fd216ba914d3b345ffe07</t>
+          <t>0x520e073f044523b55003a1d70f752c30f91cd5ebae7e23b2f294ad6679b3ed58</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>L19306782</t>
+          <t>L19306783</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2344,7 +2344,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1785062748</t>
+          <t>1785062934</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2354,7 +2354,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>25.889968</t>
+          <t>61.063291</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2371,7 +2371,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0xff313e8a80cab759f0306eced2743a83b68017dd8ecc4a5eda49613abd5f72bb</t>
+          <t>0x17ea9fc34d8d08859197baf8694510eafd385c5cb30d1bccaf4135418710a4ee</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2391,17 +2391,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.2275</t>
+          <t>1.3862</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Over 3.5</t>
+          <t>Over 2.5</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0x20fab15d1baac82bbe5a9371ad4e1e4f931edb8de76d814e671a0313aa4d8620</t>
+          <t>0x2d5eca3e665030fe8c7c2a84772b94d8fc59c9a6991fd216ba914d3b345ffe07</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1785062437</t>
+          <t>1785062748</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2466,7 +2466,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>43.956044</t>
+          <t>25.889968</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2483,7 +2483,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0x5a88256e6b892595ad641ef1ae589c088b32b6034ec557ba72582fa8c93f67e3</t>
+          <t>0xff313e8a80cab759f0306eced2743a83b68017dd8ecc4a5eda49613abd5f72bb</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2491,23 +2491,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>64.98999</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.8125</t>
+          <t>1.2275</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr"/>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
       <c r="H20" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -2530,7 +2538,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0x6de105784818e175bb2cb50f54d4325a684a5693a05f8bd5b7f2b402aeb4bdfa</t>
+          <t>0x20fab15d1baac82bbe5a9371ad4e1e4f931edb8de76d814e671a0313aa4d8620</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2560,7 +2568,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1785062111</t>
+          <t>1785062437</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2570,7 +2578,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>79.98768</t>
+          <t>43.956044</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2587,39 +2595,31 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0x21aa47ce5d327006a8fdcf609e5990b1ea5499887fd8ccd0ff96d5bbe7df2f89</t>
+          <t>0x5a88256e6b892595ad641ef1ae589c088b32b6034ec557ba72582fa8c93f67e3</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>23.39</t>
+          <t>64.98999</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.3887</t>
+          <t>1.8125</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Paju Citizen -1</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -2642,7 +2642,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0x1398d7baccf6c5154c8090892c6597852ff56e90298e81fb604a8b9bf22c47ce</t>
+          <t>0x6de105784818e175bb2cb50f54d4325a684a5693a05f8bd5b7f2b402aeb4bdfa</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2672,7 +2672,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1785061695</t>
+          <t>1785062111</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2682,7 +2682,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>60.167203</t>
+          <t>79.98768</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2699,7 +2699,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0xaa13e9d13e81cd9edae13a80c0e426e52c85c5064c5b0c34d792d027f33fe560</t>
+          <t>0x21aa47ce5d327006a8fdcf609e5990b1ea5499887fd8ccd0ff96d5bbe7df2f89</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2714,22 +2714,22 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>17.04</t>
+          <t>23.39</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.3887</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Paju Citizen -1.5</t>
+          <t>Paju Citizen -1</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2754,7 +2754,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0x48cd5a7ee72c95f57110826c0f2e2494d9438250815f7751e5e0fdce91ccbfba</t>
+          <t>0x1398d7baccf6c5154c8090892c6597852ff56e90298e81fb604a8b9bf22c47ce</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1785061694</t>
+          <t>1785061695</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2794,7 +2794,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>58.758621</t>
+          <t>60.167203</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2811,31 +2811,39 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0x9c2da91ae7561670702979941233734bebc22c36fdac867bf5bdb53a8151c6e9</t>
+          <t>0xaa13e9d13e81cd9edae13a80c0e426e52c85c5064c5b0c34d792d027f33fe560</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>4.99997</t>
+          <t>17.04</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.795</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr"/>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Paju Citizen -1.5</t>
+        </is>
+      </c>
       <c r="H23" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -2843,27 +2851,27 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC vs Yongin City</t>
+          <t>Paju Citizen vs Ansan Greeners</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0x520e073f044523b55003a1d70f752c30f91cd5ebae7e23b2f294ad6679b3ed58</t>
+          <t>0x48cd5a7ee72c95f57110826c0f2e2494d9438250815f7751e5e0fdce91ccbfba</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>L19306783</t>
+          <t>L19306782</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2888,7 +2896,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1785061651</t>
+          <t>1785061694</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -2898,7 +2906,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>6.28927</t>
+          <t>58.758621</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2915,39 +2923,31 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0x12f98497a1f2dc0a130b32665dfeea9bbd9b744c2732456c77c91801ec687167</t>
+          <t>0x9c2da91ae7561670702979941233734bebc22c36fdac867bf5bdb53a8151c6e9</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>21.14</t>
+          <t>4.99997</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.3513</t>
+          <t>1.795</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Gimpo Citizen FC -1</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -2970,7 +2970,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0x4a4b2cf0de4356e1be221d31aa0feab4af681e89956037ff111c72307c4d9af6</t>
+          <t>0x520e073f044523b55003a1d70f752c30f91cd5ebae7e23b2f294ad6679b3ed58</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1785061621</t>
+          <t>1785061651</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3010,7 +3010,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>60.185053</t>
+          <t>6.28927</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3027,7 +3027,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0x0f90aefde05859a865353743603e3925fef0a390e252c71ca62de94b7f3522d8</t>
+          <t>0x12f98497a1f2dc0a130b32665dfeea9bbd9b744c2732456c77c91801ec687167</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3035,23 +3035,31 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr"/>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>43.51167</t>
+          <t>21.14</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.795</t>
+          <t>1.3513</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr"/>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen FC -1</t>
+        </is>
+      </c>
       <c r="H25" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -3074,7 +3082,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0x520e073f044523b55003a1d70f752c30f91cd5ebae7e23b2f294ad6679b3ed58</t>
+          <t>0x4a4b2cf0de4356e1be221d31aa0feab4af681e89956037ff111c72307c4d9af6</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -3114,7 +3122,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>54.73166</t>
+          <t>60.185053</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3131,28 +3139,28 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0x45f1170f51d54ba31ead65b241ce33b618358dd91421e9194877f824ebea4f5d</t>
+          <t>0x0f90aefde05859a865353743603e3925fef0a390e252c71ca62de94b7f3522d8</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0x09b3a190a1e971Dd0B4F82Eb9008287fe43a540C</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>43.51167</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.795</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
@@ -3178,7 +3186,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0x7b353104df193f280c01b3e0a75dcbbc5dd4e628b7304c3537dff2339968d702</t>
+          <t>0x520e073f044523b55003a1d70f752c30f91cd5ebae7e23b2f294ad6679b3ed58</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -3208,7 +3216,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1785061583</t>
+          <t>1785061621</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3218,7 +3226,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>51.020408</t>
+          <t>54.73166</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3235,28 +3243,28 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0x8726e3d54f033c4394f3b9a8a297c466f26e8d1814d525163146dc1f9f836029</t>
+          <t>0x45f1170f51d54ba31ead65b241ce33b618358dd91421e9194877f824ebea4f5d</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x09b3a190a1e971Dd0B4F82Eb9008287fe43a540C</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>5.70997</t>
+          <t>25</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.795</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
@@ -3282,7 +3290,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0x520e073f044523b55003a1d70f752c30f91cd5ebae7e23b2f294ad6679b3ed58</t>
+          <t>0x7b353104df193f280c01b3e0a75dcbbc5dd4e628b7304c3537dff2339968d702</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -3312,7 +3320,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1785061581</t>
+          <t>1785061583</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3322,7 +3330,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>7.182352</t>
+          <t>51.020408</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3339,27 +3347,23 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0x78b589b7ea305b8a325e286dcbf526301e19f803d90ab77960c290d1d621d34a</t>
+          <t>0x8726e3d54f033c4394f3b9a8a297c466f26e8d1814d525163146dc1f9f836029</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0x09b3a190a1e971Dd0B4F82Eb9008287fe43a540C</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>5.01384</t>
+          <t>5.70997</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.2788</t>
+          <t>1.795</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -3367,11 +3371,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0xf93dab40773f0e01839824957e7cecd4afb676d72a13c45521719f4f5c517a27</t>
+          <t>0x520e073f044523b55003a1d70f752c30f91cd5ebae7e23b2f294ad6679b3ed58</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1785061533</t>
+          <t>1785061581</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3434,7 +3434,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>17.98687</t>
+          <t>7.182352</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3451,23 +3451,27 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0x64d493da52ab9f3215f2ee6a066aad2cbaf66597963522c2c53462ae6d466e65</t>
+          <t>0x78b589b7ea305b8a325e286dcbf526301e19f803d90ab77960c290d1d621d34a</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr"/>
+          <t>0x09b3a190a1e971Dd0B4F82Eb9008287fe43a540C</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>43.87998</t>
+          <t>5.01384</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.7988</t>
+          <t>1.2788</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -3475,7 +3479,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H29" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -3498,7 +3506,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0x520e073f044523b55003a1d70f752c30f91cd5ebae7e23b2f294ad6679b3ed58</t>
+          <t>0xf93dab40773f0e01839824957e7cecd4afb676d72a13c45521719f4f5c517a27</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -3528,7 +3536,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1785061346</t>
+          <t>1785061533</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3538,7 +3546,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>54.935812</t>
+          <t>17.98687</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3555,7 +3563,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0xb6a5b0e5cc84223b1b456506ce5bc4a60492c7d715d16ce5ba4bcbbbb205e549</t>
+          <t>0x64d493da52ab9f3215f2ee6a066aad2cbaf66597963522c2c53462ae6d466e65</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3566,7 +3574,7 @@
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>10.19999</t>
+          <t>43.87998</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -3632,7 +3640,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1785061261</t>
+          <t>1785061346</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3642,7 +3650,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>12.769941</t>
+          <t>54.935812</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3659,18 +3667,18 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0x932ea4448a5d14be89226effb4bcb8584e5004da981b9fb12e769029a2cd6a34</t>
+          <t>0xb6a5b0e5cc84223b1b456506ce5bc4a60492c7d715d16ce5ba4bcbbbb205e549</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10.19999</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -3736,7 +3744,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1785061250</t>
+          <t>1785061261</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -3746,7 +3754,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>6.259781</t>
+          <t>12.769941</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3763,23 +3771,23 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0x6ba96fe1be95723f4530ab62caaff2817e70e2c1aa504d2f0afe5b7d44447528</t>
+          <t>0x932ea4448a5d14be89226effb4bcb8584e5004da981b9fb12e769029a2cd6a34</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>43.12404</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.7975</t>
+          <t>1.7988</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -3840,7 +3848,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1785061221</t>
+          <t>1785061250</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -3850,7 +3858,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>54.074031</t>
+          <t>6.259781</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3867,27 +3875,23 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0xa4c5cc7d130116507c7f97158d19bded9ace84b90e4089b2386235aca563a109</t>
+          <t>0x6ba96fe1be95723f4530ab62caaff2817e70e2c1aa504d2f0afe5b7d44447528</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>5.54</t>
+          <t>43.12404</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.2537</t>
+          <t>1.7975</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -3895,11 +3899,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -3907,27 +3907,27 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Paju Citizen vs Ansan Greeners</t>
+          <t>Gimpo Citizen FC vs Yongin City</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Gimpo Citizen FC</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0xabfa364122222118f5f35af9ee862e2b9587e9c2f656e281725fdca100cf17bf</t>
+          <t>0x520e073f044523b55003a1d70f752c30f91cd5ebae7e23b2f294ad6679b3ed58</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>L19306782</t>
+          <t>L19306783</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -3952,7 +3952,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1785060618</t>
+          <t>1785061221</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -3962,7 +3962,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>21.832512</t>
+          <t>54.074031</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -3979,23 +3979,27 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0xed6f77aaa7a7dbe5c2457f000b022f2da0cc5bd1004291d76e71044f4e1faa36</t>
+          <t>0xa4c5cc7d130116507c7f97158d19bded9ace84b90e4089b2386235aca563a109</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>4.99999</t>
+          <t>5.54</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.7975</t>
+          <t>1.2537</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -4003,7 +4007,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H34" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -4011,27 +4019,27 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC vs Yongin City</t>
+          <t>Paju Citizen vs Ansan Greeners</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0x520e073f044523b55003a1d70f752c30f91cd5ebae7e23b2f294ad6679b3ed58</t>
+          <t>0xabfa364122222118f5f35af9ee862e2b9587e9c2f656e281725fdca100cf17bf</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>L19306783</t>
+          <t>L19306782</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -4056,7 +4064,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1785060105</t>
+          <t>1785060618</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -4066,7 +4074,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>6.26958</t>
+          <t>21.832512</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4083,7 +4091,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0xe0d4aa08492162b980b70ecc4ec3e9ae46b9fd85fea771f538c542e4e27f10ca</t>
+          <t>0xed6f77aaa7a7dbe5c2457f000b022f2da0cc5bd1004291d76e71044f4e1faa36</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4160,7 +4168,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1785060103</t>
+          <t>1785060105</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -4187,7 +4195,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0x733bd5ce99f877eba370291936b138251c1bd48cee90480bc876f49523ca7fca</t>
+          <t>0xe0d4aa08492162b980b70ecc4ec3e9ae46b9fd85fea771f538c542e4e27f10ca</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4264,7 +4272,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1785060101</t>
+          <t>1785060103</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -4291,39 +4299,31 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0xcfbe574677265ef97dc3204a001ce1b1e25523c8a98c296a3cf235f97650aace</t>
+          <t>0x733bd5ce99f877eba370291936b138251c1bd48cee90480bc876f49523ca7fca</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.99999</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.3887</t>
+          <t>1.7975</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Paju Citizen -1</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -4331,27 +4331,27 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Paju Citizen vs Ansan Greeners</t>
+          <t>Gimpo Citizen FC vs Yongin City</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Gimpo Citizen FC</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0x1398d7baccf6c5154c8090892c6597852ff56e90298e81fb604a8b9bf22c47ce</t>
+          <t>0x520e073f044523b55003a1d70f752c30f91cd5ebae7e23b2f294ad6679b3ed58</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>L19306782</t>
+          <t>L19306783</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -4376,7 +4376,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1785060085</t>
+          <t>1785060101</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>10.289389</t>
+          <t>6.26958</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4403,31 +4403,39 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0xebd1df0aa7e7f54677bedd84a6c923ca856cf657e0531639938bfb8111becc94</t>
+          <t>0xcfbe574677265ef97dc3204a001ce1b1e25523c8a98c296a3cf235f97650aace</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>22.97198</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.7963</t>
+          <t>1.3887</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr"/>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Paju Citizen -1</t>
+        </is>
+      </c>
       <c r="H38" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -4435,27 +4443,27 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC vs Yongin City</t>
+          <t>Paju Citizen vs Ansan Greeners</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0x520e073f044523b55003a1d70f752c30f91cd5ebae7e23b2f294ad6679b3ed58</t>
+          <t>0x1398d7baccf6c5154c8090892c6597852ff56e90298e81fb604a8b9bf22c47ce</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>L19306783</t>
+          <t>L19306782</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -4480,7 +4488,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1785060074</t>
+          <t>1785060085</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -4490,7 +4498,7 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>28.85021</t>
+          <t>10.289389</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4507,7 +4515,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0x9137623e3c72596dddeb8dd77deb26f0f80f5d8ad5037c9d9fd9ec11f1d3a62d</t>
+          <t>0xebd1df0aa7e7f54677bedd84a6c923ca856cf657e0531639938bfb8111becc94</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4518,7 +4526,7 @@
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>15.59279</t>
+          <t>22.97198</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -4584,7 +4592,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1785060073</t>
+          <t>1785060074</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -4594,7 +4602,7 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>19.582782</t>
+          <t>28.85021</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4611,7 +4619,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0x47fecae2c93459e7d6a1189dcb95e8bce239b7e2d26ce67db4733b564451a3fd</t>
+          <t>0x9137623e3c72596dddeb8dd77deb26f0f80f5d8ad5037c9d9fd9ec11f1d3a62d</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4622,7 +4630,7 @@
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>16.1469</t>
+          <t>15.59279</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -4688,7 +4696,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1785060072</t>
+          <t>1785060073</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -4698,7 +4706,7 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>20.278681</t>
+          <t>19.582782</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -4715,27 +4723,23 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0x7851323bb653ef81f86e4483a09baec3f52472a947788d079eacebc8ce474280</t>
+          <t>0x47fecae2c93459e7d6a1189dcb95e8bce239b7e2d26ce67db4733b564451a3fd</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>19.02</t>
+          <t>16.1469</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.275</t>
+          <t>1.7963</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -4743,11 +4747,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -4770,7 +4770,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0xf93dab40773f0e01839824957e7cecd4afb676d72a13c45521719f4f5c517a27</t>
+          <t>0x520e073f044523b55003a1d70f752c30f91cd5ebae7e23b2f294ad6679b3ed58</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -4800,7 +4800,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1785060054</t>
+          <t>1785060072</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -4810,7 +4810,7 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>69.163636</t>
+          <t>20.278681</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -4827,12 +4827,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0x5936a0069456d68663344829a3e2e9aa688da6a9e1d38de76848d1bdfb84366a</t>
+          <t>0x7851323bb653ef81f86e4483a09baec3f52472a947788d079eacebc8ce474280</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -4842,12 +4842,12 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>10.56</t>
+          <t>19.02</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.2737</t>
+          <t>1.275</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -4912,7 +4912,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1785060044</t>
+          <t>1785060054</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -4922,7 +4922,7 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>38.575342</t>
+          <t>69.163636</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -4939,31 +4939,39 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0xc27dc932de76aa5047aab63fd483f2351fd3e777a4bebc494353cf3a53c52ba9</t>
+          <t>0x5936a0069456d68663344829a3e2e9aa688da6a9e1d38de76848d1bdfb84366a</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>20.61772</t>
+          <t>10.56</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.3425</t>
+          <t>1.2737</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H43" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -4971,27 +4979,27 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Paju Citizen vs Ansan Greeners</t>
+          <t>Gimpo Citizen FC vs Yongin City</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Gimpo Citizen FC</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0x386468865ee4fb2d064354b0f4bb50fc57a8f046452fa6667bc56978f4cf3823</t>
+          <t>0xf93dab40773f0e01839824957e7cecd4afb676d72a13c45521719f4f5c517a27</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>L19306782</t>
+          <t>L19306783</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -5016,7 +5024,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1785059855</t>
+          <t>1785060044</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -5026,7 +5034,7 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>60.197723</t>
+          <t>38.575342</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -5043,7 +5051,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0x06cf39065296686830cf556b4943f2a94e035610868690980b237da489f6c32a</t>
+          <t>0xc27dc932de76aa5047aab63fd483f2351fd3e777a4bebc494353cf3a53c52ba9</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5051,31 +5059,23 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>4.94155</t>
+          <t>20.61772</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.355</t>
+          <t>1.3425</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>Gimpo Citizen FC -1</t>
-        </is>
-      </c>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -5083,27 +5083,27 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC vs Yongin City</t>
+          <t>Paju Citizen vs Ansan Greeners</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0x4a4b2cf0de4356e1be221d31aa0feab4af681e89956037ff111c72307c4d9af6</t>
+          <t>0x386468865ee4fb2d064354b0f4bb50fc57a8f046452fa6667bc56978f4cf3823</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>L19306783</t>
+          <t>L19306782</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -5128,7 +5128,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>1785059821</t>
+          <t>1785059855</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>13.919859</t>
+          <t>60.197723</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -5155,7 +5155,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0x6cad572e295e86d0eff792e6a73f1ecb4b2563c632f3a61d710a79a81bcbefc5</t>
+          <t>0x06cf39065296686830cf556b4943f2a94e035610868690980b237da489f6c32a</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5170,7 +5170,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>16.43</t>
+          <t>4.94155</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -5240,7 +5240,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>1785059820</t>
+          <t>1785059821</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
@@ -5250,7 +5250,7 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>46.28169</t>
+          <t>13.919859</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -5267,31 +5267,39 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0xd90cf2f29f54991a5ee8c926cce019177b5bb5fd98602218fb9acaaf6a910664</t>
+          <t>0x6cad572e295e86d0eff792e6a73f1ecb4b2563c632f3a61d710a79a81bcbefc5</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>16.43</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.4675</t>
+          <t>1.355</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr"/>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen FC -1</t>
+        </is>
+      </c>
       <c r="H46" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -5299,27 +5307,27 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Paju Citizen vs Ansan Greeners</t>
+          <t>Gimpo Citizen FC vs Yongin City</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Gimpo Citizen FC</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>0x90106aa6ffeea165b450ea7a1094c65ae9db8d6fdde000ce479b4af5b3fa3072</t>
+          <t>0x4a4b2cf0de4356e1be221d31aa0feab4af681e89956037ff111c72307c4d9af6</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>L19306782</t>
+          <t>L19306783</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -5344,7 +5352,7 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>1785058466</t>
+          <t>1785059820</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
@@ -5354,7 +5362,7 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>23.529412</t>
+          <t>46.28169</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -5371,27 +5379,23 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0xfaacadf40a626e2b5b306c37ecce7325e0fabbb091c125c037dd14587c31bfe4</t>
+          <t>0xd90cf2f29f54991a5ee8c926cce019177b5bb5fd98602218fb9acaaf6a910664</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>4.53</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.5212</t>
+          <t>1.4675</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -5399,11 +5403,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>Gimpo Citizen FC</t>
-        </is>
-      </c>
+      <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -5411,27 +5411,27 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC vs Yongin City</t>
+          <t>Paju Citizen vs Ansan Greeners</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>0x2725ecc350e6d5314ddee250cd3e445f586ab55a992fc73108db0913c5a41f24</t>
+          <t>0x90106aa6ffeea165b450ea7a1094c65ae9db8d6fdde000ce479b4af5b3fa3072</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>L19306783</t>
+          <t>L19306782</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>1785057353</t>
+          <t>1785058466</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>8.690647</t>
+          <t>23.529412</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -5483,7 +5483,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0x182964c6008d5b7d29731fd19876092a52fa2068fcb16aaf430dd8e0a6009721</t>
+          <t>0xfaacadf40a626e2b5b306c37ecce7325e0fabbb091c125c037dd14587c31bfe4</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>3.73</t>
+          <t>4.53</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.2763</t>
+          <t>1.5212</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -5513,7 +5513,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Gimpo Citizen FC</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -5538,7 +5538,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>0xf93dab40773f0e01839824957e7cecd4afb676d72a13c45521719f4f5c517a27</t>
+          <t>0x2725ecc350e6d5314ddee250cd3e445f586ab55a992fc73108db0913c5a41f24</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -5568,7 +5568,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>1785057212</t>
+          <t>1785057353</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
@@ -5578,7 +5578,7 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>13.502262</t>
+          <t>8.690647</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -5595,12 +5595,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0xae029509b64a4e0489363d3aa1a7e18db0cd21b4fb65f5064e49185bb4bfb2f6</t>
+          <t>0x182964c6008d5b7d29731fd19876092a52fa2068fcb16aaf430dd8e0a6009721</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3.73</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.2763</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -5625,24 +5625,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>K2-League</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen FC vs Yongin City</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
           <t>Gimpo Citizen FC</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>K2-League</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>Gimpo Citizen FC vs Yongin City</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>Gimpo Citizen FC</t>
-        </is>
-      </c>
       <c r="K49" t="inlineStr">
         <is>
           <t>Yongin City</t>
@@ -5650,7 +5650,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>0x2725ecc350e6d5314ddee250cd3e445f586ab55a992fc73108db0913c5a41f24</t>
+          <t>0xf93dab40773f0e01839824957e7cecd4afb676d72a13c45521719f4f5c517a27</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -5680,7 +5680,7 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>1785056897</t>
+          <t>1785057212</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
@@ -5690,7 +5690,7 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>9.615385</t>
+          <t>13.502262</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -5707,12 +5707,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0xd359a1bde933becdef3ca166f20bbe9291a9b81f961befead4bc72e1713c6447</t>
+          <t>0xae029509b64a4e0489363d3aa1a7e18db0cd21b4fb65f5064e49185bb4bfb2f6</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -5722,7 +5722,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>4.53999</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -5792,7 +5792,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>1785056453</t>
+          <t>1785056897</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
@@ -5802,7 +5802,7 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>8.73075</t>
+          <t>9.615385</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -5819,7 +5819,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0xe5784e1cc6cec364d74a7267a701924cf5f6543fed6d0c11d5f756f735c714f2</t>
+          <t>0xd359a1bde933becdef3ca166f20bbe9291a9b81f961befead4bc72e1713c6447</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5834,7 +5834,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>4.53999</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -5904,7 +5904,7 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>1785056153</t>
+          <t>1785056453</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
@@ -5914,7 +5914,7 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>8.75</t>
+          <t>8.73075</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -5931,7 +5931,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0x2fe44b6f9df282a6669198530843764a881fcd8c491dca571eaacc128af126e6</t>
+          <t>0xe5784e1cc6cec364d74a7267a701924cf5f6543fed6d0c11d5f756f735c714f2</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5946,12 +5946,12 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>9.99999</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1.5425</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -5961,7 +5961,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Gimpo Citizen FC</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -5971,27 +5971,27 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Paju Citizen vs Ansan Greeners</t>
+          <t>Gimpo Citizen FC vs Yongin City</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Gimpo Citizen FC</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>0x90106aa6ffeea165b450ea7a1094c65ae9db8d6fdde000ce479b4af5b3fa3072</t>
+          <t>0x2725ecc350e6d5314ddee250cd3e445f586ab55a992fc73108db0913c5a41f24</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>L19306782</t>
+          <t>L19306783</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -6016,7 +6016,7 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>1785056005</t>
+          <t>1785056153</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
@@ -6026,7 +6026,7 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>18.433161</t>
+          <t>8.75</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -6043,7 +6043,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0x318bf0ba1d202676e38a34cf3a263bf2f98d89a54dbf8acb2cccc6beaedcc4e8</t>
+          <t>0x2fe44b6f9df282a6669198530843764a881fcd8c491dca571eaacc128af126e6</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -6058,12 +6058,12 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>9.99999</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1.2575</t>
+          <t>1.5425</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -6073,7 +6073,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -6098,7 +6098,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>0xabfa364122222118f5f35af9ee862e2b9587e9c2f656e281725fdca100cf17bf</t>
+          <t>0x90106aa6ffeea165b450ea7a1094c65ae9db8d6fdde000ce479b4af5b3fa3072</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -6128,7 +6128,7 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>1785055933</t>
+          <t>1785056005</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
@@ -6138,7 +6138,7 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>4.970874</t>
+          <t>18.433161</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -6155,7 +6155,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0x5dc684f3ea699d27149c867fb82e4e6f97c7382b6d8784e4edd5bf70e604bae2</t>
+          <t>0x318bf0ba1d202676e38a34cf3a263bf2f98d89a54dbf8acb2cccc6beaedcc4e8</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -6170,7 +6170,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -6240,7 +6240,7 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>1785055931</t>
+          <t>1785055933</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>9.941748</t>
+          <t>4.970874</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -6267,7 +6267,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0x947b403314498890960e964926f3e25010f3b36a93afc49e309f7a71a57648b0</t>
+          <t>0x5dc684f3ea699d27149c867fb82e4e6f97c7382b6d8784e4edd5bf70e604bae2</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6282,12 +6282,12 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.2575</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -6297,7 +6297,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC</t>
+          <t>Tie</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -6307,27 +6307,27 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC vs Yongin City</t>
+          <t>Paju Citizen vs Ansan Greeners</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>0x2725ecc350e6d5314ddee250cd3e445f586ab55a992fc73108db0913c5a41f24</t>
+          <t>0xabfa364122222118f5f35af9ee862e2b9587e9c2f656e281725fdca100cf17bf</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>L19306783</t>
+          <t>L19306782</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -6352,7 +6352,7 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>1785055853</t>
+          <t>1785055931</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
@@ -6362,7 +6362,7 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>8.75</t>
+          <t>9.941748</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -6379,110 +6379,222 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
+          <t>0x947b403314498890960e964926f3e25010f3b36a93afc49e309f7a71a57648b0</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>4.55</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen FC</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>K2-League</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen FC vs Yongin City</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen FC</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Yongin City</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>0x2725ecc350e6d5314ddee250cd3e445f586ab55a992fc73108db0913c5a41f24</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>L19306783</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>1785055853</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>1785061800</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>8.75</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
           <t>0x4df42281e0de14de14275865cafadfb98d1cc6f76c1873f8fd64bcaa2cae8075</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
         <is>
           <t>4.99</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="E57" t="inlineStr">
         <is>
           <t>1.2775</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
+      <c r="F57" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="G57" t="inlineStr">
         <is>
           <t>Tie</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="H57" t="inlineStr">
         <is>
           <t>K2-League</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
+      <c r="I57" t="inlineStr">
         <is>
           <t>Gimpo Citizen FC vs Yongin City</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr">
+      <c r="J57" t="inlineStr">
         <is>
           <t>Gimpo Citizen FC</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
+      <c r="K57" t="inlineStr">
         <is>
           <t>Yongin City</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr">
+      <c r="L57" t="inlineStr">
         <is>
           <t>0xf93dab40773f0e01839824957e7cecd4afb676d72a13c45521719f4f5c517a27</t>
         </is>
       </c>
-      <c r="M56" t="inlineStr">
+      <c r="M57" t="inlineStr">
         <is>
           <t>L19306783</t>
         </is>
       </c>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O56" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P56" t="inlineStr">
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q56" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R56" t="inlineStr">
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
         <is>
           <t>1785044379</t>
         </is>
       </c>
-      <c r="S56" t="inlineStr">
+      <c r="S57" t="inlineStr">
         <is>
           <t>1785061800</t>
         </is>
       </c>
-      <c r="T56" t="inlineStr">
+      <c r="T57" t="inlineStr">
         <is>
           <t>17.981982</t>
         </is>
       </c>
-      <c r="U56" t="inlineStr">
+      <c r="U57" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V56" t="inlineStr">
+      <c r="V57" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/K2-League/trades.xlsx
+++ b/data/sxbet/ligas/K2-League/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V57"/>
+  <dimension ref="A1:V59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,12 +531,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x4da39049a709357f30ef968bfc90b4eec2da9d99090f3b99edf4ea11aeddd708</t>
+          <t>0x59cfeb6eefafd07022cdcaae7869afb45bc60deb8b4c0b4b96ad04ae8bbdb0d3</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -546,22 +546,22 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>32.79</t>
+          <t>321.53001</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.5488</t>
+          <t>1.525</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
+          <t>K2-League</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hwaseong FC +0.5</t>
+          <t>Chungnam Asan FC 0</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -571,27 +571,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Hwaseong FC vs Daegu FC</t>
+          <t>Chungnam Asan FC vs Seongnam FC</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Hwaseong FC</t>
+          <t>Chungnam Asan FC</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Daegu FC</t>
+          <t>Seongnam FC</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0xbde5165c3a540b0c6dd64b3df320540fd10ecb173373b087359951e7f790f852</t>
+          <t>0x5d9fd67211ec6f71728981803ac86abc94216c4e6a398285b5003dabd4e5df0f</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19382332</t>
+          <t>L19382328</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -616,7 +616,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1785527084</t>
+          <t>1785534316</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>59.753986</t>
+          <t>612.438114</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -643,7 +643,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x07b844c409deb0bc9c8e8dbda27c7c2b772aec07892356105db79f67ffb0e227</t>
+          <t>0x57f84ab38f2e25e292c948ee169e9feff1e8436efac9878d37389052fc7a8ade</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -651,23 +651,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>6.39</t>
+          <t>9.99999</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.5675</t>
+          <t>1.525</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
+          <t>K2-League</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Chungnam Asan FC 0</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -675,27 +683,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC vs Yongin City</t>
+          <t>Chungnam Asan FC vs Seongnam FC</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC</t>
+          <t>Chungnam Asan FC</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Seongnam FC</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0xf73fcbba4baac94056070f4c2db509913d7317940066a6918ac1f13256f52327</t>
+          <t>0x5d9fd67211ec6f71728981803ac86abc94216c4e6a398285b5003dabd4e5df0f</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>L19306783</t>
+          <t>L19382328</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -720,17 +728,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1785064787</t>
+          <t>1785534315</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>1785061800</t>
+          <t>1785580200</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>11.259912</t>
+          <t>19.0476</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -747,31 +755,39 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0xf95f88d59f982dc2c9ca6387361b5a066ab48deeb7f9f6071274eb879ddabdd0</t>
+          <t>0x4da39049a709357f30ef968bfc90b4eec2da9d99090f3b99edf4ea11aeddd708</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>126.4351</t>
+          <t>32.79</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.815</t>
+          <t>1.5488</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hwaseong FC +0.5</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -779,27 +795,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC vs Yongin City</t>
+          <t>Hwaseong FC vs Daegu FC</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC</t>
+          <t>Hwaseong FC</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Daegu FC</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0x1482cd21984a144c2f6033821f76b4033b1aeaebbab5c85a758b2e86c0553134</t>
+          <t>0xbde5165c3a540b0c6dd64b3df320540fd10ecb173373b087359951e7f790f852</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>L19306783</t>
+          <t>L19382332</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -824,17 +840,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1785064732</t>
+          <t>1785527084</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>1785061800</t>
+          <t>1785580200</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>155.135092</t>
+          <t>59.753986</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -851,7 +867,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0xe74ba88448233ab30d6e4b230046fe45bf1be0a6f71b8860703364abbbb40afe</t>
+          <t>0x07b844c409deb0bc9c8e8dbda27c7c2b772aec07892356105db79f67ffb0e227</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -859,19 +875,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>19.69</t>
+          <t>6.39</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.5038</t>
+          <t>1.5675</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -879,11 +891,7 @@
           <t>Under/Over (1.5)</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Over 1.5</t>
-        </is>
-      </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -891,27 +899,27 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Paju Citizen vs Ansan Greeners</t>
+          <t>Gimpo Citizen FC vs Yongin City</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Gimpo Citizen FC</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0x6a23b140597c01b1670e03fdb996fc8e94424ec45a5e6e429b292ba1688dff5c</t>
+          <t>0xf73fcbba4baac94056070f4c2db509913d7317940066a6918ac1f13256f52327</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>L19306782</t>
+          <t>L19306783</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -936,7 +944,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1785064111</t>
+          <t>1785064787</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -946,7 +954,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>39.086849</t>
+          <t>11.259912</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -963,28 +971,28 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x02858e4fe5f076373faa42c17e9058ea19bff69a0b68493520c024b133c2ceed</t>
+          <t>0xf95f88d59f982dc2c9ca6387361b5a066ab48deeb7f9f6071274eb879ddabdd0</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0x0C2DA7fC8702784d6f75c78Da25460783A6709a0</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>126.4351</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.4975</t>
+          <t>1.815</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -995,27 +1003,27 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Paju Citizen vs Ansan Greeners</t>
+          <t>Gimpo Citizen FC vs Yongin City</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Gimpo Citizen FC</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0x90106aa6ffeea165b450ea7a1094c65ae9db8d6fdde000ce479b4af5b3fa3072</t>
+          <t>0x1482cd21984a144c2f6033821f76b4033b1aeaebbab5c85a758b2e86c0553134</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>L19306782</t>
+          <t>L19306783</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1040,7 +1048,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1785063804</t>
+          <t>1785064732</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1050,7 +1058,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>6.030151</t>
+          <t>155.135092</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1067,7 +1075,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0xd6b44cd45d93535a9c1b39fad13245ea6ef0e5cbff858b443a9d40a281cf422f</t>
+          <t>0xe74ba88448233ab30d6e4b230046fe45bf1be0a6f71b8860703364abbbb40afe</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1082,22 +1090,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>21.3</t>
+          <t>19.69</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.2988</t>
+          <t>1.5038</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Over 2.5</t>
+          <t>Over 1.5</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1122,7 +1130,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0x2d5eca3e665030fe8c7c2a84772b94d8fc59c9a6991fd216ba914d3b345ffe07</t>
+          <t>0x6a23b140597c01b1670e03fdb996fc8e94424ec45a5e6e429b292ba1688dff5c</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1152,7 +1160,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1785063590</t>
+          <t>1785064111</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1162,7 +1170,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>71.297071</t>
+          <t>39.086849</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1179,27 +1187,23 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0xc41eea20c9aa34da894372c77f23e0a6ee134568f117e95b14c294310b2dc1f7</t>
+          <t>0x02858e4fe5f076373faa42c17e9058ea19bff69a0b68493520c024b133c2ceed</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x0C2DA7fC8702784d6f75c78Da25460783A6709a0</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>12.53</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.2037</t>
+          <t>1.4975</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1207,11 +1211,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Yongin City</t>
-        </is>
-      </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -1219,27 +1219,27 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC vs Yongin City</t>
+          <t>Paju Citizen vs Ansan Greeners</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0x520e073f044523b55003a1d70f752c30f91cd5ebae7e23b2f294ad6679b3ed58</t>
+          <t>0x90106aa6ffeea165b450ea7a1094c65ae9db8d6fdde000ce479b4af5b3fa3072</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>L19306783</t>
+          <t>L19306782</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1785063530</t>
+          <t>1785063804</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>61.496933</t>
+          <t>6.030151</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1291,7 +1291,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0xe5a4265d3896fe621f44bfc6c8c9d2efe8a044ac121c6a5ec411dcd8ecbb22c9</t>
+          <t>0xd6b44cd45d93535a9c1b39fad13245ea6ef0e5cbff858b443a9d40a281cf422f</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1306,22 +1306,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>21.3</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.5162</t>
+          <t>1.2988</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC</t>
+          <t>Over 2.5</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1331,27 +1331,27 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC vs Yongin City</t>
+          <t>Paju Citizen vs Ansan Greeners</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0x2725ecc350e6d5314ddee250cd3e445f586ab55a992fc73108db0913c5a41f24</t>
+          <t>0x2d5eca3e665030fe8c7c2a84772b94d8fc59c9a6991fd216ba914d3b345ffe07</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>L19306783</t>
+          <t>L19306782</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1376,7 +1376,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1785063352</t>
+          <t>1785063590</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1.937046</t>
+          <t>71.297071</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1403,7 +1403,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0x996289847910ea662fcd868b20c9fa48f68ab4d7334bac4351bc46b6d3f479df</t>
+          <t>0xc41eea20c9aa34da894372c77f23e0a6ee134568f117e95b14c294310b2dc1f7</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12.53</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.5162</t>
+          <t>1.2037</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1433,24 +1433,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
+          <t>Yongin City</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>K2-League</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen FC vs Yongin City</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>Gimpo Citizen FC</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>K2-League</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Gimpo Citizen FC vs Yongin City</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Gimpo Citizen FC</t>
-        </is>
-      </c>
       <c r="K10" t="inlineStr">
         <is>
           <t>Yongin City</t>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0x2725ecc350e6d5314ddee250cd3e445f586ab55a992fc73108db0913c5a41f24</t>
+          <t>0x520e073f044523b55003a1d70f752c30f91cd5ebae7e23b2f294ad6679b3ed58</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1785063326</t>
+          <t>1785063530</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1.937046</t>
+          <t>61.496933</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1515,7 +1515,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0xed44d31e5a5b7071006924700a0078a2f8a3710d9bb8d24217652d198ffae7d7</t>
+          <t>0xe5a4265d3896fe621f44bfc6c8c9d2efe8a044ac121c6a5ec411dcd8ecbb22c9</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>28.84</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1785063319</t>
+          <t>1785063352</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1610,7 +1610,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>55.864407</t>
+          <t>1.937046</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1627,7 +1627,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x2bcba69d716b343c190b4a215a8f323f4abe23b13cd57d716f1b386e77406d71</t>
+          <t>0x996289847910ea662fcd868b20c9fa48f68ab4d7334bac4351bc46b6d3f479df</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1635,23 +1635,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.3912</t>
+          <t>1.5162</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen FC</t>
+        </is>
+      </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -1674,7 +1682,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0xf73fcbba4baac94056070f4c2db509913d7317940066a6918ac1f13256f52327</t>
+          <t>0x2725ecc350e6d5314ddee250cd3e445f586ab55a992fc73108db0913c5a41f24</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1704,7 +1712,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1785063319</t>
+          <t>1785063326</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1714,7 +1722,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>6.696486</t>
+          <t>1.937046</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1731,7 +1739,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0x74897816645fe410040b71368723e823f96b8b8ad1a8558a60563ea6a63c17b9</t>
+          <t>0xed44d31e5a5b7071006924700a0078a2f8a3710d9bb8d24217652d198ffae7d7</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1746,12 +1754,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>28.84</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.5488</t>
+          <t>1.5162</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1761,7 +1769,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Gimpo Citizen FC</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1771,27 +1779,27 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Paju Citizen vs Ansan Greeners</t>
+          <t>Gimpo Citizen FC vs Yongin City</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Gimpo Citizen FC</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0x90106aa6ffeea165b450ea7a1094c65ae9db8d6fdde000ce479b4af5b3fa3072</t>
+          <t>0x2725ecc350e6d5314ddee250cd3e445f586ab55a992fc73108db0913c5a41f24</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>L19306782</t>
+          <t>L19306783</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1816,7 +1824,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1785063283</t>
+          <t>1785063319</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1826,7 +1834,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>18.223235</t>
+          <t>55.864407</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1843,7 +1851,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0x6c9b96e6ea55e8d6386264e63d154ad9cdf850c8f9c18b5c088abdcfcc710e8d</t>
+          <t>0x2bcba69d716b343c190b4a215a8f323f4abe23b13cd57d716f1b386e77406d71</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1854,17 +1862,17 @@
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1.74999</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.8313</t>
+          <t>1.3912</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -1875,27 +1883,27 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Paju Citizen vs Ansan Greeners</t>
+          <t>Gimpo Citizen FC vs Yongin City</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Gimpo Citizen FC</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0x6de105784818e175bb2cb50f54d4325a684a5693a05f8bd5b7f2b402aeb4bdfa</t>
+          <t>0xf73fcbba4baac94056070f4c2db509913d7317940066a6918ac1f13256f52327</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>L19306782</t>
+          <t>L19306783</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1920,7 +1928,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1785063278</t>
+          <t>1785063319</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1930,7 +1938,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2.105251</t>
+          <t>6.696486</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1947,7 +1955,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0x653ed25ca6aba498efe0c95f6d394f607985bf6c4ab830c3599772279631e8b1</t>
+          <t>0x74897816645fe410040b71368723e823f96b8b8ad1a8558a60563ea6a63c17b9</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1955,15 +1963,19 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>201.32998</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.8213</t>
+          <t>1.5488</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1971,7 +1983,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Paju Citizen</t>
+        </is>
+      </c>
       <c r="H15" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -1994,7 +2010,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0x6de105784818e175bb2cb50f54d4325a684a5693a05f8bd5b7f2b402aeb4bdfa</t>
+          <t>0x90106aa6ffeea165b450ea7a1094c65ae9db8d6fdde000ce479b4af5b3fa3072</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -2024,7 +2040,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1785063071</t>
+          <t>1785063283</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2034,7 +2050,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>245.150661</t>
+          <t>18.223235</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2051,23 +2067,23 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0xd7beeace3688b4d75f908058620cd47f10d9926e086901a2c83333dd169ec720</t>
+          <t>0x6c9b96e6ea55e8d6386264e63d154ad9cdf850c8f9c18b5c088abdcfcc710e8d</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>48.03</t>
+          <t>1.74999</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.8313</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2083,27 +2099,27 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC vs Yongin City</t>
+          <t>Paju Citizen vs Ansan Greeners</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0x2725ecc350e6d5314ddee250cd3e445f586ab55a992fc73108db0913c5a41f24</t>
+          <t>0x6de105784818e175bb2cb50f54d4325a684a5693a05f8bd5b7f2b402aeb4bdfa</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>L19306783</t>
+          <t>L19306782</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2128,7 +2144,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1785062970</t>
+          <t>1785063278</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2138,7 +2154,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>98.020408</t>
+          <t>2.105251</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2155,7 +2171,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0x8940d52e7feb848f5ca44e42ecc2fed94e942961b918122bc87142ffbf346d4c</t>
+          <t>0x653ed25ca6aba498efe0c95f6d394f607985bf6c4ab830c3599772279631e8b1</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2166,12 +2182,12 @@
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>196.03997</t>
+          <t>201.32998</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.8188</t>
+          <t>1.8213</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2232,7 +2248,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1785062953</t>
+          <t>1785063071</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2242,7 +2258,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>239.438131</t>
+          <t>245.150661</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2259,27 +2275,23 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0x2b9441f7515eb95a00a5708be64644050b069886b2e84d77ecdeea72fe8e3da7</t>
+          <t>0xd7beeace3688b4d75f908058620cd47f10d9926e086901a2c83333dd169ec720</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>12.06</t>
+          <t>48.03</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.1975</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2287,34 +2299,30 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>K2-League</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen FC vs Yongin City</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen FC</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
         <is>
           <t>Yongin City</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>K2-League</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>Gimpo Citizen FC vs Yongin City</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>Gimpo Citizen FC</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>Yongin City</t>
-        </is>
-      </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0x520e073f044523b55003a1d70f752c30f91cd5ebae7e23b2f294ad6679b3ed58</t>
+          <t>0x2725ecc350e6d5314ddee250cd3e445f586ab55a992fc73108db0913c5a41f24</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2344,7 +2352,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1785062934</t>
+          <t>1785062970</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2354,7 +2362,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>61.063291</t>
+          <t>98.020408</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2371,7 +2379,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0x17ea9fc34d8d08859197baf8694510eafd385c5cb30d1bccaf4135418710a4ee</t>
+          <t>0x8940d52e7feb848f5ca44e42ecc2fed94e942961b918122bc87142ffbf346d4c</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2379,31 +2387,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>196.03997</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.3862</t>
+          <t>1.8188</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Over 2.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -2426,7 +2426,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0x2d5eca3e665030fe8c7c2a84772b94d8fc59c9a6991fd216ba914d3b345ffe07</t>
+          <t>0x6de105784818e175bb2cb50f54d4325a684a5693a05f8bd5b7f2b402aeb4bdfa</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1785062748</t>
+          <t>1785062953</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2466,7 +2466,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>25.889968</t>
+          <t>239.438131</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2483,7 +2483,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0xff313e8a80cab759f0306eced2743a83b68017dd8ecc4a5eda49613abd5f72bb</t>
+          <t>0x2b9441f7515eb95a00a5708be64644050b069886b2e84d77ecdeea72fe8e3da7</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2498,22 +2498,22 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12.06</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.2275</t>
+          <t>1.1975</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Over 3.5</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2523,27 +2523,27 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Paju Citizen vs Ansan Greeners</t>
+          <t>Gimpo Citizen FC vs Yongin City</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Gimpo Citizen FC</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0x20fab15d1baac82bbe5a9371ad4e1e4f931edb8de76d814e671a0313aa4d8620</t>
+          <t>0x520e073f044523b55003a1d70f752c30f91cd5ebae7e23b2f294ad6679b3ed58</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>L19306782</t>
+          <t>L19306783</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1785062437</t>
+          <t>1785062934</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2578,7 +2578,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>43.956044</t>
+          <t>61.063291</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2595,7 +2595,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0x5a88256e6b892595ad641ef1ae589c088b32b6034ec557ba72582fa8c93f67e3</t>
+          <t>0x17ea9fc34d8d08859197baf8694510eafd385c5cb30d1bccaf4135418710a4ee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2603,23 +2603,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>64.98999</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.8125</t>
+          <t>1.3862</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr"/>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
       <c r="H21" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -2642,7 +2650,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0x6de105784818e175bb2cb50f54d4325a684a5693a05f8bd5b7f2b402aeb4bdfa</t>
+          <t>0x2d5eca3e665030fe8c7c2a84772b94d8fc59c9a6991fd216ba914d3b345ffe07</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2672,7 +2680,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1785062111</t>
+          <t>1785062748</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2682,7 +2690,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>79.98768</t>
+          <t>25.889968</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2699,12 +2707,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0x21aa47ce5d327006a8fdcf609e5990b1ea5499887fd8ccd0ff96d5bbe7df2f89</t>
+          <t>0xff313e8a80cab759f0306eced2743a83b68017dd8ecc4a5eda49613abd5f72bb</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2714,22 +2722,22 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>23.39</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.3887</t>
+          <t>1.2275</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Paju Citizen -1</t>
+          <t>Over 3.5</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2754,7 +2762,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0x1398d7baccf6c5154c8090892c6597852ff56e90298e81fb604a8b9bf22c47ce</t>
+          <t>0x20fab15d1baac82bbe5a9371ad4e1e4f931edb8de76d814e671a0313aa4d8620</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2784,7 +2792,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1785061695</t>
+          <t>1785062437</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2794,7 +2802,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>60.167203</t>
+          <t>43.956044</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2811,39 +2819,31 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0xaa13e9d13e81cd9edae13a80c0e426e52c85c5064c5b0c34d792d027f33fe560</t>
+          <t>0x5a88256e6b892595ad641ef1ae589c088b32b6034ec557ba72582fa8c93f67e3</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>17.04</t>
+          <t>64.98999</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.8125</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Paju Citizen -1.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -2866,7 +2866,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0x48cd5a7ee72c95f57110826c0f2e2494d9438250815f7751e5e0fdce91ccbfba</t>
+          <t>0x6de105784818e175bb2cb50f54d4325a684a5693a05f8bd5b7f2b402aeb4bdfa</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2896,7 +2896,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1785061694</t>
+          <t>1785062111</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>58.758621</t>
+          <t>79.98768</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2923,31 +2923,39 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0x9c2da91ae7561670702979941233734bebc22c36fdac867bf5bdb53a8151c6e9</t>
+          <t>0x21aa47ce5d327006a8fdcf609e5990b1ea5499887fd8ccd0ff96d5bbe7df2f89</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>4.99997</t>
+          <t>23.39</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.795</t>
+          <t>1.3887</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr"/>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Paju Citizen -1</t>
+        </is>
+      </c>
       <c r="H24" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -2955,27 +2963,27 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC vs Yongin City</t>
+          <t>Paju Citizen vs Ansan Greeners</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0x520e073f044523b55003a1d70f752c30f91cd5ebae7e23b2f294ad6679b3ed58</t>
+          <t>0x1398d7baccf6c5154c8090892c6597852ff56e90298e81fb604a8b9bf22c47ce</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>L19306783</t>
+          <t>L19306782</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -3000,7 +3008,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1785061651</t>
+          <t>1785061695</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3010,7 +3018,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>6.28927</t>
+          <t>60.167203</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3027,7 +3035,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0x12f98497a1f2dc0a130b32665dfeea9bbd9b744c2732456c77c91801ec687167</t>
+          <t>0xaa13e9d13e81cd9edae13a80c0e426e52c85c5064c5b0c34d792d027f33fe560</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3042,22 +3050,22 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>21.14</t>
+          <t>17.04</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.3513</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC -1</t>
+          <t>Paju Citizen -1.5</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3067,27 +3075,27 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC vs Yongin City</t>
+          <t>Paju Citizen vs Ansan Greeners</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0x4a4b2cf0de4356e1be221d31aa0feab4af681e89956037ff111c72307c4d9af6</t>
+          <t>0x48cd5a7ee72c95f57110826c0f2e2494d9438250815f7751e5e0fdce91ccbfba</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>L19306783</t>
+          <t>L19306782</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3112,7 +3120,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1785061621</t>
+          <t>1785061694</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3122,7 +3130,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>60.185053</t>
+          <t>58.758621</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3139,18 +3147,18 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0x0f90aefde05859a865353743603e3925fef0a390e252c71ca62de94b7f3522d8</t>
+          <t>0x9c2da91ae7561670702979941233734bebc22c36fdac867bf5bdb53a8151c6e9</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>43.51167</t>
+          <t>4.99997</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -3216,7 +3224,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1785061621</t>
+          <t>1785061651</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3226,7 +3234,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>54.73166</t>
+          <t>6.28927</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3243,31 +3251,39 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0x45f1170f51d54ba31ead65b241ce33b618358dd91421e9194877f824ebea4f5d</t>
+          <t>0x12f98497a1f2dc0a130b32665dfeea9bbd9b744c2732456c77c91801ec687167</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0x09b3a190a1e971Dd0B4F82Eb9008287fe43a540C</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>21.14</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.3513</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr"/>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen FC -1</t>
+        </is>
+      </c>
       <c r="H27" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -3290,7 +3306,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0x7b353104df193f280c01b3e0a75dcbbc5dd4e628b7304c3537dff2339968d702</t>
+          <t>0x4a4b2cf0de4356e1be221d31aa0feab4af681e89956037ff111c72307c4d9af6</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -3320,7 +3336,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1785061583</t>
+          <t>1785061621</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3330,7 +3346,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>51.020408</t>
+          <t>60.185053</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3347,18 +3363,18 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0x8726e3d54f033c4394f3b9a8a297c466f26e8d1814d525163146dc1f9f836029</t>
+          <t>0x0f90aefde05859a865353743603e3925fef0a390e252c71ca62de94b7f3522d8</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>5.70997</t>
+          <t>43.51167</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -3424,7 +3440,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1785061581</t>
+          <t>1785061621</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3434,7 +3450,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>7.182352</t>
+          <t>54.73166</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3451,7 +3467,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0x78b589b7ea305b8a325e286dcbf526301e19f803d90ab77960c290d1d621d34a</t>
+          <t>0x45f1170f51d54ba31ead65b241ce33b618358dd91421e9194877f824ebea4f5d</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3459,31 +3475,23 @@
           <t>0x09b3a190a1e971Dd0B4F82Eb9008287fe43a540C</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>5.01384</t>
+          <t>25</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.2788</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -3506,7 +3514,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0xf93dab40773f0e01839824957e7cecd4afb676d72a13c45521719f4f5c517a27</t>
+          <t>0x7b353104df193f280c01b3e0a75dcbbc5dd4e628b7304c3537dff2339968d702</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -3536,7 +3544,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1785061533</t>
+          <t>1785061583</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3546,7 +3554,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>17.98687</t>
+          <t>51.020408</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3563,7 +3571,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0x64d493da52ab9f3215f2ee6a066aad2cbaf66597963522c2c53462ae6d466e65</t>
+          <t>0x8726e3d54f033c4394f3b9a8a297c466f26e8d1814d525163146dc1f9f836029</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3574,12 +3582,12 @@
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>43.87998</t>
+          <t>5.70997</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.7988</t>
+          <t>1.795</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -3640,7 +3648,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1785061346</t>
+          <t>1785061581</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3650,7 +3658,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>54.935812</t>
+          <t>7.182352</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3667,23 +3675,27 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0xb6a5b0e5cc84223b1b456506ce5bc4a60492c7d715d16ce5ba4bcbbbb205e549</t>
+          <t>0x78b589b7ea305b8a325e286dcbf526301e19f803d90ab77960c290d1d621d34a</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr"/>
+          <t>0x09b3a190a1e971Dd0B4F82Eb9008287fe43a540C</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>10.19999</t>
+          <t>5.01384</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.7988</t>
+          <t>1.2788</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -3691,7 +3703,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H31" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -3714,7 +3730,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0x520e073f044523b55003a1d70f752c30f91cd5ebae7e23b2f294ad6679b3ed58</t>
+          <t>0xf93dab40773f0e01839824957e7cecd4afb676d72a13c45521719f4f5c517a27</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -3744,7 +3760,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1785061261</t>
+          <t>1785061533</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -3754,7 +3770,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>12.769941</t>
+          <t>17.98687</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3771,18 +3787,18 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0x932ea4448a5d14be89226effb4bcb8584e5004da981b9fb12e769029a2cd6a34</t>
+          <t>0x64d493da52ab9f3215f2ee6a066aad2cbaf66597963522c2c53462ae6d466e65</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>43.87998</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -3848,7 +3864,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1785061250</t>
+          <t>1785061346</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -3858,7 +3874,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>6.259781</t>
+          <t>54.935812</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3875,23 +3891,23 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0x6ba96fe1be95723f4530ab62caaff2817e70e2c1aa504d2f0afe5b7d44447528</t>
+          <t>0xb6a5b0e5cc84223b1b456506ce5bc4a60492c7d715d16ce5ba4bcbbbb205e549</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>43.12404</t>
+          <t>10.19999</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.7975</t>
+          <t>1.7988</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -3952,7 +3968,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1785061221</t>
+          <t>1785061261</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -3962,7 +3978,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>54.074031</t>
+          <t>12.769941</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -3979,27 +3995,23 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0xa4c5cc7d130116507c7f97158d19bded9ace84b90e4089b2386235aca563a109</t>
+          <t>0x932ea4448a5d14be89226effb4bcb8584e5004da981b9fb12e769029a2cd6a34</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>5.54</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.2537</t>
+          <t>1.7988</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -4007,11 +4019,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -4019,27 +4027,27 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Paju Citizen vs Ansan Greeners</t>
+          <t>Gimpo Citizen FC vs Yongin City</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Gimpo Citizen FC</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0xabfa364122222118f5f35af9ee862e2b9587e9c2f656e281725fdca100cf17bf</t>
+          <t>0x520e073f044523b55003a1d70f752c30f91cd5ebae7e23b2f294ad6679b3ed58</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>L19306782</t>
+          <t>L19306783</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -4064,7 +4072,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1785060618</t>
+          <t>1785061250</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -4074,7 +4082,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>21.832512</t>
+          <t>6.259781</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4091,18 +4099,18 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0xed6f77aaa7a7dbe5c2457f000b022f2da0cc5bd1004291d76e71044f4e1faa36</t>
+          <t>0x6ba96fe1be95723f4530ab62caaff2817e70e2c1aa504d2f0afe5b7d44447528</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>4.99999</t>
+          <t>43.12404</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -4168,7 +4176,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1785060105</t>
+          <t>1785061221</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -4178,7 +4186,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>6.26958</t>
+          <t>54.074031</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4195,23 +4203,27 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0xe0d4aa08492162b980b70ecc4ec3e9ae46b9fd85fea771f538c542e4e27f10ca</t>
+          <t>0xa4c5cc7d130116507c7f97158d19bded9ace84b90e4089b2386235aca563a109</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>4.99999</t>
+          <t>5.54</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.7975</t>
+          <t>1.2537</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -4219,7 +4231,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H36" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -4227,27 +4243,27 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC vs Yongin City</t>
+          <t>Paju Citizen vs Ansan Greeners</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0x520e073f044523b55003a1d70f752c30f91cd5ebae7e23b2f294ad6679b3ed58</t>
+          <t>0xabfa364122222118f5f35af9ee862e2b9587e9c2f656e281725fdca100cf17bf</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>L19306783</t>
+          <t>L19306782</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -4272,7 +4288,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1785060103</t>
+          <t>1785060618</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -4282,7 +4298,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>6.26958</t>
+          <t>21.832512</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4299,7 +4315,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0x733bd5ce99f877eba370291936b138251c1bd48cee90480bc876f49523ca7fca</t>
+          <t>0xed6f77aaa7a7dbe5c2457f000b022f2da0cc5bd1004291d76e71044f4e1faa36</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4376,7 +4392,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1785060101</t>
+          <t>1785060105</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -4403,39 +4419,31 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0xcfbe574677265ef97dc3204a001ce1b1e25523c8a98c296a3cf235f97650aace</t>
+          <t>0xe0d4aa08492162b980b70ecc4ec3e9ae46b9fd85fea771f538c542e4e27f10ca</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.99999</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.3887</t>
+          <t>1.7975</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Paju Citizen -1</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -4443,27 +4451,27 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Paju Citizen vs Ansan Greeners</t>
+          <t>Gimpo Citizen FC vs Yongin City</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Gimpo Citizen FC</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0x1398d7baccf6c5154c8090892c6597852ff56e90298e81fb604a8b9bf22c47ce</t>
+          <t>0x520e073f044523b55003a1d70f752c30f91cd5ebae7e23b2f294ad6679b3ed58</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>L19306782</t>
+          <t>L19306783</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -4488,7 +4496,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1785060085</t>
+          <t>1785060103</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -4498,7 +4506,7 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>10.289389</t>
+          <t>6.26958</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4515,23 +4523,23 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0xebd1df0aa7e7f54677bedd84a6c923ca856cf657e0531639938bfb8111becc94</t>
+          <t>0x733bd5ce99f877eba370291936b138251c1bd48cee90480bc876f49523ca7fca</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>22.97198</t>
+          <t>4.99999</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.7963</t>
+          <t>1.7975</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -4592,7 +4600,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1785060074</t>
+          <t>1785060101</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -4602,7 +4610,7 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>28.85021</t>
+          <t>6.26958</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4619,31 +4627,39 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0x9137623e3c72596dddeb8dd77deb26f0f80f5d8ad5037c9d9fd9ec11f1d3a62d</t>
+          <t>0xcfbe574677265ef97dc3204a001ce1b1e25523c8a98c296a3cf235f97650aace</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>15.59279</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.7963</t>
+          <t>1.3887</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr"/>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Paju Citizen -1</t>
+        </is>
+      </c>
       <c r="H40" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -4651,27 +4667,27 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC vs Yongin City</t>
+          <t>Paju Citizen vs Ansan Greeners</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0x520e073f044523b55003a1d70f752c30f91cd5ebae7e23b2f294ad6679b3ed58</t>
+          <t>0x1398d7baccf6c5154c8090892c6597852ff56e90298e81fb604a8b9bf22c47ce</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>L19306783</t>
+          <t>L19306782</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -4696,7 +4712,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1785060073</t>
+          <t>1785060085</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -4706,7 +4722,7 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>19.582782</t>
+          <t>10.289389</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -4723,7 +4739,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0x47fecae2c93459e7d6a1189dcb95e8bce239b7e2d26ce67db4733b564451a3fd</t>
+          <t>0xebd1df0aa7e7f54677bedd84a6c923ca856cf657e0531639938bfb8111becc94</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4734,7 +4750,7 @@
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>16.1469</t>
+          <t>22.97198</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -4800,7 +4816,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1785060072</t>
+          <t>1785060074</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -4810,7 +4826,7 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>20.278681</t>
+          <t>28.85021</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -4827,27 +4843,23 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0x7851323bb653ef81f86e4483a09baec3f52472a947788d079eacebc8ce474280</t>
+          <t>0x9137623e3c72596dddeb8dd77deb26f0f80f5d8ad5037c9d9fd9ec11f1d3a62d</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>19.02</t>
+          <t>15.59279</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.275</t>
+          <t>1.7963</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -4855,11 +4867,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -4882,7 +4890,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0xf93dab40773f0e01839824957e7cecd4afb676d72a13c45521719f4f5c517a27</t>
+          <t>0x520e073f044523b55003a1d70f752c30f91cd5ebae7e23b2f294ad6679b3ed58</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -4912,7 +4920,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1785060054</t>
+          <t>1785060073</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -4922,7 +4930,7 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>69.163636</t>
+          <t>19.582782</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -4939,27 +4947,23 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0x5936a0069456d68663344829a3e2e9aa688da6a9e1d38de76848d1bdfb84366a</t>
+          <t>0x47fecae2c93459e7d6a1189dcb95e8bce239b7e2d26ce67db4733b564451a3fd</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>10.56</t>
+          <t>16.1469</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.2737</t>
+          <t>1.7963</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -4967,11 +4971,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0xf93dab40773f0e01839824957e7cecd4afb676d72a13c45521719f4f5c517a27</t>
+          <t>0x520e073f044523b55003a1d70f752c30f91cd5ebae7e23b2f294ad6679b3ed58</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -5024,7 +5024,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1785060044</t>
+          <t>1785060072</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -5034,7 +5034,7 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>38.575342</t>
+          <t>20.278681</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -5051,31 +5051,39 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0xc27dc932de76aa5047aab63fd483f2351fd3e777a4bebc494353cf3a53c52ba9</t>
+          <t>0x7851323bb653ef81f86e4483a09baec3f52472a947788d079eacebc8ce474280</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>20.61772</t>
+          <t>19.02</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.3425</t>
+          <t>1.275</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H44" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -5083,27 +5091,27 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Paju Citizen vs Ansan Greeners</t>
+          <t>Gimpo Citizen FC vs Yongin City</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Gimpo Citizen FC</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0x386468865ee4fb2d064354b0f4bb50fc57a8f046452fa6667bc56978f4cf3823</t>
+          <t>0xf93dab40773f0e01839824957e7cecd4afb676d72a13c45521719f4f5c517a27</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>L19306782</t>
+          <t>L19306783</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -5128,7 +5136,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>1785059855</t>
+          <t>1785060054</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -5138,7 +5146,7 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>60.197723</t>
+          <t>69.163636</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -5155,12 +5163,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0x06cf39065296686830cf556b4943f2a94e035610868690980b237da489f6c32a</t>
+          <t>0x5936a0069456d68663344829a3e2e9aa688da6a9e1d38de76848d1bdfb84366a</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -5170,22 +5178,22 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>4.94155</t>
+          <t>10.56</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1.355</t>
+          <t>1.2737</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC -1</t>
+          <t>Tie</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -5210,7 +5218,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>0x4a4b2cf0de4356e1be221d31aa0feab4af681e89956037ff111c72307c4d9af6</t>
+          <t>0xf93dab40773f0e01839824957e7cecd4afb676d72a13c45521719f4f5c517a27</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -5240,7 +5248,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>1785059821</t>
+          <t>1785060044</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
@@ -5250,7 +5258,7 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>13.919859</t>
+          <t>38.575342</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -5267,7 +5275,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0x6cad572e295e86d0eff792e6a73f1ecb4b2563c632f3a61d710a79a81bcbefc5</t>
+          <t>0xc27dc932de76aa5047aab63fd483f2351fd3e777a4bebc494353cf3a53c52ba9</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5275,31 +5283,23 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>16.43</t>
+          <t>20.61772</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.355</t>
+          <t>1.3425</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>Gimpo Citizen FC -1</t>
-        </is>
-      </c>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -5307,27 +5307,27 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC vs Yongin City</t>
+          <t>Paju Citizen vs Ansan Greeners</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>0x4a4b2cf0de4356e1be221d31aa0feab4af681e89956037ff111c72307c4d9af6</t>
+          <t>0x386468865ee4fb2d064354b0f4bb50fc57a8f046452fa6667bc56978f4cf3823</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>L19306783</t>
+          <t>L19306782</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -5352,7 +5352,7 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>1785059820</t>
+          <t>1785059855</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
@@ -5362,7 +5362,7 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>46.28169</t>
+          <t>60.197723</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -5379,31 +5379,39 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0xd90cf2f29f54991a5ee8c926cce019177b5bb5fd98602218fb9acaaf6a910664</t>
+          <t>0x06cf39065296686830cf556b4943f2a94e035610868690980b237da489f6c32a</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4.94155</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.4675</t>
+          <t>1.355</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr"/>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen FC -1</t>
+        </is>
+      </c>
       <c r="H47" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -5411,27 +5419,27 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Paju Citizen vs Ansan Greeners</t>
+          <t>Gimpo Citizen FC vs Yongin City</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Gimpo Citizen FC</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>0x90106aa6ffeea165b450ea7a1094c65ae9db8d6fdde000ce479b4af5b3fa3072</t>
+          <t>0x4a4b2cf0de4356e1be221d31aa0feab4af681e89956037ff111c72307c4d9af6</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>L19306782</t>
+          <t>L19306783</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -5456,7 +5464,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>1785058466</t>
+          <t>1785059821</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
@@ -5466,7 +5474,7 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>23.529412</t>
+          <t>13.919859</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -5483,12 +5491,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0xfaacadf40a626e2b5b306c37ecce7325e0fabbb091c125c037dd14587c31bfe4</t>
+          <t>0x6cad572e295e86d0eff792e6a73f1ecb4b2563c632f3a61d710a79a81bcbefc5</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -5498,39 +5506,39 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>4.53</t>
+          <t>16.43</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.5212</t>
+          <t>1.355</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
+          <t>Gimpo Citizen FC -1</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>K2-League</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen FC vs Yongin City</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
           <t>Gimpo Citizen FC</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>K2-League</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>Gimpo Citizen FC vs Yongin City</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>Gimpo Citizen FC</t>
-        </is>
-      </c>
       <c r="K48" t="inlineStr">
         <is>
           <t>Yongin City</t>
@@ -5538,7 +5546,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>0x2725ecc350e6d5314ddee250cd3e445f586ab55a992fc73108db0913c5a41f24</t>
+          <t>0x4a4b2cf0de4356e1be221d31aa0feab4af681e89956037ff111c72307c4d9af6</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -5568,7 +5576,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>1785057353</t>
+          <t>1785059820</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
@@ -5578,7 +5586,7 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>8.690647</t>
+          <t>46.28169</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -5595,27 +5603,23 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0x182964c6008d5b7d29731fd19876092a52fa2068fcb16aaf430dd8e0a6009721</t>
+          <t>0xd90cf2f29f54991a5ee8c926cce019177b5bb5fd98602218fb9acaaf6a910664</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
-          <t>3.73</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1.2763</t>
+          <t>1.4675</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -5623,11 +5627,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -5635,27 +5635,27 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC vs Yongin City</t>
+          <t>Paju Citizen vs Ansan Greeners</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>0xf93dab40773f0e01839824957e7cecd4afb676d72a13c45521719f4f5c517a27</t>
+          <t>0x90106aa6ffeea165b450ea7a1094c65ae9db8d6fdde000ce479b4af5b3fa3072</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>L19306783</t>
+          <t>L19306782</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -5680,7 +5680,7 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>1785057212</t>
+          <t>1785058466</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
@@ -5690,7 +5690,7 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>13.502262</t>
+          <t>23.529412</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -5707,12 +5707,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0xae029509b64a4e0489363d3aa1a7e18db0cd21b4fb65f5064e49185bb4bfb2f6</t>
+          <t>0xfaacadf40a626e2b5b306c37ecce7325e0fabbb091c125c037dd14587c31bfe4</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -5722,12 +5722,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.53</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.5212</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -5792,7 +5792,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>1785056897</t>
+          <t>1785057353</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
@@ -5802,7 +5802,7 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>9.615385</t>
+          <t>8.690647</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -5819,7 +5819,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0xd359a1bde933becdef3ca166f20bbe9291a9b81f961befead4bc72e1713c6447</t>
+          <t>0x182964c6008d5b7d29731fd19876092a52fa2068fcb16aaf430dd8e0a6009721</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5834,12 +5834,12 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>4.53999</t>
+          <t>3.73</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.2763</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -5849,24 +5849,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>K2-League</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen FC vs Yongin City</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
           <t>Gimpo Citizen FC</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>K2-League</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>Gimpo Citizen FC vs Yongin City</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>Gimpo Citizen FC</t>
-        </is>
-      </c>
       <c r="K51" t="inlineStr">
         <is>
           <t>Yongin City</t>
@@ -5874,7 +5874,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>0x2725ecc350e6d5314ddee250cd3e445f586ab55a992fc73108db0913c5a41f24</t>
+          <t>0xf93dab40773f0e01839824957e7cecd4afb676d72a13c45521719f4f5c517a27</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -5904,7 +5904,7 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>1785056453</t>
+          <t>1785057212</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
@@ -5914,7 +5914,7 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>8.73075</t>
+          <t>13.502262</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -5931,12 +5931,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0xe5784e1cc6cec364d74a7267a701924cf5f6543fed6d0c11d5f756f735c714f2</t>
+          <t>0xae029509b64a4e0489363d3aa1a7e18db0cd21b4fb65f5064e49185bb4bfb2f6</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -6016,7 +6016,7 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>1785056153</t>
+          <t>1785056897</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
@@ -6026,7 +6026,7 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>8.75</t>
+          <t>9.615385</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -6043,7 +6043,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0x2fe44b6f9df282a6669198530843764a881fcd8c491dca571eaacc128af126e6</t>
+          <t>0xd359a1bde933becdef3ca166f20bbe9291a9b81f961befead4bc72e1713c6447</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -6058,12 +6058,12 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>9.99999</t>
+          <t>4.53999</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1.5425</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -6073,7 +6073,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Gimpo Citizen FC</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -6083,27 +6083,27 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Paju Citizen vs Ansan Greeners</t>
+          <t>Gimpo Citizen FC vs Yongin City</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Gimpo Citizen FC</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>0x90106aa6ffeea165b450ea7a1094c65ae9db8d6fdde000ce479b4af5b3fa3072</t>
+          <t>0x2725ecc350e6d5314ddee250cd3e445f586ab55a992fc73108db0913c5a41f24</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>L19306782</t>
+          <t>L19306783</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -6128,7 +6128,7 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>1785056005</t>
+          <t>1785056453</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
@@ -6138,7 +6138,7 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>18.433161</t>
+          <t>8.73075</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -6155,7 +6155,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0x318bf0ba1d202676e38a34cf3a263bf2f98d89a54dbf8acb2cccc6beaedcc4e8</t>
+          <t>0xe5784e1cc6cec364d74a7267a701924cf5f6543fed6d0c11d5f756f735c714f2</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -6170,12 +6170,12 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1.2575</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -6185,7 +6185,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Gimpo Citizen FC</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -6195,27 +6195,27 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Paju Citizen vs Ansan Greeners</t>
+          <t>Gimpo Citizen FC vs Yongin City</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Gimpo Citizen FC</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>0xabfa364122222118f5f35af9ee862e2b9587e9c2f656e281725fdca100cf17bf</t>
+          <t>0x2725ecc350e6d5314ddee250cd3e445f586ab55a992fc73108db0913c5a41f24</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>L19306782</t>
+          <t>L19306783</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -6240,7 +6240,7 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>1785055933</t>
+          <t>1785056153</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>4.970874</t>
+          <t>8.75</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -6267,7 +6267,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0x5dc684f3ea699d27149c867fb82e4e6f97c7382b6d8784e4edd5bf70e604bae2</t>
+          <t>0x2fe44b6f9df282a6669198530843764a881fcd8c491dca571eaacc128af126e6</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6282,12 +6282,12 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>9.99999</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1.2575</t>
+          <t>1.5425</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -6297,7 +6297,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -6322,7 +6322,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>0xabfa364122222118f5f35af9ee862e2b9587e9c2f656e281725fdca100cf17bf</t>
+          <t>0x90106aa6ffeea165b450ea7a1094c65ae9db8d6fdde000ce479b4af5b3fa3072</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -6352,7 +6352,7 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>1785055931</t>
+          <t>1785056005</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
@@ -6362,7 +6362,7 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>9.941748</t>
+          <t>18.433161</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -6379,7 +6379,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0x947b403314498890960e964926f3e25010f3b36a93afc49e309f7a71a57648b0</t>
+          <t>0x318bf0ba1d202676e38a34cf3a263bf2f98d89a54dbf8acb2cccc6beaedcc4e8</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6394,12 +6394,12 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.2575</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -6409,7 +6409,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC</t>
+          <t>Tie</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -6419,27 +6419,27 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC vs Yongin City</t>
+          <t>Paju Citizen vs Ansan Greeners</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>0x2725ecc350e6d5314ddee250cd3e445f586ab55a992fc73108db0913c5a41f24</t>
+          <t>0xabfa364122222118f5f35af9ee862e2b9587e9c2f656e281725fdca100cf17bf</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>L19306783</t>
+          <t>L19306782</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -6464,7 +6464,7 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>1785055853</t>
+          <t>1785055933</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
@@ -6474,7 +6474,7 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>8.75</t>
+          <t>4.970874</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -6491,110 +6491,334 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
+          <t>0x5dc684f3ea699d27149c867fb82e4e6f97c7382b6d8784e4edd5bf70e604bae2</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2.56</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>1.2575</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>K2-League</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Paju Citizen vs Ansan Greeners</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Paju Citizen</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Ansan Greeners</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>0xabfa364122222118f5f35af9ee862e2b9587e9c2f656e281725fdca100cf17bf</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>L19306782</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>1785055931</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>1785061800</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>9.941748</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>0x947b403314498890960e964926f3e25010f3b36a93afc49e309f7a71a57648b0</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>4.55</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen FC</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>K2-League</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen FC vs Yongin City</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen FC</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Yongin City</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>0x2725ecc350e6d5314ddee250cd3e445f586ab55a992fc73108db0913c5a41f24</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>L19306783</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>1785055853</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>1785061800</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>8.75</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
           <t>0x4df42281e0de14de14275865cafadfb98d1cc6f76c1873f8fd64bcaa2cae8075</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B59" t="inlineStr">
         <is>
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
         <is>
           <t>4.99</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="E59" t="inlineStr">
         <is>
           <t>1.2775</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
+      <c r="F59" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="G59" t="inlineStr">
         <is>
           <t>Tie</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="H59" t="inlineStr">
         <is>
           <t>K2-League</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
+      <c r="I59" t="inlineStr">
         <is>
           <t>Gimpo Citizen FC vs Yongin City</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr">
+      <c r="J59" t="inlineStr">
         <is>
           <t>Gimpo Citizen FC</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
+      <c r="K59" t="inlineStr">
         <is>
           <t>Yongin City</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr">
+      <c r="L59" t="inlineStr">
         <is>
           <t>0xf93dab40773f0e01839824957e7cecd4afb676d72a13c45521719f4f5c517a27</t>
         </is>
       </c>
-      <c r="M57" t="inlineStr">
+      <c r="M59" t="inlineStr">
         <is>
           <t>L19306783</t>
         </is>
       </c>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O57" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P57" t="inlineStr">
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R57" t="inlineStr">
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
         <is>
           <t>1785044379</t>
         </is>
       </c>
-      <c r="S57" t="inlineStr">
+      <c r="S59" t="inlineStr">
         <is>
           <t>1785061800</t>
         </is>
       </c>
-      <c r="T57" t="inlineStr">
+      <c r="T59" t="inlineStr">
         <is>
           <t>17.981982</t>
         </is>
       </c>
-      <c r="U57" t="inlineStr">
+      <c r="U59" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V57" t="inlineStr">
+      <c r="V59" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/K2-League/trades.xlsx
+++ b/data/sxbet/ligas/K2-League/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V59"/>
+  <dimension ref="A1:V98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,67 +531,59 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x59cfeb6eefafd07022cdcaae7869afb45bc60deb8b4c0b4b96ad04ae8bbdb0d3</t>
+          <t>0x72792262ae431dbdddbf088471b45079d60981e999bef9626fbfb120b75bf4d9</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>321.53001</t>
+          <t>4.99999</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.525</t>
+          <t>1.8388</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>K2-League</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Chungnam Asan FC 0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>K2-League</t>
-        </is>
-      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Chungnam Asan FC vs Seongnam FC</t>
+          <t>Chungbuk Cheongju FC vs Suwon Samsung Bluewings</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Chungnam Asan FC</t>
+          <t>Chungbuk Cheongju FC</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Seongnam FC</t>
+          <t>Suwon Samsung Bluewings</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x5d9fd67211ec6f71728981803ac86abc94216c4e6a398285b5003dabd4e5df0f</t>
+          <t>0x47b6ff226935cb58cf016dcbca241d4de16dbfae419d63e4b73b31ca8333c27c</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19382328</t>
+          <t>L19382330</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -616,7 +608,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1785534316</t>
+          <t>1785578466</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -626,7 +618,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>612.438114</t>
+          <t>5.96124</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -643,7 +635,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x57f84ab38f2e25e292c948ee169e9feff1e8436efac9878d37389052fc7a8ade</t>
+          <t>0xd8137a83eb126ced1479e30bbe78433f31664b78e4e08119e4c5e0e06678d90f</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -651,59 +643,51 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>9.99999</t>
+          <t>11.09996</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.525</t>
+          <t>1.8388</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
           <t>K2-League</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Chungnam Asan FC 0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>K2-League</t>
-        </is>
-      </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Chungnam Asan FC vs Seongnam FC</t>
+          <t>Chungbuk Cheongju FC vs Suwon Samsung Bluewings</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Chungnam Asan FC</t>
+          <t>Chungbuk Cheongju FC</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Seongnam FC</t>
+          <t>Suwon Samsung Bluewings</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0x5d9fd67211ec6f71728981803ac86abc94216c4e6a398285b5003dabd4e5df0f</t>
+          <t>0x47b6ff226935cb58cf016dcbca241d4de16dbfae419d63e4b73b31ca8333c27c</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>L19382328</t>
+          <t>L19382330</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -728,7 +712,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1785534315</t>
+          <t>1785578456</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -738,7 +722,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>19.0476</t>
+          <t>13.233931</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -755,39 +739,31 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x4da39049a709357f30ef968bfc90b4eec2da9d99090f3b99edf4ea11aeddd708</t>
+          <t>0x45dd4119f9e9c4b0d949d74afa77a8e1b81e558353af15d7945dc9acc34f137b</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>32.79</t>
+          <t>23.71902</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.5488</t>
+          <t>1.8388</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Hwaseong FC +0.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -795,27 +771,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Hwaseong FC vs Daegu FC</t>
+          <t>Chungbuk Cheongju FC vs Suwon Samsung Bluewings</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Hwaseong FC</t>
+          <t>Chungbuk Cheongju FC</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Daegu FC</t>
+          <t>Suwon Samsung Bluewings</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0xbde5165c3a540b0c6dd64b3df320540fd10ecb173373b087359951e7f790f852</t>
+          <t>0x47b6ff226935cb58cf016dcbca241d4de16dbfae419d63e4b73b31ca8333c27c</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>L19382332</t>
+          <t>L19382330</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -840,7 +816,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1785527084</t>
+          <t>1785578456</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -850,7 +826,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>59.753986</t>
+          <t>28.27901</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -867,7 +843,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x07b844c409deb0bc9c8e8dbda27c7c2b772aec07892356105db79f67ffb0e227</t>
+          <t>0xc5f6a546dd78c3c6c0c2b63058f45984183690baa2a85baf30f35fc6e6a95fbb</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -878,17 +854,17 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6.39</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.5675</t>
+          <t>1.8388</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -899,27 +875,27 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC vs Yongin City</t>
+          <t>Chungbuk Cheongju FC vs Suwon Samsung Bluewings</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC</t>
+          <t>Chungbuk Cheongju FC</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Suwon Samsung Bluewings</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0xf73fcbba4baac94056070f4c2db509913d7317940066a6918ac1f13256f52327</t>
+          <t>0x47b6ff226935cb58cf016dcbca241d4de16dbfae419d63e4b73b31ca8333c27c</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>L19306783</t>
+          <t>L19382330</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -944,17 +920,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1785064787</t>
+          <t>1785578455</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>1785061800</t>
+          <t>1785580200</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>11.259912</t>
+          <t>1.19225</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -971,7 +947,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0xf95f88d59f982dc2c9ca6387361b5a066ab48deeb7f9f6071274eb879ddabdd0</t>
+          <t>0x071e0dd48a8b69c5fd46a90d3fd6130a920ae4675f78336d20fd540e2fb36e19</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -982,17 +958,17 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>126.4351</t>
+          <t>14.2522</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.815</t>
+          <t>1.8388</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -1003,27 +979,27 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC vs Yongin City</t>
+          <t>Chungbuk Cheongju FC vs Suwon Samsung Bluewings</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC</t>
+          <t>Chungbuk Cheongju FC</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Suwon Samsung Bluewings</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0x1482cd21984a144c2f6033821f76b4033b1aeaebbab5c85a758b2e86c0553134</t>
+          <t>0x47b6ff226935cb58cf016dcbca241d4de16dbfae419d63e4b73b31ca8333c27c</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>L19306783</t>
+          <t>L19382330</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1048,17 +1024,17 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1785064732</t>
+          <t>1785578454</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>1785061800</t>
+          <t>1785580200</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>155.135092</t>
+          <t>16.992191</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1075,7 +1051,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0xe74ba88448233ab30d6e4b230046fe45bf1be0a6f71b8860703364abbbb40afe</t>
+          <t>0xd80db373e4b7ed691e095b9dd8e2c3060b27dd3b9d96138e938f8b834ed11575</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1090,22 +1066,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>19.69</t>
+          <t>9.99836</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.5038</t>
+          <t>1.2375</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Over 1.5</t>
+          <t>Tie</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1115,27 +1091,27 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Paju Citizen vs Ansan Greeners</t>
+          <t>Chungbuk Cheongju FC vs Suwon Samsung Bluewings</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Chungbuk Cheongju FC</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Suwon Samsung Bluewings</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0x6a23b140597c01b1670e03fdb996fc8e94424ec45a5e6e429b292ba1688dff5c</t>
+          <t>0xcbe732f420e35966f1693736f4eff7ac82d6eb79649c462d0b0da88b23389fd7</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>L19306782</t>
+          <t>L19382330</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1160,17 +1136,17 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1785064111</t>
+          <t>1785578439</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>1785061800</t>
+          <t>1785580200</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>39.086849</t>
+          <t>42.098358</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1187,23 +1163,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x02858e4fe5f076373faa42c17e9058ea19bff69a0b68493520c024b133c2ceed</t>
+          <t>0xd3730071ad09e64f8d94dd7eafe50fd030d149170edc5f0a6980a5b293fbdf6c</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0x0C2DA7fC8702784d6f75c78Da25460783A6709a0</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>12.54</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.4975</t>
+          <t>1.2363</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1211,7 +1191,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H8" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -1219,27 +1203,27 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Paju Citizen vs Ansan Greeners</t>
+          <t>Chungbuk Cheongju FC vs Suwon Samsung Bluewings</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Chungbuk Cheongju FC</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Suwon Samsung Bluewings</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0x90106aa6ffeea165b450ea7a1094c65ae9db8d6fdde000ce479b4af5b3fa3072</t>
+          <t>0xcbe732f420e35966f1693736f4eff7ac82d6eb79649c462d0b0da88b23389fd7</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>L19306782</t>
+          <t>L19382330</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1264,17 +1248,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1785063804</t>
+          <t>1785578425</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>1785061800</t>
+          <t>1785580200</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>6.030151</t>
+          <t>53.079365</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1291,7 +1275,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0xd6b44cd45d93535a9c1b39fad13245ea6ef0e5cbff858b443a9d40a281cf422f</t>
+          <t>0x0030d78c7fa3ca6505041a6863683acfc5d44fd46db42676d8fab5fface0f896</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1299,31 +1283,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>21.3</t>
+          <t>33.00917</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.2988</t>
+          <t>1.6637</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Over 2.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -1331,27 +1307,27 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Paju Citizen vs Ansan Greeners</t>
+          <t>Chungnam Asan FC vs Seongnam FC</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Chungnam Asan FC</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Seongnam FC</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0x2d5eca3e665030fe8c7c2a84772b94d8fc59c9a6991fd216ba914d3b345ffe07</t>
+          <t>0xdc5a3c94507978b475275edc3f202e74993cdff1bf5f2e138cb9ec5c9fdab56b</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>L19306782</t>
+          <t>L19382328</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1376,17 +1352,17 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1785063590</t>
+          <t>1785578412</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>1785061800</t>
+          <t>1785580200</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>71.297071</t>
+          <t>49.73133</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1403,7 +1379,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0xc41eea20c9aa34da894372c77f23e0a6ee134568f117e95b14c294310b2dc1f7</t>
+          <t>0x220dcc2e193d2914753c8ca31c20857d1cba243ec4469ca1444318967b690306</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1418,12 +1394,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>12.53</t>
+          <t>27.01</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.2037</t>
+          <t>1.3625</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1433,7 +1409,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Chungnam Asan FC</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1443,27 +1419,27 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC vs Yongin City</t>
+          <t>Chungnam Asan FC vs Seongnam FC</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC</t>
+          <t>Chungnam Asan FC</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Seongnam FC</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0x520e073f044523b55003a1d70f752c30f91cd5ebae7e23b2f294ad6679b3ed58</t>
+          <t>0x122be21c6184231146fb4c55c0406dac2859200e923b24d2b4641ce66abf29f4</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>L19306783</t>
+          <t>L19382328</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1488,17 +1464,17 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1785063530</t>
+          <t>1785578411</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>1785061800</t>
+          <t>1785580200</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>61.496933</t>
+          <t>74.510345</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1515,7 +1491,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0xe5a4265d3896fe621f44bfc6c8c9d2efe8a044ac121c6a5ec411dcd8ecbb22c9</t>
+          <t>0xa1105617e22069824dc4bb3cbe2a43733b8051deee672c5eb37dab4d3fe5e57d</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1523,19 +1499,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5.62999</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.5162</t>
+          <t>1.8438</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1543,11 +1515,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Gimpo Citizen FC</t>
-        </is>
-      </c>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -1555,27 +1523,27 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC vs Yongin City</t>
+          <t>Chungbuk Cheongju FC vs Suwon Samsung Bluewings</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC</t>
+          <t>Chungbuk Cheongju FC</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Suwon Samsung Bluewings</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0x2725ecc350e6d5314ddee250cd3e445f586ab55a992fc73108db0913c5a41f24</t>
+          <t>0x47b6ff226935cb58cf016dcbca241d4de16dbfae419d63e4b73b31ca8333c27c</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>L19306783</t>
+          <t>L19382330</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1600,17 +1568,17 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1785063352</t>
+          <t>1785578250</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>1785061800</t>
+          <t>1785580200</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1.937046</t>
+          <t>6.672581</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1627,7 +1595,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x996289847910ea662fcd868b20c9fa48f68ab4d7334bac4351bc46b6d3f479df</t>
+          <t>0xab0581f4aab772a5e75f6983d6a981e9515dda6c22e94295de4804365f5a78cd</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1635,19 +1603,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.99998</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.5162</t>
+          <t>1.8438</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1655,11 +1619,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Gimpo Citizen FC</t>
-        </is>
-      </c>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -1667,27 +1627,27 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC vs Yongin City</t>
+          <t>Chungbuk Cheongju FC vs Suwon Samsung Bluewings</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC</t>
+          <t>Chungbuk Cheongju FC</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Suwon Samsung Bluewings</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0x2725ecc350e6d5314ddee250cd3e445f586ab55a992fc73108db0913c5a41f24</t>
+          <t>0x47b6ff226935cb58cf016dcbca241d4de16dbfae419d63e4b73b31ca8333c27c</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>L19306783</t>
+          <t>L19382330</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1712,17 +1672,17 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1785063326</t>
+          <t>1785577978</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>1785061800</t>
+          <t>1785580200</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1.937046</t>
+          <t>1.185161</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1739,27 +1699,23 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0xed44d31e5a5b7071006924700a0078a2f8a3710d9bb8d24217652d198ffae7d7</t>
+          <t>0xd2748c10f4095190f2c2b3649173009f55db5d97aee6e8a15de89cc6f7dc2d94</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>28.84</t>
+          <t>4.99997</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.5162</t>
+          <t>1.8438</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1767,11 +1723,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Gimpo Citizen FC</t>
-        </is>
-      </c>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -1779,27 +1731,27 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC vs Yongin City</t>
+          <t>Chungbuk Cheongju FC vs Suwon Samsung Bluewings</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC</t>
+          <t>Chungbuk Cheongju FC</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Suwon Samsung Bluewings</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0x2725ecc350e6d5314ddee250cd3e445f586ab55a992fc73108db0913c5a41f24</t>
+          <t>0x47b6ff226935cb58cf016dcbca241d4de16dbfae419d63e4b73b31ca8333c27c</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>L19306783</t>
+          <t>L19382330</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1824,17 +1776,17 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1785063319</t>
+          <t>1785577974</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>1785061800</t>
+          <t>1785580200</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>55.864407</t>
+          <t>5.92589</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1851,28 +1803,28 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0x2bcba69d716b343c190b4a215a8f323f4abe23b13cd57d716f1b386e77406d71</t>
+          <t>0xb473a9bcd28ce7eb541287850173d36b188eb2ce16684b4f47feec73017ef210</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>4.99997</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.3912</t>
+          <t>1.8438</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -1883,27 +1835,27 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC vs Yongin City</t>
+          <t>Chungbuk Cheongju FC vs Suwon Samsung Bluewings</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC</t>
+          <t>Chungbuk Cheongju FC</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Suwon Samsung Bluewings</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0xf73fcbba4baac94056070f4c2db509913d7317940066a6918ac1f13256f52327</t>
+          <t>0x47b6ff226935cb58cf016dcbca241d4de16dbfae419d63e4b73b31ca8333c27c</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>L19306783</t>
+          <t>L19382330</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1928,17 +1880,17 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1785063319</t>
+          <t>1785577972</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>1785061800</t>
+          <t>1785580200</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>6.696486</t>
+          <t>5.92589</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1955,27 +1907,23 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0x74897816645fe410040b71368723e823f96b8b8ad1a8558a60563ea6a63c17b9</t>
+          <t>0x1c7c5e1e91914e15cd389ea78b98ffc4af816835d6679433a97a2be50034a7f1</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4.99997</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.5488</t>
+          <t>1.8438</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1983,11 +1931,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Paju Citizen</t>
-        </is>
-      </c>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -1995,27 +1939,27 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Paju Citizen vs Ansan Greeners</t>
+          <t>Chungbuk Cheongju FC vs Suwon Samsung Bluewings</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Chungbuk Cheongju FC</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Suwon Samsung Bluewings</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0x90106aa6ffeea165b450ea7a1094c65ae9db8d6fdde000ce479b4af5b3fa3072</t>
+          <t>0x47b6ff226935cb58cf016dcbca241d4de16dbfae419d63e4b73b31ca8333c27c</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>L19306782</t>
+          <t>L19382330</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2040,17 +1984,17 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1785063283</t>
+          <t>1785577971</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>1785061800</t>
+          <t>1785580200</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>18.223235</t>
+          <t>5.92589</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2067,23 +2011,23 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0x6c9b96e6ea55e8d6386264e63d154ad9cdf850c8f9c18b5c088abdcfcc710e8d</t>
+          <t>0x570a559aaadf75a6ed1acd4ccb5ddd8e55ce1e7f522824b57494899c861e8d6a</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.74999</t>
+          <t>5.34932</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.8313</t>
+          <t>1.8425</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2099,27 +2043,27 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Paju Citizen vs Ansan Greeners</t>
+          <t>Chungbuk Cheongju FC vs Suwon Samsung Bluewings</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Chungbuk Cheongju FC</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Suwon Samsung Bluewings</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0x6de105784818e175bb2cb50f54d4325a684a5693a05f8bd5b7f2b402aeb4bdfa</t>
+          <t>0x47b6ff226935cb58cf016dcbca241d4de16dbfae419d63e4b73b31ca8333c27c</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>L19306782</t>
+          <t>L19382330</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2144,17 +2088,17 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1785063278</t>
+          <t>1785577945</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>1785061800</t>
+          <t>1785580200</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2.105251</t>
+          <t>6.349341</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2171,23 +2115,23 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0x653ed25ca6aba498efe0c95f6d394f607985bf6c4ab830c3599772279631e8b1</t>
+          <t>0x8faf54553900d697a6ef224191c3c314fce17df8a2ec46f32c8f5f4664872c42</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>201.32998</t>
+          <t>30.16947</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.8213</t>
+          <t>1.8425</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2203,27 +2147,27 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Paju Citizen vs Ansan Greeners</t>
+          <t>Chungbuk Cheongju FC vs Suwon Samsung Bluewings</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Chungbuk Cheongju FC</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Suwon Samsung Bluewings</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0x6de105784818e175bb2cb50f54d4325a684a5693a05f8bd5b7f2b402aeb4bdfa</t>
+          <t>0x47b6ff226935cb58cf016dcbca241d4de16dbfae419d63e4b73b31ca8333c27c</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>L19306782</t>
+          <t>L19382330</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2248,17 +2192,17 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1785063071</t>
+          <t>1785577943</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>1785061800</t>
+          <t>1785580200</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>245.150661</t>
+          <t>35.80946</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2275,23 +2219,23 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0xd7beeace3688b4d75f908058620cd47f10d9926e086901a2c83333dd169ec720</t>
+          <t>0x87d245204fb6266d66f05bad0f085ef14e0002175ce19e9ca19fc941bd2840c8</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>48.03</t>
+          <t>28.6717</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.8425</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2307,27 +2251,27 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC vs Yongin City</t>
+          <t>Chungbuk Cheongju FC vs Suwon Samsung Bluewings</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC</t>
+          <t>Chungbuk Cheongju FC</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Suwon Samsung Bluewings</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0x2725ecc350e6d5314ddee250cd3e445f586ab55a992fc73108db0913c5a41f24</t>
+          <t>0x47b6ff226935cb58cf016dcbca241d4de16dbfae419d63e4b73b31ca8333c27c</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>L19306783</t>
+          <t>L19382330</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2352,17 +2296,17 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1785062970</t>
+          <t>1785577942</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>1785061800</t>
+          <t>1785580200</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>98.020408</t>
+          <t>34.031691</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2379,7 +2323,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0x8940d52e7feb848f5ca44e42ecc2fed94e942961b918122bc87142ffbf346d4c</t>
+          <t>0xa3ba7bafd18b1a2ed7a2d9f70c9f9f14d910d1148a0051bb51394a7e0b839c92</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2387,15 +2331,19 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>196.03997</t>
+          <t>3.66</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.8188</t>
+          <t>1.2937</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2403,7 +2351,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H19" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -2411,27 +2363,27 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Paju Citizen vs Ansan Greeners</t>
+          <t>Cheonan City vs Yongin City</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0x6de105784818e175bb2cb50f54d4325a684a5693a05f8bd5b7f2b402aeb4bdfa</t>
+          <t>0x4f0eac96e527e303ba7f731f63206ea5d322051eee61a9087848437cebf10534</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>L19306782</t>
+          <t>L19382335</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2456,17 +2408,17 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1785062953</t>
+          <t>1785577801</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>1785061800</t>
+          <t>1785580200</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>239.438131</t>
+          <t>12.459574</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2483,7 +2435,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0x2b9441f7515eb95a00a5708be64644050b069886b2e84d77ecdeea72fe8e3da7</t>
+          <t>0x2ff9636c19015324567a484925b48b01572feafd96dfae06927e7d28a91accb4</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2491,19 +2443,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>12.06</t>
+          <t>20.20568</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.1975</t>
+          <t>1.6475</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2511,11 +2459,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Yongin City</t>
-        </is>
-      </c>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -2523,27 +2467,27 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC vs Yongin City</t>
+          <t>Chungnam Asan FC vs Seongnam FC</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC</t>
+          <t>Chungnam Asan FC</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Seongnam FC</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0x520e073f044523b55003a1d70f752c30f91cd5ebae7e23b2f294ad6679b3ed58</t>
+          <t>0x122be21c6184231146fb4c55c0406dac2859200e923b24d2b4641ce66abf29f4</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>L19306783</t>
+          <t>L19382328</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2568,17 +2512,17 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1785062934</t>
+          <t>1785577136</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>1785061800</t>
+          <t>1785580200</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>61.063291</t>
+          <t>31.205683</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2595,7 +2539,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0x17ea9fc34d8d08859197baf8694510eafd385c5cb30d1bccaf4135418710a4ee</t>
+          <t>0xd04f669dbfe7947145022fe948220730e2200d0302b6c375521b18cfb89478d9</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2603,31 +2547,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>59.4</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.3862</t>
+          <t>1.8438</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Over 2.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -2635,27 +2571,27 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Paju Citizen vs Ansan Greeners</t>
+          <t>Chungbuk Cheongju FC vs Suwon Samsung Bluewings</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Chungbuk Cheongju FC</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Suwon Samsung Bluewings</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0x2d5eca3e665030fe8c7c2a84772b94d8fc59c9a6991fd216ba914d3b345ffe07</t>
+          <t>0x47b6ff226935cb58cf016dcbca241d4de16dbfae419d63e4b73b31ca8333c27c</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>L19306782</t>
+          <t>L19382330</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2680,17 +2616,17 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1785062748</t>
+          <t>1785577059</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>1785061800</t>
+          <t>1785580200</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>25.889968</t>
+          <t>70.4</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2707,7 +2643,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0xff313e8a80cab759f0306eced2743a83b68017dd8ecc4a5eda49613abd5f72bb</t>
+          <t>0xd6e59c4a6fedc3fc306e81e55a5678b03ee303e96a9653c49b87b641e05fecf5</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2715,31 +2651,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>58.83999</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.2275</t>
+          <t>1.8425</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Over 3.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -2747,27 +2675,27 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Paju Citizen vs Ansan Greeners</t>
+          <t>Chungbuk Cheongju FC vs Suwon Samsung Bluewings</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Chungbuk Cheongju FC</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Suwon Samsung Bluewings</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0x20fab15d1baac82bbe5a9371ad4e1e4f931edb8de76d814e671a0313aa4d8620</t>
+          <t>0x47b6ff226935cb58cf016dcbca241d4de16dbfae419d63e4b73b31ca8333c27c</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>L19306782</t>
+          <t>L19382330</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2792,17 +2720,17 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1785062437</t>
+          <t>1785577058</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>1785061800</t>
+          <t>1785580200</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>43.956044</t>
+          <t>69.839751</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2819,7 +2747,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0x5a88256e6b892595ad641ef1ae589c088b32b6034ec557ba72582fa8c93f67e3</t>
+          <t>0xbdaeb9efa9099daa54488930d7f3e08686658f371f2ca9deb5dee1fb018d5dc9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2830,12 +2758,12 @@
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>64.98999</t>
+          <t>15.11</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.8125</t>
+          <t>1.6713</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2851,27 +2779,27 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Paju Citizen vs Ansan Greeners</t>
+          <t>Cheonan City vs Yongin City</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0x6de105784818e175bb2cb50f54d4325a684a5693a05f8bd5b7f2b402aeb4bdfa</t>
+          <t>0xc44350683931fa086c3759e22036c1861e9430054b71327499cb1ad0357c41af</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>L19306782</t>
+          <t>L19382335</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2896,17 +2824,17 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1785062111</t>
+          <t>1785576608</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>1785061800</t>
+          <t>1785580200</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>79.98768</t>
+          <t>22.510242</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2923,12 +2851,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0x21aa47ce5d327006a8fdcf609e5990b1ea5499887fd8ccd0ff96d5bbe7df2f89</t>
+          <t>0x89e7975252a4021e2edec5b41c422fb0f9e0b0bd71b44469db8e27760ccfec81</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2938,22 +2866,22 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>23.39</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.3887</t>
+          <t>1.3838</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Paju Citizen -1</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2963,27 +2891,27 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Paju Citizen vs Ansan Greeners</t>
+          <t>Cheonan City vs Yongin City</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0x1398d7baccf6c5154c8090892c6597852ff56e90298e81fb604a8b9bf22c47ce</t>
+          <t>0x0ae3c1437f52d2b3c8a4d033ef252880ab9d9fee58c4335b560a2a5bdf7ec6bf</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>L19306782</t>
+          <t>L19382335</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -3008,17 +2936,17 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1785061695</t>
+          <t>1785576308</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>1785061800</t>
+          <t>1785580200</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>60.167203</t>
+          <t>7.504886</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3035,12 +2963,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0xaa13e9d13e81cd9edae13a80c0e426e52c85c5064c5b0c34d792d027f33fe560</t>
+          <t>0x2cbe5fb46a011721b21db0e317c482acbdda4529d7e20e5694a7635608189873</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3050,22 +2978,22 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>17.04</t>
+          <t>5.01495</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.2925</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Paju Citizen -1.5</t>
+          <t>Tie</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3075,27 +3003,27 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Paju Citizen vs Ansan Greeners</t>
+          <t>Cheonan City vs Yongin City</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0x48cd5a7ee72c95f57110826c0f2e2494d9438250815f7751e5e0fdce91ccbfba</t>
+          <t>0x4f0eac96e527e303ba7f731f63206ea5d322051eee61a9087848437cebf10534</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>L19306782</t>
+          <t>L19382335</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3120,17 +3048,17 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1785061694</t>
+          <t>1785576164</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>1785061800</t>
+          <t>1785580200</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>58.758621</t>
+          <t>17.145128</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3147,23 +3075,27 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0x9c2da91ae7561670702979941233734bebc22c36fdac867bf5bdb53a8151c6e9</t>
+          <t>0x6427a9b06be945650ac5754ea9013bd388bb7fd63b9fea057a31d292e952be4b</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>4.99997</t>
+          <t>4.99</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.795</t>
+          <t>1.2925</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -3171,7 +3103,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H26" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -3179,12 +3115,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC vs Yongin City</t>
+          <t>Cheonan City vs Yongin City</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -3194,12 +3130,12 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0x520e073f044523b55003a1d70f752c30f91cd5ebae7e23b2f294ad6679b3ed58</t>
+          <t>0x4f0eac96e527e303ba7f731f63206ea5d322051eee61a9087848437cebf10534</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>L19306783</t>
+          <t>L19382335</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -3224,17 +3160,17 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1785061651</t>
+          <t>1785576163</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>1785061800</t>
+          <t>1785580200</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>6.28927</t>
+          <t>17.059829</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3251,12 +3187,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0x12f98497a1f2dc0a130b32665dfeea9bbd9b744c2732456c77c91801ec687167</t>
+          <t>0xd7b3568a3172d11868a8c52422c6edb93781f013948e3cbe3187ecd49450a2ed</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3266,22 +3202,22 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>21.14</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.3513</t>
+          <t>1.3013</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC -1</t>
+          <t>Tie</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3291,27 +3227,27 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC vs Yongin City</t>
+          <t>Chungnam Asan FC vs Seongnam FC</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC</t>
+          <t>Chungnam Asan FC</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Seongnam FC</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0x4a4b2cf0de4356e1be221d31aa0feab4af681e89956037ff111c72307c4d9af6</t>
+          <t>0x3908aa00f1ce849001a57f81937948c4a35c187a56fca542d1c26ac2a5aa578c</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>L19306783</t>
+          <t>L19382328</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -3336,17 +3272,17 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1785061621</t>
+          <t>1785576156</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>1785061800</t>
+          <t>1785580200</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>60.185053</t>
+          <t>19.917012</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3363,23 +3299,27 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0x0f90aefde05859a865353743603e3925fef0a390e252c71ca62de94b7f3522d8</t>
+          <t>0x385d3c2ccc1504b8b62960b052836b16848b30f964e71dbb330e557b9d5b0958</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>43.51167</t>
+          <t>9.01646</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.795</t>
+          <t>1.3025</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -3387,7 +3327,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H28" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -3395,27 +3339,27 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC vs Yongin City</t>
+          <t>Chungnam Asan FC vs Seongnam FC</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC</t>
+          <t>Chungnam Asan FC</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Seongnam FC</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0x520e073f044523b55003a1d70f752c30f91cd5ebae7e23b2f294ad6679b3ed58</t>
+          <t>0x3908aa00f1ce849001a57f81937948c4a35c187a56fca542d1c26ac2a5aa578c</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>L19306783</t>
+          <t>L19382328</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -3440,17 +3384,17 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1785061621</t>
+          <t>1785576156</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>1785061800</t>
+          <t>1785580200</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>54.73166</t>
+          <t>29.806479</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3467,31 +3411,39 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0x45f1170f51d54ba31ead65b241ce33b618358dd91421e9194877f824ebea4f5d</t>
+          <t>0x81bc6461a5498bb098f71cbd0566c77991625c35e512a092b27824593eb64b44</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0x09b3a190a1e971Dd0B4F82Eb9008287fe43a540C</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>5.76</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.3838</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Cheonan City</t>
+        </is>
+      </c>
       <c r="H29" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -3499,12 +3451,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC vs Yongin City</t>
+          <t>Cheonan City vs Yongin City</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -3514,12 +3466,12 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0x7b353104df193f280c01b3e0a75dcbbc5dd4e628b7304c3537dff2339968d702</t>
+          <t>0x0ae3c1437f52d2b3c8a4d033ef252880ab9d9fee58c4335b560a2a5bdf7ec6bf</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>L19306783</t>
+          <t>L19382335</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -3544,17 +3496,17 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1785061583</t>
+          <t>1785576008</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>1785061800</t>
+          <t>1785580200</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>51.020408</t>
+          <t>15.009772</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3571,7 +3523,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0x8726e3d54f033c4394f3b9a8a297c466f26e8d1814d525163146dc1f9f836029</t>
+          <t>0x20a26ca056f3f25e1f8971a88b06b55502b7f6fd7d4ead5f9ed5057ee98ecf34</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3582,17 +3534,17 @@
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>5.70997</t>
+          <t>7.77558</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.795</t>
+          <t>1.3413</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
@@ -3603,27 +3555,27 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC vs Yongin City</t>
+          <t>Chungbuk Cheongju FC vs Suwon Samsung Bluewings</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC</t>
+          <t>Chungbuk Cheongju FC</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Suwon Samsung Bluewings</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0x520e073f044523b55003a1d70f752c30f91cd5ebae7e23b2f294ad6679b3ed58</t>
+          <t>0x9e11ba3ce6b4420e4e452b60f302739f1d8467716ba519ebe3f8132832094348</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>L19306783</t>
+          <t>L19382330</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -3648,17 +3600,17 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1785061581</t>
+          <t>1785576008</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>1785061800</t>
+          <t>1785580200</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>7.182352</t>
+          <t>22.785582</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3675,12 +3627,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0x78b589b7ea305b8a325e286dcbf526301e19f803d90ab77960c290d1d621d34a</t>
+          <t>0xd9d9b0ddddc1467f24d4b982d44a16b3c39903ee63500a8ec66563c6202bfcf9</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0x09b3a190a1e971Dd0B4F82Eb9008287fe43a540C</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -3690,12 +3642,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>5.01384</t>
+          <t>5.71</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.2788</t>
+          <t>1.3838</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -3705,7 +3657,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3715,12 +3667,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC vs Yongin City</t>
+          <t>Cheonan City vs Yongin City</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -3730,12 +3682,12 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0xf93dab40773f0e01839824957e7cecd4afb676d72a13c45521719f4f5c517a27</t>
+          <t>0x0ae3c1437f52d2b3c8a4d033ef252880ab9d9fee58c4335b560a2a5bdf7ec6bf</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>L19306783</t>
+          <t>L19382335</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -3760,17 +3712,17 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1785061533</t>
+          <t>1785575708</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>1785061800</t>
+          <t>1785580200</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>17.98687</t>
+          <t>14.879479</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3787,7 +3739,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0x64d493da52ab9f3215f2ee6a066aad2cbaf66597963522c2c53462ae6d466e65</t>
+          <t>0x087314e5ace3bbb3bbb4f703bfe21af2df9ef3152845f56763bcabd878659d88</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3795,15 +3747,19 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr"/>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>43.87998</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.7988</t>
+          <t>1.385</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -3811,7 +3767,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Cheonan City</t>
+        </is>
+      </c>
       <c r="H32" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -3819,12 +3779,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC vs Yongin City</t>
+          <t>Cheonan City vs Yongin City</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -3834,12 +3794,12 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0x520e073f044523b55003a1d70f752c30f91cd5ebae7e23b2f294ad6679b3ed58</t>
+          <t>0x0ae3c1437f52d2b3c8a4d033ef252880ab9d9fee58c4335b560a2a5bdf7ec6bf</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>L19306783</t>
+          <t>L19382335</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -3864,17 +3824,17 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1785061346</t>
+          <t>1785574808</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>1785061800</t>
+          <t>1785580200</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>54.935812</t>
+          <t>8.181818</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3891,7 +3851,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0xb6a5b0e5cc84223b1b456506ce5bc4a60492c7d715d16ce5ba4bcbbbb205e549</t>
+          <t>0x1665cbfdd918d1b313ff8b09985889ba3e20ffef471ed1f77d4454a6d4870eb1</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3899,15 +3859,19 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr"/>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>10.19999</t>
+          <t>10.96</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.7988</t>
+          <t>1.6113</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -3915,7 +3879,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Suwon Samsung Bluewings</t>
+        </is>
+      </c>
       <c r="H33" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -3923,27 +3891,27 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC vs Yongin City</t>
+          <t>Chungbuk Cheongju FC vs Suwon Samsung Bluewings</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC</t>
+          <t>Chungbuk Cheongju FC</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Suwon Samsung Bluewings</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0x520e073f044523b55003a1d70f752c30f91cd5ebae7e23b2f294ad6679b3ed58</t>
+          <t>0xb29a7409dfd5ac0b7a29e92e49cc6bab92af282a2f9d95f3eeb630ed33eb7a3a</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>L19306783</t>
+          <t>L19382330</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -3968,17 +3936,17 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1785061261</t>
+          <t>1785574796</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>1785061800</t>
+          <t>1785580200</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>12.769941</t>
+          <t>17.93047</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -3995,23 +3963,23 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0x932ea4448a5d14be89226effb4bcb8584e5004da981b9fb12e769029a2cd6a34</t>
+          <t>0xf5159a5ea43cd4f5bd5f77236fb23f24714602f00b37c28d1f70bb3786749e16</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.7988</t>
+          <t>1.5413</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -4027,27 +3995,27 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC vs Yongin City</t>
+          <t>Hwaseong FC vs Daegu FC</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC</t>
+          <t>Hwaseong FC</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Daegu FC</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0x520e073f044523b55003a1d70f752c30f91cd5ebae7e23b2f294ad6679b3ed58</t>
+          <t>0x3673fddffb9c10163590d13afe39cb241b3c0284138745deddac5c176ba19ebd</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>L19306783</t>
+          <t>L19382332</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -4072,17 +4040,17 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1785061250</t>
+          <t>1785574516</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>1785061800</t>
+          <t>1785580200</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>6.259781</t>
+          <t>6.060046</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4099,23 +4067,27 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0x6ba96fe1be95723f4530ab62caaff2817e70e2c1aa504d2f0afe5b7d44447528</t>
+          <t>0x1d3e02f07b5d6a05bde415b055541ce4395cbd9016dfcb7b067173b6ff538c00</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>43.12404</t>
+          <t>5.76</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.7975</t>
+          <t>1.3838</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -4123,7 +4095,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Cheonan City</t>
+        </is>
+      </c>
       <c r="H35" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -4131,12 +4107,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC vs Yongin City</t>
+          <t>Cheonan City vs Yongin City</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -4146,12 +4122,12 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0x520e073f044523b55003a1d70f752c30f91cd5ebae7e23b2f294ad6679b3ed58</t>
+          <t>0x0ae3c1437f52d2b3c8a4d033ef252880ab9d9fee58c4335b560a2a5bdf7ec6bf</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>L19306783</t>
+          <t>L19382335</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -4176,17 +4152,17 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1785061221</t>
+          <t>1785573908</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>1785061800</t>
+          <t>1785580200</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>54.074031</t>
+          <t>15.009772</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4203,7 +4179,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0xa4c5cc7d130116507c7f97158d19bded9ace84b90e4089b2386235aca563a109</t>
+          <t>0x43f4e76dc758bd60088f0e19fe831ad6e231cfd3f25713ee2197b0c4c12225c4</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4211,31 +4187,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>5.54</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.2537</t>
+          <t>1.335</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -4243,27 +4211,27 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Paju Citizen vs Ansan Greeners</t>
+          <t>Chungbuk Cheongju FC vs Suwon Samsung Bluewings</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Chungbuk Cheongju FC</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Suwon Samsung Bluewings</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0xabfa364122222118f5f35af9ee862e2b9587e9c2f656e281725fdca100cf17bf</t>
+          <t>0x9e11ba3ce6b4420e4e452b60f302739f1d8467716ba519ebe3f8132832094348</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>L19306782</t>
+          <t>L19382330</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -4288,17 +4256,17 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1785060618</t>
+          <t>1785573008</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>1785061800</t>
+          <t>1785580200</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>21.832512</t>
+          <t>17.164179</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4315,28 +4283,28 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0xed6f77aaa7a7dbe5c2457f000b022f2da0cc5bd1004291d76e71044f4e1faa36</t>
+          <t>0xcc556a2f534d604ca3147c77e407c4a3caccfb460a650afb93e92f95893a83f3</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>4.99999</t>
+          <t>5.74</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.7975</t>
+          <t>1.335</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
@@ -4347,27 +4315,27 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC vs Yongin City</t>
+          <t>Chungbuk Cheongju FC vs Suwon Samsung Bluewings</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC</t>
+          <t>Chungbuk Cheongju FC</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Suwon Samsung Bluewings</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0x520e073f044523b55003a1d70f752c30f91cd5ebae7e23b2f294ad6679b3ed58</t>
+          <t>0x9e11ba3ce6b4420e4e452b60f302739f1d8467716ba519ebe3f8132832094348</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>L19306783</t>
+          <t>L19382330</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -4392,17 +4360,17 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1785060105</t>
+          <t>1785572408</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>1785061800</t>
+          <t>1785580200</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>6.26958</t>
+          <t>17.134328</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4419,23 +4387,27 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0xe0d4aa08492162b980b70ecc4ec3e9ae46b9fd85fea771f538c542e4e27f10ca</t>
+          <t>0xe6b9109907b0068b7b44342bbfe6aa4e4f925a1808a4234ef25d5964c06e8a19</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>4.99999</t>
+          <t>4.99</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.7975</t>
+          <t>1.2913</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -4443,7 +4415,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H38" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -4451,12 +4427,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC vs Yongin City</t>
+          <t>Cheonan City vs Yongin City</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -4466,12 +4442,12 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0x520e073f044523b55003a1d70f752c30f91cd5ebae7e23b2f294ad6679b3ed58</t>
+          <t>0x4f0eac96e527e303ba7f731f63206ea5d322051eee61a9087848437cebf10534</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>L19306783</t>
+          <t>L19382335</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -4496,17 +4472,17 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1785060103</t>
+          <t>1785571129</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>1785061800</t>
+          <t>1785580200</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>6.26958</t>
+          <t>17.133047</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4523,23 +4499,27 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0x733bd5ce99f877eba370291936b138251c1bd48cee90480bc876f49523ca7fca</t>
+          <t>0x3adcd675a8ad2ac41cfe2151a15dc0861c045d26ad2b087ec6303e2e6bc75b83</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>4.99999</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.7975</t>
+          <t>1.2412</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -4547,7 +4527,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H39" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -4555,27 +4539,27 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC vs Yongin City</t>
+          <t>Chungbuk Cheongju FC vs Suwon Samsung Bluewings</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC</t>
+          <t>Chungbuk Cheongju FC</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Suwon Samsung Bluewings</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0x520e073f044523b55003a1d70f752c30f91cd5ebae7e23b2f294ad6679b3ed58</t>
+          <t>0xcbe732f420e35966f1693736f4eff7ac82d6eb79649c462d0b0da88b23389fd7</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>L19306783</t>
+          <t>L19382330</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -4600,17 +4584,17 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1785060101</t>
+          <t>1785561333</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>1785061800</t>
+          <t>1785580200</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>6.26958</t>
+          <t>4.601036</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4627,7 +4611,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0xcfbe574677265ef97dc3204a001ce1b1e25523c8a98c296a3cf235f97650aace</t>
+          <t>0x0ba2bf9f0fc74c97ade129a1430bdc4cd89f8fecee54ee5b1f9876c41b38c180</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4642,22 +4626,22 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.3887</t>
+          <t>1.2662</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Paju Citizen -1</t>
+          <t>Tie</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -4667,27 +4651,27 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Paju Citizen vs Ansan Greeners</t>
+          <t>Hwaseong FC vs Daegu FC</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Hwaseong FC</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Daegu FC</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0x1398d7baccf6c5154c8090892c6597852ff56e90298e81fb604a8b9bf22c47ce</t>
+          <t>0xda1e33e5fc880742964769df06cb9c83769ec80d9cb168728d3a3467d0a0473b</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>L19306782</t>
+          <t>L19382332</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -4712,17 +4696,17 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1785060085</t>
+          <t>1785558588</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>1785061800</t>
+          <t>1785580200</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>10.289389</t>
+          <t>12.995305</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -4739,31 +4723,39 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0xebd1df0aa7e7f54677bedd84a6c923ca856cf657e0531639938bfb8111becc94</t>
+          <t>0x59cfeb6eefafd07022cdcaae7869afb45bc60deb8b4c0b4b96ad04ae8bbdb0d3</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>22.97198</t>
+          <t>321.53001</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.7963</t>
+          <t>1.525</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr"/>
+          <t>K2-League</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Chungnam Asan FC 0</t>
+        </is>
+      </c>
       <c r="H41" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -4771,27 +4763,27 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC vs Yongin City</t>
+          <t>Chungnam Asan FC vs Seongnam FC</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC</t>
+          <t>Chungnam Asan FC</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Seongnam FC</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0x520e073f044523b55003a1d70f752c30f91cd5ebae7e23b2f294ad6679b3ed58</t>
+          <t>0x5d9fd67211ec6f71728981803ac86abc94216c4e6a398285b5003dabd4e5df0f</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>L19306783</t>
+          <t>L19382328</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -4816,17 +4808,17 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1785060074</t>
+          <t>1785534316</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>1785061800</t>
+          <t>1785580200</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>28.85021</t>
+          <t>612.438114</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -4843,31 +4835,39 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0x9137623e3c72596dddeb8dd77deb26f0f80f5d8ad5037c9d9fd9ec11f1d3a62d</t>
+          <t>0x57f84ab38f2e25e292c948ee169e9feff1e8436efac9878d37389052fc7a8ade</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>15.59279</t>
+          <t>9.99999</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.7963</t>
+          <t>1.525</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr"/>
+          <t>K2-League</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Chungnam Asan FC 0</t>
+        </is>
+      </c>
       <c r="H42" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -4875,27 +4875,27 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC vs Yongin City</t>
+          <t>Chungnam Asan FC vs Seongnam FC</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC</t>
+          <t>Chungnam Asan FC</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Seongnam FC</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0x520e073f044523b55003a1d70f752c30f91cd5ebae7e23b2f294ad6679b3ed58</t>
+          <t>0x5d9fd67211ec6f71728981803ac86abc94216c4e6a398285b5003dabd4e5df0f</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>L19306783</t>
+          <t>L19382328</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -4920,17 +4920,17 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1785060073</t>
+          <t>1785534315</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>1785061800</t>
+          <t>1785580200</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>19.582782</t>
+          <t>19.0476</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -4947,31 +4947,39 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0x47fecae2c93459e7d6a1189dcb95e8bce239b7e2d26ce67db4733b564451a3fd</t>
+          <t>0x4da39049a709357f30ef968bfc90b4eec2da9d99090f3b99edf4ea11aeddd708</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>16.1469</t>
+          <t>32.79</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.7963</t>
+          <t>1.5488</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr"/>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Hwaseong FC +0.5</t>
+        </is>
+      </c>
       <c r="H43" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -4979,27 +4987,27 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC vs Yongin City</t>
+          <t>Hwaseong FC vs Daegu FC</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC</t>
+          <t>Hwaseong FC</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Daegu FC</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0x520e073f044523b55003a1d70f752c30f91cd5ebae7e23b2f294ad6679b3ed58</t>
+          <t>0xbde5165c3a540b0c6dd64b3df320540fd10ecb173373b087359951e7f790f852</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>L19306783</t>
+          <t>L19382332</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -5024,17 +5032,17 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1785060072</t>
+          <t>1785527084</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>1785061800</t>
+          <t>1785580200</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>20.278681</t>
+          <t>59.753986</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -5051,39 +5059,31 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0x7851323bb653ef81f86e4483a09baec3f52472a947788d079eacebc8ce474280</t>
+          <t>0x07b844c409deb0bc9c8e8dbda27c7c2b772aec07892356105db79f67ffb0e227</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>19.02</t>
+          <t>6.39</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.275</t>
+          <t>1.5675</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -5106,7 +5106,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0xf93dab40773f0e01839824957e7cecd4afb676d72a13c45521719f4f5c517a27</t>
+          <t>0xf73fcbba4baac94056070f4c2db509913d7317940066a6918ac1f13256f52327</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -5136,7 +5136,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>1785060054</t>
+          <t>1785064787</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>69.163636</t>
+          <t>11.259912</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -5163,39 +5163,31 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0x5936a0069456d68663344829a3e2e9aa688da6a9e1d38de76848d1bdfb84366a</t>
+          <t>0xf95f88d59f982dc2c9ca6387361b5a066ab48deeb7f9f6071274eb879ddabdd0</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t>10.56</t>
+          <t>126.4351</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1.2737</t>
+          <t>1.815</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -5218,7 +5210,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>0xf93dab40773f0e01839824957e7cecd4afb676d72a13c45521719f4f5c517a27</t>
+          <t>0x1482cd21984a144c2f6033821f76b4033b1aeaebbab5c85a758b2e86c0553134</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -5248,7 +5240,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>1785060044</t>
+          <t>1785064732</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
@@ -5258,7 +5250,7 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>38.575342</t>
+          <t>155.135092</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -5275,31 +5267,39 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0xc27dc932de76aa5047aab63fd483f2351fd3e777a4bebc494353cf3a53c52ba9</t>
+          <t>0xe74ba88448233ab30d6e4b230046fe45bf1be0a6f71b8860703364abbbb40afe</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>20.61772</t>
+          <t>19.69</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.3425</t>
+          <t>1.5038</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr"/>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Over 1.5</t>
+        </is>
+      </c>
       <c r="H46" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -5322,7 +5322,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>0x386468865ee4fb2d064354b0f4bb50fc57a8f046452fa6667bc56978f4cf3823</t>
+          <t>0x6a23b140597c01b1670e03fdb996fc8e94424ec45a5e6e429b292ba1688dff5c</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -5352,7 +5352,7 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>1785059855</t>
+          <t>1785064111</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
@@ -5362,7 +5362,7 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>60.197723</t>
+          <t>39.086849</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -5379,39 +5379,31 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0x06cf39065296686830cf556b4943f2a94e035610868690980b237da489f6c32a</t>
+          <t>0x02858e4fe5f076373faa42c17e9058ea19bff69a0b68493520c024b133c2ceed</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x0C2DA7fC8702784d6f75c78Da25460783A6709a0</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>4.94155</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.355</t>
+          <t>1.4975</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>Gimpo Citizen FC -1</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -5419,27 +5411,27 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC vs Yongin City</t>
+          <t>Paju Citizen vs Ansan Greeners</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>0x4a4b2cf0de4356e1be221d31aa0feab4af681e89956037ff111c72307c4d9af6</t>
+          <t>0x90106aa6ffeea165b450ea7a1094c65ae9db8d6fdde000ce479b4af5b3fa3072</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>L19306783</t>
+          <t>L19306782</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -5464,7 +5456,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>1785059821</t>
+          <t>1785063804</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
@@ -5474,7 +5466,7 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>13.919859</t>
+          <t>6.030151</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -5491,12 +5483,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0x6cad572e295e86d0eff792e6a73f1ecb4b2563c632f3a61d710a79a81bcbefc5</t>
+          <t>0xd6b44cd45d93535a9c1b39fad13245ea6ef0e5cbff858b443a9d40a281cf422f</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -5506,22 +5498,22 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>16.43</t>
+          <t>21.3</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.355</t>
+          <t>1.2988</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC -1</t>
+          <t>Over 2.5</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -5531,27 +5523,27 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC vs Yongin City</t>
+          <t>Paju Citizen vs Ansan Greeners</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>0x4a4b2cf0de4356e1be221d31aa0feab4af681e89956037ff111c72307c4d9af6</t>
+          <t>0x2d5eca3e665030fe8c7c2a84772b94d8fc59c9a6991fd216ba914d3b345ffe07</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>L19306783</t>
+          <t>L19306782</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -5576,7 +5568,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>1785059820</t>
+          <t>1785063590</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
@@ -5586,7 +5578,7 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>46.28169</t>
+          <t>71.297071</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -5603,23 +5595,27 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0xd90cf2f29f54991a5ee8c926cce019177b5bb5fd98602218fb9acaaf6a910664</t>
+          <t>0xc41eea20c9aa34da894372c77f23e0a6ee134568f117e95b14c294310b2dc1f7</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12.53</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1.4675</t>
+          <t>1.2037</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -5627,7 +5623,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Yongin City</t>
+        </is>
+      </c>
       <c r="H49" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -5635,27 +5635,27 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Paju Citizen vs Ansan Greeners</t>
+          <t>Gimpo Citizen FC vs Yongin City</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Gimpo Citizen FC</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>0x90106aa6ffeea165b450ea7a1094c65ae9db8d6fdde000ce479b4af5b3fa3072</t>
+          <t>0x520e073f044523b55003a1d70f752c30f91cd5ebae7e23b2f294ad6679b3ed58</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>L19306782</t>
+          <t>L19306783</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -5680,7 +5680,7 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>1785058466</t>
+          <t>1785063530</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
@@ -5690,7 +5690,7 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>23.529412</t>
+          <t>61.496933</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -5707,7 +5707,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0xfaacadf40a626e2b5b306c37ecce7325e0fabbb091c125c037dd14587c31bfe4</t>
+          <t>0xe5a4265d3896fe621f44bfc6c8c9d2efe8a044ac121c6a5ec411dcd8ecbb22c9</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5722,12 +5722,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>4.53</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1.5212</t>
+          <t>1.5162</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -5792,7 +5792,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>1785057353</t>
+          <t>1785063352</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
@@ -5802,7 +5802,7 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>8.690647</t>
+          <t>1.937046</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -5819,7 +5819,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0x182964c6008d5b7d29731fd19876092a52fa2068fcb16aaf430dd8e0a6009721</t>
+          <t>0x996289847910ea662fcd868b20c9fa48f68ab4d7334bac4351bc46b6d3f479df</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5834,12 +5834,12 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>3.73</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1.2763</t>
+          <t>1.5162</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -5849,7 +5849,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Gimpo Citizen FC</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -5874,7 +5874,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>0xf93dab40773f0e01839824957e7cecd4afb676d72a13c45521719f4f5c517a27</t>
+          <t>0x2725ecc350e6d5314ddee250cd3e445f586ab55a992fc73108db0913c5a41f24</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -5904,7 +5904,7 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>1785057212</t>
+          <t>1785063326</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
@@ -5914,7 +5914,7 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>13.502262</t>
+          <t>1.937046</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -5931,12 +5931,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0xae029509b64a4e0489363d3aa1a7e18db0cd21b4fb65f5064e49185bb4bfb2f6</t>
+          <t>0xed44d31e5a5b7071006924700a0078a2f8a3710d9bb8d24217652d198ffae7d7</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -5946,12 +5946,12 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>28.84</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.5162</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -6016,7 +6016,7 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>1785056897</t>
+          <t>1785063319</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
@@ -6026,7 +6026,7 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>9.615385</t>
+          <t>55.864407</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -6043,7 +6043,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0xd359a1bde933becdef3ca166f20bbe9291a9b81f961befead4bc72e1713c6447</t>
+          <t>0x2bcba69d716b343c190b4a215a8f323f4abe23b13cd57d716f1b386e77406d71</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -6051,46 +6051,38 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
-          <t>4.53999</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.3912</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>K2-League</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen FC vs Yongin City</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
         <is>
           <t>Gimpo Citizen FC</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>K2-League</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>Gimpo Citizen FC vs Yongin City</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>Gimpo Citizen FC</t>
-        </is>
-      </c>
       <c r="K53" t="inlineStr">
         <is>
           <t>Yongin City</t>
@@ -6098,7 +6090,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>0x2725ecc350e6d5314ddee250cd3e445f586ab55a992fc73108db0913c5a41f24</t>
+          <t>0xf73fcbba4baac94056070f4c2db509913d7317940066a6918ac1f13256f52327</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -6128,7 +6120,7 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>1785056453</t>
+          <t>1785063319</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
@@ -6138,7 +6130,7 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>8.73075</t>
+          <t>6.696486</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -6155,7 +6147,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0xe5784e1cc6cec364d74a7267a701924cf5f6543fed6d0c11d5f756f735c714f2</t>
+          <t>0x74897816645fe410040b71368723e823f96b8b8ad1a8558a60563ea6a63c17b9</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -6170,12 +6162,12 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.5488</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -6185,7 +6177,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -6195,27 +6187,27 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC vs Yongin City</t>
+          <t>Paju Citizen vs Ansan Greeners</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>0x2725ecc350e6d5314ddee250cd3e445f586ab55a992fc73108db0913c5a41f24</t>
+          <t>0x90106aa6ffeea165b450ea7a1094c65ae9db8d6fdde000ce479b4af5b3fa3072</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>L19306783</t>
+          <t>L19306782</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -6240,7 +6232,7 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>1785056153</t>
+          <t>1785063283</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
@@ -6250,7 +6242,7 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>8.75</t>
+          <t>18.223235</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -6267,7 +6259,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0x2fe44b6f9df282a6669198530843764a881fcd8c491dca571eaacc128af126e6</t>
+          <t>0x6c9b96e6ea55e8d6386264e63d154ad9cdf850c8f9c18b5c088abdcfcc710e8d</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6275,19 +6267,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
-          <t>9.99999</t>
+          <t>1.74999</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1.5425</t>
+          <t>1.8313</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -6295,26 +6283,22 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>K2-League</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Paju Citizen vs Ansan Greeners</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
         <is>
           <t>Paju Citizen</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>K2-League</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>Paju Citizen vs Ansan Greeners</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>Paju Citizen</t>
-        </is>
-      </c>
       <c r="K55" t="inlineStr">
         <is>
           <t>Ansan Greeners</t>
@@ -6322,7 +6306,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>0x90106aa6ffeea165b450ea7a1094c65ae9db8d6fdde000ce479b4af5b3fa3072</t>
+          <t>0x6de105784818e175bb2cb50f54d4325a684a5693a05f8bd5b7f2b402aeb4bdfa</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -6352,7 +6336,7 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>1785056005</t>
+          <t>1785063278</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
@@ -6362,7 +6346,7 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>18.433161</t>
+          <t>2.105251</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -6379,7 +6363,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0x318bf0ba1d202676e38a34cf3a263bf2f98d89a54dbf8acb2cccc6beaedcc4e8</t>
+          <t>0x653ed25ca6aba498efe0c95f6d394f607985bf6c4ab830c3599772279631e8b1</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6387,19 +6371,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>201.32998</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1.2575</t>
+          <t>1.8213</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -6407,11 +6387,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -6434,7 +6410,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>0xabfa364122222118f5f35af9ee862e2b9587e9c2f656e281725fdca100cf17bf</t>
+          <t>0x6de105784818e175bb2cb50f54d4325a684a5693a05f8bd5b7f2b402aeb4bdfa</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -6464,7 +6440,7 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>1785055933</t>
+          <t>1785063071</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
@@ -6474,7 +6450,7 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>4.970874</t>
+          <t>245.150661</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -6491,27 +6467,23 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0x5dc684f3ea699d27149c867fb82e4e6f97c7382b6d8784e4edd5bf70e604bae2</t>
+          <t>0xd7beeace3688b4d75f908058620cd47f10d9926e086901a2c83333dd169ec720</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>48.03</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>1.2575</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -6519,11 +6491,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -6531,27 +6499,27 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Paju Citizen vs Ansan Greeners</t>
+          <t>Gimpo Citizen FC vs Yongin City</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Gimpo Citizen FC</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>0xabfa364122222118f5f35af9ee862e2b9587e9c2f656e281725fdca100cf17bf</t>
+          <t>0x2725ecc350e6d5314ddee250cd3e445f586ab55a992fc73108db0913c5a41f24</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>L19306782</t>
+          <t>L19306783</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -6576,7 +6544,7 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>1785055931</t>
+          <t>1785062970</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
@@ -6586,7 +6554,7 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>9.941748</t>
+          <t>98.020408</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -6603,7 +6571,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0x947b403314498890960e964926f3e25010f3b36a93afc49e309f7a71a57648b0</t>
+          <t>0x8940d52e7feb848f5ca44e42ecc2fed94e942961b918122bc87142ffbf346d4c</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6611,19 +6579,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>196.03997</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.8188</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -6631,11 +6595,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>Gimpo Citizen FC</t>
-        </is>
-      </c>
+      <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -6643,27 +6603,27 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC vs Yongin City</t>
+          <t>Paju Citizen vs Ansan Greeners</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>0x2725ecc350e6d5314ddee250cd3e445f586ab55a992fc73108db0913c5a41f24</t>
+          <t>0x6de105784818e175bb2cb50f54d4325a684a5693a05f8bd5b7f2b402aeb4bdfa</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>L19306783</t>
+          <t>L19306782</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -6688,7 +6648,7 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>1785055853</t>
+          <t>1785062953</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
@@ -6698,7 +6658,7 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>8.75</t>
+          <t>239.438131</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
@@ -6715,110 +6675,4342 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
+          <t>0x2b9441f7515eb95a00a5708be64644050b069886b2e84d77ecdeea72fe8e3da7</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>12.06</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>1.1975</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Yongin City</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>K2-League</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen FC vs Yongin City</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen FC</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Yongin City</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>0x520e073f044523b55003a1d70f752c30f91cd5ebae7e23b2f294ad6679b3ed58</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>L19306783</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>1785062934</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>1785061800</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>61.063291</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>0x17ea9fc34d8d08859197baf8694510eafd385c5cb30d1bccaf4135418710a4ee</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>1.3862</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>K2-League</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Paju Citizen vs Ansan Greeners</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Paju Citizen</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Ansan Greeners</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>0x2d5eca3e665030fe8c7c2a84772b94d8fc59c9a6991fd216ba914d3b345ffe07</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>L19306782</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>1785062748</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>1785061800</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>25.889968</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>0xff313e8a80cab759f0306eced2743a83b68017dd8ecc4a5eda49613abd5f72bb</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>1.2275</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>K2-League</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Paju Citizen vs Ansan Greeners</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Paju Citizen</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Ansan Greeners</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>0x20fab15d1baac82bbe5a9371ad4e1e4f931edb8de76d814e671a0313aa4d8620</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>L19306782</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>1785062437</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>1785061800</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>43.956044</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>0x5a88256e6b892595ad641ef1ae589c088b32b6034ec557ba72582fa8c93f67e3</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr"/>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>64.98999</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>1.8125</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>K2-League</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Paju Citizen vs Ansan Greeners</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Paju Citizen</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Ansan Greeners</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>0x6de105784818e175bb2cb50f54d4325a684a5693a05f8bd5b7f2b402aeb4bdfa</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>L19306782</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>1785062111</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>1785061800</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>79.98768</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>0x21aa47ce5d327006a8fdcf609e5990b1ea5499887fd8ccd0ff96d5bbe7df2f89</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>23.39</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>1.3887</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Paju Citizen -1</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>K2-League</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Paju Citizen vs Ansan Greeners</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Paju Citizen</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Ansan Greeners</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>0x1398d7baccf6c5154c8090892c6597852ff56e90298e81fb604a8b9bf22c47ce</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>L19306782</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>1785061695</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>1785061800</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>60.167203</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>0xaa13e9d13e81cd9edae13a80c0e426e52c85c5064c5b0c34d792d027f33fe560</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>17.04</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Paju Citizen -1.5</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>K2-League</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Paju Citizen vs Ansan Greeners</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Paju Citizen</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Ansan Greeners</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>0x48cd5a7ee72c95f57110826c0f2e2494d9438250815f7751e5e0fdce91ccbfba</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>L19306782</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>1785061694</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>1785061800</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>58.758621</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>0x9c2da91ae7561670702979941233734bebc22c36fdac867bf5bdb53a8151c6e9</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>4.99997</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>1.795</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>K2-League</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen FC vs Yongin City</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen FC</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Yongin City</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>0x520e073f044523b55003a1d70f752c30f91cd5ebae7e23b2f294ad6679b3ed58</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>L19306783</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>1785061651</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>1785061800</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>6.28927</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>0x12f98497a1f2dc0a130b32665dfeea9bbd9b744c2732456c77c91801ec687167</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>21.14</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>1.3513</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen FC -1</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>K2-League</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen FC vs Yongin City</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen FC</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Yongin City</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>0x4a4b2cf0de4356e1be221d31aa0feab4af681e89956037ff111c72307c4d9af6</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>L19306783</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>1785061621</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>1785061800</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>60.185053</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>0x0f90aefde05859a865353743603e3925fef0a390e252c71ca62de94b7f3522d8</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>43.51167</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>1.795</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>K2-League</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen FC vs Yongin City</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen FC</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Yongin City</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>0x520e073f044523b55003a1d70f752c30f91cd5ebae7e23b2f294ad6679b3ed58</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>L19306783</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>1785061621</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>1785061800</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>54.73166</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>0x45f1170f51d54ba31ead65b241ce33b618358dd91421e9194877f824ebea4f5d</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>0x09b3a190a1e971Dd0B4F82Eb9008287fe43a540C</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr"/>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>K2-League</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen FC vs Yongin City</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen FC</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Yongin City</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>0x7b353104df193f280c01b3e0a75dcbbc5dd4e628b7304c3537dff2339968d702</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>L19306783</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>1785061583</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>1785061800</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>51.020408</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>0x8726e3d54f033c4394f3b9a8a297c466f26e8d1814d525163146dc1f9f836029</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>5.70997</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>1.795</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>K2-League</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen FC vs Yongin City</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen FC</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Yongin City</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>0x520e073f044523b55003a1d70f752c30f91cd5ebae7e23b2f294ad6679b3ed58</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>L19306783</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>1785061581</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>1785061800</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>7.182352</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>0x78b589b7ea305b8a325e286dcbf526301e19f803d90ab77960c290d1d621d34a</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>0x09b3a190a1e971Dd0B4F82Eb9008287fe43a540C</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>5.01384</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>1.2788</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>K2-League</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen FC vs Yongin City</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen FC</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Yongin City</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>0xf93dab40773f0e01839824957e7cecd4afb676d72a13c45521719f4f5c517a27</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>L19306783</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>1785061533</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>1785061800</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>17.98687</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>0x64d493da52ab9f3215f2ee6a066aad2cbaf66597963522c2c53462ae6d466e65</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr"/>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>43.87998</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>1.7988</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>K2-League</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen FC vs Yongin City</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen FC</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Yongin City</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>0x520e073f044523b55003a1d70f752c30f91cd5ebae7e23b2f294ad6679b3ed58</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>L19306783</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>1785061346</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>1785061800</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>54.935812</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>0xb6a5b0e5cc84223b1b456506ce5bc4a60492c7d715d16ce5ba4bcbbbb205e549</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr"/>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>10.19999</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>1.7988</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>K2-League</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen FC vs Yongin City</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen FC</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Yongin City</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>0x520e073f044523b55003a1d70f752c30f91cd5ebae7e23b2f294ad6679b3ed58</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>L19306783</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>1785061261</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>1785061800</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>12.769941</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>0x932ea4448a5d14be89226effb4bcb8584e5004da981b9fb12e769029a2cd6a34</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr"/>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>1.7988</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>K2-League</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen FC vs Yongin City</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen FC</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Yongin City</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>0x520e073f044523b55003a1d70f752c30f91cd5ebae7e23b2f294ad6679b3ed58</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>L19306783</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>1785061250</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>1785061800</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>6.259781</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>0x6ba96fe1be95723f4530ab62caaff2817e70e2c1aa504d2f0afe5b7d44447528</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr"/>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>43.12404</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>1.7975</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>K2-League</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen FC vs Yongin City</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen FC</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Yongin City</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>0x520e073f044523b55003a1d70f752c30f91cd5ebae7e23b2f294ad6679b3ed58</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>L19306783</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>1785061221</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>1785061800</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>54.074031</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>0xa4c5cc7d130116507c7f97158d19bded9ace84b90e4089b2386235aca563a109</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>5.54</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>1.2537</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>K2-League</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Paju Citizen vs Ansan Greeners</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>Paju Citizen</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Ansan Greeners</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>0xabfa364122222118f5f35af9ee862e2b9587e9c2f656e281725fdca100cf17bf</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>L19306782</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>1785060618</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>1785061800</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>21.832512</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>0xed6f77aaa7a7dbe5c2457f000b022f2da0cc5bd1004291d76e71044f4e1faa36</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>4.99999</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>1.7975</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>K2-League</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen FC vs Yongin City</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen FC</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Yongin City</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>0x520e073f044523b55003a1d70f752c30f91cd5ebae7e23b2f294ad6679b3ed58</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>L19306783</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>1785060105</t>
+        </is>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>1785061800</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>6.26958</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>0xe0d4aa08492162b980b70ecc4ec3e9ae46b9fd85fea771f538c542e4e27f10ca</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr"/>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>4.99999</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>1.7975</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>K2-League</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen FC vs Yongin City</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen FC</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Yongin City</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>0x520e073f044523b55003a1d70f752c30f91cd5ebae7e23b2f294ad6679b3ed58</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>L19306783</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>1785060103</t>
+        </is>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>1785061800</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>6.26958</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>0x733bd5ce99f877eba370291936b138251c1bd48cee90480bc876f49523ca7fca</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr"/>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>4.99999</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>1.7975</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>K2-League</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen FC vs Yongin City</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen FC</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Yongin City</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>0x520e073f044523b55003a1d70f752c30f91cd5ebae7e23b2f294ad6679b3ed58</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>L19306783</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>1785060101</t>
+        </is>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>1785061800</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>6.26958</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>0xcfbe574677265ef97dc3204a001ce1b1e25523c8a98c296a3cf235f97650aace</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>1.3887</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Paju Citizen -1</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>K2-League</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Paju Citizen vs Ansan Greeners</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>Paju Citizen</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Ansan Greeners</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>0x1398d7baccf6c5154c8090892c6597852ff56e90298e81fb604a8b9bf22c47ce</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>L19306782</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>1785060085</t>
+        </is>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>1785061800</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>10.289389</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>0xebd1df0aa7e7f54677bedd84a6c923ca856cf657e0531639938bfb8111becc94</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr"/>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>22.97198</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>1.7963</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>K2-League</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen FC vs Yongin City</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen FC</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Yongin City</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>0x520e073f044523b55003a1d70f752c30f91cd5ebae7e23b2f294ad6679b3ed58</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>L19306783</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>1785060074</t>
+        </is>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>1785061800</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>28.85021</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>0x9137623e3c72596dddeb8dd77deb26f0f80f5d8ad5037c9d9fd9ec11f1d3a62d</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr"/>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>15.59279</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>1.7963</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>K2-League</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen FC vs Yongin City</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen FC</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Yongin City</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>0x520e073f044523b55003a1d70f752c30f91cd5ebae7e23b2f294ad6679b3ed58</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>L19306783</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>1785060073</t>
+        </is>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>1785061800</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>19.582782</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>0x47fecae2c93459e7d6a1189dcb95e8bce239b7e2d26ce67db4733b564451a3fd</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr"/>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>16.1469</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>1.7963</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>K2-League</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen FC vs Yongin City</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen FC</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Yongin City</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>0x520e073f044523b55003a1d70f752c30f91cd5ebae7e23b2f294ad6679b3ed58</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>L19306783</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>1785060072</t>
+        </is>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>1785061800</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>20.278681</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>0x7851323bb653ef81f86e4483a09baec3f52472a947788d079eacebc8ce474280</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>19.02</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>1.275</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>K2-League</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen FC vs Yongin City</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen FC</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Yongin City</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>0xf93dab40773f0e01839824957e7cecd4afb676d72a13c45521719f4f5c517a27</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>L19306783</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>1785060054</t>
+        </is>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>1785061800</t>
+        </is>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>69.163636</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>0x5936a0069456d68663344829a3e2e9aa688da6a9e1d38de76848d1bdfb84366a</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>10.56</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>1.2737</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>K2-League</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen FC vs Yongin City</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen FC</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Yongin City</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>0xf93dab40773f0e01839824957e7cecd4afb676d72a13c45521719f4f5c517a27</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>L19306783</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>1785060044</t>
+        </is>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>1785061800</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>38.575342</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>0xc27dc932de76aa5047aab63fd483f2351fd3e777a4bebc494353cf3a53c52ba9</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr"/>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>20.61772</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>1.3425</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>K2-League</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Paju Citizen vs Ansan Greeners</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>Paju Citizen</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Ansan Greeners</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>0x386468865ee4fb2d064354b0f4bb50fc57a8f046452fa6667bc56978f4cf3823</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>L19306782</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>1785059855</t>
+        </is>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>1785061800</t>
+        </is>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>60.197723</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>0x06cf39065296686830cf556b4943f2a94e035610868690980b237da489f6c32a</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>4.94155</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>1.355</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen FC -1</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>K2-League</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen FC vs Yongin City</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen FC</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Yongin City</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>0x4a4b2cf0de4356e1be221d31aa0feab4af681e89956037ff111c72307c4d9af6</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>L19306783</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>1785059821</t>
+        </is>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>1785061800</t>
+        </is>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>13.919859</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>0x6cad572e295e86d0eff792e6a73f1ecb4b2563c632f3a61d710a79a81bcbefc5</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>16.43</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>1.355</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen FC -1</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>K2-League</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen FC vs Yongin City</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen FC</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Yongin City</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>0x4a4b2cf0de4356e1be221d31aa0feab4af681e89956037ff111c72307c4d9af6</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>L19306783</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>1785059820</t>
+        </is>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>1785061800</t>
+        </is>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>46.28169</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>0xd90cf2f29f54991a5ee8c926cce019177b5bb5fd98602218fb9acaaf6a910664</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr"/>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>1.4675</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>K2-League</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Paju Citizen vs Ansan Greeners</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>Paju Citizen</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Ansan Greeners</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>0x90106aa6ffeea165b450ea7a1094c65ae9db8d6fdde000ce479b4af5b3fa3072</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>L19306782</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>1785058466</t>
+        </is>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>1785061800</t>
+        </is>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>23.529412</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>0xfaacadf40a626e2b5b306c37ecce7325e0fabbb091c125c037dd14587c31bfe4</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>4.53</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>1.5212</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen FC</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>K2-League</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen FC vs Yongin City</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen FC</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Yongin City</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>0x2725ecc350e6d5314ddee250cd3e445f586ab55a992fc73108db0913c5a41f24</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>L19306783</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>1785057353</t>
+        </is>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>1785061800</t>
+        </is>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>8.690647</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>0x182964c6008d5b7d29731fd19876092a52fa2068fcb16aaf430dd8e0a6009721</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>3.73</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>1.2763</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>K2-League</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen FC vs Yongin City</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen FC</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Yongin City</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>0xf93dab40773f0e01839824957e7cecd4afb676d72a13c45521719f4f5c517a27</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>L19306783</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>1785057212</t>
+        </is>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>1785061800</t>
+        </is>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>13.502262</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>0xae029509b64a4e0489363d3aa1a7e18db0cd21b4fb65f5064e49185bb4bfb2f6</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen FC</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>K2-League</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen FC vs Yongin City</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen FC</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Yongin City</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>0x2725ecc350e6d5314ddee250cd3e445f586ab55a992fc73108db0913c5a41f24</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>L19306783</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R91" t="inlineStr">
+        <is>
+          <t>1785056897</t>
+        </is>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>1785061800</t>
+        </is>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>9.615385</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>0xd359a1bde933becdef3ca166f20bbe9291a9b81f961befead4bc72e1713c6447</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>4.53999</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen FC</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>K2-League</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen FC vs Yongin City</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen FC</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Yongin City</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>0x2725ecc350e6d5314ddee250cd3e445f586ab55a992fc73108db0913c5a41f24</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>L19306783</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R92" t="inlineStr">
+        <is>
+          <t>1785056453</t>
+        </is>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>1785061800</t>
+        </is>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>8.73075</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>0xe5784e1cc6cec364d74a7267a701924cf5f6543fed6d0c11d5f756f735c714f2</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>4.55</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen FC</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>K2-League</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen FC vs Yongin City</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen FC</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Yongin City</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>0x2725ecc350e6d5314ddee250cd3e445f586ab55a992fc73108db0913c5a41f24</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>L19306783</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R93" t="inlineStr">
+        <is>
+          <t>1785056153</t>
+        </is>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>1785061800</t>
+        </is>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>8.75</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>0x2fe44b6f9df282a6669198530843764a881fcd8c491dca571eaacc128af126e6</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>9.99999</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>1.5425</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Paju Citizen</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>K2-League</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Paju Citizen vs Ansan Greeners</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>Paju Citizen</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Ansan Greeners</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>0x90106aa6ffeea165b450ea7a1094c65ae9db8d6fdde000ce479b4af5b3fa3072</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>L19306782</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R94" t="inlineStr">
+        <is>
+          <t>1785056005</t>
+        </is>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>1785061800</t>
+        </is>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>18.433161</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>0x318bf0ba1d202676e38a34cf3a263bf2f98d89a54dbf8acb2cccc6beaedcc4e8</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>1.28</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>1.2575</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>K2-League</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Paju Citizen vs Ansan Greeners</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>Paju Citizen</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Ansan Greeners</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>0xabfa364122222118f5f35af9ee862e2b9587e9c2f656e281725fdca100cf17bf</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>L19306782</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R95" t="inlineStr">
+        <is>
+          <t>1785055933</t>
+        </is>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>1785061800</t>
+        </is>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>4.970874</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>0x5dc684f3ea699d27149c867fb82e4e6f97c7382b6d8784e4edd5bf70e604bae2</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>2.56</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>1.2575</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>K2-League</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Paju Citizen vs Ansan Greeners</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>Paju Citizen</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Ansan Greeners</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>0xabfa364122222118f5f35af9ee862e2b9587e9c2f656e281725fdca100cf17bf</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>L19306782</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R96" t="inlineStr">
+        <is>
+          <t>1785055931</t>
+        </is>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>1785061800</t>
+        </is>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>9.941748</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>0x947b403314498890960e964926f3e25010f3b36a93afc49e309f7a71a57648b0</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>4.55</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen FC</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>K2-League</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen FC vs Yongin City</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen FC</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Yongin City</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>0x2725ecc350e6d5314ddee250cd3e445f586ab55a992fc73108db0913c5a41f24</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>L19306783</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R97" t="inlineStr">
+        <is>
+          <t>1785055853</t>
+        </is>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>1785061800</t>
+        </is>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>8.75</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
           <t>0x4df42281e0de14de14275865cafadfb98d1cc6f76c1873f8fd64bcaa2cae8075</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="B98" t="inlineStr">
         <is>
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
         <is>
           <t>4.99</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="E98" t="inlineStr">
         <is>
           <t>1.2775</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
+      <c r="F98" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="G98" t="inlineStr">
         <is>
           <t>Tie</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
+      <c r="H98" t="inlineStr">
         <is>
           <t>K2-League</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
+      <c r="I98" t="inlineStr">
         <is>
           <t>Gimpo Citizen FC vs Yongin City</t>
         </is>
       </c>
-      <c r="J59" t="inlineStr">
+      <c r="J98" t="inlineStr">
         <is>
           <t>Gimpo Citizen FC</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr">
+      <c r="K98" t="inlineStr">
         <is>
           <t>Yongin City</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr">
+      <c r="L98" t="inlineStr">
         <is>
           <t>0xf93dab40773f0e01839824957e7cecd4afb676d72a13c45521719f4f5c517a27</t>
         </is>
       </c>
-      <c r="M59" t="inlineStr">
+      <c r="M98" t="inlineStr">
         <is>
           <t>L19306783</t>
         </is>
       </c>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O59" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P59" t="inlineStr">
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R59" t="inlineStr">
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R98" t="inlineStr">
         <is>
           <t>1785044379</t>
         </is>
       </c>
-      <c r="S59" t="inlineStr">
+      <c r="S98" t="inlineStr">
         <is>
           <t>1785061800</t>
         </is>
       </c>
-      <c r="T59" t="inlineStr">
+      <c r="T98" t="inlineStr">
         <is>
           <t>17.981982</t>
         </is>
       </c>
-      <c r="U59" t="inlineStr">
+      <c r="U98" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V59" t="inlineStr">
+      <c r="V98" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/K2-League/trades.xlsx
+++ b/data/sxbet/ligas/K2-League/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V98"/>
+  <dimension ref="A1:V99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,28 +531,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x72792262ae431dbdddbf088471b45079d60981e999bef9626fbfb120b75bf4d9</t>
+          <t>0x8a4af3a0b4b13cf57049ab82f395d7d34f9a5fd506160c67bbdd18174b6ad54e</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>4.99999</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.8388</t>
+          <t>1.2662</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
@@ -563,27 +563,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Chungbuk Cheongju FC vs Suwon Samsung Bluewings</t>
+          <t>Ansan Greeners vs Gimhae City</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Chungbuk Cheongju FC</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Suwon Samsung Bluewings</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x47b6ff226935cb58cf016dcbca241d4de16dbfae419d63e4b73b31ca8333c27c</t>
+          <t>0x88b7c7348c4915e417185345face1c028319f7a4edf6917e10541c5cf3904388</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19382330</t>
+          <t>L19391911</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -608,17 +608,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1785578466</t>
+          <t>1785605666</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1785580200</t>
+          <t>1785666600</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>5.96124</t>
+          <t>24.037559</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -635,18 +635,18 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0xd8137a83eb126ced1479e30bbe78433f31664b78e4e08119e4c5e0e06678d90f</t>
+          <t>0x72792262ae431dbdddbf088471b45079d60981e999bef9626fbfb120b75bf4d9</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>11.09996</t>
+          <t>4.99999</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -712,7 +712,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1785578456</t>
+          <t>1785578466</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -722,7 +722,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>13.233931</t>
+          <t>5.96124</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -739,18 +739,18 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x45dd4119f9e9c4b0d949d74afa77a8e1b81e558353af15d7945dc9acc34f137b</t>
+          <t>0xd8137a83eb126ced1479e30bbe78433f31664b78e4e08119e4c5e0e06678d90f</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>23.71902</t>
+          <t>11.09996</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>28.27901</t>
+          <t>13.233931</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -843,18 +843,18 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0xc5f6a546dd78c3c6c0c2b63058f45984183690baa2a85baf30f35fc6e6a95fbb</t>
+          <t>0x45dd4119f9e9c4b0d949d74afa77a8e1b81e558353af15d7945dc9acc34f137b</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>23.71902</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1785578455</t>
+          <t>1785578456</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1.19225</t>
+          <t>28.27901</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -947,18 +947,18 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x071e0dd48a8b69c5fd46a90d3fd6130a920ae4675f78336d20fd540e2fb36e19</t>
+          <t>0xc5f6a546dd78c3c6c0c2b63058f45984183690baa2a85baf30f35fc6e6a95fbb</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>14.2522</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1785578454</t>
+          <t>1785578455</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>16.992191</t>
+          <t>1.19225</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1051,27 +1051,23 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0xd80db373e4b7ed691e095b9dd8e2c3060b27dd3b9d96138e938f8b834ed11575</t>
+          <t>0x071e0dd48a8b69c5fd46a90d3fd6130a920ae4675f78336d20fd540e2fb36e19</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>9.99836</t>
+          <t>14.2522</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.2375</t>
+          <t>1.8388</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1079,11 +1075,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -1106,7 +1098,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0xcbe732f420e35966f1693736f4eff7ac82d6eb79649c462d0b0da88b23389fd7</t>
+          <t>0x47b6ff226935cb58cf016dcbca241d4de16dbfae419d63e4b73b31ca8333c27c</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1136,7 +1128,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1785578439</t>
+          <t>1785578454</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1146,7 +1138,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>42.098358</t>
+          <t>16.992191</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1163,12 +1155,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0xd3730071ad09e64f8d94dd7eafe50fd030d149170edc5f0a6980a5b293fbdf6c</t>
+          <t>0xd80db373e4b7ed691e095b9dd8e2c3060b27dd3b9d96138e938f8b834ed11575</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1178,12 +1170,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>12.54</t>
+          <t>9.99836</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.2363</t>
+          <t>1.2375</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1248,7 +1240,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1785578425</t>
+          <t>1785578439</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1258,7 +1250,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>53.079365</t>
+          <t>42.098358</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1275,23 +1267,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0x0030d78c7fa3ca6505041a6863683acfc5d44fd46db42676d8fab5fface0f896</t>
+          <t>0xd3730071ad09e64f8d94dd7eafe50fd030d149170edc5f0a6980a5b293fbdf6c</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>33.00917</t>
+          <t>12.54</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.6637</t>
+          <t>1.2363</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1299,7 +1295,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H9" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -1307,27 +1307,27 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Chungnam Asan FC vs Seongnam FC</t>
+          <t>Chungbuk Cheongju FC vs Suwon Samsung Bluewings</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Chungnam Asan FC</t>
+          <t>Chungbuk Cheongju FC</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Seongnam FC</t>
+          <t>Suwon Samsung Bluewings</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0xdc5a3c94507978b475275edc3f202e74993cdff1bf5f2e138cb9ec5c9fdab56b</t>
+          <t>0xcbe732f420e35966f1693736f4eff7ac82d6eb79649c462d0b0da88b23389fd7</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>L19382328</t>
+          <t>L19382330</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1785578412</t>
+          <t>1785578425</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>49.73133</t>
+          <t>53.079365</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1379,7 +1379,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0x220dcc2e193d2914753c8ca31c20857d1cba243ec4469ca1444318967b690306</t>
+          <t>0x0030d78c7fa3ca6505041a6863683acfc5d44fd46db42676d8fab5fface0f896</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1387,19 +1387,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>27.01</t>
+          <t>33.00917</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.3625</t>
+          <t>1.6637</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1407,26 +1403,22 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>K2-League</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Chungnam Asan FC vs Seongnam FC</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
         <is>
           <t>Chungnam Asan FC</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>K2-League</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Chungnam Asan FC vs Seongnam FC</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Chungnam Asan FC</t>
-        </is>
-      </c>
       <c r="K10" t="inlineStr">
         <is>
           <t>Seongnam FC</t>
@@ -1434,7 +1426,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0x122be21c6184231146fb4c55c0406dac2859200e923b24d2b4641ce66abf29f4</t>
+          <t>0xdc5a3c94507978b475275edc3f202e74993cdff1bf5f2e138cb9ec5c9fdab56b</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1464,7 +1456,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1785578411</t>
+          <t>1785578412</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1474,7 +1466,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>74.510345</t>
+          <t>49.73133</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1491,7 +1483,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0xa1105617e22069824dc4bb3cbe2a43733b8051deee672c5eb37dab4d3fe5e57d</t>
+          <t>0x220dcc2e193d2914753c8ca31c20857d1cba243ec4469ca1444318967b690306</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1499,15 +1491,19 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>5.62999</t>
+          <t>27.01</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.8438</t>
+          <t>1.3625</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1515,7 +1511,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Chungnam Asan FC</t>
+        </is>
+      </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -1523,27 +1523,27 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Chungbuk Cheongju FC vs Suwon Samsung Bluewings</t>
+          <t>Chungnam Asan FC vs Seongnam FC</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Chungbuk Cheongju FC</t>
+          <t>Chungnam Asan FC</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Suwon Samsung Bluewings</t>
+          <t>Seongnam FC</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0x47b6ff226935cb58cf016dcbca241d4de16dbfae419d63e4b73b31ca8333c27c</t>
+          <t>0x122be21c6184231146fb4c55c0406dac2859200e923b24d2b4641ce66abf29f4</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>L19382330</t>
+          <t>L19382328</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1785578250</t>
+          <t>1785578411</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>6.672581</t>
+          <t>74.510345</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1595,7 +1595,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0xab0581f4aab772a5e75f6983d6a981e9515dda6c22e94295de4804365f5a78cd</t>
+          <t>0xa1105617e22069824dc4bb3cbe2a43733b8051deee672c5eb37dab4d3fe5e57d</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1606,7 +1606,7 @@
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.99998</t>
+          <t>5.62999</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1785577978</t>
+          <t>1785578250</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1.185161</t>
+          <t>6.672581</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1699,18 +1699,18 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0xd2748c10f4095190f2c2b3649173009f55db5d97aee6e8a15de89cc6f7dc2d94</t>
+          <t>0xab0581f4aab772a5e75f6983d6a981e9515dda6c22e94295de4804365f5a78cd</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>4.99997</t>
+          <t>0.99998</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1785577974</t>
+          <t>1785577978</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>5.92589</t>
+          <t>1.185161</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1803,7 +1803,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0xb473a9bcd28ce7eb541287850173d36b188eb2ce16684b4f47feec73017ef210</t>
+          <t>0xd2748c10f4095190f2c2b3649173009f55db5d97aee6e8a15de89cc6f7dc2d94</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1785577972</t>
+          <t>1785577974</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1907,7 +1907,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0x1c7c5e1e91914e15cd389ea78b98ffc4af816835d6679433a97a2be50034a7f1</t>
+          <t>0xb473a9bcd28ce7eb541287850173d36b188eb2ce16684b4f47feec73017ef210</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1984,7 +1984,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1785577971</t>
+          <t>1785577972</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2011,23 +2011,23 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0x570a559aaadf75a6ed1acd4ccb5ddd8e55ce1e7f522824b57494899c861e8d6a</t>
+          <t>0x1c7c5e1e91914e15cd389ea78b98ffc4af816835d6679433a97a2be50034a7f1</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>5.34932</t>
+          <t>4.99997</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.8425</t>
+          <t>1.8438</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2088,7 +2088,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1785577945</t>
+          <t>1785577971</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2098,7 +2098,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>6.349341</t>
+          <t>5.92589</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2115,7 +2115,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0x8faf54553900d697a6ef224191c3c314fce17df8a2ec46f32c8f5f4664872c42</t>
+          <t>0x570a559aaadf75a6ed1acd4ccb5ddd8e55ce1e7f522824b57494899c861e8d6a</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2126,7 +2126,7 @@
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>30.16947</t>
+          <t>5.34932</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1785577943</t>
+          <t>1785577945</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>35.80946</t>
+          <t>6.349341</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2219,7 +2219,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0x87d245204fb6266d66f05bad0f085ef14e0002175ce19e9ca19fc941bd2840c8</t>
+          <t>0x8faf54553900d697a6ef224191c3c314fce17df8a2ec46f32c8f5f4664872c42</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2230,7 +2230,7 @@
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>28.6717</t>
+          <t>30.16947</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2296,7 +2296,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1785577942</t>
+          <t>1785577943</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>34.031691</t>
+          <t>35.80946</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2323,27 +2323,23 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0xa3ba7bafd18b1a2ed7a2d9f70c9f9f14d910d1148a0051bb51394a7e0b839c92</t>
+          <t>0x87d245204fb6266d66f05bad0f085ef14e0002175ce19e9ca19fc941bd2840c8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>3.66</t>
+          <t>28.6717</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.2937</t>
+          <t>1.8425</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2351,11 +2347,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -2363,27 +2355,27 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Cheonan City vs Yongin City</t>
+          <t>Chungbuk Cheongju FC vs Suwon Samsung Bluewings</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Chungbuk Cheongju FC</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Suwon Samsung Bluewings</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0x4f0eac96e527e303ba7f731f63206ea5d322051eee61a9087848437cebf10534</t>
+          <t>0x47b6ff226935cb58cf016dcbca241d4de16dbfae419d63e4b73b31ca8333c27c</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>L19382335</t>
+          <t>L19382330</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2408,7 +2400,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1785577801</t>
+          <t>1785577942</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2418,7 +2410,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>12.459574</t>
+          <t>34.031691</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2435,7 +2427,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0x2ff9636c19015324567a484925b48b01572feafd96dfae06927e7d28a91accb4</t>
+          <t>0xa3ba7bafd18b1a2ed7a2d9f70c9f9f14d910d1148a0051bb51394a7e0b839c92</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2443,15 +2435,19 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>20.20568</t>
+          <t>3.66</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.6475</t>
+          <t>1.2937</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2459,7 +2455,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H20" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -2467,27 +2467,27 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Chungnam Asan FC vs Seongnam FC</t>
+          <t>Cheonan City vs Yongin City</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Chungnam Asan FC</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Seongnam FC</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0x122be21c6184231146fb4c55c0406dac2859200e923b24d2b4641ce66abf29f4</t>
+          <t>0x4f0eac96e527e303ba7f731f63206ea5d322051eee61a9087848437cebf10534</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>L19382328</t>
+          <t>L19382335</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2512,7 +2512,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1785577136</t>
+          <t>1785577801</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2522,7 +2522,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>31.205683</t>
+          <t>12.459574</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2539,7 +2539,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0xd04f669dbfe7947145022fe948220730e2200d0302b6c375521b18cfb89478d9</t>
+          <t>0x2ff9636c19015324567a484925b48b01572feafd96dfae06927e7d28a91accb4</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2550,12 +2550,12 @@
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>59.4</t>
+          <t>20.20568</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.8438</t>
+          <t>1.6475</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2571,27 +2571,27 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Chungbuk Cheongju FC vs Suwon Samsung Bluewings</t>
+          <t>Chungnam Asan FC vs Seongnam FC</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Chungbuk Cheongju FC</t>
+          <t>Chungnam Asan FC</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Suwon Samsung Bluewings</t>
+          <t>Seongnam FC</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0x47b6ff226935cb58cf016dcbca241d4de16dbfae419d63e4b73b31ca8333c27c</t>
+          <t>0x122be21c6184231146fb4c55c0406dac2859200e923b24d2b4641ce66abf29f4</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>L19382330</t>
+          <t>L19382328</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2616,7 +2616,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1785577059</t>
+          <t>1785577136</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>70.4</t>
+          <t>31.205683</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2643,7 +2643,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0xd6e59c4a6fedc3fc306e81e55a5678b03ee303e96a9653c49b87b641e05fecf5</t>
+          <t>0xd04f669dbfe7947145022fe948220730e2200d0302b6c375521b18cfb89478d9</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2654,12 +2654,12 @@
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>58.83999</t>
+          <t>59.4</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.8425</t>
+          <t>1.8438</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2720,7 +2720,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1785577058</t>
+          <t>1785577059</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2730,7 +2730,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>69.839751</t>
+          <t>70.4</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2747,7 +2747,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0xbdaeb9efa9099daa54488930d7f3e08686658f371f2ca9deb5dee1fb018d5dc9</t>
+          <t>0xd6e59c4a6fedc3fc306e81e55a5678b03ee303e96a9653c49b87b641e05fecf5</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2758,12 +2758,12 @@
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>15.11</t>
+          <t>58.83999</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.6713</t>
+          <t>1.8425</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2779,27 +2779,27 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Cheonan City vs Yongin City</t>
+          <t>Chungbuk Cheongju FC vs Suwon Samsung Bluewings</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Chungbuk Cheongju FC</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Suwon Samsung Bluewings</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0xc44350683931fa086c3759e22036c1861e9430054b71327499cb1ad0357c41af</t>
+          <t>0x47b6ff226935cb58cf016dcbca241d4de16dbfae419d63e4b73b31ca8333c27c</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>L19382335</t>
+          <t>L19382330</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1785576608</t>
+          <t>1785577058</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>22.510242</t>
+          <t>69.839751</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2851,7 +2851,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0x89e7975252a4021e2edec5b41c422fb0f9e0b0bd71b44469db8e27760ccfec81</t>
+          <t>0xbdaeb9efa9099daa54488930d7f3e08686658f371f2ca9deb5dee1fb018d5dc9</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2859,19 +2859,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>15.11</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.3838</t>
+          <t>1.6713</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2879,26 +2875,22 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>K2-League</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Cheonan City vs Yongin City</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
         <is>
           <t>Cheonan City</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>K2-League</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>Cheonan City vs Yongin City</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>Cheonan City</t>
-        </is>
-      </c>
       <c r="K24" t="inlineStr">
         <is>
           <t>Yongin City</t>
@@ -2906,7 +2898,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0x0ae3c1437f52d2b3c8a4d033ef252880ab9d9fee58c4335b560a2a5bdf7ec6bf</t>
+          <t>0xc44350683931fa086c3759e22036c1861e9430054b71327499cb1ad0357c41af</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2936,7 +2928,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1785576308</t>
+          <t>1785576608</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -2946,7 +2938,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>7.504886</t>
+          <t>22.510242</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -2963,7 +2955,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0x2cbe5fb46a011721b21db0e317c482acbdda4529d7e20e5694a7635608189873</t>
+          <t>0x89e7975252a4021e2edec5b41c422fb0f9e0b0bd71b44469db8e27760ccfec81</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2978,12 +2970,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>5.01495</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.2925</t>
+          <t>1.3838</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2993,7 +2985,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3018,7 +3010,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0x4f0eac96e527e303ba7f731f63206ea5d322051eee61a9087848437cebf10534</t>
+          <t>0x0ae3c1437f52d2b3c8a4d033ef252880ab9d9fee58c4335b560a2a5bdf7ec6bf</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -3048,7 +3040,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1785576164</t>
+          <t>1785576308</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3058,7 +3050,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>17.145128</t>
+          <t>7.504886</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3075,7 +3067,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0x6427a9b06be945650ac5754ea9013bd388bb7fd63b9fea057a31d292e952be4b</t>
+          <t>0x2cbe5fb46a011721b21db0e317c482acbdda4529d7e20e5694a7635608189873</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3090,7 +3082,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>4.99</t>
+          <t>5.01495</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -3160,7 +3152,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1785576163</t>
+          <t>1785576164</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3170,7 +3162,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>17.059829</t>
+          <t>17.145128</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3187,7 +3179,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0xd7b3568a3172d11868a8c52422c6edb93781f013948e3cbe3187ecd49450a2ed</t>
+          <t>0x6427a9b06be945650ac5754ea9013bd388bb7fd63b9fea057a31d292e952be4b</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3202,12 +3194,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4.99</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.3013</t>
+          <t>1.2925</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -3227,27 +3219,27 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Chungnam Asan FC vs Seongnam FC</t>
+          <t>Cheonan City vs Yongin City</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Chungnam Asan FC</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Seongnam FC</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0x3908aa00f1ce849001a57f81937948c4a35c187a56fca542d1c26ac2a5aa578c</t>
+          <t>0x4f0eac96e527e303ba7f731f63206ea5d322051eee61a9087848437cebf10534</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>L19382328</t>
+          <t>L19382335</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -3272,7 +3264,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1785576156</t>
+          <t>1785576163</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3282,7 +3274,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>19.917012</t>
+          <t>17.059829</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3299,7 +3291,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0x385d3c2ccc1504b8b62960b052836b16848b30f964e71dbb330e557b9d5b0958</t>
+          <t>0xd7b3568a3172d11868a8c52422c6edb93781f013948e3cbe3187ecd49450a2ed</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3314,12 +3306,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>9.01646</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.3025</t>
+          <t>1.3013</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -3394,7 +3386,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>29.806479</t>
+          <t>19.917012</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3411,7 +3403,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0x81bc6461a5498bb098f71cbd0566c77991625c35e512a092b27824593eb64b44</t>
+          <t>0x385d3c2ccc1504b8b62960b052836b16848b30f964e71dbb330e557b9d5b0958</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3426,12 +3418,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>5.76</t>
+          <t>9.01646</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.3838</t>
+          <t>1.3025</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -3441,7 +3433,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Tie</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3451,27 +3443,27 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Cheonan City vs Yongin City</t>
+          <t>Chungnam Asan FC vs Seongnam FC</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Chungnam Asan FC</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Seongnam FC</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0x0ae3c1437f52d2b3c8a4d033ef252880ab9d9fee58c4335b560a2a5bdf7ec6bf</t>
+          <t>0x3908aa00f1ce849001a57f81937948c4a35c187a56fca542d1c26ac2a5aa578c</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>L19382335</t>
+          <t>L19382328</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -3496,7 +3488,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1785576008</t>
+          <t>1785576156</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3506,7 +3498,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>15.009772</t>
+          <t>29.806479</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3523,7 +3515,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0x20a26ca056f3f25e1f8971a88b06b55502b7f6fd7d4ead5f9ed5057ee98ecf34</t>
+          <t>0x81bc6461a5498bb098f71cbd0566c77991625c35e512a092b27824593eb64b44</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3531,23 +3523,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr"/>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>7.77558</t>
+          <t>5.76</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.3413</t>
+          <t>1.3838</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Cheonan City</t>
+        </is>
+      </c>
       <c r="H30" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -3555,27 +3555,27 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Chungbuk Cheongju FC vs Suwon Samsung Bluewings</t>
+          <t>Cheonan City vs Yongin City</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Chungbuk Cheongju FC</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Suwon Samsung Bluewings</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0x9e11ba3ce6b4420e4e452b60f302739f1d8467716ba519ebe3f8132832094348</t>
+          <t>0x0ae3c1437f52d2b3c8a4d033ef252880ab9d9fee58c4335b560a2a5bdf7ec6bf</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>L19382330</t>
+          <t>L19382335</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -3610,7 +3610,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>22.785582</t>
+          <t>15.009772</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3627,7 +3627,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0xd9d9b0ddddc1467f24d4b982d44a16b3c39903ee63500a8ec66563c6202bfcf9</t>
+          <t>0x20a26ca056f3f25e1f8971a88b06b55502b7f6fd7d4ead5f9ed5057ee98ecf34</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3635,31 +3635,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>5.71</t>
+          <t>7.77558</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.3838</t>
+          <t>1.3413</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Cheonan City</t>
-        </is>
-      </c>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -3667,27 +3659,27 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Cheonan City vs Yongin City</t>
+          <t>Chungbuk Cheongju FC vs Suwon Samsung Bluewings</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Chungbuk Cheongju FC</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Suwon Samsung Bluewings</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0x0ae3c1437f52d2b3c8a4d033ef252880ab9d9fee58c4335b560a2a5bdf7ec6bf</t>
+          <t>0x9e11ba3ce6b4420e4e452b60f302739f1d8467716ba519ebe3f8132832094348</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>L19382335</t>
+          <t>L19382330</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -3712,7 +3704,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1785575708</t>
+          <t>1785576008</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -3722,7 +3714,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>14.879479</t>
+          <t>22.785582</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3739,7 +3731,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0x087314e5ace3bbb3bbb4f703bfe21af2df9ef3152845f56763bcabd878659d88</t>
+          <t>0xd9d9b0ddddc1467f24d4b982d44a16b3c39903ee63500a8ec66563c6202bfcf9</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3754,12 +3746,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>5.71</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.385</t>
+          <t>1.3838</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -3824,7 +3816,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1785574808</t>
+          <t>1785575708</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -3834,7 +3826,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>8.181818</t>
+          <t>14.879479</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3851,7 +3843,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0x1665cbfdd918d1b313ff8b09985889ba3e20ffef471ed1f77d4454a6d4870eb1</t>
+          <t>0x087314e5ace3bbb3bbb4f703bfe21af2df9ef3152845f56763bcabd878659d88</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3866,12 +3858,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>10.96</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.6113</t>
+          <t>1.385</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -3881,7 +3873,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Suwon Samsung Bluewings</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3891,27 +3883,27 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Chungbuk Cheongju FC vs Suwon Samsung Bluewings</t>
+          <t>Cheonan City vs Yongin City</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Chungbuk Cheongju FC</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Suwon Samsung Bluewings</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0xb29a7409dfd5ac0b7a29e92e49cc6bab92af282a2f9d95f3eeb630ed33eb7a3a</t>
+          <t>0x0ae3c1437f52d2b3c8a4d033ef252880ab9d9fee58c4335b560a2a5bdf7ec6bf</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>L19382330</t>
+          <t>L19382335</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -3936,7 +3928,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1785574796</t>
+          <t>1785574808</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -3946,7 +3938,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>17.93047</t>
+          <t>8.181818</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -3963,7 +3955,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0xf5159a5ea43cd4f5bd5f77236fb23f24714602f00b37c28d1f70bb3786749e16</t>
+          <t>0x1665cbfdd918d1b313ff8b09985889ba3e20ffef471ed1f77d4454a6d4870eb1</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3971,15 +3963,19 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr"/>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>10.96</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.5413</t>
+          <t>1.6113</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -3987,7 +3983,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Suwon Samsung Bluewings</t>
+        </is>
+      </c>
       <c r="H34" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -3995,27 +3995,27 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Hwaseong FC vs Daegu FC</t>
+          <t>Chungbuk Cheongju FC vs Suwon Samsung Bluewings</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Hwaseong FC</t>
+          <t>Chungbuk Cheongju FC</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Daegu FC</t>
+          <t>Suwon Samsung Bluewings</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0x3673fddffb9c10163590d13afe39cb241b3c0284138745deddac5c176ba19ebd</t>
+          <t>0xb29a7409dfd5ac0b7a29e92e49cc6bab92af282a2f9d95f3eeb630ed33eb7a3a</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>L19382332</t>
+          <t>L19382330</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -4040,7 +4040,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1785574516</t>
+          <t>1785574796</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -4050,7 +4050,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>6.060046</t>
+          <t>17.93047</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4067,7 +4067,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0x1d3e02f07b5d6a05bde415b055541ce4395cbd9016dfcb7b067173b6ff538c00</t>
+          <t>0xf5159a5ea43cd4f5bd5f77236fb23f24714602f00b37c28d1f70bb3786749e16</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4075,19 +4075,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>5.76</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.3838</t>
+          <t>1.5413</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -4095,11 +4091,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Cheonan City</t>
-        </is>
-      </c>
+      <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -4107,27 +4099,27 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Cheonan City vs Yongin City</t>
+          <t>Hwaseong FC vs Daegu FC</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Hwaseong FC</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Daegu FC</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0x0ae3c1437f52d2b3c8a4d033ef252880ab9d9fee58c4335b560a2a5bdf7ec6bf</t>
+          <t>0x3673fddffb9c10163590d13afe39cb241b3c0284138745deddac5c176ba19ebd</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>L19382335</t>
+          <t>L19382332</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -4152,7 +4144,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1785573908</t>
+          <t>1785574516</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -4162,7 +4154,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>15.009772</t>
+          <t>6.060046</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4179,7 +4171,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0x43f4e76dc758bd60088f0e19fe831ad6e231cfd3f25713ee2197b0c4c12225c4</t>
+          <t>0x1d3e02f07b5d6a05bde415b055541ce4395cbd9016dfcb7b067173b6ff538c00</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4187,23 +4179,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr"/>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>5.76</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.335</t>
+          <t>1.3838</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Cheonan City</t>
+        </is>
+      </c>
       <c r="H36" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -4211,27 +4211,27 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Chungbuk Cheongju FC vs Suwon Samsung Bluewings</t>
+          <t>Cheonan City vs Yongin City</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Chungbuk Cheongju FC</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Suwon Samsung Bluewings</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0x9e11ba3ce6b4420e4e452b60f302739f1d8467716ba519ebe3f8132832094348</t>
+          <t>0x0ae3c1437f52d2b3c8a4d033ef252880ab9d9fee58c4335b560a2a5bdf7ec6bf</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>L19382330</t>
+          <t>L19382335</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -4256,7 +4256,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1785573008</t>
+          <t>1785573908</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>17.164179</t>
+          <t>15.009772</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4283,7 +4283,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0xcc556a2f534d604ca3147c77e407c4a3caccfb460a650afb93e92f95893a83f3</t>
+          <t>0x43f4e76dc758bd60088f0e19fe831ad6e231cfd3f25713ee2197b0c4c12225c4</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4294,7 +4294,7 @@
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>5.74</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -4360,7 +4360,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1785572408</t>
+          <t>1785573008</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -4370,7 +4370,7 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>17.134328</t>
+          <t>17.164179</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4387,7 +4387,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0xe6b9109907b0068b7b44342bbfe6aa4e4f925a1808a4234ef25d5964c06e8a19</t>
+          <t>0xcc556a2f534d604ca3147c77e407c4a3caccfb460a650afb93e92f95893a83f3</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4395,31 +4395,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>4.99</t>
+          <t>5.74</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.2913</t>
+          <t>1.335</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -4427,27 +4419,27 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Cheonan City vs Yongin City</t>
+          <t>Chungbuk Cheongju FC vs Suwon Samsung Bluewings</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Chungbuk Cheongju FC</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Suwon Samsung Bluewings</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0x4f0eac96e527e303ba7f731f63206ea5d322051eee61a9087848437cebf10534</t>
+          <t>0x9e11ba3ce6b4420e4e452b60f302739f1d8467716ba519ebe3f8132832094348</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>L19382335</t>
+          <t>L19382330</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -4472,7 +4464,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1785571129</t>
+          <t>1785572408</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -4482,7 +4474,7 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>17.133047</t>
+          <t>17.134328</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4499,7 +4491,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0x3adcd675a8ad2ac41cfe2151a15dc0861c045d26ad2b087ec6303e2e6bc75b83</t>
+          <t>0xe6b9109907b0068b7b44342bbfe6aa4e4f925a1808a4234ef25d5964c06e8a19</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4514,12 +4506,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>4.99</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.2412</t>
+          <t>1.2913</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -4539,27 +4531,27 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Chungbuk Cheongju FC vs Suwon Samsung Bluewings</t>
+          <t>Cheonan City vs Yongin City</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Chungbuk Cheongju FC</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Suwon Samsung Bluewings</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0xcbe732f420e35966f1693736f4eff7ac82d6eb79649c462d0b0da88b23389fd7</t>
+          <t>0x4f0eac96e527e303ba7f731f63206ea5d322051eee61a9087848437cebf10534</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>L19382330</t>
+          <t>L19382335</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -4584,7 +4576,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1785561333</t>
+          <t>1785571129</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -4594,7 +4586,7 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>4.601036</t>
+          <t>17.133047</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4611,7 +4603,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0x0ba2bf9f0fc74c97ade129a1430bdc4cd89f8fecee54ee5b1f9876c41b38c180</t>
+          <t>0x3adcd675a8ad2ac41cfe2151a15dc0861c045d26ad2b087ec6303e2e6bc75b83</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4626,12 +4618,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.2662</t>
+          <t>1.2412</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -4651,27 +4643,27 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Hwaseong FC vs Daegu FC</t>
+          <t>Chungbuk Cheongju FC vs Suwon Samsung Bluewings</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Hwaseong FC</t>
+          <t>Chungbuk Cheongju FC</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Daegu FC</t>
+          <t>Suwon Samsung Bluewings</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0xda1e33e5fc880742964769df06cb9c83769ec80d9cb168728d3a3467d0a0473b</t>
+          <t>0xcbe732f420e35966f1693736f4eff7ac82d6eb79649c462d0b0da88b23389fd7</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>L19382332</t>
+          <t>L19382330</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -4696,7 +4688,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1785558588</t>
+          <t>1785561333</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -4706,7 +4698,7 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>12.995305</t>
+          <t>4.601036</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -4723,7 +4715,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0x59cfeb6eefafd07022cdcaae7869afb45bc60deb8b4c0b4b96ad04ae8bbdb0d3</t>
+          <t>0x0ba2bf9f0fc74c97ade129a1430bdc4cd89f8fecee54ee5b1f9876c41b38c180</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4738,52 +4730,52 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>321.53001</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.525</t>
+          <t>1.2662</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
           <t>K2-League</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Chungnam Asan FC 0</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>K2-League</t>
-        </is>
-      </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Chungnam Asan FC vs Seongnam FC</t>
+          <t>Hwaseong FC vs Daegu FC</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Chungnam Asan FC</t>
+          <t>Hwaseong FC</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Seongnam FC</t>
+          <t>Daegu FC</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0x5d9fd67211ec6f71728981803ac86abc94216c4e6a398285b5003dabd4e5df0f</t>
+          <t>0xda1e33e5fc880742964769df06cb9c83769ec80d9cb168728d3a3467d0a0473b</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>L19382328</t>
+          <t>L19382332</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -4808,7 +4800,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1785534316</t>
+          <t>1785558588</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -4818,7 +4810,7 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>612.438114</t>
+          <t>12.995305</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -4835,7 +4827,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0x57f84ab38f2e25e292c948ee169e9feff1e8436efac9878d37389052fc7a8ade</t>
+          <t>0x59cfeb6eefafd07022cdcaae7869afb45bc60deb8b4c0b4b96ad04ae8bbdb0d3</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4850,7 +4842,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>9.99999</t>
+          <t>321.53001</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -4920,7 +4912,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1785534315</t>
+          <t>1785534316</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -4930,7 +4922,7 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>19.0476</t>
+          <t>612.438114</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -4947,12 +4939,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0x4da39049a709357f30ef968bfc90b4eec2da9d99090f3b99edf4ea11aeddd708</t>
+          <t>0x57f84ab38f2e25e292c948ee169e9feff1e8436efac9878d37389052fc7a8ade</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -4962,22 +4954,22 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>32.79</t>
+          <t>9.99999</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.5488</t>
+          <t>1.525</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
+          <t>K2-League</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hwaseong FC +0.5</t>
+          <t>Chungnam Asan FC 0</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -4987,27 +4979,27 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Hwaseong FC vs Daegu FC</t>
+          <t>Chungnam Asan FC vs Seongnam FC</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Hwaseong FC</t>
+          <t>Chungnam Asan FC</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Daegu FC</t>
+          <t>Seongnam FC</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0xbde5165c3a540b0c6dd64b3df320540fd10ecb173373b087359951e7f790f852</t>
+          <t>0x5d9fd67211ec6f71728981803ac86abc94216c4e6a398285b5003dabd4e5df0f</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>L19382332</t>
+          <t>L19382328</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -5032,7 +5024,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1785527084</t>
+          <t>1785534315</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -5042,7 +5034,7 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>59.753986</t>
+          <t>19.0476</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -5059,31 +5051,39 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0x07b844c409deb0bc9c8e8dbda27c7c2b772aec07892356105db79f67ffb0e227</t>
+          <t>0x4da39049a709357f30ef968bfc90b4eec2da9d99090f3b99edf4ea11aeddd708</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>6.39</t>
+          <t>32.79</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.5675</t>
+          <t>1.5488</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr"/>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Hwaseong FC +0.5</t>
+        </is>
+      </c>
       <c r="H44" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -5091,27 +5091,27 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC vs Yongin City</t>
+          <t>Hwaseong FC vs Daegu FC</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC</t>
+          <t>Hwaseong FC</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Daegu FC</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0xf73fcbba4baac94056070f4c2db509913d7317940066a6918ac1f13256f52327</t>
+          <t>0xbde5165c3a540b0c6dd64b3df320540fd10ecb173373b087359951e7f790f852</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>L19306783</t>
+          <t>L19382332</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -5136,17 +5136,17 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>1785064787</t>
+          <t>1785527084</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>1785061800</t>
+          <t>1785580200</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>11.259912</t>
+          <t>59.753986</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -5163,28 +5163,28 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0xf95f88d59f982dc2c9ca6387361b5a066ab48deeb7f9f6071274eb879ddabdd0</t>
+          <t>0x07b844c409deb0bc9c8e8dbda27c7c2b772aec07892356105db79f67ffb0e227</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t>126.4351</t>
+          <t>6.39</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1.815</t>
+          <t>1.5675</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G45" t="inlineStr"/>
@@ -5210,7 +5210,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>0x1482cd21984a144c2f6033821f76b4033b1aeaebbab5c85a758b2e86c0553134</t>
+          <t>0xf73fcbba4baac94056070f4c2db509913d7317940066a6918ac1f13256f52327</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -5240,7 +5240,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>1785064732</t>
+          <t>1785064787</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
@@ -5250,7 +5250,7 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>155.135092</t>
+          <t>11.259912</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -5267,39 +5267,31 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0xe74ba88448233ab30d6e4b230046fe45bf1be0a6f71b8860703364abbbb40afe</t>
+          <t>0xf95f88d59f982dc2c9ca6387361b5a066ab48deeb7f9f6071274eb879ddabdd0</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>19.69</t>
+          <t>126.4351</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.5038</t>
+          <t>1.815</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>Over 1.5</t>
-        </is>
-      </c>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -5307,27 +5299,27 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Paju Citizen vs Ansan Greeners</t>
+          <t>Gimpo Citizen FC vs Yongin City</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Gimpo Citizen FC</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>0x6a23b140597c01b1670e03fdb996fc8e94424ec45a5e6e429b292ba1688dff5c</t>
+          <t>0x1482cd21984a144c2f6033821f76b4033b1aeaebbab5c85a758b2e86c0553134</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>L19306782</t>
+          <t>L19306783</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -5352,7 +5344,7 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>1785064111</t>
+          <t>1785064732</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
@@ -5362,7 +5354,7 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>39.086849</t>
+          <t>155.135092</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -5379,31 +5371,39 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0x02858e4fe5f076373faa42c17e9058ea19bff69a0b68493520c024b133c2ceed</t>
+          <t>0xe74ba88448233ab30d6e4b230046fe45bf1be0a6f71b8860703364abbbb40afe</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0x0C2DA7fC8702784d6f75c78Da25460783A6709a0</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>19.69</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.4975</t>
+          <t>1.5038</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr"/>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Over 1.5</t>
+        </is>
+      </c>
       <c r="H47" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -5426,7 +5426,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>0x90106aa6ffeea165b450ea7a1094c65ae9db8d6fdde000ce479b4af5b3fa3072</t>
+          <t>0x6a23b140597c01b1670e03fdb996fc8e94424ec45a5e6e429b292ba1688dff5c</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>1785063804</t>
+          <t>1785064111</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>6.030151</t>
+          <t>39.086849</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -5483,39 +5483,31 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0xd6b44cd45d93535a9c1b39fad13245ea6ef0e5cbff858b443a9d40a281cf422f</t>
+          <t>0x02858e4fe5f076373faa42c17e9058ea19bff69a0b68493520c024b133c2ceed</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x0C2DA7fC8702784d6f75c78Da25460783A6709a0</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
-          <t>21.3</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.2988</t>
+          <t>1.4975</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>Over 2.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -5538,7 +5530,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>0x2d5eca3e665030fe8c7c2a84772b94d8fc59c9a6991fd216ba914d3b345ffe07</t>
+          <t>0x90106aa6ffeea165b450ea7a1094c65ae9db8d6fdde000ce479b4af5b3fa3072</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -5568,7 +5560,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>1785063590</t>
+          <t>1785063804</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
@@ -5578,7 +5570,7 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>71.297071</t>
+          <t>6.030151</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -5595,7 +5587,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0xc41eea20c9aa34da894372c77f23e0a6ee134568f117e95b14c294310b2dc1f7</t>
+          <t>0xd6b44cd45d93535a9c1b39fad13245ea6ef0e5cbff858b443a9d40a281cf422f</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5610,22 +5602,22 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>12.53</t>
+          <t>21.3</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1.2037</t>
+          <t>1.2988</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Over 2.5</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -5635,27 +5627,27 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC vs Yongin City</t>
+          <t>Paju Citizen vs Ansan Greeners</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>0x520e073f044523b55003a1d70f752c30f91cd5ebae7e23b2f294ad6679b3ed58</t>
+          <t>0x2d5eca3e665030fe8c7c2a84772b94d8fc59c9a6991fd216ba914d3b345ffe07</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>L19306783</t>
+          <t>L19306782</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -5680,7 +5672,7 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>1785063530</t>
+          <t>1785063590</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
@@ -5690,7 +5682,7 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>61.496933</t>
+          <t>71.297071</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -5707,7 +5699,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0xe5a4265d3896fe621f44bfc6c8c9d2efe8a044ac121c6a5ec411dcd8ecbb22c9</t>
+          <t>0xc41eea20c9aa34da894372c77f23e0a6ee134568f117e95b14c294310b2dc1f7</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5722,12 +5714,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12.53</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1.5162</t>
+          <t>1.2037</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -5737,24 +5729,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
+          <t>Yongin City</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>K2-League</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen FC vs Yongin City</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
           <t>Gimpo Citizen FC</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>K2-League</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>Gimpo Citizen FC vs Yongin City</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>Gimpo Citizen FC</t>
-        </is>
-      </c>
       <c r="K50" t="inlineStr">
         <is>
           <t>Yongin City</t>
@@ -5762,7 +5754,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>0x2725ecc350e6d5314ddee250cd3e445f586ab55a992fc73108db0913c5a41f24</t>
+          <t>0x520e073f044523b55003a1d70f752c30f91cd5ebae7e23b2f294ad6679b3ed58</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -5792,7 +5784,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>1785063352</t>
+          <t>1785063530</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
@@ -5802,7 +5794,7 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>1.937046</t>
+          <t>61.496933</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -5819,7 +5811,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0x996289847910ea662fcd868b20c9fa48f68ab4d7334bac4351bc46b6d3f479df</t>
+          <t>0xe5a4265d3896fe621f44bfc6c8c9d2efe8a044ac121c6a5ec411dcd8ecbb22c9</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5904,7 +5896,7 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>1785063326</t>
+          <t>1785063352</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
@@ -5931,7 +5923,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0xed44d31e5a5b7071006924700a0078a2f8a3710d9bb8d24217652d198ffae7d7</t>
+          <t>0x996289847910ea662fcd868b20c9fa48f68ab4d7334bac4351bc46b6d3f479df</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5946,7 +5938,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>28.84</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -6016,7 +6008,7 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>1785063319</t>
+          <t>1785063326</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
@@ -6026,7 +6018,7 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>55.864407</t>
+          <t>1.937046</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -6043,7 +6035,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0x2bcba69d716b343c190b4a215a8f323f4abe23b13cd57d716f1b386e77406d71</t>
+          <t>0xed44d31e5a5b7071006924700a0078a2f8a3710d9bb8d24217652d198ffae7d7</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -6051,23 +6043,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr"/>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>28.84</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1.3912</t>
+          <t>1.5162</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen FC</t>
+        </is>
+      </c>
       <c r="H53" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -6090,7 +6090,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>0xf73fcbba4baac94056070f4c2db509913d7317940066a6918ac1f13256f52327</t>
+          <t>0x2725ecc350e6d5314ddee250cd3e445f586ab55a992fc73108db0913c5a41f24</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>6.696486</t>
+          <t>55.864407</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -6147,7 +6147,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0x74897816645fe410040b71368723e823f96b8b8ad1a8558a60563ea6a63c17b9</t>
+          <t>0x2bcba69d716b343c190b4a215a8f323f4abe23b13cd57d716f1b386e77406d71</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -6155,31 +6155,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1.5488</t>
+          <t>1.3912</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>Paju Citizen</t>
-        </is>
-      </c>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -6187,27 +6179,27 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Paju Citizen vs Ansan Greeners</t>
+          <t>Gimpo Citizen FC vs Yongin City</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Gimpo Citizen FC</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>0x90106aa6ffeea165b450ea7a1094c65ae9db8d6fdde000ce479b4af5b3fa3072</t>
+          <t>0xf73fcbba4baac94056070f4c2db509913d7317940066a6918ac1f13256f52327</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>L19306782</t>
+          <t>L19306783</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -6232,7 +6224,7 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>1785063283</t>
+          <t>1785063319</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
@@ -6242,7 +6234,7 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>18.223235</t>
+          <t>6.696486</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -6259,7 +6251,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0x6c9b96e6ea55e8d6386264e63d154ad9cdf850c8f9c18b5c088abdcfcc710e8d</t>
+          <t>0x74897816645fe410040b71368723e823f96b8b8ad1a8558a60563ea6a63c17b9</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6267,15 +6259,19 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr"/>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>1.74999</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1.8313</t>
+          <t>1.5488</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -6283,7 +6279,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Paju Citizen</t>
+        </is>
+      </c>
       <c r="H55" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -6306,7 +6306,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>0x6de105784818e175bb2cb50f54d4325a684a5693a05f8bd5b7f2b402aeb4bdfa</t>
+          <t>0x90106aa6ffeea165b450ea7a1094c65ae9db8d6fdde000ce479b4af5b3fa3072</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -6336,7 +6336,7 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>1785063278</t>
+          <t>1785063283</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
@@ -6346,7 +6346,7 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>2.105251</t>
+          <t>18.223235</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -6363,7 +6363,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0x653ed25ca6aba498efe0c95f6d394f607985bf6c4ab830c3599772279631e8b1</t>
+          <t>0x6c9b96e6ea55e8d6386264e63d154ad9cdf850c8f9c18b5c088abdcfcc710e8d</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6374,12 +6374,12 @@
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
-          <t>201.32998</t>
+          <t>1.74999</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1.8213</t>
+          <t>1.8313</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -6440,7 +6440,7 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>1785063071</t>
+          <t>1785063278</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
@@ -6450,7 +6450,7 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>245.150661</t>
+          <t>2.105251</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -6467,23 +6467,23 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0xd7beeace3688b4d75f908058620cd47f10d9926e086901a2c83333dd169ec720</t>
+          <t>0x653ed25ca6aba498efe0c95f6d394f607985bf6c4ab830c3599772279631e8b1</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
-          <t>48.03</t>
+          <t>201.32998</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.8213</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -6499,27 +6499,27 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC vs Yongin City</t>
+          <t>Paju Citizen vs Ansan Greeners</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>0x2725ecc350e6d5314ddee250cd3e445f586ab55a992fc73108db0913c5a41f24</t>
+          <t>0x6de105784818e175bb2cb50f54d4325a684a5693a05f8bd5b7f2b402aeb4bdfa</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>L19306783</t>
+          <t>L19306782</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -6544,7 +6544,7 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>1785062970</t>
+          <t>1785063071</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
@@ -6554,7 +6554,7 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>98.020408</t>
+          <t>245.150661</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -6571,23 +6571,23 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0x8940d52e7feb848f5ca44e42ecc2fed94e942961b918122bc87142ffbf346d4c</t>
+          <t>0xd7beeace3688b4d75f908058620cd47f10d9926e086901a2c83333dd169ec720</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr">
         <is>
-          <t>196.03997</t>
+          <t>48.03</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>1.8188</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -6603,27 +6603,27 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Paju Citizen vs Ansan Greeners</t>
+          <t>Gimpo Citizen FC vs Yongin City</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Gimpo Citizen FC</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>0x6de105784818e175bb2cb50f54d4325a684a5693a05f8bd5b7f2b402aeb4bdfa</t>
+          <t>0x2725ecc350e6d5314ddee250cd3e445f586ab55a992fc73108db0913c5a41f24</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>L19306782</t>
+          <t>L19306783</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -6648,7 +6648,7 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>1785062953</t>
+          <t>1785062970</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
@@ -6658,7 +6658,7 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>239.438131</t>
+          <t>98.020408</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
@@ -6675,7 +6675,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0x2b9441f7515eb95a00a5708be64644050b069886b2e84d77ecdeea72fe8e3da7</t>
+          <t>0x8940d52e7feb848f5ca44e42ecc2fed94e942961b918122bc87142ffbf346d4c</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6683,19 +6683,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
-          <t>12.06</t>
+          <t>196.03997</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>1.1975</t>
+          <t>1.8188</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -6703,11 +6699,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>Yongin City</t>
-        </is>
-      </c>
+      <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -6715,27 +6707,27 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC vs Yongin City</t>
+          <t>Paju Citizen vs Ansan Greeners</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>0x520e073f044523b55003a1d70f752c30f91cd5ebae7e23b2f294ad6679b3ed58</t>
+          <t>0x6de105784818e175bb2cb50f54d4325a684a5693a05f8bd5b7f2b402aeb4bdfa</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>L19306783</t>
+          <t>L19306782</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -6760,7 +6752,7 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>1785062934</t>
+          <t>1785062953</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
@@ -6770,7 +6762,7 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>61.063291</t>
+          <t>239.438131</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
@@ -6787,7 +6779,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0x17ea9fc34d8d08859197baf8694510eafd385c5cb30d1bccaf4135418710a4ee</t>
+          <t>0x2b9441f7515eb95a00a5708be64644050b069886b2e84d77ecdeea72fe8e3da7</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6802,22 +6794,22 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12.06</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>1.3862</t>
+          <t>1.1975</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Over 2.5</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -6827,27 +6819,27 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Paju Citizen vs Ansan Greeners</t>
+          <t>Gimpo Citizen FC vs Yongin City</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Gimpo Citizen FC</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>0x2d5eca3e665030fe8c7c2a84772b94d8fc59c9a6991fd216ba914d3b345ffe07</t>
+          <t>0x520e073f044523b55003a1d70f752c30f91cd5ebae7e23b2f294ad6679b3ed58</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>L19306782</t>
+          <t>L19306783</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -6872,7 +6864,7 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>1785062748</t>
+          <t>1785062934</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
@@ -6882,7 +6874,7 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>25.889968</t>
+          <t>61.063291</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
@@ -6899,7 +6891,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0xff313e8a80cab759f0306eced2743a83b68017dd8ecc4a5eda49613abd5f72bb</t>
+          <t>0x17ea9fc34d8d08859197baf8694510eafd385c5cb30d1bccaf4135418710a4ee</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6919,17 +6911,17 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>1.2275</t>
+          <t>1.3862</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Over 3.5</t>
+          <t>Over 2.5</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -6954,7 +6946,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>0x20fab15d1baac82bbe5a9371ad4e1e4f931edb8de76d814e671a0313aa4d8620</t>
+          <t>0x2d5eca3e665030fe8c7c2a84772b94d8fc59c9a6991fd216ba914d3b345ffe07</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -6984,7 +6976,7 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>1785062437</t>
+          <t>1785062748</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
@@ -6994,7 +6986,7 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>43.956044</t>
+          <t>25.889968</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
@@ -7011,7 +7003,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0x5a88256e6b892595ad641ef1ae589c088b32b6034ec557ba72582fa8c93f67e3</t>
+          <t>0xff313e8a80cab759f0306eced2743a83b68017dd8ecc4a5eda49613abd5f72bb</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -7019,23 +7011,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr"/>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>64.98999</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>1.8125</t>
+          <t>1.2275</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr"/>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
       <c r="H62" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -7058,7 +7058,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>0x6de105784818e175bb2cb50f54d4325a684a5693a05f8bd5b7f2b402aeb4bdfa</t>
+          <t>0x20fab15d1baac82bbe5a9371ad4e1e4f931edb8de76d814e671a0313aa4d8620</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -7088,7 +7088,7 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>1785062111</t>
+          <t>1785062437</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
@@ -7098,7 +7098,7 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>79.98768</t>
+          <t>43.956044</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
@@ -7115,39 +7115,31 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0x21aa47ce5d327006a8fdcf609e5990b1ea5499887fd8ccd0ff96d5bbe7df2f89</t>
+          <t>0x5a88256e6b892595ad641ef1ae589c088b32b6034ec557ba72582fa8c93f67e3</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr">
         <is>
-          <t>23.39</t>
+          <t>64.98999</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>1.3887</t>
+          <t>1.8125</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>Paju Citizen -1</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -7170,7 +7162,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>0x1398d7baccf6c5154c8090892c6597852ff56e90298e81fb604a8b9bf22c47ce</t>
+          <t>0x6de105784818e175bb2cb50f54d4325a684a5693a05f8bd5b7f2b402aeb4bdfa</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -7200,7 +7192,7 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>1785061695</t>
+          <t>1785062111</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
@@ -7210,7 +7202,7 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>60.167203</t>
+          <t>79.98768</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
@@ -7227,7 +7219,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0xaa13e9d13e81cd9edae13a80c0e426e52c85c5064c5b0c34d792d027f33fe560</t>
+          <t>0x21aa47ce5d327006a8fdcf609e5990b1ea5499887fd8ccd0ff96d5bbe7df2f89</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -7242,22 +7234,22 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>17.04</t>
+          <t>23.39</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.3887</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Paju Citizen -1.5</t>
+          <t>Paju Citizen -1</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -7282,7 +7274,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>0x48cd5a7ee72c95f57110826c0f2e2494d9438250815f7751e5e0fdce91ccbfba</t>
+          <t>0x1398d7baccf6c5154c8090892c6597852ff56e90298e81fb604a8b9bf22c47ce</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -7312,7 +7304,7 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>1785061694</t>
+          <t>1785061695</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
@@ -7322,7 +7314,7 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>58.758621</t>
+          <t>60.167203</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
@@ -7339,31 +7331,39 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0x9c2da91ae7561670702979941233734bebc22c36fdac867bf5bdb53a8151c6e9</t>
+          <t>0xaa13e9d13e81cd9edae13a80c0e426e52c85c5064c5b0c34d792d027f33fe560</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>4.99997</t>
+          <t>17.04</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>1.795</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr"/>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Paju Citizen -1.5</t>
+        </is>
+      </c>
       <c r="H65" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -7371,27 +7371,27 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC vs Yongin City</t>
+          <t>Paju Citizen vs Ansan Greeners</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>0x520e073f044523b55003a1d70f752c30f91cd5ebae7e23b2f294ad6679b3ed58</t>
+          <t>0x48cd5a7ee72c95f57110826c0f2e2494d9438250815f7751e5e0fdce91ccbfba</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>L19306783</t>
+          <t>L19306782</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -7416,7 +7416,7 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>1785061651</t>
+          <t>1785061694</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
@@ -7426,7 +7426,7 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>6.28927</t>
+          <t>58.758621</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
@@ -7443,39 +7443,31 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0x12f98497a1f2dc0a130b32665dfeea9bbd9b744c2732456c77c91801ec687167</t>
+          <t>0x9c2da91ae7561670702979941233734bebc22c36fdac867bf5bdb53a8151c6e9</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr">
         <is>
-          <t>21.14</t>
+          <t>4.99997</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>1.3513</t>
+          <t>1.795</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>Gimpo Citizen FC -1</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -7498,7 +7490,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>0x4a4b2cf0de4356e1be221d31aa0feab4af681e89956037ff111c72307c4d9af6</t>
+          <t>0x520e073f044523b55003a1d70f752c30f91cd5ebae7e23b2f294ad6679b3ed58</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -7528,7 +7520,7 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>1785061621</t>
+          <t>1785061651</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
@@ -7538,7 +7530,7 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>60.185053</t>
+          <t>6.28927</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
@@ -7555,7 +7547,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0x0f90aefde05859a865353743603e3925fef0a390e252c71ca62de94b7f3522d8</t>
+          <t>0x12f98497a1f2dc0a130b32665dfeea9bbd9b744c2732456c77c91801ec687167</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -7563,23 +7555,31 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr"/>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>43.51167</t>
+          <t>21.14</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>1.795</t>
+          <t>1.3513</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr"/>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen FC -1</t>
+        </is>
+      </c>
       <c r="H67" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -7602,7 +7602,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>0x520e073f044523b55003a1d70f752c30f91cd5ebae7e23b2f294ad6679b3ed58</t>
+          <t>0x4a4b2cf0de4356e1be221d31aa0feab4af681e89956037ff111c72307c4d9af6</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -7642,7 +7642,7 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>54.73166</t>
+          <t>60.185053</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
@@ -7659,28 +7659,28 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0x45f1170f51d54ba31ead65b241ce33b618358dd91421e9194877f824ebea4f5d</t>
+          <t>0x0f90aefde05859a865353743603e3925fef0a390e252c71ca62de94b7f3522d8</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0x09b3a190a1e971Dd0B4F82Eb9008287fe43a540C</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>43.51167</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.795</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G68" t="inlineStr"/>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>0x7b353104df193f280c01b3e0a75dcbbc5dd4e628b7304c3537dff2339968d702</t>
+          <t>0x520e073f044523b55003a1d70f752c30f91cd5ebae7e23b2f294ad6679b3ed58</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -7736,7 +7736,7 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>1785061583</t>
+          <t>1785061621</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>51.020408</t>
+          <t>54.73166</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
@@ -7763,28 +7763,28 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0x8726e3d54f033c4394f3b9a8a297c466f26e8d1814d525163146dc1f9f836029</t>
+          <t>0x45f1170f51d54ba31ead65b241ce33b618358dd91421e9194877f824ebea4f5d</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x09b3a190a1e971Dd0B4F82Eb9008287fe43a540C</t>
         </is>
       </c>
       <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr">
         <is>
-          <t>5.70997</t>
+          <t>25</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>1.795</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G69" t="inlineStr"/>
@@ -7810,7 +7810,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>0x520e073f044523b55003a1d70f752c30f91cd5ebae7e23b2f294ad6679b3ed58</t>
+          <t>0x7b353104df193f280c01b3e0a75dcbbc5dd4e628b7304c3537dff2339968d702</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -7840,7 +7840,7 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>1785061581</t>
+          <t>1785061583</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
@@ -7850,7 +7850,7 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>7.182352</t>
+          <t>51.020408</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
@@ -7867,27 +7867,23 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0x78b589b7ea305b8a325e286dcbf526301e19f803d90ab77960c290d1d621d34a</t>
+          <t>0x8726e3d54f033c4394f3b9a8a297c466f26e8d1814d525163146dc1f9f836029</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0x09b3a190a1e971Dd0B4F82Eb9008287fe43a540C</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr">
         <is>
-          <t>5.01384</t>
+          <t>5.70997</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>1.2788</t>
+          <t>1.795</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -7895,11 +7891,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -7922,7 +7914,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>0xf93dab40773f0e01839824957e7cecd4afb676d72a13c45521719f4f5c517a27</t>
+          <t>0x520e073f044523b55003a1d70f752c30f91cd5ebae7e23b2f294ad6679b3ed58</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -7952,7 +7944,7 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>1785061533</t>
+          <t>1785061581</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
@@ -7962,7 +7954,7 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>17.98687</t>
+          <t>7.182352</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
@@ -7979,23 +7971,27 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0x64d493da52ab9f3215f2ee6a066aad2cbaf66597963522c2c53462ae6d466e65</t>
+          <t>0x78b589b7ea305b8a325e286dcbf526301e19f803d90ab77960c290d1d621d34a</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr"/>
+          <t>0x09b3a190a1e971Dd0B4F82Eb9008287fe43a540C</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>43.87998</t>
+          <t>5.01384</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>1.7988</t>
+          <t>1.2788</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -8003,7 +7999,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H71" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -8026,7 +8026,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>0x520e073f044523b55003a1d70f752c30f91cd5ebae7e23b2f294ad6679b3ed58</t>
+          <t>0xf93dab40773f0e01839824957e7cecd4afb676d72a13c45521719f4f5c517a27</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -8056,7 +8056,7 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>1785061346</t>
+          <t>1785061533</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
@@ -8066,7 +8066,7 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>54.935812</t>
+          <t>17.98687</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
@@ -8083,7 +8083,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0xb6a5b0e5cc84223b1b456506ce5bc4a60492c7d715d16ce5ba4bcbbbb205e549</t>
+          <t>0x64d493da52ab9f3215f2ee6a066aad2cbaf66597963522c2c53462ae6d466e65</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -8094,7 +8094,7 @@
       <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr">
         <is>
-          <t>10.19999</t>
+          <t>43.87998</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -8160,7 +8160,7 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>1785061261</t>
+          <t>1785061346</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
@@ -8170,7 +8170,7 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>12.769941</t>
+          <t>54.935812</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
@@ -8187,18 +8187,18 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0x932ea4448a5d14be89226effb4bcb8584e5004da981b9fb12e769029a2cd6a34</t>
+          <t>0xb6a5b0e5cc84223b1b456506ce5bc4a60492c7d715d16ce5ba4bcbbbb205e549</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10.19999</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -8264,7 +8264,7 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>1785061250</t>
+          <t>1785061261</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
@@ -8274,7 +8274,7 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>6.259781</t>
+          <t>12.769941</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
@@ -8291,23 +8291,23 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0x6ba96fe1be95723f4530ab62caaff2817e70e2c1aa504d2f0afe5b7d44447528</t>
+          <t>0x932ea4448a5d14be89226effb4bcb8584e5004da981b9fb12e769029a2cd6a34</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr">
         <is>
-          <t>43.12404</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>1.7975</t>
+          <t>1.7988</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -8368,7 +8368,7 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>1785061221</t>
+          <t>1785061250</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
@@ -8378,7 +8378,7 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>54.074031</t>
+          <t>6.259781</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
@@ -8395,27 +8395,23 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0xa4c5cc7d130116507c7f97158d19bded9ace84b90e4089b2386235aca563a109</t>
+          <t>0x6ba96fe1be95723f4530ab62caaff2817e70e2c1aa504d2f0afe5b7d44447528</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr">
         <is>
-          <t>5.54</t>
+          <t>43.12404</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>1.2537</t>
+          <t>1.7975</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -8423,11 +8419,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -8435,27 +8427,27 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Paju Citizen vs Ansan Greeners</t>
+          <t>Gimpo Citizen FC vs Yongin City</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Gimpo Citizen FC</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>0xabfa364122222118f5f35af9ee862e2b9587e9c2f656e281725fdca100cf17bf</t>
+          <t>0x520e073f044523b55003a1d70f752c30f91cd5ebae7e23b2f294ad6679b3ed58</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>L19306782</t>
+          <t>L19306783</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -8480,7 +8472,7 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>1785060618</t>
+          <t>1785061221</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
@@ -8490,7 +8482,7 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>21.832512</t>
+          <t>54.074031</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
@@ -8507,23 +8499,27 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0xed6f77aaa7a7dbe5c2457f000b022f2da0cc5bd1004291d76e71044f4e1faa36</t>
+          <t>0xa4c5cc7d130116507c7f97158d19bded9ace84b90e4089b2386235aca563a109</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>4.99999</t>
+          <t>5.54</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>1.7975</t>
+          <t>1.2537</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -8531,7 +8527,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H76" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -8539,27 +8539,27 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC vs Yongin City</t>
+          <t>Paju Citizen vs Ansan Greeners</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>0x520e073f044523b55003a1d70f752c30f91cd5ebae7e23b2f294ad6679b3ed58</t>
+          <t>0xabfa364122222118f5f35af9ee862e2b9587e9c2f656e281725fdca100cf17bf</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>L19306783</t>
+          <t>L19306782</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -8584,7 +8584,7 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>1785060105</t>
+          <t>1785060618</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
@@ -8594,7 +8594,7 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>6.26958</t>
+          <t>21.832512</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
@@ -8611,7 +8611,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0xe0d4aa08492162b980b70ecc4ec3e9ae46b9fd85fea771f538c542e4e27f10ca</t>
+          <t>0xed6f77aaa7a7dbe5c2457f000b022f2da0cc5bd1004291d76e71044f4e1faa36</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -8688,7 +8688,7 @@
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>1785060103</t>
+          <t>1785060105</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
@@ -8715,7 +8715,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0x733bd5ce99f877eba370291936b138251c1bd48cee90480bc876f49523ca7fca</t>
+          <t>0xe0d4aa08492162b980b70ecc4ec3e9ae46b9fd85fea771f538c542e4e27f10ca</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -8792,7 +8792,7 @@
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>1785060101</t>
+          <t>1785060103</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
@@ -8819,39 +8819,31 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0xcfbe574677265ef97dc3204a001ce1b1e25523c8a98c296a3cf235f97650aace</t>
+          <t>0x733bd5ce99f877eba370291936b138251c1bd48cee90480bc876f49523ca7fca</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.99999</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>1.3887</t>
+          <t>1.7975</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>Paju Citizen -1</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -8859,27 +8851,27 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Paju Citizen vs Ansan Greeners</t>
+          <t>Gimpo Citizen FC vs Yongin City</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Gimpo Citizen FC</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>0x1398d7baccf6c5154c8090892c6597852ff56e90298e81fb604a8b9bf22c47ce</t>
+          <t>0x520e073f044523b55003a1d70f752c30f91cd5ebae7e23b2f294ad6679b3ed58</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>L19306782</t>
+          <t>L19306783</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -8904,7 +8896,7 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>1785060085</t>
+          <t>1785060101</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
@@ -8914,7 +8906,7 @@
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>10.289389</t>
+          <t>6.26958</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
@@ -8931,31 +8923,39 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0xebd1df0aa7e7f54677bedd84a6c923ca856cf657e0531639938bfb8111becc94</t>
+          <t>0xcfbe574677265ef97dc3204a001ce1b1e25523c8a98c296a3cf235f97650aace</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>22.97198</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>1.7963</t>
+          <t>1.3887</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr"/>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Paju Citizen -1</t>
+        </is>
+      </c>
       <c r="H80" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -8963,27 +8963,27 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC vs Yongin City</t>
+          <t>Paju Citizen vs Ansan Greeners</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>0x520e073f044523b55003a1d70f752c30f91cd5ebae7e23b2f294ad6679b3ed58</t>
+          <t>0x1398d7baccf6c5154c8090892c6597852ff56e90298e81fb604a8b9bf22c47ce</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>L19306783</t>
+          <t>L19306782</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -9008,7 +9008,7 @@
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>1785060074</t>
+          <t>1785060085</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
@@ -9018,7 +9018,7 @@
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>28.85021</t>
+          <t>10.289389</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
@@ -9035,7 +9035,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0x9137623e3c72596dddeb8dd77deb26f0f80f5d8ad5037c9d9fd9ec11f1d3a62d</t>
+          <t>0xebd1df0aa7e7f54677bedd84a6c923ca856cf657e0531639938bfb8111becc94</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -9046,7 +9046,7 @@
       <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr">
         <is>
-          <t>15.59279</t>
+          <t>22.97198</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -9112,7 +9112,7 @@
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>1785060073</t>
+          <t>1785060074</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">
@@ -9122,7 +9122,7 @@
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>19.582782</t>
+          <t>28.85021</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
@@ -9139,7 +9139,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0x47fecae2c93459e7d6a1189dcb95e8bce239b7e2d26ce67db4733b564451a3fd</t>
+          <t>0x9137623e3c72596dddeb8dd77deb26f0f80f5d8ad5037c9d9fd9ec11f1d3a62d</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -9150,7 +9150,7 @@
       <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr">
         <is>
-          <t>16.1469</t>
+          <t>15.59279</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -9216,7 +9216,7 @@
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>1785060072</t>
+          <t>1785060073</t>
         </is>
       </c>
       <c r="S82" t="inlineStr">
@@ -9226,7 +9226,7 @@
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>20.278681</t>
+          <t>19.582782</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
@@ -9243,27 +9243,23 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0x7851323bb653ef81f86e4483a09baec3f52472a947788d079eacebc8ce474280</t>
+          <t>0x47fecae2c93459e7d6a1189dcb95e8bce239b7e2d26ce67db4733b564451a3fd</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr">
         <is>
-          <t>19.02</t>
+          <t>16.1469</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>1.275</t>
+          <t>1.7963</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -9271,11 +9267,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -9298,7 +9290,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>0xf93dab40773f0e01839824957e7cecd4afb676d72a13c45521719f4f5c517a27</t>
+          <t>0x520e073f044523b55003a1d70f752c30f91cd5ebae7e23b2f294ad6679b3ed58</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -9328,7 +9320,7 @@
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>1785060054</t>
+          <t>1785060072</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
@@ -9338,7 +9330,7 @@
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>69.163636</t>
+          <t>20.278681</t>
         </is>
       </c>
       <c r="U83" t="inlineStr">
@@ -9355,12 +9347,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0x5936a0069456d68663344829a3e2e9aa688da6a9e1d38de76848d1bdfb84366a</t>
+          <t>0x7851323bb653ef81f86e4483a09baec3f52472a947788d079eacebc8ce474280</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -9370,12 +9362,12 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>10.56</t>
+          <t>19.02</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>1.2737</t>
+          <t>1.275</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -9440,7 +9432,7 @@
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>1785060044</t>
+          <t>1785060054</t>
         </is>
       </c>
       <c r="S84" t="inlineStr">
@@ -9450,7 +9442,7 @@
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>38.575342</t>
+          <t>69.163636</t>
         </is>
       </c>
       <c r="U84" t="inlineStr">
@@ -9467,31 +9459,39 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0xc27dc932de76aa5047aab63fd483f2351fd3e777a4bebc494353cf3a53c52ba9</t>
+          <t>0x5936a0069456d68663344829a3e2e9aa688da6a9e1d38de76848d1bdfb84366a</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>20.61772</t>
+          <t>10.56</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>1.3425</t>
+          <t>1.2737</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H85" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -9499,27 +9499,27 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Paju Citizen vs Ansan Greeners</t>
+          <t>Gimpo Citizen FC vs Yongin City</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Gimpo Citizen FC</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>0x386468865ee4fb2d064354b0f4bb50fc57a8f046452fa6667bc56978f4cf3823</t>
+          <t>0xf93dab40773f0e01839824957e7cecd4afb676d72a13c45521719f4f5c517a27</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>L19306782</t>
+          <t>L19306783</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -9544,7 +9544,7 @@
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>1785059855</t>
+          <t>1785060044</t>
         </is>
       </c>
       <c r="S85" t="inlineStr">
@@ -9554,7 +9554,7 @@
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>60.197723</t>
+          <t>38.575342</t>
         </is>
       </c>
       <c r="U85" t="inlineStr">
@@ -9571,7 +9571,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>0x06cf39065296686830cf556b4943f2a94e035610868690980b237da489f6c32a</t>
+          <t>0xc27dc932de76aa5047aab63fd483f2351fd3e777a4bebc494353cf3a53c52ba9</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -9579,31 +9579,23 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr">
         <is>
-          <t>4.94155</t>
+          <t>20.61772</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>1.355</t>
+          <t>1.3425</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>Gimpo Citizen FC -1</t>
-        </is>
-      </c>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr"/>
       <c r="H86" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -9611,27 +9603,27 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC vs Yongin City</t>
+          <t>Paju Citizen vs Ansan Greeners</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>0x4a4b2cf0de4356e1be221d31aa0feab4af681e89956037ff111c72307c4d9af6</t>
+          <t>0x386468865ee4fb2d064354b0f4bb50fc57a8f046452fa6667bc56978f4cf3823</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>L19306783</t>
+          <t>L19306782</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -9656,7 +9648,7 @@
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>1785059821</t>
+          <t>1785059855</t>
         </is>
       </c>
       <c r="S86" t="inlineStr">
@@ -9666,7 +9658,7 @@
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>13.919859</t>
+          <t>60.197723</t>
         </is>
       </c>
       <c r="U86" t="inlineStr">
@@ -9683,7 +9675,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>0x6cad572e295e86d0eff792e6a73f1ecb4b2563c632f3a61d710a79a81bcbefc5</t>
+          <t>0x06cf39065296686830cf556b4943f2a94e035610868690980b237da489f6c32a</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -9698,7 +9690,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>16.43</t>
+          <t>4.94155</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -9768,7 +9760,7 @@
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>1785059820</t>
+          <t>1785059821</t>
         </is>
       </c>
       <c r="S87" t="inlineStr">
@@ -9778,7 +9770,7 @@
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>46.28169</t>
+          <t>13.919859</t>
         </is>
       </c>
       <c r="U87" t="inlineStr">
@@ -9795,31 +9787,39 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>0xd90cf2f29f54991a5ee8c926cce019177b5bb5fd98602218fb9acaaf6a910664</t>
+          <t>0x6cad572e295e86d0eff792e6a73f1ecb4b2563c632f3a61d710a79a81bcbefc5</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>16.43</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>1.4675</t>
+          <t>1.355</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr"/>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen FC -1</t>
+        </is>
+      </c>
       <c r="H88" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -9827,27 +9827,27 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Paju Citizen vs Ansan Greeners</t>
+          <t>Gimpo Citizen FC vs Yongin City</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Gimpo Citizen FC</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>0x90106aa6ffeea165b450ea7a1094c65ae9db8d6fdde000ce479b4af5b3fa3072</t>
+          <t>0x4a4b2cf0de4356e1be221d31aa0feab4af681e89956037ff111c72307c4d9af6</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>L19306782</t>
+          <t>L19306783</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -9872,7 +9872,7 @@
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>1785058466</t>
+          <t>1785059820</t>
         </is>
       </c>
       <c r="S88" t="inlineStr">
@@ -9882,7 +9882,7 @@
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>23.529412</t>
+          <t>46.28169</t>
         </is>
       </c>
       <c r="U88" t="inlineStr">
@@ -9899,27 +9899,23 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>0xfaacadf40a626e2b5b306c37ecce7325e0fabbb091c125c037dd14587c31bfe4</t>
+          <t>0xd90cf2f29f54991a5ee8c926cce019177b5bb5fd98602218fb9acaaf6a910664</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr"/>
       <c r="D89" t="inlineStr">
         <is>
-          <t>4.53</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>1.5212</t>
+          <t>1.4675</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -9927,11 +9923,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>Gimpo Citizen FC</t>
-        </is>
-      </c>
+      <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -9939,27 +9931,27 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC vs Yongin City</t>
+          <t>Paju Citizen vs Ansan Greeners</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>0x2725ecc350e6d5314ddee250cd3e445f586ab55a992fc73108db0913c5a41f24</t>
+          <t>0x90106aa6ffeea165b450ea7a1094c65ae9db8d6fdde000ce479b4af5b3fa3072</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>L19306783</t>
+          <t>L19306782</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -9984,7 +9976,7 @@
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>1785057353</t>
+          <t>1785058466</t>
         </is>
       </c>
       <c r="S89" t="inlineStr">
@@ -9994,7 +9986,7 @@
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t>8.690647</t>
+          <t>23.529412</t>
         </is>
       </c>
       <c r="U89" t="inlineStr">
@@ -10011,7 +10003,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>0x182964c6008d5b7d29731fd19876092a52fa2068fcb16aaf430dd8e0a6009721</t>
+          <t>0xfaacadf40a626e2b5b306c37ecce7325e0fabbb091c125c037dd14587c31bfe4</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -10026,12 +10018,12 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>3.73</t>
+          <t>4.53</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>1.2763</t>
+          <t>1.5212</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -10041,7 +10033,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Gimpo Citizen FC</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -10066,7 +10058,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>0xf93dab40773f0e01839824957e7cecd4afb676d72a13c45521719f4f5c517a27</t>
+          <t>0x2725ecc350e6d5314ddee250cd3e445f586ab55a992fc73108db0913c5a41f24</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -10096,7 +10088,7 @@
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>1785057212</t>
+          <t>1785057353</t>
         </is>
       </c>
       <c r="S90" t="inlineStr">
@@ -10106,7 +10098,7 @@
       </c>
       <c r="T90" t="inlineStr">
         <is>
-          <t>13.502262</t>
+          <t>8.690647</t>
         </is>
       </c>
       <c r="U90" t="inlineStr">
@@ -10123,12 +10115,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>0xae029509b64a4e0489363d3aa1a7e18db0cd21b4fb65f5064e49185bb4bfb2f6</t>
+          <t>0x182964c6008d5b7d29731fd19876092a52fa2068fcb16aaf430dd8e0a6009721</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -10138,12 +10130,12 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3.73</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.2763</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -10153,24 +10145,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>K2-League</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen FC vs Yongin City</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
           <t>Gimpo Citizen FC</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>K2-League</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>Gimpo Citizen FC vs Yongin City</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>Gimpo Citizen FC</t>
-        </is>
-      </c>
       <c r="K91" t="inlineStr">
         <is>
           <t>Yongin City</t>
@@ -10178,7 +10170,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>0x2725ecc350e6d5314ddee250cd3e445f586ab55a992fc73108db0913c5a41f24</t>
+          <t>0xf93dab40773f0e01839824957e7cecd4afb676d72a13c45521719f4f5c517a27</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -10208,7 +10200,7 @@
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>1785056897</t>
+          <t>1785057212</t>
         </is>
       </c>
       <c r="S91" t="inlineStr">
@@ -10218,7 +10210,7 @@
       </c>
       <c r="T91" t="inlineStr">
         <is>
-          <t>9.615385</t>
+          <t>13.502262</t>
         </is>
       </c>
       <c r="U91" t="inlineStr">
@@ -10235,12 +10227,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>0xd359a1bde933becdef3ca166f20bbe9291a9b81f961befead4bc72e1713c6447</t>
+          <t>0xae029509b64a4e0489363d3aa1a7e18db0cd21b4fb65f5064e49185bb4bfb2f6</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -10250,7 +10242,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>4.53999</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -10320,7 +10312,7 @@
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>1785056453</t>
+          <t>1785056897</t>
         </is>
       </c>
       <c r="S92" t="inlineStr">
@@ -10330,7 +10322,7 @@
       </c>
       <c r="T92" t="inlineStr">
         <is>
-          <t>8.73075</t>
+          <t>9.615385</t>
         </is>
       </c>
       <c r="U92" t="inlineStr">
@@ -10347,7 +10339,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>0xe5784e1cc6cec364d74a7267a701924cf5f6543fed6d0c11d5f756f735c714f2</t>
+          <t>0xd359a1bde933becdef3ca166f20bbe9291a9b81f961befead4bc72e1713c6447</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -10362,7 +10354,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>4.53999</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -10432,7 +10424,7 @@
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>1785056153</t>
+          <t>1785056453</t>
         </is>
       </c>
       <c r="S93" t="inlineStr">
@@ -10442,7 +10434,7 @@
       </c>
       <c r="T93" t="inlineStr">
         <is>
-          <t>8.75</t>
+          <t>8.73075</t>
         </is>
       </c>
       <c r="U93" t="inlineStr">
@@ -10459,7 +10451,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>0x2fe44b6f9df282a6669198530843764a881fcd8c491dca571eaacc128af126e6</t>
+          <t>0xe5784e1cc6cec364d74a7267a701924cf5f6543fed6d0c11d5f756f735c714f2</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -10474,12 +10466,12 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>9.99999</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>1.5425</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -10489,7 +10481,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Gimpo Citizen FC</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -10499,27 +10491,27 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Paju Citizen vs Ansan Greeners</t>
+          <t>Gimpo Citizen FC vs Yongin City</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Gimpo Citizen FC</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>0x90106aa6ffeea165b450ea7a1094c65ae9db8d6fdde000ce479b4af5b3fa3072</t>
+          <t>0x2725ecc350e6d5314ddee250cd3e445f586ab55a992fc73108db0913c5a41f24</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>L19306782</t>
+          <t>L19306783</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -10544,7 +10536,7 @@
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>1785056005</t>
+          <t>1785056153</t>
         </is>
       </c>
       <c r="S94" t="inlineStr">
@@ -10554,7 +10546,7 @@
       </c>
       <c r="T94" t="inlineStr">
         <is>
-          <t>18.433161</t>
+          <t>8.75</t>
         </is>
       </c>
       <c r="U94" t="inlineStr">
@@ -10571,7 +10563,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>0x318bf0ba1d202676e38a34cf3a263bf2f98d89a54dbf8acb2cccc6beaedcc4e8</t>
+          <t>0x2fe44b6f9df282a6669198530843764a881fcd8c491dca571eaacc128af126e6</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -10586,12 +10578,12 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>9.99999</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>1.2575</t>
+          <t>1.5425</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -10601,7 +10593,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -10626,7 +10618,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>0xabfa364122222118f5f35af9ee862e2b9587e9c2f656e281725fdca100cf17bf</t>
+          <t>0x90106aa6ffeea165b450ea7a1094c65ae9db8d6fdde000ce479b4af5b3fa3072</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -10656,7 +10648,7 @@
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>1785055933</t>
+          <t>1785056005</t>
         </is>
       </c>
       <c r="S95" t="inlineStr">
@@ -10666,7 +10658,7 @@
       </c>
       <c r="T95" t="inlineStr">
         <is>
-          <t>4.970874</t>
+          <t>18.433161</t>
         </is>
       </c>
       <c r="U95" t="inlineStr">
@@ -10683,7 +10675,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>0x5dc684f3ea699d27149c867fb82e4e6f97c7382b6d8784e4edd5bf70e604bae2</t>
+          <t>0x318bf0ba1d202676e38a34cf3a263bf2f98d89a54dbf8acb2cccc6beaedcc4e8</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -10698,7 +10690,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -10768,7 +10760,7 @@
       </c>
       <c r="R96" t="inlineStr">
         <is>
-          <t>1785055931</t>
+          <t>1785055933</t>
         </is>
       </c>
       <c r="S96" t="inlineStr">
@@ -10778,7 +10770,7 @@
       </c>
       <c r="T96" t="inlineStr">
         <is>
-          <t>9.941748</t>
+          <t>4.970874</t>
         </is>
       </c>
       <c r="U96" t="inlineStr">
@@ -10795,7 +10787,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>0x947b403314498890960e964926f3e25010f3b36a93afc49e309f7a71a57648b0</t>
+          <t>0x5dc684f3ea699d27149c867fb82e4e6f97c7382b6d8784e4edd5bf70e604bae2</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -10810,12 +10802,12 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.2575</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -10825,7 +10817,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC</t>
+          <t>Tie</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -10835,27 +10827,27 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC vs Yongin City</t>
+          <t>Paju Citizen vs Ansan Greeners</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>0x2725ecc350e6d5314ddee250cd3e445f586ab55a992fc73108db0913c5a41f24</t>
+          <t>0xabfa364122222118f5f35af9ee862e2b9587e9c2f656e281725fdca100cf17bf</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>L19306783</t>
+          <t>L19306782</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
@@ -10880,7 +10872,7 @@
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>1785055853</t>
+          <t>1785055931</t>
         </is>
       </c>
       <c r="S97" t="inlineStr">
@@ -10890,7 +10882,7 @@
       </c>
       <c r="T97" t="inlineStr">
         <is>
-          <t>8.75</t>
+          <t>9.941748</t>
         </is>
       </c>
       <c r="U97" t="inlineStr">
@@ -10907,110 +10899,222 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
+          <t>0x947b403314498890960e964926f3e25010f3b36a93afc49e309f7a71a57648b0</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>4.55</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen FC</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>K2-League</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen FC vs Yongin City</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen FC</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Yongin City</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>0x2725ecc350e6d5314ddee250cd3e445f586ab55a992fc73108db0913c5a41f24</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>L19306783</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R98" t="inlineStr">
+        <is>
+          <t>1785055853</t>
+        </is>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>1785061800</t>
+        </is>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>8.75</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
           <t>0x4df42281e0de14de14275865cafadfb98d1cc6f76c1873f8fd64bcaa2cae8075</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr">
+      <c r="B99" t="inlineStr">
         <is>
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
         <is>
           <t>4.99</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr">
+      <c r="E99" t="inlineStr">
         <is>
           <t>1.2775</t>
         </is>
       </c>
-      <c r="F98" t="inlineStr">
+      <c r="F99" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr">
+      <c r="G99" t="inlineStr">
         <is>
           <t>Tie</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
+      <c r="H99" t="inlineStr">
         <is>
           <t>K2-League</t>
         </is>
       </c>
-      <c r="I98" t="inlineStr">
+      <c r="I99" t="inlineStr">
         <is>
           <t>Gimpo Citizen FC vs Yongin City</t>
         </is>
       </c>
-      <c r="J98" t="inlineStr">
+      <c r="J99" t="inlineStr">
         <is>
           <t>Gimpo Citizen FC</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr">
+      <c r="K99" t="inlineStr">
         <is>
           <t>Yongin City</t>
         </is>
       </c>
-      <c r="L98" t="inlineStr">
+      <c r="L99" t="inlineStr">
         <is>
           <t>0xf93dab40773f0e01839824957e7cecd4afb676d72a13c45521719f4f5c517a27</t>
         </is>
       </c>
-      <c r="M98" t="inlineStr">
+      <c r="M99" t="inlineStr">
         <is>
           <t>L19306783</t>
         </is>
       </c>
-      <c r="N98" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O98" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P98" t="inlineStr">
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q98" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R98" t="inlineStr">
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R99" t="inlineStr">
         <is>
           <t>1785044379</t>
         </is>
       </c>
-      <c r="S98" t="inlineStr">
+      <c r="S99" t="inlineStr">
         <is>
           <t>1785061800</t>
         </is>
       </c>
-      <c r="T98" t="inlineStr">
+      <c r="T99" t="inlineStr">
         <is>
           <t>17.981982</t>
         </is>
       </c>
-      <c r="U98" t="inlineStr">
+      <c r="U99" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V98" t="inlineStr">
+      <c r="V99" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/K2-League/trades.xlsx
+++ b/data/sxbet/ligas/K2-League/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V99"/>
+  <dimension ref="A1:V104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,7 +531,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x8a4af3a0b4b13cf57049ab82f395d7d34f9a5fd506160c67bbdd18174b6ad54e</t>
+          <t>0xd6d89d8b0c84fd0ec81a6b4192717012bb022d33dcacfee66f877d683dd4d611</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -539,23 +539,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>6.99</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.2662</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -563,27 +571,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Ansan Greeners vs Gimhae City</t>
+          <t>Gimpo Citizen FC vs Gyeongnam FC</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Gimpo Citizen FC</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Gyeongnam FC</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x88b7c7348c4915e417185345face1c028319f7a4edf6917e10541c5cf3904388</t>
+          <t>0xa00e8c256c66631472e12714859a797c90cf51583b5a4d0291530ebabda74786</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19391911</t>
+          <t>L19391910</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -608,7 +616,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1785605666</t>
+          <t>1785650299</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -618,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>24.037559</t>
+          <t>23.3</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -635,23 +643,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x72792262ae431dbdddbf088471b45079d60981e999bef9626fbfb120b75bf4d9</t>
+          <t>0x03d276695324f5778dc7acae7d1c8ccf471fa6903faf5477e59eee03458a3bfb</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>4.99999</t>
+          <t>8.98</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.8388</t>
+          <t>1.3275</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -659,7 +671,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Ansan Greeners</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -667,27 +683,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Chungbuk Cheongju FC vs Suwon Samsung Bluewings</t>
+          <t>Ansan Greeners vs Gimhae City</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Chungbuk Cheongju FC</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Suwon Samsung Bluewings</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0x47b6ff226935cb58cf016dcbca241d4de16dbfae419d63e4b73b31ca8333c27c</t>
+          <t>0x7d12a2dd53643f7bc82bf12edb22fd5c911d957e5077e96a6f07442b24f9e80a</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>L19382330</t>
+          <t>L19391911</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -712,17 +728,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1785578466</t>
+          <t>1785648537</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>1785580200</t>
+          <t>1785666600</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>5.96124</t>
+          <t>27.419847</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -739,7 +755,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0xd8137a83eb126ced1479e30bbe78433f31664b78e4e08119e4c5e0e06678d90f</t>
+          <t>0x2dc8ccfff3d666979cf43cfc872503cdcdd080abdd51de5f9eaafbdcf02e8dd1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -747,15 +763,19 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>11.09996</t>
+          <t>3.55</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.8388</t>
+          <t>1.3262</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -763,7 +783,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Ansan Greeners</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -771,27 +795,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Chungbuk Cheongju FC vs Suwon Samsung Bluewings</t>
+          <t>Ansan Greeners vs Gimhae City</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Chungbuk Cheongju FC</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Suwon Samsung Bluewings</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0x47b6ff226935cb58cf016dcbca241d4de16dbfae419d63e4b73b31ca8333c27c</t>
+          <t>0x7d12a2dd53643f7bc82bf12edb22fd5c911d957e5077e96a6f07442b24f9e80a</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>L19382330</t>
+          <t>L19391911</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -816,17 +840,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1785578456</t>
+          <t>1785648487</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>1785580200</t>
+          <t>1785666600</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>13.233931</t>
+          <t>10.881226</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -843,23 +867,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x45dd4119f9e9c4b0d949d74afa77a8e1b81e558353af15d7945dc9acc34f137b</t>
+          <t>0xf6008c4a4394aaa4d9bdde81644581532afef8e3bb1592c8ab8a428c02cc7ba6</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>23.71902</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.8388</t>
+          <t>1.3237</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -867,7 +895,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Ansan Greeners</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -875,27 +907,27 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Chungbuk Cheongju FC vs Suwon Samsung Bluewings</t>
+          <t>Ansan Greeners vs Gimhae City</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Chungbuk Cheongju FC</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Suwon Samsung Bluewings</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0x47b6ff226935cb58cf016dcbca241d4de16dbfae419d63e4b73b31ca8333c27c</t>
+          <t>0x7d12a2dd53643f7bc82bf12edb22fd5c911d957e5077e96a6f07442b24f9e80a</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>L19382330</t>
+          <t>L19391911</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -920,17 +952,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1785578456</t>
+          <t>1785648374</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>1785580200</t>
+          <t>1785666600</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>28.27901</t>
+          <t>21.621622</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -947,7 +979,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0xc5f6a546dd78c3c6c0c2b63058f45984183690baa2a85baf30f35fc6e6a95fbb</t>
+          <t>0xe77b567a8d83cd8a6dda10df24dccee1bb8a84363935c220b1fef7d1cb59ac3d</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -955,15 +987,19 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4.09</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.8388</t>
+          <t>1.2788</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -971,7 +1007,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -979,27 +1019,27 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Chungbuk Cheongju FC vs Suwon Samsung Bluewings</t>
+          <t>Jeonnam Dragons vs Paju Citizen</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Chungbuk Cheongju FC</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Suwon Samsung Bluewings</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0x47b6ff226935cb58cf016dcbca241d4de16dbfae419d63e4b73b31ca8333c27c</t>
+          <t>0x47bc42cdde4f45b45de3e45623d2a4551e6f614f6b6fa873e0c5368e0fb39c1d</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>L19382330</t>
+          <t>L19391909</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1024,17 +1064,17 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1785578455</t>
+          <t>1785647749</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>1785580200</t>
+          <t>1785666600</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1.19225</t>
+          <t>14.672646</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1051,28 +1091,28 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x071e0dd48a8b69c5fd46a90d3fd6130a920ae4675f78336d20fd540e2fb36e19</t>
+          <t>0x8a4af3a0b4b13cf57049ab82f395d7d34f9a5fd506160c67bbdd18174b6ad54e</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>14.2522</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.8388</t>
+          <t>1.2662</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -1083,27 +1123,27 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Chungbuk Cheongju FC vs Suwon Samsung Bluewings</t>
+          <t>Ansan Greeners vs Gimhae City</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Chungbuk Cheongju FC</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Suwon Samsung Bluewings</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0x47b6ff226935cb58cf016dcbca241d4de16dbfae419d63e4b73b31ca8333c27c</t>
+          <t>0x88b7c7348c4915e417185345face1c028319f7a4edf6917e10541c5cf3904388</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>L19382330</t>
+          <t>L19391911</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1128,17 +1168,17 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1785578454</t>
+          <t>1785605666</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>1785580200</t>
+          <t>1785666600</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>16.992191</t>
+          <t>24.037559</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1155,27 +1195,23 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0xd80db373e4b7ed691e095b9dd8e2c3060b27dd3b9d96138e938f8b834ed11575</t>
+          <t>0x72792262ae431dbdddbf088471b45079d60981e999bef9626fbfb120b75bf4d9</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>9.99836</t>
+          <t>4.99999</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.2375</t>
+          <t>1.8388</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1183,11 +1219,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -1210,7 +1242,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0xcbe732f420e35966f1693736f4eff7ac82d6eb79649c462d0b0da88b23389fd7</t>
+          <t>0x47b6ff226935cb58cf016dcbca241d4de16dbfae419d63e4b73b31ca8333c27c</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1240,7 +1272,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1785578439</t>
+          <t>1785578466</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1250,7 +1282,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>42.098358</t>
+          <t>5.96124</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1267,27 +1299,23 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0xd3730071ad09e64f8d94dd7eafe50fd030d149170edc5f0a6980a5b293fbdf6c</t>
+          <t>0xd8137a83eb126ced1479e30bbe78433f31664b78e4e08119e4c5e0e06678d90f</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>12.54</t>
+          <t>11.09996</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.2363</t>
+          <t>1.8388</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1295,11 +1323,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -1322,7 +1346,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0xcbe732f420e35966f1693736f4eff7ac82d6eb79649c462d0b0da88b23389fd7</t>
+          <t>0x47b6ff226935cb58cf016dcbca241d4de16dbfae419d63e4b73b31ca8333c27c</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1352,7 +1376,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1785578425</t>
+          <t>1785578456</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1362,7 +1386,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>53.079365</t>
+          <t>13.233931</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1379,23 +1403,23 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0x0030d78c7fa3ca6505041a6863683acfc5d44fd46db42676d8fab5fface0f896</t>
+          <t>0x45dd4119f9e9c4b0d949d74afa77a8e1b81e558353af15d7945dc9acc34f137b</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>33.00917</t>
+          <t>23.71902</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.6637</t>
+          <t>1.8388</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1411,27 +1435,27 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Chungnam Asan FC vs Seongnam FC</t>
+          <t>Chungbuk Cheongju FC vs Suwon Samsung Bluewings</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Chungnam Asan FC</t>
+          <t>Chungbuk Cheongju FC</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Seongnam FC</t>
+          <t>Suwon Samsung Bluewings</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0xdc5a3c94507978b475275edc3f202e74993cdff1bf5f2e138cb9ec5c9fdab56b</t>
+          <t>0x47b6ff226935cb58cf016dcbca241d4de16dbfae419d63e4b73b31ca8333c27c</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>L19382328</t>
+          <t>L19382330</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1456,7 +1480,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1785578412</t>
+          <t>1785578456</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1466,7 +1490,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>49.73133</t>
+          <t>28.27901</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1483,7 +1507,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x220dcc2e193d2914753c8ca31c20857d1cba243ec4469ca1444318967b690306</t>
+          <t>0xc5f6a546dd78c3c6c0c2b63058f45984183690baa2a85baf30f35fc6e6a95fbb</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1491,19 +1515,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>27.01</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.3625</t>
+          <t>1.8388</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1511,11 +1531,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Chungnam Asan FC</t>
-        </is>
-      </c>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -1523,27 +1539,27 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Chungnam Asan FC vs Seongnam FC</t>
+          <t>Chungbuk Cheongju FC vs Suwon Samsung Bluewings</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Chungnam Asan FC</t>
+          <t>Chungbuk Cheongju FC</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Seongnam FC</t>
+          <t>Suwon Samsung Bluewings</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0x122be21c6184231146fb4c55c0406dac2859200e923b24d2b4641ce66abf29f4</t>
+          <t>0x47b6ff226935cb58cf016dcbca241d4de16dbfae419d63e4b73b31ca8333c27c</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>L19382328</t>
+          <t>L19382330</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1568,7 +1584,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1785578411</t>
+          <t>1785578455</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1578,7 +1594,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>74.510345</t>
+          <t>1.19225</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1595,23 +1611,23 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0xa1105617e22069824dc4bb3cbe2a43733b8051deee672c5eb37dab4d3fe5e57d</t>
+          <t>0x071e0dd48a8b69c5fd46a90d3fd6130a920ae4675f78336d20fd540e2fb36e19</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>5.62999</t>
+          <t>14.2522</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.8438</t>
+          <t>1.8388</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1672,7 +1688,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1785578250</t>
+          <t>1785578454</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1682,7 +1698,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>6.672581</t>
+          <t>16.992191</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1699,7 +1715,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0xab0581f4aab772a5e75f6983d6a981e9515dda6c22e94295de4804365f5a78cd</t>
+          <t>0xd80db373e4b7ed691e095b9dd8e2c3060b27dd3b9d96138e938f8b834ed11575</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1707,15 +1723,19 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.99998</t>
+          <t>9.99836</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.8438</t>
+          <t>1.2375</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1723,7 +1743,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -1746,7 +1770,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0x47b6ff226935cb58cf016dcbca241d4de16dbfae419d63e4b73b31ca8333c27c</t>
+          <t>0xcbe732f420e35966f1693736f4eff7ac82d6eb79649c462d0b0da88b23389fd7</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1776,7 +1800,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1785577978</t>
+          <t>1785578439</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1786,7 +1810,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1.185161</t>
+          <t>42.098358</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1803,23 +1827,27 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0xd2748c10f4095190f2c2b3649173009f55db5d97aee6e8a15de89cc6f7dc2d94</t>
+          <t>0xd3730071ad09e64f8d94dd7eafe50fd030d149170edc5f0a6980a5b293fbdf6c</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>4.99997</t>
+          <t>12.54</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.8438</t>
+          <t>1.2363</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1827,7 +1855,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H14" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -1850,7 +1882,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0x47b6ff226935cb58cf016dcbca241d4de16dbfae419d63e4b73b31ca8333c27c</t>
+          <t>0xcbe732f420e35966f1693736f4eff7ac82d6eb79649c462d0b0da88b23389fd7</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1880,7 +1912,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1785577974</t>
+          <t>1785578425</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1890,7 +1922,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>5.92589</t>
+          <t>53.079365</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1907,23 +1939,23 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0xb473a9bcd28ce7eb541287850173d36b188eb2ce16684b4f47feec73017ef210</t>
+          <t>0x0030d78c7fa3ca6505041a6863683acfc5d44fd46db42676d8fab5fface0f896</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>4.99997</t>
+          <t>33.00917</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.8438</t>
+          <t>1.6637</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1939,27 +1971,27 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Chungbuk Cheongju FC vs Suwon Samsung Bluewings</t>
+          <t>Chungnam Asan FC vs Seongnam FC</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Chungbuk Cheongju FC</t>
+          <t>Chungnam Asan FC</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Suwon Samsung Bluewings</t>
+          <t>Seongnam FC</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0x47b6ff226935cb58cf016dcbca241d4de16dbfae419d63e4b73b31ca8333c27c</t>
+          <t>0xdc5a3c94507978b475275edc3f202e74993cdff1bf5f2e138cb9ec5c9fdab56b</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>L19382330</t>
+          <t>L19382328</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1984,7 +2016,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1785577972</t>
+          <t>1785578412</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -1994,7 +2026,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>5.92589</t>
+          <t>49.73133</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2011,23 +2043,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0x1c7c5e1e91914e15cd389ea78b98ffc4af816835d6679433a97a2be50034a7f1</t>
+          <t>0x220dcc2e193d2914753c8ca31c20857d1cba243ec4469ca1444318967b690306</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>4.99997</t>
+          <t>27.01</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.8438</t>
+          <t>1.3625</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2035,7 +2071,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Chungnam Asan FC</t>
+        </is>
+      </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -2043,27 +2083,27 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Chungbuk Cheongju FC vs Suwon Samsung Bluewings</t>
+          <t>Chungnam Asan FC vs Seongnam FC</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Chungbuk Cheongju FC</t>
+          <t>Chungnam Asan FC</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Suwon Samsung Bluewings</t>
+          <t>Seongnam FC</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0x47b6ff226935cb58cf016dcbca241d4de16dbfae419d63e4b73b31ca8333c27c</t>
+          <t>0x122be21c6184231146fb4c55c0406dac2859200e923b24d2b4641ce66abf29f4</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>L19382330</t>
+          <t>L19382328</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2088,7 +2128,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1785577971</t>
+          <t>1785578411</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2098,7 +2138,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>5.92589</t>
+          <t>74.510345</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2115,23 +2155,23 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0x570a559aaadf75a6ed1acd4ccb5ddd8e55ce1e7f522824b57494899c861e8d6a</t>
+          <t>0xa1105617e22069824dc4bb3cbe2a43733b8051deee672c5eb37dab4d3fe5e57d</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>5.34932</t>
+          <t>5.62999</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.8425</t>
+          <t>1.8438</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2192,7 +2232,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1785577945</t>
+          <t>1785578250</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2202,7 +2242,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>6.349341</t>
+          <t>6.672581</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2219,23 +2259,23 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0x8faf54553900d697a6ef224191c3c314fce17df8a2ec46f32c8f5f4664872c42</t>
+          <t>0xab0581f4aab772a5e75f6983d6a981e9515dda6c22e94295de4804365f5a78cd</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>30.16947</t>
+          <t>0.99998</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.8425</t>
+          <t>1.8438</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2296,7 +2336,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1785577943</t>
+          <t>1785577978</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2306,7 +2346,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>35.80946</t>
+          <t>1.185161</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2323,23 +2363,23 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0x87d245204fb6266d66f05bad0f085ef14e0002175ce19e9ca19fc941bd2840c8</t>
+          <t>0xd2748c10f4095190f2c2b3649173009f55db5d97aee6e8a15de89cc6f7dc2d94</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>28.6717</t>
+          <t>4.99997</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.8425</t>
+          <t>1.8438</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2400,7 +2440,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1785577942</t>
+          <t>1785577974</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2410,7 +2450,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>34.031691</t>
+          <t>5.92589</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2427,27 +2467,23 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0xa3ba7bafd18b1a2ed7a2d9f70c9f9f14d910d1148a0051bb51394a7e0b839c92</t>
+          <t>0xb473a9bcd28ce7eb541287850173d36b188eb2ce16684b4f47feec73017ef210</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>3.66</t>
+          <t>4.99997</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.2937</t>
+          <t>1.8438</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2455,11 +2491,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -2467,27 +2499,27 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Cheonan City vs Yongin City</t>
+          <t>Chungbuk Cheongju FC vs Suwon Samsung Bluewings</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Chungbuk Cheongju FC</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Suwon Samsung Bluewings</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0x4f0eac96e527e303ba7f731f63206ea5d322051eee61a9087848437cebf10534</t>
+          <t>0x47b6ff226935cb58cf016dcbca241d4de16dbfae419d63e4b73b31ca8333c27c</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>L19382335</t>
+          <t>L19382330</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2512,7 +2544,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1785577801</t>
+          <t>1785577972</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2522,7 +2554,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>12.459574</t>
+          <t>5.92589</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2539,23 +2571,23 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0x2ff9636c19015324567a484925b48b01572feafd96dfae06927e7d28a91accb4</t>
+          <t>0x1c7c5e1e91914e15cd389ea78b98ffc4af816835d6679433a97a2be50034a7f1</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>20.20568</t>
+          <t>4.99997</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.6475</t>
+          <t>1.8438</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2571,27 +2603,27 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Chungnam Asan FC vs Seongnam FC</t>
+          <t>Chungbuk Cheongju FC vs Suwon Samsung Bluewings</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Chungnam Asan FC</t>
+          <t>Chungbuk Cheongju FC</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Seongnam FC</t>
+          <t>Suwon Samsung Bluewings</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0x122be21c6184231146fb4c55c0406dac2859200e923b24d2b4641ce66abf29f4</t>
+          <t>0x47b6ff226935cb58cf016dcbca241d4de16dbfae419d63e4b73b31ca8333c27c</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>L19382328</t>
+          <t>L19382330</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2616,7 +2648,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1785577136</t>
+          <t>1785577971</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2626,7 +2658,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>31.205683</t>
+          <t>5.92589</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2643,23 +2675,23 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0xd04f669dbfe7947145022fe948220730e2200d0302b6c375521b18cfb89478d9</t>
+          <t>0x570a559aaadf75a6ed1acd4ccb5ddd8e55ce1e7f522824b57494899c861e8d6a</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>59.4</t>
+          <t>5.34932</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.8438</t>
+          <t>1.8425</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2720,7 +2752,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1785577059</t>
+          <t>1785577945</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2730,7 +2762,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>70.4</t>
+          <t>6.349341</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2747,18 +2779,18 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0xd6e59c4a6fedc3fc306e81e55a5678b03ee303e96a9653c49b87b641e05fecf5</t>
+          <t>0x8faf54553900d697a6ef224191c3c314fce17df8a2ec46f32c8f5f4664872c42</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>58.83999</t>
+          <t>30.16947</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2824,7 +2856,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1785577058</t>
+          <t>1785577943</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -2834,7 +2866,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>69.839751</t>
+          <t>35.80946</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2851,23 +2883,23 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0xbdaeb9efa9099daa54488930d7f3e08686658f371f2ca9deb5dee1fb018d5dc9</t>
+          <t>0x87d245204fb6266d66f05bad0f085ef14e0002175ce19e9ca19fc941bd2840c8</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>15.11</t>
+          <t>28.6717</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.6713</t>
+          <t>1.8425</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2883,27 +2915,27 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Cheonan City vs Yongin City</t>
+          <t>Chungbuk Cheongju FC vs Suwon Samsung Bluewings</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Chungbuk Cheongju FC</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Suwon Samsung Bluewings</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0xc44350683931fa086c3759e22036c1861e9430054b71327499cb1ad0357c41af</t>
+          <t>0x47b6ff226935cb58cf016dcbca241d4de16dbfae419d63e4b73b31ca8333c27c</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>L19382335</t>
+          <t>L19382330</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2928,7 +2960,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1785576608</t>
+          <t>1785577942</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -2938,7 +2970,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>22.510242</t>
+          <t>34.031691</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -2955,7 +2987,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0x89e7975252a4021e2edec5b41c422fb0f9e0b0bd71b44469db8e27760ccfec81</t>
+          <t>0xa3ba7bafd18b1a2ed7a2d9f70c9f9f14d910d1148a0051bb51394a7e0b839c92</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2970,12 +3002,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>3.66</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.3838</t>
+          <t>1.2937</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2985,24 +3017,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>K2-League</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Cheonan City vs Yongin City</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
           <t>Cheonan City</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>K2-League</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>Cheonan City vs Yongin City</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>Cheonan City</t>
-        </is>
-      </c>
       <c r="K25" t="inlineStr">
         <is>
           <t>Yongin City</t>
@@ -3010,7 +3042,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0x0ae3c1437f52d2b3c8a4d033ef252880ab9d9fee58c4335b560a2a5bdf7ec6bf</t>
+          <t>0x4f0eac96e527e303ba7f731f63206ea5d322051eee61a9087848437cebf10534</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -3040,7 +3072,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1785576308</t>
+          <t>1785577801</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3050,7 +3082,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>7.504886</t>
+          <t>12.459574</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3067,7 +3099,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0x2cbe5fb46a011721b21db0e317c482acbdda4529d7e20e5694a7635608189873</t>
+          <t>0x2ff9636c19015324567a484925b48b01572feafd96dfae06927e7d28a91accb4</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3075,19 +3107,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>5.01495</t>
+          <t>20.20568</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.2925</t>
+          <t>1.6475</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -3095,11 +3123,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -3107,27 +3131,27 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Cheonan City vs Yongin City</t>
+          <t>Chungnam Asan FC vs Seongnam FC</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Chungnam Asan FC</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Seongnam FC</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0x4f0eac96e527e303ba7f731f63206ea5d322051eee61a9087848437cebf10534</t>
+          <t>0x122be21c6184231146fb4c55c0406dac2859200e923b24d2b4641ce66abf29f4</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>L19382335</t>
+          <t>L19382328</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -3152,7 +3176,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1785576164</t>
+          <t>1785577136</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3162,7 +3186,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>17.145128</t>
+          <t>31.205683</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3179,7 +3203,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0x6427a9b06be945650ac5754ea9013bd388bb7fd63b9fea057a31d292e952be4b</t>
+          <t>0xd04f669dbfe7947145022fe948220730e2200d0302b6c375521b18cfb89478d9</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3187,19 +3211,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>4.99</t>
+          <t>59.4</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.2925</t>
+          <t>1.8438</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -3207,11 +3227,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -3219,27 +3235,27 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Cheonan City vs Yongin City</t>
+          <t>Chungbuk Cheongju FC vs Suwon Samsung Bluewings</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Chungbuk Cheongju FC</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Suwon Samsung Bluewings</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0x4f0eac96e527e303ba7f731f63206ea5d322051eee61a9087848437cebf10534</t>
+          <t>0x47b6ff226935cb58cf016dcbca241d4de16dbfae419d63e4b73b31ca8333c27c</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>L19382335</t>
+          <t>L19382330</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -3264,7 +3280,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1785576163</t>
+          <t>1785577059</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3274,7 +3290,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>17.059829</t>
+          <t>70.4</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3291,7 +3307,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0xd7b3568a3172d11868a8c52422c6edb93781f013948e3cbe3187ecd49450a2ed</t>
+          <t>0xd6e59c4a6fedc3fc306e81e55a5678b03ee303e96a9653c49b87b641e05fecf5</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3299,19 +3315,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>58.83999</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.3013</t>
+          <t>1.8425</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -3319,11 +3331,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -3331,27 +3339,27 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Chungnam Asan FC vs Seongnam FC</t>
+          <t>Chungbuk Cheongju FC vs Suwon Samsung Bluewings</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Chungnam Asan FC</t>
+          <t>Chungbuk Cheongju FC</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Seongnam FC</t>
+          <t>Suwon Samsung Bluewings</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0x3908aa00f1ce849001a57f81937948c4a35c187a56fca542d1c26ac2a5aa578c</t>
+          <t>0x47b6ff226935cb58cf016dcbca241d4de16dbfae419d63e4b73b31ca8333c27c</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>L19382328</t>
+          <t>L19382330</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -3376,7 +3384,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1785576156</t>
+          <t>1785577058</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3386,7 +3394,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>19.917012</t>
+          <t>69.839751</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3403,7 +3411,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0x385d3c2ccc1504b8b62960b052836b16848b30f964e71dbb330e557b9d5b0958</t>
+          <t>0xbdaeb9efa9099daa54488930d7f3e08686658f371f2ca9deb5dee1fb018d5dc9</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3411,19 +3419,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>9.01646</t>
+          <t>15.11</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.3025</t>
+          <t>1.6713</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -3431,11 +3435,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -3443,27 +3443,27 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Chungnam Asan FC vs Seongnam FC</t>
+          <t>Cheonan City vs Yongin City</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Chungnam Asan FC</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Seongnam FC</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0x3908aa00f1ce849001a57f81937948c4a35c187a56fca542d1c26ac2a5aa578c</t>
+          <t>0xc44350683931fa086c3759e22036c1861e9430054b71327499cb1ad0357c41af</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>L19382328</t>
+          <t>L19382335</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1785576156</t>
+          <t>1785576608</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>29.806479</t>
+          <t>22.510242</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3515,7 +3515,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0x81bc6461a5498bb098f71cbd0566c77991625c35e512a092b27824593eb64b44</t>
+          <t>0x89e7975252a4021e2edec5b41c422fb0f9e0b0bd71b44469db8e27760ccfec81</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3530,7 +3530,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>5.76</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -3600,7 +3600,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1785576008</t>
+          <t>1785576308</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3610,7 +3610,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>15.009772</t>
+          <t>7.504886</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3627,7 +3627,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0x20a26ca056f3f25e1f8971a88b06b55502b7f6fd7d4ead5f9ed5057ee98ecf34</t>
+          <t>0x2cbe5fb46a011721b21db0e317c482acbdda4529d7e20e5694a7635608189873</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3635,23 +3635,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr"/>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>7.77558</t>
+          <t>5.01495</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.3413</t>
+          <t>1.2925</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H31" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -3659,27 +3667,27 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Chungbuk Cheongju FC vs Suwon Samsung Bluewings</t>
+          <t>Cheonan City vs Yongin City</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Chungbuk Cheongju FC</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Suwon Samsung Bluewings</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0x9e11ba3ce6b4420e4e452b60f302739f1d8467716ba519ebe3f8132832094348</t>
+          <t>0x4f0eac96e527e303ba7f731f63206ea5d322051eee61a9087848437cebf10534</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>L19382330</t>
+          <t>L19382335</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -3704,7 +3712,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1785576008</t>
+          <t>1785576164</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -3714,7 +3722,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>22.785582</t>
+          <t>17.145128</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3731,7 +3739,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0xd9d9b0ddddc1467f24d4b982d44a16b3c39903ee63500a8ec66563c6202bfcf9</t>
+          <t>0x6427a9b06be945650ac5754ea9013bd388bb7fd63b9fea057a31d292e952be4b</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3746,12 +3754,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>5.71</t>
+          <t>4.99</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.3838</t>
+          <t>1.2925</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -3761,24 +3769,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>K2-League</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Cheonan City vs Yongin City</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
           <t>Cheonan City</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>K2-League</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>Cheonan City vs Yongin City</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>Cheonan City</t>
-        </is>
-      </c>
       <c r="K32" t="inlineStr">
         <is>
           <t>Yongin City</t>
@@ -3786,7 +3794,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0x0ae3c1437f52d2b3c8a4d033ef252880ab9d9fee58c4335b560a2a5bdf7ec6bf</t>
+          <t>0x4f0eac96e527e303ba7f731f63206ea5d322051eee61a9087848437cebf10534</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -3816,7 +3824,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1785575708</t>
+          <t>1785576163</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -3826,7 +3834,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>14.879479</t>
+          <t>17.059829</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3843,7 +3851,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0x087314e5ace3bbb3bbb4f703bfe21af2df9ef3152845f56763bcabd878659d88</t>
+          <t>0xd7b3568a3172d11868a8c52422c6edb93781f013948e3cbe3187ecd49450a2ed</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3858,12 +3866,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.385</t>
+          <t>1.3013</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -3873,7 +3881,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Tie</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3883,27 +3891,27 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Cheonan City vs Yongin City</t>
+          <t>Chungnam Asan FC vs Seongnam FC</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Chungnam Asan FC</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Seongnam FC</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0x0ae3c1437f52d2b3c8a4d033ef252880ab9d9fee58c4335b560a2a5bdf7ec6bf</t>
+          <t>0x3908aa00f1ce849001a57f81937948c4a35c187a56fca542d1c26ac2a5aa578c</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>L19382335</t>
+          <t>L19382328</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -3928,7 +3936,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1785574808</t>
+          <t>1785576156</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -3938,7 +3946,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>8.181818</t>
+          <t>19.917012</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -3955,7 +3963,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0x1665cbfdd918d1b313ff8b09985889ba3e20ffef471ed1f77d4454a6d4870eb1</t>
+          <t>0x385d3c2ccc1504b8b62960b052836b16848b30f964e71dbb330e557b9d5b0958</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3970,12 +3978,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>10.96</t>
+          <t>9.01646</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.6113</t>
+          <t>1.3025</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -3985,7 +3993,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Suwon Samsung Bluewings</t>
+          <t>Tie</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3995,27 +4003,27 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Chungbuk Cheongju FC vs Suwon Samsung Bluewings</t>
+          <t>Chungnam Asan FC vs Seongnam FC</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Chungbuk Cheongju FC</t>
+          <t>Chungnam Asan FC</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Suwon Samsung Bluewings</t>
+          <t>Seongnam FC</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0xb29a7409dfd5ac0b7a29e92e49cc6bab92af282a2f9d95f3eeb630ed33eb7a3a</t>
+          <t>0x3908aa00f1ce849001a57f81937948c4a35c187a56fca542d1c26ac2a5aa578c</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>L19382330</t>
+          <t>L19382328</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -4040,7 +4048,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1785574796</t>
+          <t>1785576156</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -4050,7 +4058,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>17.93047</t>
+          <t>29.806479</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4067,7 +4075,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0xf5159a5ea43cd4f5bd5f77236fb23f24714602f00b37c28d1f70bb3786749e16</t>
+          <t>0x81bc6461a5498bb098f71cbd0566c77991625c35e512a092b27824593eb64b44</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4075,15 +4083,19 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr"/>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>5.76</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.5413</t>
+          <t>1.3838</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -4091,7 +4103,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Cheonan City</t>
+        </is>
+      </c>
       <c r="H35" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -4099,27 +4115,27 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Hwaseong FC vs Daegu FC</t>
+          <t>Cheonan City vs Yongin City</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Hwaseong FC</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Daegu FC</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0x3673fddffb9c10163590d13afe39cb241b3c0284138745deddac5c176ba19ebd</t>
+          <t>0x0ae3c1437f52d2b3c8a4d033ef252880ab9d9fee58c4335b560a2a5bdf7ec6bf</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>L19382332</t>
+          <t>L19382335</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -4144,7 +4160,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1785574516</t>
+          <t>1785576008</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -4154,7 +4170,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>6.060046</t>
+          <t>15.009772</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4171,7 +4187,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0x1d3e02f07b5d6a05bde415b055541ce4395cbd9016dfcb7b067173b6ff538c00</t>
+          <t>0x20a26ca056f3f25e1f8971a88b06b55502b7f6fd7d4ead5f9ed5057ee98ecf34</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4179,31 +4195,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>5.76</t>
+          <t>7.77558</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.3838</t>
+          <t>1.3413</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Cheonan City</t>
-        </is>
-      </c>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -4211,27 +4219,27 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Cheonan City vs Yongin City</t>
+          <t>Chungbuk Cheongju FC vs Suwon Samsung Bluewings</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Chungbuk Cheongju FC</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Suwon Samsung Bluewings</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0x0ae3c1437f52d2b3c8a4d033ef252880ab9d9fee58c4335b560a2a5bdf7ec6bf</t>
+          <t>0x9e11ba3ce6b4420e4e452b60f302739f1d8467716ba519ebe3f8132832094348</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>L19382335</t>
+          <t>L19382330</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -4256,7 +4264,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1785573908</t>
+          <t>1785576008</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -4266,7 +4274,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>15.009772</t>
+          <t>22.785582</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4283,7 +4291,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0x43f4e76dc758bd60088f0e19fe831ad6e231cfd3f25713ee2197b0c4c12225c4</t>
+          <t>0xd9d9b0ddddc1467f24d4b982d44a16b3c39903ee63500a8ec66563c6202bfcf9</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4291,23 +4299,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr"/>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>5.71</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.335</t>
+          <t>1.3838</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Cheonan City</t>
+        </is>
+      </c>
       <c r="H37" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -4315,27 +4331,27 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Chungbuk Cheongju FC vs Suwon Samsung Bluewings</t>
+          <t>Cheonan City vs Yongin City</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Chungbuk Cheongju FC</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Suwon Samsung Bluewings</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0x9e11ba3ce6b4420e4e452b60f302739f1d8467716ba519ebe3f8132832094348</t>
+          <t>0x0ae3c1437f52d2b3c8a4d033ef252880ab9d9fee58c4335b560a2a5bdf7ec6bf</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>L19382330</t>
+          <t>L19382335</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -4360,7 +4376,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1785573008</t>
+          <t>1785575708</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -4370,7 +4386,7 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>17.164179</t>
+          <t>14.879479</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4387,7 +4403,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0xcc556a2f534d604ca3147c77e407c4a3caccfb460a650afb93e92f95893a83f3</t>
+          <t>0x087314e5ace3bbb3bbb4f703bfe21af2df9ef3152845f56763bcabd878659d88</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4395,23 +4411,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr"/>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>5.74</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.335</t>
+          <t>1.385</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Cheonan City</t>
+        </is>
+      </c>
       <c r="H38" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -4419,27 +4443,27 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Chungbuk Cheongju FC vs Suwon Samsung Bluewings</t>
+          <t>Cheonan City vs Yongin City</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Chungbuk Cheongju FC</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Suwon Samsung Bluewings</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0x9e11ba3ce6b4420e4e452b60f302739f1d8467716ba519ebe3f8132832094348</t>
+          <t>0x0ae3c1437f52d2b3c8a4d033ef252880ab9d9fee58c4335b560a2a5bdf7ec6bf</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>L19382330</t>
+          <t>L19382335</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -4464,7 +4488,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1785572408</t>
+          <t>1785574808</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -4474,7 +4498,7 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>17.134328</t>
+          <t>8.181818</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4491,7 +4515,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0xe6b9109907b0068b7b44342bbfe6aa4e4f925a1808a4234ef25d5964c06e8a19</t>
+          <t>0x1665cbfdd918d1b313ff8b09985889ba3e20ffef471ed1f77d4454a6d4870eb1</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4506,12 +4530,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>4.99</t>
+          <t>10.96</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.2913</t>
+          <t>1.6113</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -4521,7 +4545,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Suwon Samsung Bluewings</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -4531,27 +4555,27 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Cheonan City vs Yongin City</t>
+          <t>Chungbuk Cheongju FC vs Suwon Samsung Bluewings</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Chungbuk Cheongju FC</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Suwon Samsung Bluewings</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0x4f0eac96e527e303ba7f731f63206ea5d322051eee61a9087848437cebf10534</t>
+          <t>0xb29a7409dfd5ac0b7a29e92e49cc6bab92af282a2f9d95f3eeb630ed33eb7a3a</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>L19382335</t>
+          <t>L19382330</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -4576,7 +4600,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1785571129</t>
+          <t>1785574796</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -4586,7 +4610,7 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>17.133047</t>
+          <t>17.93047</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4603,7 +4627,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0x3adcd675a8ad2ac41cfe2151a15dc0861c045d26ad2b087ec6303e2e6bc75b83</t>
+          <t>0xf5159a5ea43cd4f5bd5f77236fb23f24714602f00b37c28d1f70bb3786749e16</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4611,19 +4635,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.2412</t>
+          <t>1.5413</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -4631,11 +4651,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -4643,27 +4659,27 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Chungbuk Cheongju FC vs Suwon Samsung Bluewings</t>
+          <t>Hwaseong FC vs Daegu FC</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Chungbuk Cheongju FC</t>
+          <t>Hwaseong FC</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Suwon Samsung Bluewings</t>
+          <t>Daegu FC</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0xcbe732f420e35966f1693736f4eff7ac82d6eb79649c462d0b0da88b23389fd7</t>
+          <t>0x3673fddffb9c10163590d13afe39cb241b3c0284138745deddac5c176ba19ebd</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>L19382330</t>
+          <t>L19382332</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -4688,7 +4704,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1785561333</t>
+          <t>1785574516</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -4698,7 +4714,7 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>4.601036</t>
+          <t>6.060046</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -4715,7 +4731,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0x0ba2bf9f0fc74c97ade129a1430bdc4cd89f8fecee54ee5b1f9876c41b38c180</t>
+          <t>0x1d3e02f07b5d6a05bde415b055541ce4395cbd9016dfcb7b067173b6ff538c00</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4730,12 +4746,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>5.76</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.2662</t>
+          <t>1.3838</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -4745,7 +4761,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -4755,27 +4771,27 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Hwaseong FC vs Daegu FC</t>
+          <t>Cheonan City vs Yongin City</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Hwaseong FC</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Daegu FC</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0xda1e33e5fc880742964769df06cb9c83769ec80d9cb168728d3a3467d0a0473b</t>
+          <t>0x0ae3c1437f52d2b3c8a4d033ef252880ab9d9fee58c4335b560a2a5bdf7ec6bf</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>L19382332</t>
+          <t>L19382335</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -4800,7 +4816,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1785558588</t>
+          <t>1785573908</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -4810,7 +4826,7 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>12.995305</t>
+          <t>15.009772</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -4827,7 +4843,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0x59cfeb6eefafd07022cdcaae7869afb45bc60deb8b4c0b4b96ad04ae8bbdb0d3</t>
+          <t>0x43f4e76dc758bd60088f0e19fe831ad6e231cfd3f25713ee2197b0c4c12225c4</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4835,59 +4851,51 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>321.53001</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.525</t>
+          <t>1.335</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr">
+        <is>
           <t>K2-League</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>Chungnam Asan FC 0</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>K2-League</t>
-        </is>
-      </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Chungnam Asan FC vs Seongnam FC</t>
+          <t>Chungbuk Cheongju FC vs Suwon Samsung Bluewings</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Chungnam Asan FC</t>
+          <t>Chungbuk Cheongju FC</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Seongnam FC</t>
+          <t>Suwon Samsung Bluewings</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0x5d9fd67211ec6f71728981803ac86abc94216c4e6a398285b5003dabd4e5df0f</t>
+          <t>0x9e11ba3ce6b4420e4e452b60f302739f1d8467716ba519ebe3f8132832094348</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>L19382328</t>
+          <t>L19382330</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -4912,7 +4920,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1785534316</t>
+          <t>1785573008</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -4922,7 +4930,7 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>612.438114</t>
+          <t>17.164179</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -4939,7 +4947,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0x57f84ab38f2e25e292c948ee169e9feff1e8436efac9878d37389052fc7a8ade</t>
+          <t>0xcc556a2f534d604ca3147c77e407c4a3caccfb460a650afb93e92f95893a83f3</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4947,59 +4955,51 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>9.99999</t>
+          <t>5.74</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.525</t>
+          <t>1.335</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr">
+        <is>
           <t>K2-League</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>Chungnam Asan FC 0</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>K2-League</t>
-        </is>
-      </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Chungnam Asan FC vs Seongnam FC</t>
+          <t>Chungbuk Cheongju FC vs Suwon Samsung Bluewings</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Chungnam Asan FC</t>
+          <t>Chungbuk Cheongju FC</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Seongnam FC</t>
+          <t>Suwon Samsung Bluewings</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0x5d9fd67211ec6f71728981803ac86abc94216c4e6a398285b5003dabd4e5df0f</t>
+          <t>0x9e11ba3ce6b4420e4e452b60f302739f1d8467716ba519ebe3f8132832094348</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>L19382328</t>
+          <t>L19382330</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -5024,7 +5024,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1785534315</t>
+          <t>1785572408</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -5034,7 +5034,7 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>19.0476</t>
+          <t>17.134328</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -5051,12 +5051,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0x4da39049a709357f30ef968bfc90b4eec2da9d99090f3b99edf4ea11aeddd708</t>
+          <t>0xe6b9109907b0068b7b44342bbfe6aa4e4f925a1808a4234ef25d5964c06e8a19</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -5066,22 +5066,22 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>32.79</t>
+          <t>4.99</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.5488</t>
+          <t>1.2913</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hwaseong FC +0.5</t>
+          <t>Tie</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -5091,27 +5091,27 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Hwaseong FC vs Daegu FC</t>
+          <t>Cheonan City vs Yongin City</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Hwaseong FC</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Daegu FC</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0xbde5165c3a540b0c6dd64b3df320540fd10ecb173373b087359951e7f790f852</t>
+          <t>0x4f0eac96e527e303ba7f731f63206ea5d322051eee61a9087848437cebf10534</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>L19382332</t>
+          <t>L19382335</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -5136,7 +5136,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>1785527084</t>
+          <t>1785571129</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>59.753986</t>
+          <t>17.133047</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -5163,7 +5163,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0x07b844c409deb0bc9c8e8dbda27c7c2b772aec07892356105db79f67ffb0e227</t>
+          <t>0x3adcd675a8ad2ac41cfe2151a15dc0861c045d26ad2b087ec6303e2e6bc75b83</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5171,23 +5171,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr"/>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>6.39</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1.5675</t>
+          <t>1.2412</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H45" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -5195,27 +5203,27 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC vs Yongin City</t>
+          <t>Chungbuk Cheongju FC vs Suwon Samsung Bluewings</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC</t>
+          <t>Chungbuk Cheongju FC</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Suwon Samsung Bluewings</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>0xf73fcbba4baac94056070f4c2db509913d7317940066a6918ac1f13256f52327</t>
+          <t>0xcbe732f420e35966f1693736f4eff7ac82d6eb79649c462d0b0da88b23389fd7</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>L19306783</t>
+          <t>L19382330</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -5240,17 +5248,17 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>1785064787</t>
+          <t>1785561333</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>1785061800</t>
+          <t>1785580200</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>11.259912</t>
+          <t>4.601036</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -5267,31 +5275,39 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0xf95f88d59f982dc2c9ca6387361b5a066ab48deeb7f9f6071274eb879ddabdd0</t>
+          <t>0x0ba2bf9f0fc74c97ade129a1430bdc4cd89f8fecee54ee5b1f9876c41b38c180</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>126.4351</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.815</t>
+          <t>1.2662</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H46" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -5299,27 +5315,27 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC vs Yongin City</t>
+          <t>Hwaseong FC vs Daegu FC</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC</t>
+          <t>Hwaseong FC</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Daegu FC</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>0x1482cd21984a144c2f6033821f76b4033b1aeaebbab5c85a758b2e86c0553134</t>
+          <t>0xda1e33e5fc880742964769df06cb9c83769ec80d9cb168728d3a3467d0a0473b</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>L19306783</t>
+          <t>L19382332</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -5344,17 +5360,17 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>1785064732</t>
+          <t>1785558588</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>1785061800</t>
+          <t>1785580200</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>155.135092</t>
+          <t>12.995305</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -5371,7 +5387,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0xe74ba88448233ab30d6e4b230046fe45bf1be0a6f71b8860703364abbbb40afe</t>
+          <t>0x59cfeb6eefafd07022cdcaae7869afb45bc60deb8b4c0b4b96ad04ae8bbdb0d3</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5386,22 +5402,22 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>19.69</t>
+          <t>321.53001</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.5038</t>
+          <t>1.525</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>K2-League</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Over 1.5</t>
+          <t>Chungnam Asan FC 0</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -5411,27 +5427,27 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Paju Citizen vs Ansan Greeners</t>
+          <t>Chungnam Asan FC vs Seongnam FC</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Chungnam Asan FC</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Seongnam FC</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>0x6a23b140597c01b1670e03fdb996fc8e94424ec45a5e6e429b292ba1688dff5c</t>
+          <t>0x5d9fd67211ec6f71728981803ac86abc94216c4e6a398285b5003dabd4e5df0f</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>L19306782</t>
+          <t>L19382328</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -5456,17 +5472,17 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>1785064111</t>
+          <t>1785534316</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>1785061800</t>
+          <t>1785580200</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>39.086849</t>
+          <t>612.438114</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -5483,31 +5499,39 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0x02858e4fe5f076373faa42c17e9058ea19bff69a0b68493520c024b133c2ceed</t>
+          <t>0x57f84ab38f2e25e292c948ee169e9feff1e8436efac9878d37389052fc7a8ade</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0x0C2DA7fC8702784d6f75c78Da25460783A6709a0</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9.99999</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.4975</t>
+          <t>1.525</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr"/>
+          <t>K2-League</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Chungnam Asan FC 0</t>
+        </is>
+      </c>
       <c r="H48" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -5515,27 +5539,27 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Paju Citizen vs Ansan Greeners</t>
+          <t>Chungnam Asan FC vs Seongnam FC</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Chungnam Asan FC</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Seongnam FC</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>0x90106aa6ffeea165b450ea7a1094c65ae9db8d6fdde000ce479b4af5b3fa3072</t>
+          <t>0x5d9fd67211ec6f71728981803ac86abc94216c4e6a398285b5003dabd4e5df0f</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>L19306782</t>
+          <t>L19382328</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -5560,17 +5584,17 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>1785063804</t>
+          <t>1785534315</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>1785061800</t>
+          <t>1785580200</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>6.030151</t>
+          <t>19.0476</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -5587,12 +5611,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0xd6b44cd45d93535a9c1b39fad13245ea6ef0e5cbff858b443a9d40a281cf422f</t>
+          <t>0x4da39049a709357f30ef968bfc90b4eec2da9d99090f3b99edf4ea11aeddd708</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -5602,22 +5626,22 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>21.3</t>
+          <t>32.79</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1.2988</t>
+          <t>1.5488</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Asian Handicap (0.5)</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Over 2.5</t>
+          <t>Hwaseong FC +0.5</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -5627,27 +5651,27 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Paju Citizen vs Ansan Greeners</t>
+          <t>Hwaseong FC vs Daegu FC</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Hwaseong FC</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Daegu FC</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>0x2d5eca3e665030fe8c7c2a84772b94d8fc59c9a6991fd216ba914d3b345ffe07</t>
+          <t>0xbde5165c3a540b0c6dd64b3df320540fd10ecb173373b087359951e7f790f852</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>L19306782</t>
+          <t>L19382332</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -5672,17 +5696,17 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>1785063590</t>
+          <t>1785527084</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>1785061800</t>
+          <t>1785580200</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>71.297071</t>
+          <t>59.753986</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -5699,7 +5723,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0xc41eea20c9aa34da894372c77f23e0a6ee134568f117e95b14c294310b2dc1f7</t>
+          <t>0x07b844c409deb0bc9c8e8dbda27c7c2b772aec07892356105db79f67ffb0e227</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5707,54 +5731,46 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>12.53</t>
+          <t>6.39</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1.2037</t>
+          <t>1.5675</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>K2-League</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen FC vs Yongin City</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen FC</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
         <is>
           <t>Yongin City</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>K2-League</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>Gimpo Citizen FC vs Yongin City</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>Gimpo Citizen FC</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>Yongin City</t>
-        </is>
-      </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>0x520e073f044523b55003a1d70f752c30f91cd5ebae7e23b2f294ad6679b3ed58</t>
+          <t>0xf73fcbba4baac94056070f4c2db509913d7317940066a6918ac1f13256f52327</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -5784,7 +5800,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>1785063530</t>
+          <t>1785064787</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
@@ -5794,7 +5810,7 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>61.496933</t>
+          <t>11.259912</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -5811,54 +5827,46 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0xe5a4265d3896fe621f44bfc6c8c9d2efe8a044ac121c6a5ec411dcd8ecbb22c9</t>
+          <t>0xf95f88d59f982dc2c9ca6387361b5a066ab48deeb7f9f6071274eb879ddabdd0</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>126.4351</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1.5162</t>
+          <t>1.815</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>K2-League</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen FC vs Yongin City</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
         <is>
           <t>Gimpo Citizen FC</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>K2-League</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>Gimpo Citizen FC vs Yongin City</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>Gimpo Citizen FC</t>
-        </is>
-      </c>
       <c r="K51" t="inlineStr">
         <is>
           <t>Yongin City</t>
@@ -5866,7 +5874,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>0x2725ecc350e6d5314ddee250cd3e445f586ab55a992fc73108db0913c5a41f24</t>
+          <t>0x1482cd21984a144c2f6033821f76b4033b1aeaebbab5c85a758b2e86c0553134</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -5896,7 +5904,7 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>1785063352</t>
+          <t>1785064732</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
@@ -5906,7 +5914,7 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>1.937046</t>
+          <t>155.135092</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -5923,7 +5931,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0x996289847910ea662fcd868b20c9fa48f68ab4d7334bac4351bc46b6d3f479df</t>
+          <t>0xe74ba88448233ab30d6e4b230046fe45bf1be0a6f71b8860703364abbbb40afe</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5938,22 +5946,22 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>19.69</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1.5162</t>
+          <t>1.5038</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC</t>
+          <t>Over 1.5</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -5963,27 +5971,27 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC vs Yongin City</t>
+          <t>Paju Citizen vs Ansan Greeners</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>0x2725ecc350e6d5314ddee250cd3e445f586ab55a992fc73108db0913c5a41f24</t>
+          <t>0x6a23b140597c01b1670e03fdb996fc8e94424ec45a5e6e429b292ba1688dff5c</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>L19306783</t>
+          <t>L19306782</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -6008,7 +6016,7 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>1785063326</t>
+          <t>1785064111</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
@@ -6018,7 +6026,7 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>1.937046</t>
+          <t>39.086849</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -6035,27 +6043,23 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0xed44d31e5a5b7071006924700a0078a2f8a3710d9bb8d24217652d198ffae7d7</t>
+          <t>0x02858e4fe5f076373faa42c17e9058ea19bff69a0b68493520c024b133c2ceed</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x0C2DA7fC8702784d6f75c78Da25460783A6709a0</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
-          <t>28.84</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1.5162</t>
+          <t>1.4975</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -6063,11 +6067,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>Gimpo Citizen FC</t>
-        </is>
-      </c>
+      <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -6075,27 +6075,27 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC vs Yongin City</t>
+          <t>Paju Citizen vs Ansan Greeners</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>0x2725ecc350e6d5314ddee250cd3e445f586ab55a992fc73108db0913c5a41f24</t>
+          <t>0x90106aa6ffeea165b450ea7a1094c65ae9db8d6fdde000ce479b4af5b3fa3072</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>L19306783</t>
+          <t>L19306782</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -6120,7 +6120,7 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>1785063319</t>
+          <t>1785063804</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>55.864407</t>
+          <t>6.030151</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -6147,7 +6147,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0x2bcba69d716b343c190b4a215a8f323f4abe23b13cd57d716f1b386e77406d71</t>
+          <t>0xd6b44cd45d93535a9c1b39fad13245ea6ef0e5cbff858b443a9d40a281cf422f</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -6155,23 +6155,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr"/>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>21.3</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1.3912</t>
+          <t>1.2988</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr"/>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
       <c r="H54" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -6179,27 +6187,27 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC vs Yongin City</t>
+          <t>Paju Citizen vs Ansan Greeners</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>0xf73fcbba4baac94056070f4c2db509913d7317940066a6918ac1f13256f52327</t>
+          <t>0x2d5eca3e665030fe8c7c2a84772b94d8fc59c9a6991fd216ba914d3b345ffe07</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>L19306783</t>
+          <t>L19306782</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -6224,7 +6232,7 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>1785063319</t>
+          <t>1785063590</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
@@ -6234,7 +6242,7 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>6.696486</t>
+          <t>71.297071</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -6251,7 +6259,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0x74897816645fe410040b71368723e823f96b8b8ad1a8558a60563ea6a63c17b9</t>
+          <t>0xc41eea20c9aa34da894372c77f23e0a6ee134568f117e95b14c294310b2dc1f7</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6266,12 +6274,12 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12.53</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1.5488</t>
+          <t>1.2037</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -6281,7 +6289,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -6291,27 +6299,27 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Paju Citizen vs Ansan Greeners</t>
+          <t>Gimpo Citizen FC vs Yongin City</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Gimpo Citizen FC</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>0x90106aa6ffeea165b450ea7a1094c65ae9db8d6fdde000ce479b4af5b3fa3072</t>
+          <t>0x520e073f044523b55003a1d70f752c30f91cd5ebae7e23b2f294ad6679b3ed58</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>L19306782</t>
+          <t>L19306783</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -6336,7 +6344,7 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>1785063283</t>
+          <t>1785063530</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
@@ -6346,7 +6354,7 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>18.223235</t>
+          <t>61.496933</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -6363,7 +6371,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0x6c9b96e6ea55e8d6386264e63d154ad9cdf850c8f9c18b5c088abdcfcc710e8d</t>
+          <t>0xe5a4265d3896fe621f44bfc6c8c9d2efe8a044ac121c6a5ec411dcd8ecbb22c9</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6371,15 +6379,19 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr"/>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>1.74999</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1.8313</t>
+          <t>1.5162</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -6387,7 +6399,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen FC</t>
+        </is>
+      </c>
       <c r="H56" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -6395,27 +6411,27 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Paju Citizen vs Ansan Greeners</t>
+          <t>Gimpo Citizen FC vs Yongin City</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Gimpo Citizen FC</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>0x6de105784818e175bb2cb50f54d4325a684a5693a05f8bd5b7f2b402aeb4bdfa</t>
+          <t>0x2725ecc350e6d5314ddee250cd3e445f586ab55a992fc73108db0913c5a41f24</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>L19306782</t>
+          <t>L19306783</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -6440,7 +6456,7 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>1785063278</t>
+          <t>1785063352</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
@@ -6450,7 +6466,7 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>2.105251</t>
+          <t>1.937046</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -6467,7 +6483,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0x653ed25ca6aba498efe0c95f6d394f607985bf6c4ab830c3599772279631e8b1</t>
+          <t>0x996289847910ea662fcd868b20c9fa48f68ab4d7334bac4351bc46b6d3f479df</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6475,15 +6491,19 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr"/>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>201.32998</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>1.8213</t>
+          <t>1.5162</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -6491,7 +6511,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen FC</t>
+        </is>
+      </c>
       <c r="H57" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -6499,27 +6523,27 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Paju Citizen vs Ansan Greeners</t>
+          <t>Gimpo Citizen FC vs Yongin City</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Gimpo Citizen FC</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>0x6de105784818e175bb2cb50f54d4325a684a5693a05f8bd5b7f2b402aeb4bdfa</t>
+          <t>0x2725ecc350e6d5314ddee250cd3e445f586ab55a992fc73108db0913c5a41f24</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>L19306782</t>
+          <t>L19306783</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -6544,7 +6568,7 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>1785063071</t>
+          <t>1785063326</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
@@ -6554,7 +6578,7 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>245.150661</t>
+          <t>1.937046</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -6571,23 +6595,27 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0xd7beeace3688b4d75f908058620cd47f10d9926e086901a2c83333dd169ec720</t>
+          <t>0xed44d31e5a5b7071006924700a0078a2f8a3710d9bb8d24217652d198ffae7d7</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>48.03</t>
+          <t>28.84</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.5162</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -6595,7 +6623,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen FC</t>
+        </is>
+      </c>
       <c r="H58" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -6648,7 +6680,7 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>1785062970</t>
+          <t>1785063319</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
@@ -6658,7 +6690,7 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>98.020408</t>
+          <t>55.864407</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
@@ -6675,7 +6707,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0x8940d52e7feb848f5ca44e42ecc2fed94e942961b918122bc87142ffbf346d4c</t>
+          <t>0x2bcba69d716b343c190b4a215a8f323f4abe23b13cd57d716f1b386e77406d71</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6686,17 +6718,17 @@
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
-          <t>196.03997</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>1.8188</t>
+          <t>1.3912</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G59" t="inlineStr"/>
@@ -6707,27 +6739,27 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Paju Citizen vs Ansan Greeners</t>
+          <t>Gimpo Citizen FC vs Yongin City</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Gimpo Citizen FC</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>0x6de105784818e175bb2cb50f54d4325a684a5693a05f8bd5b7f2b402aeb4bdfa</t>
+          <t>0xf73fcbba4baac94056070f4c2db509913d7317940066a6918ac1f13256f52327</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>L19306782</t>
+          <t>L19306783</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -6752,7 +6784,7 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>1785062953</t>
+          <t>1785063319</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
@@ -6762,7 +6794,7 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>239.438131</t>
+          <t>6.696486</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
@@ -6779,7 +6811,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0x2b9441f7515eb95a00a5708be64644050b069886b2e84d77ecdeea72fe8e3da7</t>
+          <t>0x74897816645fe410040b71368723e823f96b8b8ad1a8558a60563ea6a63c17b9</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6794,12 +6826,12 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>12.06</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>1.1975</t>
+          <t>1.5488</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -6809,7 +6841,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -6819,27 +6851,27 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC vs Yongin City</t>
+          <t>Paju Citizen vs Ansan Greeners</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>0x520e073f044523b55003a1d70f752c30f91cd5ebae7e23b2f294ad6679b3ed58</t>
+          <t>0x90106aa6ffeea165b450ea7a1094c65ae9db8d6fdde000ce479b4af5b3fa3072</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>L19306783</t>
+          <t>L19306782</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -6864,7 +6896,7 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>1785062934</t>
+          <t>1785063283</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
@@ -6874,7 +6906,7 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>61.063291</t>
+          <t>18.223235</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
@@ -6891,7 +6923,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0x17ea9fc34d8d08859197baf8694510eafd385c5cb30d1bccaf4135418710a4ee</t>
+          <t>0x6c9b96e6ea55e8d6386264e63d154ad9cdf850c8f9c18b5c088abdcfcc710e8d</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6899,31 +6931,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1.74999</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>1.3862</t>
+          <t>1.8313</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>Over 2.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -6946,7 +6970,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>0x2d5eca3e665030fe8c7c2a84772b94d8fc59c9a6991fd216ba914d3b345ffe07</t>
+          <t>0x6de105784818e175bb2cb50f54d4325a684a5693a05f8bd5b7f2b402aeb4bdfa</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -6976,7 +7000,7 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>1785062748</t>
+          <t>1785063278</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
@@ -6986,7 +7010,7 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>25.889968</t>
+          <t>2.105251</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
@@ -7003,7 +7027,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0xff313e8a80cab759f0306eced2743a83b68017dd8ecc4a5eda49613abd5f72bb</t>
+          <t>0x653ed25ca6aba498efe0c95f6d394f607985bf6c4ab830c3599772279631e8b1</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -7011,31 +7035,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>201.32998</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>1.2275</t>
+          <t>1.8213</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>Over 3.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -7058,7 +7074,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>0x20fab15d1baac82bbe5a9371ad4e1e4f931edb8de76d814e671a0313aa4d8620</t>
+          <t>0x6de105784818e175bb2cb50f54d4325a684a5693a05f8bd5b7f2b402aeb4bdfa</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -7088,7 +7104,7 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>1785062437</t>
+          <t>1785063071</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
@@ -7098,7 +7114,7 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>43.956044</t>
+          <t>245.150661</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
@@ -7115,23 +7131,23 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0x5a88256e6b892595ad641ef1ae589c088b32b6034ec557ba72582fa8c93f67e3</t>
+          <t>0xd7beeace3688b4d75f908058620cd47f10d9926e086901a2c83333dd169ec720</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr">
         <is>
-          <t>64.98999</t>
+          <t>48.03</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>1.8125</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -7147,27 +7163,27 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Paju Citizen vs Ansan Greeners</t>
+          <t>Gimpo Citizen FC vs Yongin City</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Gimpo Citizen FC</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>0x6de105784818e175bb2cb50f54d4325a684a5693a05f8bd5b7f2b402aeb4bdfa</t>
+          <t>0x2725ecc350e6d5314ddee250cd3e445f586ab55a992fc73108db0913c5a41f24</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>L19306782</t>
+          <t>L19306783</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -7192,7 +7208,7 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>1785062111</t>
+          <t>1785062970</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
@@ -7202,7 +7218,7 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>79.98768</t>
+          <t>98.020408</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
@@ -7219,39 +7235,31 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0x21aa47ce5d327006a8fdcf609e5990b1ea5499887fd8ccd0ff96d5bbe7df2f89</t>
+          <t>0x8940d52e7feb848f5ca44e42ecc2fed94e942961b918122bc87142ffbf346d4c</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr">
         <is>
-          <t>23.39</t>
+          <t>196.03997</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>1.3887</t>
+          <t>1.8188</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>Paju Citizen -1</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -7274,7 +7282,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>0x1398d7baccf6c5154c8090892c6597852ff56e90298e81fb604a8b9bf22c47ce</t>
+          <t>0x6de105784818e175bb2cb50f54d4325a684a5693a05f8bd5b7f2b402aeb4bdfa</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -7304,7 +7312,7 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>1785061695</t>
+          <t>1785062953</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
@@ -7314,7 +7322,7 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>60.167203</t>
+          <t>239.438131</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
@@ -7331,12 +7339,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0xaa13e9d13e81cd9edae13a80c0e426e52c85c5064c5b0c34d792d027f33fe560</t>
+          <t>0x2b9441f7515eb95a00a5708be64644050b069886b2e84d77ecdeea72fe8e3da7</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -7346,22 +7354,22 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>17.04</t>
+          <t>12.06</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.1975</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Paju Citizen -1.5</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -7371,27 +7379,27 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Paju Citizen vs Ansan Greeners</t>
+          <t>Gimpo Citizen FC vs Yongin City</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Gimpo Citizen FC</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>0x48cd5a7ee72c95f57110826c0f2e2494d9438250815f7751e5e0fdce91ccbfba</t>
+          <t>0x520e073f044523b55003a1d70f752c30f91cd5ebae7e23b2f294ad6679b3ed58</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>L19306782</t>
+          <t>L19306783</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -7416,7 +7424,7 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>1785061694</t>
+          <t>1785062934</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
@@ -7426,7 +7434,7 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>58.758621</t>
+          <t>61.063291</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
@@ -7443,31 +7451,39 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0x9c2da91ae7561670702979941233734bebc22c36fdac867bf5bdb53a8151c6e9</t>
+          <t>0x17ea9fc34d8d08859197baf8694510eafd385c5cb30d1bccaf4135418710a4ee</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>4.99997</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>1.795</t>
+          <t>1.3862</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr"/>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
       <c r="H66" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -7475,27 +7491,27 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC vs Yongin City</t>
+          <t>Paju Citizen vs Ansan Greeners</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>0x520e073f044523b55003a1d70f752c30f91cd5ebae7e23b2f294ad6679b3ed58</t>
+          <t>0x2d5eca3e665030fe8c7c2a84772b94d8fc59c9a6991fd216ba914d3b345ffe07</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>L19306783</t>
+          <t>L19306782</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -7520,7 +7536,7 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>1785061651</t>
+          <t>1785062748</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
@@ -7530,7 +7546,7 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>6.28927</t>
+          <t>25.889968</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
@@ -7547,12 +7563,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0x12f98497a1f2dc0a130b32665dfeea9bbd9b744c2732456c77c91801ec687167</t>
+          <t>0xff313e8a80cab759f0306eced2743a83b68017dd8ecc4a5eda49613abd5f72bb</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -7562,22 +7578,22 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>21.14</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>1.3513</t>
+          <t>1.2275</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC -1</t>
+          <t>Over 3.5</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -7587,27 +7603,27 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC vs Yongin City</t>
+          <t>Paju Citizen vs Ansan Greeners</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>0x4a4b2cf0de4356e1be221d31aa0feab4af681e89956037ff111c72307c4d9af6</t>
+          <t>0x20fab15d1baac82bbe5a9371ad4e1e4f931edb8de76d814e671a0313aa4d8620</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>L19306783</t>
+          <t>L19306782</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -7632,7 +7648,7 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>1785061621</t>
+          <t>1785062437</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
@@ -7642,7 +7658,7 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>60.185053</t>
+          <t>43.956044</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
@@ -7659,23 +7675,23 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0x0f90aefde05859a865353743603e3925fef0a390e252c71ca62de94b7f3522d8</t>
+          <t>0x5a88256e6b892595ad641ef1ae589c088b32b6034ec557ba72582fa8c93f67e3</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr">
         <is>
-          <t>43.51167</t>
+          <t>64.98999</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>1.795</t>
+          <t>1.8125</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -7691,27 +7707,27 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC vs Yongin City</t>
+          <t>Paju Citizen vs Ansan Greeners</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>0x520e073f044523b55003a1d70f752c30f91cd5ebae7e23b2f294ad6679b3ed58</t>
+          <t>0x6de105784818e175bb2cb50f54d4325a684a5693a05f8bd5b7f2b402aeb4bdfa</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>L19306783</t>
+          <t>L19306782</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -7736,7 +7752,7 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>1785061621</t>
+          <t>1785062111</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
@@ -7746,7 +7762,7 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>54.73166</t>
+          <t>79.98768</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
@@ -7763,31 +7779,39 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0x45f1170f51d54ba31ead65b241ce33b618358dd91421e9194877f824ebea4f5d</t>
+          <t>0x21aa47ce5d327006a8fdcf609e5990b1ea5499887fd8ccd0ff96d5bbe7df2f89</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0x09b3a190a1e971Dd0B4F82Eb9008287fe43a540C</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23.39</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.3887</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr"/>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Paju Citizen -1</t>
+        </is>
+      </c>
       <c r="H69" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -7795,27 +7819,27 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC vs Yongin City</t>
+          <t>Paju Citizen vs Ansan Greeners</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>0x7b353104df193f280c01b3e0a75dcbbc5dd4e628b7304c3537dff2339968d702</t>
+          <t>0x1398d7baccf6c5154c8090892c6597852ff56e90298e81fb604a8b9bf22c47ce</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>L19306783</t>
+          <t>L19306782</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -7840,7 +7864,7 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>1785061583</t>
+          <t>1785061695</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
@@ -7850,7 +7874,7 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>51.020408</t>
+          <t>60.167203</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
@@ -7867,31 +7891,39 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0x8726e3d54f033c4394f3b9a8a297c466f26e8d1814d525163146dc1f9f836029</t>
+          <t>0xaa13e9d13e81cd9edae13a80c0e426e52c85c5064c5b0c34d792d027f33fe560</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>5.70997</t>
+          <t>17.04</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>1.795</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr"/>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Paju Citizen -1.5</t>
+        </is>
+      </c>
       <c r="H70" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -7899,27 +7931,27 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC vs Yongin City</t>
+          <t>Paju Citizen vs Ansan Greeners</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>0x520e073f044523b55003a1d70f752c30f91cd5ebae7e23b2f294ad6679b3ed58</t>
+          <t>0x48cd5a7ee72c95f57110826c0f2e2494d9438250815f7751e5e0fdce91ccbfba</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>L19306783</t>
+          <t>L19306782</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -7944,7 +7976,7 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>1785061581</t>
+          <t>1785061694</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
@@ -7954,7 +7986,7 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>7.182352</t>
+          <t>58.758621</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
@@ -7971,27 +8003,23 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0x78b589b7ea305b8a325e286dcbf526301e19f803d90ab77960c290d1d621d34a</t>
+          <t>0x9c2da91ae7561670702979941233734bebc22c36fdac867bf5bdb53a8151c6e9</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0x09b3a190a1e971Dd0B4F82Eb9008287fe43a540C</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr">
         <is>
-          <t>5.01384</t>
+          <t>4.99997</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>1.2788</t>
+          <t>1.795</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -7999,11 +8027,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -8026,7 +8050,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>0xf93dab40773f0e01839824957e7cecd4afb676d72a13c45521719f4f5c517a27</t>
+          <t>0x520e073f044523b55003a1d70f752c30f91cd5ebae7e23b2f294ad6679b3ed58</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -8056,7 +8080,7 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>1785061533</t>
+          <t>1785061651</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
@@ -8066,7 +8090,7 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>17.98687</t>
+          <t>6.28927</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
@@ -8083,31 +8107,39 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0x64d493da52ab9f3215f2ee6a066aad2cbaf66597963522c2c53462ae6d466e65</t>
+          <t>0x12f98497a1f2dc0a130b32665dfeea9bbd9b744c2732456c77c91801ec687167</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>43.87998</t>
+          <t>21.14</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>1.7988</t>
+          <t>1.3513</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr"/>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen FC -1</t>
+        </is>
+      </c>
       <c r="H72" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -8130,7 +8162,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>0x520e073f044523b55003a1d70f752c30f91cd5ebae7e23b2f294ad6679b3ed58</t>
+          <t>0x4a4b2cf0de4356e1be221d31aa0feab4af681e89956037ff111c72307c4d9af6</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -8160,7 +8192,7 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>1785061346</t>
+          <t>1785061621</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
@@ -8170,7 +8202,7 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>54.935812</t>
+          <t>60.185053</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
@@ -8187,23 +8219,23 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0xb6a5b0e5cc84223b1b456506ce5bc4a60492c7d715d16ce5ba4bcbbbb205e549</t>
+          <t>0x0f90aefde05859a865353743603e3925fef0a390e252c71ca62de94b7f3522d8</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr">
         <is>
-          <t>10.19999</t>
+          <t>43.51167</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>1.7988</t>
+          <t>1.795</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -8264,7 +8296,7 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>1785061261</t>
+          <t>1785061621</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
@@ -8274,7 +8306,7 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>12.769941</t>
+          <t>54.73166</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
@@ -8291,28 +8323,28 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0x932ea4448a5d14be89226effb4bcb8584e5004da981b9fb12e769029a2cd6a34</t>
+          <t>0x45f1170f51d54ba31ead65b241ce33b618358dd91421e9194877f824ebea4f5d</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0x09b3a190a1e971Dd0B4F82Eb9008287fe43a540C</t>
         </is>
       </c>
       <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>25</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>1.7988</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G74" t="inlineStr"/>
@@ -8338,7 +8370,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>0x520e073f044523b55003a1d70f752c30f91cd5ebae7e23b2f294ad6679b3ed58</t>
+          <t>0x7b353104df193f280c01b3e0a75dcbbc5dd4e628b7304c3537dff2339968d702</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -8368,7 +8400,7 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>1785061250</t>
+          <t>1785061583</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
@@ -8378,7 +8410,7 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>6.259781</t>
+          <t>51.020408</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
@@ -8395,23 +8427,23 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0x6ba96fe1be95723f4530ab62caaff2817e70e2c1aa504d2f0afe5b7d44447528</t>
+          <t>0x8726e3d54f033c4394f3b9a8a297c466f26e8d1814d525163146dc1f9f836029</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr">
         <is>
-          <t>43.12404</t>
+          <t>5.70997</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>1.7975</t>
+          <t>1.795</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -8472,7 +8504,7 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>1785061221</t>
+          <t>1785061581</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
@@ -8482,7 +8514,7 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>54.074031</t>
+          <t>7.182352</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
@@ -8499,12 +8531,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0xa4c5cc7d130116507c7f97158d19bded9ace84b90e4089b2386235aca563a109</t>
+          <t>0x78b589b7ea305b8a325e286dcbf526301e19f803d90ab77960c290d1d621d34a</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x09b3a190a1e971Dd0B4F82Eb9008287fe43a540C</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -8514,12 +8546,12 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>5.54</t>
+          <t>5.01384</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>1.2537</t>
+          <t>1.2788</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -8539,27 +8571,27 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Paju Citizen vs Ansan Greeners</t>
+          <t>Gimpo Citizen FC vs Yongin City</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Gimpo Citizen FC</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>0xabfa364122222118f5f35af9ee862e2b9587e9c2f656e281725fdca100cf17bf</t>
+          <t>0xf93dab40773f0e01839824957e7cecd4afb676d72a13c45521719f4f5c517a27</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>L19306782</t>
+          <t>L19306783</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -8584,7 +8616,7 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>1785060618</t>
+          <t>1785061533</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
@@ -8594,7 +8626,7 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>21.832512</t>
+          <t>17.98687</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
@@ -8611,23 +8643,23 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0xed6f77aaa7a7dbe5c2457f000b022f2da0cc5bd1004291d76e71044f4e1faa36</t>
+          <t>0x64d493da52ab9f3215f2ee6a066aad2cbaf66597963522c2c53462ae6d466e65</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr">
         <is>
-          <t>4.99999</t>
+          <t>43.87998</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>1.7975</t>
+          <t>1.7988</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -8688,7 +8720,7 @@
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>1785060105</t>
+          <t>1785061346</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
@@ -8698,7 +8730,7 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>6.26958</t>
+          <t>54.935812</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
@@ -8715,23 +8747,23 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0xe0d4aa08492162b980b70ecc4ec3e9ae46b9fd85fea771f538c542e4e27f10ca</t>
+          <t>0xb6a5b0e5cc84223b1b456506ce5bc4a60492c7d715d16ce5ba4bcbbbb205e549</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr">
         <is>
-          <t>4.99999</t>
+          <t>10.19999</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>1.7975</t>
+          <t>1.7988</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -8792,7 +8824,7 @@
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>1785060103</t>
+          <t>1785061261</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
@@ -8802,7 +8834,7 @@
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>6.26958</t>
+          <t>12.769941</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
@@ -8819,7 +8851,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0x733bd5ce99f877eba370291936b138251c1bd48cee90480bc876f49523ca7fca</t>
+          <t>0x932ea4448a5d14be89226effb4bcb8584e5004da981b9fb12e769029a2cd6a34</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -8830,12 +8862,12 @@
       <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr">
         <is>
-          <t>4.99999</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>1.7975</t>
+          <t>1.7988</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -8896,7 +8928,7 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>1785060101</t>
+          <t>1785061250</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
@@ -8906,7 +8938,7 @@
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>6.26958</t>
+          <t>6.259781</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
@@ -8923,39 +8955,31 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0xcfbe574677265ef97dc3204a001ce1b1e25523c8a98c296a3cf235f97650aace</t>
+          <t>0x6ba96fe1be95723f4530ab62caaff2817e70e2c1aa504d2f0afe5b7d44447528</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>43.12404</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>1.3887</t>
+          <t>1.7975</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>Paju Citizen -1</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -8963,27 +8987,27 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Paju Citizen vs Ansan Greeners</t>
+          <t>Gimpo Citizen FC vs Yongin City</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Gimpo Citizen FC</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>0x1398d7baccf6c5154c8090892c6597852ff56e90298e81fb604a8b9bf22c47ce</t>
+          <t>0x520e073f044523b55003a1d70f752c30f91cd5ebae7e23b2f294ad6679b3ed58</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>L19306782</t>
+          <t>L19306783</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -9008,7 +9032,7 @@
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>1785060085</t>
+          <t>1785061221</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
@@ -9018,7 +9042,7 @@
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>10.289389</t>
+          <t>54.074031</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
@@ -9035,23 +9059,27 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0xebd1df0aa7e7f54677bedd84a6c923ca856cf657e0531639938bfb8111becc94</t>
+          <t>0xa4c5cc7d130116507c7f97158d19bded9ace84b90e4089b2386235aca563a109</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>22.97198</t>
+          <t>5.54</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>1.7963</t>
+          <t>1.2537</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -9059,7 +9087,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H81" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -9067,27 +9099,27 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC vs Yongin City</t>
+          <t>Paju Citizen vs Ansan Greeners</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>0x520e073f044523b55003a1d70f752c30f91cd5ebae7e23b2f294ad6679b3ed58</t>
+          <t>0xabfa364122222118f5f35af9ee862e2b9587e9c2f656e281725fdca100cf17bf</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>L19306783</t>
+          <t>L19306782</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -9112,7 +9144,7 @@
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>1785060074</t>
+          <t>1785060618</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">
@@ -9122,7 +9154,7 @@
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>28.85021</t>
+          <t>21.832512</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
@@ -9139,23 +9171,23 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0x9137623e3c72596dddeb8dd77deb26f0f80f5d8ad5037c9d9fd9ec11f1d3a62d</t>
+          <t>0xed6f77aaa7a7dbe5c2457f000b022f2da0cc5bd1004291d76e71044f4e1faa36</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr">
         <is>
-          <t>15.59279</t>
+          <t>4.99999</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>1.7963</t>
+          <t>1.7975</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -9216,7 +9248,7 @@
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>1785060073</t>
+          <t>1785060105</t>
         </is>
       </c>
       <c r="S82" t="inlineStr">
@@ -9226,7 +9258,7 @@
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>19.582782</t>
+          <t>6.26958</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
@@ -9243,23 +9275,23 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0x47fecae2c93459e7d6a1189dcb95e8bce239b7e2d26ce67db4733b564451a3fd</t>
+          <t>0xe0d4aa08492162b980b70ecc4ec3e9ae46b9fd85fea771f538c542e4e27f10ca</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr">
         <is>
-          <t>16.1469</t>
+          <t>4.99999</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>1.7963</t>
+          <t>1.7975</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -9320,7 +9352,7 @@
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>1785060072</t>
+          <t>1785060103</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
@@ -9330,7 +9362,7 @@
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>20.278681</t>
+          <t>6.26958</t>
         </is>
       </c>
       <c r="U83" t="inlineStr">
@@ -9347,27 +9379,23 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0x7851323bb653ef81f86e4483a09baec3f52472a947788d079eacebc8ce474280</t>
+          <t>0x733bd5ce99f877eba370291936b138251c1bd48cee90480bc876f49523ca7fca</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr">
         <is>
-          <t>19.02</t>
+          <t>4.99999</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>1.275</t>
+          <t>1.7975</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -9375,11 +9403,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G84" t="inlineStr"/>
       <c r="H84" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -9402,7 +9426,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>0xf93dab40773f0e01839824957e7cecd4afb676d72a13c45521719f4f5c517a27</t>
+          <t>0x520e073f044523b55003a1d70f752c30f91cd5ebae7e23b2f294ad6679b3ed58</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -9432,7 +9456,7 @@
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>1785060054</t>
+          <t>1785060101</t>
         </is>
       </c>
       <c r="S84" t="inlineStr">
@@ -9442,7 +9466,7 @@
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>69.163636</t>
+          <t>6.26958</t>
         </is>
       </c>
       <c r="U84" t="inlineStr">
@@ -9459,7 +9483,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0x5936a0069456d68663344829a3e2e9aa688da6a9e1d38de76848d1bdfb84366a</t>
+          <t>0xcfbe574677265ef97dc3204a001ce1b1e25523c8a98c296a3cf235f97650aace</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -9474,22 +9498,22 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>10.56</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>1.2737</t>
+          <t>1.3887</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Paju Citizen -1</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -9499,27 +9523,27 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC vs Yongin City</t>
+          <t>Paju Citizen vs Ansan Greeners</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>0xf93dab40773f0e01839824957e7cecd4afb676d72a13c45521719f4f5c517a27</t>
+          <t>0x1398d7baccf6c5154c8090892c6597852ff56e90298e81fb604a8b9bf22c47ce</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>L19306783</t>
+          <t>L19306782</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -9544,7 +9568,7 @@
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>1785060044</t>
+          <t>1785060085</t>
         </is>
       </c>
       <c r="S85" t="inlineStr">
@@ -9554,7 +9578,7 @@
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>38.575342</t>
+          <t>10.289389</t>
         </is>
       </c>
       <c r="U85" t="inlineStr">
@@ -9571,7 +9595,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>0xc27dc932de76aa5047aab63fd483f2351fd3e777a4bebc494353cf3a53c52ba9</t>
+          <t>0xebd1df0aa7e7f54677bedd84a6c923ca856cf657e0531639938bfb8111becc94</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -9582,17 +9606,17 @@
       <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr">
         <is>
-          <t>20.61772</t>
+          <t>22.97198</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>1.3425</t>
+          <t>1.7963</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G86" t="inlineStr"/>
@@ -9603,27 +9627,27 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Paju Citizen vs Ansan Greeners</t>
+          <t>Gimpo Citizen FC vs Yongin City</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Gimpo Citizen FC</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>0x386468865ee4fb2d064354b0f4bb50fc57a8f046452fa6667bc56978f4cf3823</t>
+          <t>0x520e073f044523b55003a1d70f752c30f91cd5ebae7e23b2f294ad6679b3ed58</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>L19306782</t>
+          <t>L19306783</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -9648,7 +9672,7 @@
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>1785059855</t>
+          <t>1785060074</t>
         </is>
       </c>
       <c r="S86" t="inlineStr">
@@ -9658,7 +9682,7 @@
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>60.197723</t>
+          <t>28.85021</t>
         </is>
       </c>
       <c r="U86" t="inlineStr">
@@ -9675,7 +9699,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>0x06cf39065296686830cf556b4943f2a94e035610868690980b237da489f6c32a</t>
+          <t>0x9137623e3c72596dddeb8dd77deb26f0f80f5d8ad5037c9d9fd9ec11f1d3a62d</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -9683,31 +9707,23 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr">
         <is>
-          <t>4.94155</t>
+          <t>15.59279</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>1.355</t>
+          <t>1.7963</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>Gimpo Citizen FC -1</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -9730,7 +9746,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>0x4a4b2cf0de4356e1be221d31aa0feab4af681e89956037ff111c72307c4d9af6</t>
+          <t>0x520e073f044523b55003a1d70f752c30f91cd5ebae7e23b2f294ad6679b3ed58</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
@@ -9760,7 +9776,7 @@
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>1785059821</t>
+          <t>1785060073</t>
         </is>
       </c>
       <c r="S87" t="inlineStr">
@@ -9770,7 +9786,7 @@
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>13.919859</t>
+          <t>19.582782</t>
         </is>
       </c>
       <c r="U87" t="inlineStr">
@@ -9787,7 +9803,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>0x6cad572e295e86d0eff792e6a73f1ecb4b2563c632f3a61d710a79a81bcbefc5</t>
+          <t>0x47fecae2c93459e7d6a1189dcb95e8bce239b7e2d26ce67db4733b564451a3fd</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -9795,31 +9811,23 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr">
         <is>
-          <t>16.43</t>
+          <t>16.1469</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>1.355</t>
+          <t>1.7963</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>Gimpo Citizen FC -1</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -9842,7 +9850,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>0x4a4b2cf0de4356e1be221d31aa0feab4af681e89956037ff111c72307c4d9af6</t>
+          <t>0x520e073f044523b55003a1d70f752c30f91cd5ebae7e23b2f294ad6679b3ed58</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
@@ -9872,7 +9880,7 @@
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>1785059820</t>
+          <t>1785060072</t>
         </is>
       </c>
       <c r="S88" t="inlineStr">
@@ -9882,7 +9890,7 @@
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>46.28169</t>
+          <t>20.278681</t>
         </is>
       </c>
       <c r="U88" t="inlineStr">
@@ -9899,7 +9907,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>0xd90cf2f29f54991a5ee8c926cce019177b5bb5fd98602218fb9acaaf6a910664</t>
+          <t>0x7851323bb653ef81f86e4483a09baec3f52472a947788d079eacebc8ce474280</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -9907,15 +9915,19 @@
           <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr"/>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>19.02</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>1.4675</t>
+          <t>1.275</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -9923,7 +9935,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr"/>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H89" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -9931,27 +9947,27 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Paju Citizen vs Ansan Greeners</t>
+          <t>Gimpo Citizen FC vs Yongin City</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Gimpo Citizen FC</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>0x90106aa6ffeea165b450ea7a1094c65ae9db8d6fdde000ce479b4af5b3fa3072</t>
+          <t>0xf93dab40773f0e01839824957e7cecd4afb676d72a13c45521719f4f5c517a27</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>L19306782</t>
+          <t>L19306783</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -9976,7 +9992,7 @@
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>1785058466</t>
+          <t>1785060054</t>
         </is>
       </c>
       <c r="S89" t="inlineStr">
@@ -9986,7 +10002,7 @@
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t>23.529412</t>
+          <t>69.163636</t>
         </is>
       </c>
       <c r="U89" t="inlineStr">
@@ -10003,7 +10019,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>0xfaacadf40a626e2b5b306c37ecce7325e0fabbb091c125c037dd14587c31bfe4</t>
+          <t>0x5936a0069456d68663344829a3e2e9aa688da6a9e1d38de76848d1bdfb84366a</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -10018,12 +10034,12 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>4.53</t>
+          <t>10.56</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>1.5212</t>
+          <t>1.2737</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -10033,24 +10049,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>K2-League</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen FC vs Yongin City</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
           <t>Gimpo Citizen FC</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>K2-League</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>Gimpo Citizen FC vs Yongin City</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>Gimpo Citizen FC</t>
-        </is>
-      </c>
       <c r="K90" t="inlineStr">
         <is>
           <t>Yongin City</t>
@@ -10058,7 +10074,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>0x2725ecc350e6d5314ddee250cd3e445f586ab55a992fc73108db0913c5a41f24</t>
+          <t>0xf93dab40773f0e01839824957e7cecd4afb676d72a13c45521719f4f5c517a27</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -10088,7 +10104,7 @@
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>1785057353</t>
+          <t>1785060044</t>
         </is>
       </c>
       <c r="S90" t="inlineStr">
@@ -10098,7 +10114,7 @@
       </c>
       <c r="T90" t="inlineStr">
         <is>
-          <t>8.690647</t>
+          <t>38.575342</t>
         </is>
       </c>
       <c r="U90" t="inlineStr">
@@ -10115,39 +10131,31 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>0x182964c6008d5b7d29731fd19876092a52fa2068fcb16aaf430dd8e0a6009721</t>
+          <t>0xc27dc932de76aa5047aab63fd483f2351fd3e777a4bebc494353cf3a53c52ba9</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr"/>
       <c r="D91" t="inlineStr">
         <is>
-          <t>3.73</t>
+          <t>20.61772</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>1.2763</t>
+          <t>1.3425</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -10155,27 +10163,27 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC vs Yongin City</t>
+          <t>Paju Citizen vs Ansan Greeners</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>0xf93dab40773f0e01839824957e7cecd4afb676d72a13c45521719f4f5c517a27</t>
+          <t>0x386468865ee4fb2d064354b0f4bb50fc57a8f046452fa6667bc56978f4cf3823</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>L19306783</t>
+          <t>L19306782</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
@@ -10200,7 +10208,7 @@
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>1785057212</t>
+          <t>1785059855</t>
         </is>
       </c>
       <c r="S91" t="inlineStr">
@@ -10210,7 +10218,7 @@
       </c>
       <c r="T91" t="inlineStr">
         <is>
-          <t>13.502262</t>
+          <t>60.197723</t>
         </is>
       </c>
       <c r="U91" t="inlineStr">
@@ -10227,12 +10235,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>0xae029509b64a4e0489363d3aa1a7e18db0cd21b4fb65f5064e49185bb4bfb2f6</t>
+          <t>0x06cf39065296686830cf556b4943f2a94e035610868690980b237da489f6c32a</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -10242,39 +10250,39 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.94155</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.355</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
+          <t>Gimpo Citizen FC -1</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>K2-League</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen FC vs Yongin City</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
           <t>Gimpo Citizen FC</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>K2-League</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>Gimpo Citizen FC vs Yongin City</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>Gimpo Citizen FC</t>
-        </is>
-      </c>
       <c r="K92" t="inlineStr">
         <is>
           <t>Yongin City</t>
@@ -10282,7 +10290,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>0x2725ecc350e6d5314ddee250cd3e445f586ab55a992fc73108db0913c5a41f24</t>
+          <t>0x4a4b2cf0de4356e1be221d31aa0feab4af681e89956037ff111c72307c4d9af6</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -10312,7 +10320,7 @@
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>1785056897</t>
+          <t>1785059821</t>
         </is>
       </c>
       <c r="S92" t="inlineStr">
@@ -10322,7 +10330,7 @@
       </c>
       <c r="T92" t="inlineStr">
         <is>
-          <t>9.615385</t>
+          <t>13.919859</t>
         </is>
       </c>
       <c r="U92" t="inlineStr">
@@ -10339,12 +10347,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>0xd359a1bde933becdef3ca166f20bbe9291a9b81f961befead4bc72e1713c6447</t>
+          <t>0x6cad572e295e86d0eff792e6a73f1ecb4b2563c632f3a61d710a79a81bcbefc5</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -10354,39 +10362,39 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>4.53999</t>
+          <t>16.43</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.355</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
+          <t>Gimpo Citizen FC -1</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>K2-League</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen FC vs Yongin City</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
           <t>Gimpo Citizen FC</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>K2-League</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>Gimpo Citizen FC vs Yongin City</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>Gimpo Citizen FC</t>
-        </is>
-      </c>
       <c r="K93" t="inlineStr">
         <is>
           <t>Yongin City</t>
@@ -10394,7 +10402,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>0x2725ecc350e6d5314ddee250cd3e445f586ab55a992fc73108db0913c5a41f24</t>
+          <t>0x4a4b2cf0de4356e1be221d31aa0feab4af681e89956037ff111c72307c4d9af6</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
@@ -10424,7 +10432,7 @@
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>1785056453</t>
+          <t>1785059820</t>
         </is>
       </c>
       <c r="S93" t="inlineStr">
@@ -10434,7 +10442,7 @@
       </c>
       <c r="T93" t="inlineStr">
         <is>
-          <t>8.73075</t>
+          <t>46.28169</t>
         </is>
       </c>
       <c r="U93" t="inlineStr">
@@ -10451,27 +10459,23 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>0xe5784e1cc6cec364d74a7267a701924cf5f6543fed6d0c11d5f756f735c714f2</t>
+          <t>0xd90cf2f29f54991a5ee8c926cce019177b5bb5fd98602218fb9acaaf6a910664</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr"/>
       <c r="D94" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.4675</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -10479,11 +10483,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>Gimpo Citizen FC</t>
-        </is>
-      </c>
+      <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -10491,27 +10491,27 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC vs Yongin City</t>
+          <t>Paju Citizen vs Ansan Greeners</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>0x2725ecc350e6d5314ddee250cd3e445f586ab55a992fc73108db0913c5a41f24</t>
+          <t>0x90106aa6ffeea165b450ea7a1094c65ae9db8d6fdde000ce479b4af5b3fa3072</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>L19306783</t>
+          <t>L19306782</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -10536,7 +10536,7 @@
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>1785056153</t>
+          <t>1785058466</t>
         </is>
       </c>
       <c r="S94" t="inlineStr">
@@ -10546,7 +10546,7 @@
       </c>
       <c r="T94" t="inlineStr">
         <is>
-          <t>8.75</t>
+          <t>23.529412</t>
         </is>
       </c>
       <c r="U94" t="inlineStr">
@@ -10563,7 +10563,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>0x2fe44b6f9df282a6669198530843764a881fcd8c491dca571eaacc128af126e6</t>
+          <t>0xfaacadf40a626e2b5b306c37ecce7325e0fabbb091c125c037dd14587c31bfe4</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -10578,12 +10578,12 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>9.99999</t>
+          <t>4.53</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>1.5425</t>
+          <t>1.5212</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -10593,7 +10593,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Gimpo Citizen FC</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -10603,27 +10603,27 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Paju Citizen vs Ansan Greeners</t>
+          <t>Gimpo Citizen FC vs Yongin City</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Gimpo Citizen FC</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>0x90106aa6ffeea165b450ea7a1094c65ae9db8d6fdde000ce479b4af5b3fa3072</t>
+          <t>0x2725ecc350e6d5314ddee250cd3e445f586ab55a992fc73108db0913c5a41f24</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>L19306782</t>
+          <t>L19306783</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
@@ -10648,7 +10648,7 @@
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>1785056005</t>
+          <t>1785057353</t>
         </is>
       </c>
       <c r="S95" t="inlineStr">
@@ -10658,7 +10658,7 @@
       </c>
       <c r="T95" t="inlineStr">
         <is>
-          <t>18.433161</t>
+          <t>8.690647</t>
         </is>
       </c>
       <c r="U95" t="inlineStr">
@@ -10675,7 +10675,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>0x318bf0ba1d202676e38a34cf3a263bf2f98d89a54dbf8acb2cccc6beaedcc4e8</t>
+          <t>0x182964c6008d5b7d29731fd19876092a52fa2068fcb16aaf430dd8e0a6009721</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -10690,12 +10690,12 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>3.73</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>1.2575</t>
+          <t>1.2763</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -10715,27 +10715,27 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Paju Citizen vs Ansan Greeners</t>
+          <t>Gimpo Citizen FC vs Yongin City</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Gimpo Citizen FC</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>0xabfa364122222118f5f35af9ee862e2b9587e9c2f656e281725fdca100cf17bf</t>
+          <t>0xf93dab40773f0e01839824957e7cecd4afb676d72a13c45521719f4f5c517a27</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>L19306782</t>
+          <t>L19306783</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
@@ -10760,7 +10760,7 @@
       </c>
       <c r="R96" t="inlineStr">
         <is>
-          <t>1785055933</t>
+          <t>1785057212</t>
         </is>
       </c>
       <c r="S96" t="inlineStr">
@@ -10770,7 +10770,7 @@
       </c>
       <c r="T96" t="inlineStr">
         <is>
-          <t>4.970874</t>
+          <t>13.502262</t>
         </is>
       </c>
       <c r="U96" t="inlineStr">
@@ -10787,12 +10787,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>0x5dc684f3ea699d27149c867fb82e4e6f97c7382b6d8784e4edd5bf70e604bae2</t>
+          <t>0xae029509b64a4e0489363d3aa1a7e18db0cd21b4fb65f5064e49185bb4bfb2f6</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -10802,12 +10802,12 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>1.2575</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -10817,7 +10817,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Gimpo Citizen FC</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -10827,27 +10827,27 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Paju Citizen vs Ansan Greeners</t>
+          <t>Gimpo Citizen FC vs Yongin City</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Gimpo Citizen FC</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>0xabfa364122222118f5f35af9ee862e2b9587e9c2f656e281725fdca100cf17bf</t>
+          <t>0x2725ecc350e6d5314ddee250cd3e445f586ab55a992fc73108db0913c5a41f24</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>L19306782</t>
+          <t>L19306783</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
@@ -10872,7 +10872,7 @@
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>1785055931</t>
+          <t>1785056897</t>
         </is>
       </c>
       <c r="S97" t="inlineStr">
@@ -10882,7 +10882,7 @@
       </c>
       <c r="T97" t="inlineStr">
         <is>
-          <t>9.941748</t>
+          <t>9.615385</t>
         </is>
       </c>
       <c r="U97" t="inlineStr">
@@ -10899,7 +10899,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>0x947b403314498890960e964926f3e25010f3b36a93afc49e309f7a71a57648b0</t>
+          <t>0xd359a1bde933becdef3ca166f20bbe9291a9b81f961befead4bc72e1713c6447</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -10914,7 +10914,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>4.53999</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -10984,7 +10984,7 @@
       </c>
       <c r="R98" t="inlineStr">
         <is>
-          <t>1785055853</t>
+          <t>1785056453</t>
         </is>
       </c>
       <c r="S98" t="inlineStr">
@@ -10994,7 +10994,7 @@
       </c>
       <c r="T98" t="inlineStr">
         <is>
-          <t>8.75</t>
+          <t>8.73075</t>
         </is>
       </c>
       <c r="U98" t="inlineStr">
@@ -11011,110 +11011,670 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
+          <t>0xe5784e1cc6cec364d74a7267a701924cf5f6543fed6d0c11d5f756f735c714f2</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>4.55</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen FC</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>K2-League</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen FC vs Yongin City</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen FC</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Yongin City</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>0x2725ecc350e6d5314ddee250cd3e445f586ab55a992fc73108db0913c5a41f24</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>L19306783</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R99" t="inlineStr">
+        <is>
+          <t>1785056153</t>
+        </is>
+      </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>1785061800</t>
+        </is>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>8.75</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>0x2fe44b6f9df282a6669198530843764a881fcd8c491dca571eaacc128af126e6</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>9.99999</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>1.5425</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Paju Citizen</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>K2-League</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>Paju Citizen vs Ansan Greeners</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>Paju Citizen</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Ansan Greeners</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>0x90106aa6ffeea165b450ea7a1094c65ae9db8d6fdde000ce479b4af5b3fa3072</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>L19306782</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R100" t="inlineStr">
+        <is>
+          <t>1785056005</t>
+        </is>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>1785061800</t>
+        </is>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>18.433161</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>0x318bf0ba1d202676e38a34cf3a263bf2f98d89a54dbf8acb2cccc6beaedcc4e8</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>1.28</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>1.2575</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>K2-League</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>Paju Citizen vs Ansan Greeners</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>Paju Citizen</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Ansan Greeners</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>0xabfa364122222118f5f35af9ee862e2b9587e9c2f656e281725fdca100cf17bf</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>L19306782</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q101" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R101" t="inlineStr">
+        <is>
+          <t>1785055933</t>
+        </is>
+      </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>1785061800</t>
+        </is>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>4.970874</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>0x5dc684f3ea699d27149c867fb82e4e6f97c7382b6d8784e4edd5bf70e604bae2</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>2.56</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>1.2575</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>K2-League</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>Paju Citizen vs Ansan Greeners</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>Paju Citizen</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Ansan Greeners</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>0xabfa364122222118f5f35af9ee862e2b9587e9c2f656e281725fdca100cf17bf</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>L19306782</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q102" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R102" t="inlineStr">
+        <is>
+          <t>1785055931</t>
+        </is>
+      </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>1785061800</t>
+        </is>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>9.941748</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>0x947b403314498890960e964926f3e25010f3b36a93afc49e309f7a71a57648b0</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>4.55</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen FC</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>K2-League</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen FC vs Yongin City</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen FC</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Yongin City</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>0x2725ecc350e6d5314ddee250cd3e445f586ab55a992fc73108db0913c5a41f24</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>L19306783</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q103" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R103" t="inlineStr">
+        <is>
+          <t>1785055853</t>
+        </is>
+      </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>1785061800</t>
+        </is>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>8.75</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
           <t>0x4df42281e0de14de14275865cafadfb98d1cc6f76c1873f8fd64bcaa2cae8075</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr">
+      <c r="B104" t="inlineStr">
         <is>
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
         <is>
           <t>4.99</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr">
+      <c r="E104" t="inlineStr">
         <is>
           <t>1.2775</t>
         </is>
       </c>
-      <c r="F99" t="inlineStr">
+      <c r="F104" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr">
+      <c r="G104" t="inlineStr">
         <is>
           <t>Tie</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
+      <c r="H104" t="inlineStr">
         <is>
           <t>K2-League</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr">
+      <c r="I104" t="inlineStr">
         <is>
           <t>Gimpo Citizen FC vs Yongin City</t>
         </is>
       </c>
-      <c r="J99" t="inlineStr">
+      <c r="J104" t="inlineStr">
         <is>
           <t>Gimpo Citizen FC</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr">
+      <c r="K104" t="inlineStr">
         <is>
           <t>Yongin City</t>
         </is>
       </c>
-      <c r="L99" t="inlineStr">
+      <c r="L104" t="inlineStr">
         <is>
           <t>0xf93dab40773f0e01839824957e7cecd4afb676d72a13c45521719f4f5c517a27</t>
         </is>
       </c>
-      <c r="M99" t="inlineStr">
+      <c r="M104" t="inlineStr">
         <is>
           <t>L19306783</t>
         </is>
       </c>
-      <c r="N99" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O99" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P99" t="inlineStr">
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P104" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q99" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R99" t="inlineStr">
+      <c r="Q104" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R104" t="inlineStr">
         <is>
           <t>1785044379</t>
         </is>
       </c>
-      <c r="S99" t="inlineStr">
+      <c r="S104" t="inlineStr">
         <is>
           <t>1785061800</t>
         </is>
       </c>
-      <c r="T99" t="inlineStr">
+      <c r="T104" t="inlineStr">
         <is>
           <t>17.981982</t>
         </is>
       </c>
-      <c r="U99" t="inlineStr">
+      <c r="U104" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V99" t="inlineStr">
+      <c r="V104" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/K2-League/trades.xlsx
+++ b/data/sxbet/ligas/K2-League/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V104"/>
+  <dimension ref="A1:V106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,12 +531,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0xd6d89d8b0c84fd0ec81a6b4192717012bb022d33dcacfee66f877d683dd4d611</t>
+          <t>0x858d8c111f892643e6e663ae07c90316cdfa2ea47299d1e5cc20fefaa3ae0a65</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -546,12 +546,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6.99</t>
+          <t>10.01</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.355</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -561,7 +561,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Busan Ipark</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -571,27 +571,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC vs Gyeongnam FC</t>
+          <t>Busan Ipark vs Seoul E-Land FC</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC</t>
+          <t>Busan Ipark</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Gyeongnam FC</t>
+          <t>Seoul E-Land FC</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0xa00e8c256c66631472e12714859a797c90cf51583b5a4d0291530ebabda74786</t>
+          <t>0xa7828b1b389a0563c5b82fb38239241943f7e9a78b6f452131852f1a5382e6e3</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19391910</t>
+          <t>L19391908</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -616,7 +616,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1785650299</t>
+          <t>1785653954</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>23.3</t>
+          <t>28.197183</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -643,12 +643,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x03d276695324f5778dc7acae7d1c8ccf471fa6903faf5477e59eee03458a3bfb</t>
+          <t>0xc2fdc391b8174c1e7939ec16d46c1414229492833ec07f12223df7804eaa0fb4</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -658,12 +658,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>8.98</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.3275</t>
+          <t>1.465</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -673,7 +673,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Gimpo Citizen FC</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -683,27 +683,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Ansan Greeners vs Gimhae City</t>
+          <t>Gimpo Citizen FC vs Gyeongnam FC</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Gimpo Citizen FC</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Gyeongnam FC</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0x7d12a2dd53643f7bc82bf12edb22fd5c911d957e5077e96a6f07442b24f9e80a</t>
+          <t>0xfb250be9cc7c42d9a09fc00e8b57816cad05cf3e851cb635f8686a55671a4080</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>L19391911</t>
+          <t>L19391910</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -728,7 +728,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1785648537</t>
+          <t>1785652403</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>27.419847</t>
+          <t>21.505376</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -755,7 +755,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x2dc8ccfff3d666979cf43cfc872503cdcdd080abdd51de5f9eaafbdcf02e8dd1</t>
+          <t>0xd6d89d8b0c84fd0ec81a6b4192717012bb022d33dcacfee66f877d683dd4d611</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -770,12 +770,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3.55</t>
+          <t>6.99</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.3262</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Tie</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -795,27 +795,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Ansan Greeners vs Gimhae City</t>
+          <t>Gimpo Citizen FC vs Gyeongnam FC</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Gimpo Citizen FC</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Gyeongnam FC</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0x7d12a2dd53643f7bc82bf12edb22fd5c911d957e5077e96a6f07442b24f9e80a</t>
+          <t>0xa00e8c256c66631472e12714859a797c90cf51583b5a4d0291530ebabda74786</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>L19391911</t>
+          <t>L19391910</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1785648487</t>
+          <t>1785650299</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>10.881226</t>
+          <t>23.3</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -867,7 +867,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0xf6008c4a4394aaa4d9bdde81644581532afef8e3bb1592c8ab8a428c02cc7ba6</t>
+          <t>0x03d276695324f5778dc7acae7d1c8ccf471fa6903faf5477e59eee03458a3bfb</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -882,12 +882,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8.98</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.3237</t>
+          <t>1.3275</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -952,7 +952,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1785648374</t>
+          <t>1785648537</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>21.621622</t>
+          <t>27.419847</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -979,7 +979,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0xe77b567a8d83cd8a6dda10df24dccee1bb8a84363935c220b1fef7d1cb59ac3d</t>
+          <t>0x2dc8ccfff3d666979cf43cfc872503cdcdd080abdd51de5f9eaafbdcf02e8dd1</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>4.09</t>
+          <t>3.55</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.2788</t>
+          <t>1.3262</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1019,27 +1019,27 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons vs Paju Citizen</t>
+          <t>Ansan Greeners vs Gimhae City</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0x47bc42cdde4f45b45de3e45623d2a4551e6f614f6b6fa873e0c5368e0fb39c1d</t>
+          <t>0x7d12a2dd53643f7bc82bf12edb22fd5c911d957e5077e96a6f07442b24f9e80a</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>L19391909</t>
+          <t>L19391911</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1785647749</t>
+          <t>1785648487</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>14.672646</t>
+          <t>10.881226</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1091,31 +1091,39 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x8a4af3a0b4b13cf57049ab82f395d7d34f9a5fd506160c67bbdd18174b6ad54e</t>
+          <t>0xf6008c4a4394aaa4d9bdde81644581532afef8e3bb1592c8ab8a428c02cc7ba6</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.2662</t>
+          <t>1.3237</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Ansan Greeners</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -1138,7 +1146,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0x88b7c7348c4915e417185345face1c028319f7a4edf6917e10541c5cf3904388</t>
+          <t>0x7d12a2dd53643f7bc82bf12edb22fd5c911d957e5077e96a6f07442b24f9e80a</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1168,7 +1176,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1785605666</t>
+          <t>1785648374</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1178,7 +1186,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>24.037559</t>
+          <t>21.621622</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1195,23 +1203,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x72792262ae431dbdddbf088471b45079d60981e999bef9626fbfb120b75bf4d9</t>
+          <t>0xe77b567a8d83cd8a6dda10df24dccee1bb8a84363935c220b1fef7d1cb59ac3d</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>4.99999</t>
+          <t>4.09</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.8388</t>
+          <t>1.2788</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1219,7 +1231,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H8" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -1227,27 +1243,27 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Chungbuk Cheongju FC vs Suwon Samsung Bluewings</t>
+          <t>Jeonnam Dragons vs Paju Citizen</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Chungbuk Cheongju FC</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Suwon Samsung Bluewings</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0x47b6ff226935cb58cf016dcbca241d4de16dbfae419d63e4b73b31ca8333c27c</t>
+          <t>0x47bc42cdde4f45b45de3e45623d2a4551e6f614f6b6fa873e0c5368e0fb39c1d</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>L19382330</t>
+          <t>L19391909</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1272,17 +1288,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1785578466</t>
+          <t>1785647749</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>1785580200</t>
+          <t>1785666600</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>5.96124</t>
+          <t>14.672646</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1299,7 +1315,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0xd8137a83eb126ced1479e30bbe78433f31664b78e4e08119e4c5e0e06678d90f</t>
+          <t>0x8a4af3a0b4b13cf57049ab82f395d7d34f9a5fd506160c67bbdd18174b6ad54e</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1310,17 +1326,17 @@
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>11.09996</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.8388</t>
+          <t>1.2662</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
@@ -1331,27 +1347,27 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Chungbuk Cheongju FC vs Suwon Samsung Bluewings</t>
+          <t>Ansan Greeners vs Gimhae City</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Chungbuk Cheongju FC</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Suwon Samsung Bluewings</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0x47b6ff226935cb58cf016dcbca241d4de16dbfae419d63e4b73b31ca8333c27c</t>
+          <t>0x88b7c7348c4915e417185345face1c028319f7a4edf6917e10541c5cf3904388</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>L19382330</t>
+          <t>L19391911</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1376,17 +1392,17 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1785578456</t>
+          <t>1785605666</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>1785580200</t>
+          <t>1785666600</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>13.233931</t>
+          <t>24.037559</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1403,18 +1419,18 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0x45dd4119f9e9c4b0d949d74afa77a8e1b81e558353af15d7945dc9acc34f137b</t>
+          <t>0x72792262ae431dbdddbf088471b45079d60981e999bef9626fbfb120b75bf4d9</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>23.71902</t>
+          <t>4.99999</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1480,7 +1496,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1785578456</t>
+          <t>1785578466</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1490,7 +1506,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>28.27901</t>
+          <t>5.96124</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1507,7 +1523,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0xc5f6a546dd78c3c6c0c2b63058f45984183690baa2a85baf30f35fc6e6a95fbb</t>
+          <t>0xd8137a83eb126ced1479e30bbe78433f31664b78e4e08119e4c5e0e06678d90f</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1518,7 +1534,7 @@
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11.09996</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1584,7 +1600,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1785578455</t>
+          <t>1785578456</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1594,7 +1610,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1.19225</t>
+          <t>13.233931</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1611,7 +1627,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x071e0dd48a8b69c5fd46a90d3fd6130a920ae4675f78336d20fd540e2fb36e19</t>
+          <t>0x45dd4119f9e9c4b0d949d74afa77a8e1b81e558353af15d7945dc9acc34f137b</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1622,7 +1638,7 @@
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>14.2522</t>
+          <t>23.71902</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1688,7 +1704,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1785578454</t>
+          <t>1785578456</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1698,7 +1714,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>16.992191</t>
+          <t>28.27901</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1715,7 +1731,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0xd80db373e4b7ed691e095b9dd8e2c3060b27dd3b9d96138e938f8b834ed11575</t>
+          <t>0xc5f6a546dd78c3c6c0c2b63058f45984183690baa2a85baf30f35fc6e6a95fbb</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1723,19 +1739,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>9.99836</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.2375</t>
+          <t>1.8388</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1743,11 +1755,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -1770,7 +1778,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0xcbe732f420e35966f1693736f4eff7ac82d6eb79649c462d0b0da88b23389fd7</t>
+          <t>0x47b6ff226935cb58cf016dcbca241d4de16dbfae419d63e4b73b31ca8333c27c</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1800,7 +1808,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1785578439</t>
+          <t>1785578455</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1810,7 +1818,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>42.098358</t>
+          <t>1.19225</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1827,27 +1835,23 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0xd3730071ad09e64f8d94dd7eafe50fd030d149170edc5f0a6980a5b293fbdf6c</t>
+          <t>0x071e0dd48a8b69c5fd46a90d3fd6130a920ae4675f78336d20fd540e2fb36e19</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>12.54</t>
+          <t>14.2522</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.2363</t>
+          <t>1.8388</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1855,11 +1859,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0xcbe732f420e35966f1693736f4eff7ac82d6eb79649c462d0b0da88b23389fd7</t>
+          <t>0x47b6ff226935cb58cf016dcbca241d4de16dbfae419d63e4b73b31ca8333c27c</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1912,7 +1912,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1785578425</t>
+          <t>1785578454</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>53.079365</t>
+          <t>16.992191</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1939,7 +1939,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0x0030d78c7fa3ca6505041a6863683acfc5d44fd46db42676d8fab5fface0f896</t>
+          <t>0xd80db373e4b7ed691e095b9dd8e2c3060b27dd3b9d96138e938f8b834ed11575</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1947,15 +1947,19 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>33.00917</t>
+          <t>9.99836</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.6637</t>
+          <t>1.2375</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1963,7 +1967,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H15" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -1971,27 +1979,27 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Chungnam Asan FC vs Seongnam FC</t>
+          <t>Chungbuk Cheongju FC vs Suwon Samsung Bluewings</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Chungnam Asan FC</t>
+          <t>Chungbuk Cheongju FC</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Seongnam FC</t>
+          <t>Suwon Samsung Bluewings</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0xdc5a3c94507978b475275edc3f202e74993cdff1bf5f2e138cb9ec5c9fdab56b</t>
+          <t>0xcbe732f420e35966f1693736f4eff7ac82d6eb79649c462d0b0da88b23389fd7</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>L19382328</t>
+          <t>L19382330</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2016,7 +2024,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1785578412</t>
+          <t>1785578439</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2026,7 +2034,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>49.73133</t>
+          <t>42.098358</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2043,12 +2051,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0x220dcc2e193d2914753c8ca31c20857d1cba243ec4469ca1444318967b690306</t>
+          <t>0xd3730071ad09e64f8d94dd7eafe50fd030d149170edc5f0a6980a5b293fbdf6c</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2058,12 +2066,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>27.01</t>
+          <t>12.54</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.3625</t>
+          <t>1.2363</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2073,7 +2081,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chungnam Asan FC</t>
+          <t>Tie</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2083,27 +2091,27 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Chungnam Asan FC vs Seongnam FC</t>
+          <t>Chungbuk Cheongju FC vs Suwon Samsung Bluewings</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Chungnam Asan FC</t>
+          <t>Chungbuk Cheongju FC</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Seongnam FC</t>
+          <t>Suwon Samsung Bluewings</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0x122be21c6184231146fb4c55c0406dac2859200e923b24d2b4641ce66abf29f4</t>
+          <t>0xcbe732f420e35966f1693736f4eff7ac82d6eb79649c462d0b0da88b23389fd7</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>L19382328</t>
+          <t>L19382330</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2128,7 +2136,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1785578411</t>
+          <t>1785578425</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2138,7 +2146,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>74.510345</t>
+          <t>53.079365</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2155,7 +2163,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0xa1105617e22069824dc4bb3cbe2a43733b8051deee672c5eb37dab4d3fe5e57d</t>
+          <t>0x0030d78c7fa3ca6505041a6863683acfc5d44fd46db42676d8fab5fface0f896</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2166,12 +2174,12 @@
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>5.62999</t>
+          <t>33.00917</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.8438</t>
+          <t>1.6637</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2187,27 +2195,27 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Chungbuk Cheongju FC vs Suwon Samsung Bluewings</t>
+          <t>Chungnam Asan FC vs Seongnam FC</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Chungbuk Cheongju FC</t>
+          <t>Chungnam Asan FC</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Suwon Samsung Bluewings</t>
+          <t>Seongnam FC</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0x47b6ff226935cb58cf016dcbca241d4de16dbfae419d63e4b73b31ca8333c27c</t>
+          <t>0xdc5a3c94507978b475275edc3f202e74993cdff1bf5f2e138cb9ec5c9fdab56b</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>L19382330</t>
+          <t>L19382328</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2232,7 +2240,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1785578250</t>
+          <t>1785578412</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2242,7 +2250,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>6.672581</t>
+          <t>49.73133</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2259,7 +2267,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0xab0581f4aab772a5e75f6983d6a981e9515dda6c22e94295de4804365f5a78cd</t>
+          <t>0x220dcc2e193d2914753c8ca31c20857d1cba243ec4469ca1444318967b690306</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2267,15 +2275,19 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>0.99998</t>
+          <t>27.01</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.8438</t>
+          <t>1.3625</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2283,7 +2295,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Chungnam Asan FC</t>
+        </is>
+      </c>
       <c r="H18" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -2291,27 +2307,27 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Chungbuk Cheongju FC vs Suwon Samsung Bluewings</t>
+          <t>Chungnam Asan FC vs Seongnam FC</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Chungbuk Cheongju FC</t>
+          <t>Chungnam Asan FC</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Suwon Samsung Bluewings</t>
+          <t>Seongnam FC</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0x47b6ff226935cb58cf016dcbca241d4de16dbfae419d63e4b73b31ca8333c27c</t>
+          <t>0x122be21c6184231146fb4c55c0406dac2859200e923b24d2b4641ce66abf29f4</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>L19382330</t>
+          <t>L19382328</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2336,7 +2352,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1785577978</t>
+          <t>1785578411</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2346,7 +2362,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>1.185161</t>
+          <t>74.510345</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2363,18 +2379,18 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0xd2748c10f4095190f2c2b3649173009f55db5d97aee6e8a15de89cc6f7dc2d94</t>
+          <t>0xa1105617e22069824dc4bb3cbe2a43733b8051deee672c5eb37dab4d3fe5e57d</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>4.99997</t>
+          <t>5.62999</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2440,7 +2456,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1785577974</t>
+          <t>1785578250</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2450,7 +2466,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>5.92589</t>
+          <t>6.672581</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2467,18 +2483,18 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0xb473a9bcd28ce7eb541287850173d36b188eb2ce16684b4f47feec73017ef210</t>
+          <t>0xab0581f4aab772a5e75f6983d6a981e9515dda6c22e94295de4804365f5a78cd</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>4.99997</t>
+          <t>0.99998</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2544,7 +2560,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1785577972</t>
+          <t>1785577978</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2554,7 +2570,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>5.92589</t>
+          <t>1.185161</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2571,7 +2587,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0x1c7c5e1e91914e15cd389ea78b98ffc4af816835d6679433a97a2be50034a7f1</t>
+          <t>0xd2748c10f4095190f2c2b3649173009f55db5d97aee6e8a15de89cc6f7dc2d94</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2648,7 +2664,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1785577971</t>
+          <t>1785577974</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2675,23 +2691,23 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0x570a559aaadf75a6ed1acd4ccb5ddd8e55ce1e7f522824b57494899c861e8d6a</t>
+          <t>0xb473a9bcd28ce7eb541287850173d36b188eb2ce16684b4f47feec73017ef210</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>5.34932</t>
+          <t>4.99997</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.8425</t>
+          <t>1.8438</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2752,7 +2768,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1785577945</t>
+          <t>1785577972</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2762,7 +2778,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>6.349341</t>
+          <t>5.92589</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2779,23 +2795,23 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0x8faf54553900d697a6ef224191c3c314fce17df8a2ec46f32c8f5f4664872c42</t>
+          <t>0x1c7c5e1e91914e15cd389ea78b98ffc4af816835d6679433a97a2be50034a7f1</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>30.16947</t>
+          <t>4.99997</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.8425</t>
+          <t>1.8438</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2856,7 +2872,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1785577943</t>
+          <t>1785577971</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -2866,7 +2882,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>35.80946</t>
+          <t>5.92589</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2883,7 +2899,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0x87d245204fb6266d66f05bad0f085ef14e0002175ce19e9ca19fc941bd2840c8</t>
+          <t>0x570a559aaadf75a6ed1acd4ccb5ddd8e55ce1e7f522824b57494899c861e8d6a</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2894,7 +2910,7 @@
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>28.6717</t>
+          <t>5.34932</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2960,7 +2976,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1785577942</t>
+          <t>1785577945</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -2970,7 +2986,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>34.031691</t>
+          <t>6.349341</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -2987,27 +3003,23 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0xa3ba7bafd18b1a2ed7a2d9f70c9f9f14d910d1148a0051bb51394a7e0b839c92</t>
+          <t>0x8faf54553900d697a6ef224191c3c314fce17df8a2ec46f32c8f5f4664872c42</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>3.66</t>
+          <t>30.16947</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.2937</t>
+          <t>1.8425</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -3015,11 +3027,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -3027,27 +3035,27 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Cheonan City vs Yongin City</t>
+          <t>Chungbuk Cheongju FC vs Suwon Samsung Bluewings</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Chungbuk Cheongju FC</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Suwon Samsung Bluewings</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0x4f0eac96e527e303ba7f731f63206ea5d322051eee61a9087848437cebf10534</t>
+          <t>0x47b6ff226935cb58cf016dcbca241d4de16dbfae419d63e4b73b31ca8333c27c</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>L19382335</t>
+          <t>L19382330</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3072,7 +3080,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1785577801</t>
+          <t>1785577943</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3082,7 +3090,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>12.459574</t>
+          <t>35.80946</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3099,23 +3107,23 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0x2ff9636c19015324567a484925b48b01572feafd96dfae06927e7d28a91accb4</t>
+          <t>0x87d245204fb6266d66f05bad0f085ef14e0002175ce19e9ca19fc941bd2840c8</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>20.20568</t>
+          <t>28.6717</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.6475</t>
+          <t>1.8425</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -3131,27 +3139,27 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Chungnam Asan FC vs Seongnam FC</t>
+          <t>Chungbuk Cheongju FC vs Suwon Samsung Bluewings</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Chungnam Asan FC</t>
+          <t>Chungbuk Cheongju FC</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Seongnam FC</t>
+          <t>Suwon Samsung Bluewings</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0x122be21c6184231146fb4c55c0406dac2859200e923b24d2b4641ce66abf29f4</t>
+          <t>0x47b6ff226935cb58cf016dcbca241d4de16dbfae419d63e4b73b31ca8333c27c</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>L19382328</t>
+          <t>L19382330</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -3176,7 +3184,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1785577136</t>
+          <t>1785577942</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3186,7 +3194,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>31.205683</t>
+          <t>34.031691</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3203,7 +3211,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0xd04f669dbfe7947145022fe948220730e2200d0302b6c375521b18cfb89478d9</t>
+          <t>0xa3ba7bafd18b1a2ed7a2d9f70c9f9f14d910d1148a0051bb51394a7e0b839c92</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3211,15 +3219,19 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr"/>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>59.4</t>
+          <t>3.66</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.8438</t>
+          <t>1.2937</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -3227,7 +3239,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H27" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -3235,27 +3251,27 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Chungbuk Cheongju FC vs Suwon Samsung Bluewings</t>
+          <t>Cheonan City vs Yongin City</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Chungbuk Cheongju FC</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Suwon Samsung Bluewings</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0x47b6ff226935cb58cf016dcbca241d4de16dbfae419d63e4b73b31ca8333c27c</t>
+          <t>0x4f0eac96e527e303ba7f731f63206ea5d322051eee61a9087848437cebf10534</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>L19382330</t>
+          <t>L19382335</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -3280,7 +3296,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1785577059</t>
+          <t>1785577801</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3290,7 +3306,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>70.4</t>
+          <t>12.459574</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3307,7 +3323,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0xd6e59c4a6fedc3fc306e81e55a5678b03ee303e96a9653c49b87b641e05fecf5</t>
+          <t>0x2ff9636c19015324567a484925b48b01572feafd96dfae06927e7d28a91accb4</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3318,12 +3334,12 @@
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>58.83999</t>
+          <t>20.20568</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.8425</t>
+          <t>1.6475</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -3339,27 +3355,27 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Chungbuk Cheongju FC vs Suwon Samsung Bluewings</t>
+          <t>Chungnam Asan FC vs Seongnam FC</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Chungbuk Cheongju FC</t>
+          <t>Chungnam Asan FC</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Suwon Samsung Bluewings</t>
+          <t>Seongnam FC</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0x47b6ff226935cb58cf016dcbca241d4de16dbfae419d63e4b73b31ca8333c27c</t>
+          <t>0x122be21c6184231146fb4c55c0406dac2859200e923b24d2b4641ce66abf29f4</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>L19382330</t>
+          <t>L19382328</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -3384,7 +3400,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1785577058</t>
+          <t>1785577136</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3394,7 +3410,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>69.839751</t>
+          <t>31.205683</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3411,7 +3427,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0xbdaeb9efa9099daa54488930d7f3e08686658f371f2ca9deb5dee1fb018d5dc9</t>
+          <t>0xd04f669dbfe7947145022fe948220730e2200d0302b6c375521b18cfb89478d9</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3422,12 +3438,12 @@
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>15.11</t>
+          <t>59.4</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.6713</t>
+          <t>1.8438</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -3443,27 +3459,27 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Cheonan City vs Yongin City</t>
+          <t>Chungbuk Cheongju FC vs Suwon Samsung Bluewings</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Chungbuk Cheongju FC</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Suwon Samsung Bluewings</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0xc44350683931fa086c3759e22036c1861e9430054b71327499cb1ad0357c41af</t>
+          <t>0x47b6ff226935cb58cf016dcbca241d4de16dbfae419d63e4b73b31ca8333c27c</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>L19382335</t>
+          <t>L19382330</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -3488,7 +3504,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1785576608</t>
+          <t>1785577059</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3498,7 +3514,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>22.510242</t>
+          <t>70.4</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3515,7 +3531,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0x89e7975252a4021e2edec5b41c422fb0f9e0b0bd71b44469db8e27760ccfec81</t>
+          <t>0xd6e59c4a6fedc3fc306e81e55a5678b03ee303e96a9653c49b87b641e05fecf5</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3523,19 +3539,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>58.83999</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.3838</t>
+          <t>1.8425</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -3543,11 +3555,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Cheonan City</t>
-        </is>
-      </c>
+      <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -3555,27 +3563,27 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Cheonan City vs Yongin City</t>
+          <t>Chungbuk Cheongju FC vs Suwon Samsung Bluewings</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Chungbuk Cheongju FC</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Suwon Samsung Bluewings</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0x0ae3c1437f52d2b3c8a4d033ef252880ab9d9fee58c4335b560a2a5bdf7ec6bf</t>
+          <t>0x47b6ff226935cb58cf016dcbca241d4de16dbfae419d63e4b73b31ca8333c27c</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>L19382335</t>
+          <t>L19382330</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -3600,7 +3608,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1785576308</t>
+          <t>1785577058</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3610,7 +3618,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>7.504886</t>
+          <t>69.839751</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3627,7 +3635,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0x2cbe5fb46a011721b21db0e317c482acbdda4529d7e20e5694a7635608189873</t>
+          <t>0xbdaeb9efa9099daa54488930d7f3e08686658f371f2ca9deb5dee1fb018d5dc9</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3635,19 +3643,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>5.01495</t>
+          <t>15.11</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.2925</t>
+          <t>1.6713</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -3655,11 +3659,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -3682,7 +3682,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0x4f0eac96e527e303ba7f731f63206ea5d322051eee61a9087848437cebf10534</t>
+          <t>0xc44350683931fa086c3759e22036c1861e9430054b71327499cb1ad0357c41af</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -3712,7 +3712,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1785576164</t>
+          <t>1785576608</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -3722,7 +3722,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>17.145128</t>
+          <t>22.510242</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3739,7 +3739,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0x6427a9b06be945650ac5754ea9013bd388bb7fd63b9fea057a31d292e952be4b</t>
+          <t>0x89e7975252a4021e2edec5b41c422fb0f9e0b0bd71b44469db8e27760ccfec81</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3754,12 +3754,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>4.99</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.2925</t>
+          <t>1.3838</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -3769,7 +3769,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0x4f0eac96e527e303ba7f731f63206ea5d322051eee61a9087848437cebf10534</t>
+          <t>0x0ae3c1437f52d2b3c8a4d033ef252880ab9d9fee58c4335b560a2a5bdf7ec6bf</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -3824,7 +3824,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1785576163</t>
+          <t>1785576308</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -3834,7 +3834,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>17.059829</t>
+          <t>7.504886</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3851,7 +3851,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0xd7b3568a3172d11868a8c52422c6edb93781f013948e3cbe3187ecd49450a2ed</t>
+          <t>0x2cbe5fb46a011721b21db0e317c482acbdda4529d7e20e5694a7635608189873</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3866,12 +3866,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5.01495</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.3013</t>
+          <t>1.2925</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -3891,27 +3891,27 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Chungnam Asan FC vs Seongnam FC</t>
+          <t>Cheonan City vs Yongin City</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Chungnam Asan FC</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Seongnam FC</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0x3908aa00f1ce849001a57f81937948c4a35c187a56fca542d1c26ac2a5aa578c</t>
+          <t>0x4f0eac96e527e303ba7f731f63206ea5d322051eee61a9087848437cebf10534</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>L19382328</t>
+          <t>L19382335</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -3936,7 +3936,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1785576156</t>
+          <t>1785576164</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -3946,7 +3946,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>19.917012</t>
+          <t>17.145128</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -3963,7 +3963,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0x385d3c2ccc1504b8b62960b052836b16848b30f964e71dbb330e557b9d5b0958</t>
+          <t>0x6427a9b06be945650ac5754ea9013bd388bb7fd63b9fea057a31d292e952be4b</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3978,12 +3978,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>9.01646</t>
+          <t>4.99</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.3025</t>
+          <t>1.2925</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -4003,27 +4003,27 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Chungnam Asan FC vs Seongnam FC</t>
+          <t>Cheonan City vs Yongin City</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Chungnam Asan FC</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Seongnam FC</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0x3908aa00f1ce849001a57f81937948c4a35c187a56fca542d1c26ac2a5aa578c</t>
+          <t>0x4f0eac96e527e303ba7f731f63206ea5d322051eee61a9087848437cebf10534</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>L19382328</t>
+          <t>L19382335</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -4048,7 +4048,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1785576156</t>
+          <t>1785576163</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -4058,7 +4058,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>29.806479</t>
+          <t>17.059829</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4075,7 +4075,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0x81bc6461a5498bb098f71cbd0566c77991625c35e512a092b27824593eb64b44</t>
+          <t>0xd7b3568a3172d11868a8c52422c6edb93781f013948e3cbe3187ecd49450a2ed</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>5.76</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.3838</t>
+          <t>1.3013</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -4105,7 +4105,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Tie</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4115,27 +4115,27 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Cheonan City vs Yongin City</t>
+          <t>Chungnam Asan FC vs Seongnam FC</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Chungnam Asan FC</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Seongnam FC</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0x0ae3c1437f52d2b3c8a4d033ef252880ab9d9fee58c4335b560a2a5bdf7ec6bf</t>
+          <t>0x3908aa00f1ce849001a57f81937948c4a35c187a56fca542d1c26ac2a5aa578c</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>L19382335</t>
+          <t>L19382328</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -4160,7 +4160,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1785576008</t>
+          <t>1785576156</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -4170,7 +4170,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>15.009772</t>
+          <t>19.917012</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4187,7 +4187,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0x20a26ca056f3f25e1f8971a88b06b55502b7f6fd7d4ead5f9ed5057ee98ecf34</t>
+          <t>0x385d3c2ccc1504b8b62960b052836b16848b30f964e71dbb330e557b9d5b0958</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4195,23 +4195,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr"/>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>7.77558</t>
+          <t>9.01646</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.3413</t>
+          <t>1.3025</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H36" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -4219,27 +4227,27 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Chungbuk Cheongju FC vs Suwon Samsung Bluewings</t>
+          <t>Chungnam Asan FC vs Seongnam FC</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Chungbuk Cheongju FC</t>
+          <t>Chungnam Asan FC</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Suwon Samsung Bluewings</t>
+          <t>Seongnam FC</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0x9e11ba3ce6b4420e4e452b60f302739f1d8467716ba519ebe3f8132832094348</t>
+          <t>0x3908aa00f1ce849001a57f81937948c4a35c187a56fca542d1c26ac2a5aa578c</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>L19382330</t>
+          <t>L19382328</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -4264,7 +4272,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1785576008</t>
+          <t>1785576156</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -4274,7 +4282,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>22.785582</t>
+          <t>29.806479</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4291,7 +4299,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0xd9d9b0ddddc1467f24d4b982d44a16b3c39903ee63500a8ec66563c6202bfcf9</t>
+          <t>0x81bc6461a5498bb098f71cbd0566c77991625c35e512a092b27824593eb64b44</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4306,7 +4314,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>5.71</t>
+          <t>5.76</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -4376,7 +4384,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1785575708</t>
+          <t>1785576008</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -4386,7 +4394,7 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>14.879479</t>
+          <t>15.009772</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4403,7 +4411,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0x087314e5ace3bbb3bbb4f703bfe21af2df9ef3152845f56763bcabd878659d88</t>
+          <t>0x20a26ca056f3f25e1f8971a88b06b55502b7f6fd7d4ead5f9ed5057ee98ecf34</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4411,31 +4419,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>7.77558</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.385</t>
+          <t>1.3413</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Cheonan City</t>
-        </is>
-      </c>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -4443,27 +4443,27 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Cheonan City vs Yongin City</t>
+          <t>Chungbuk Cheongju FC vs Suwon Samsung Bluewings</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Chungbuk Cheongju FC</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Suwon Samsung Bluewings</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0x0ae3c1437f52d2b3c8a4d033ef252880ab9d9fee58c4335b560a2a5bdf7ec6bf</t>
+          <t>0x9e11ba3ce6b4420e4e452b60f302739f1d8467716ba519ebe3f8132832094348</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>L19382335</t>
+          <t>L19382330</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -4488,7 +4488,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1785574808</t>
+          <t>1785576008</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -4498,7 +4498,7 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>8.181818</t>
+          <t>22.785582</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4515,7 +4515,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0x1665cbfdd918d1b313ff8b09985889ba3e20ffef471ed1f77d4454a6d4870eb1</t>
+          <t>0xd9d9b0ddddc1467f24d4b982d44a16b3c39903ee63500a8ec66563c6202bfcf9</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4530,12 +4530,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>10.96</t>
+          <t>5.71</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.6113</t>
+          <t>1.3838</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -4545,7 +4545,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Suwon Samsung Bluewings</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -4555,27 +4555,27 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Chungbuk Cheongju FC vs Suwon Samsung Bluewings</t>
+          <t>Cheonan City vs Yongin City</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Chungbuk Cheongju FC</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Suwon Samsung Bluewings</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0xb29a7409dfd5ac0b7a29e92e49cc6bab92af282a2f9d95f3eeb630ed33eb7a3a</t>
+          <t>0x0ae3c1437f52d2b3c8a4d033ef252880ab9d9fee58c4335b560a2a5bdf7ec6bf</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>L19382330</t>
+          <t>L19382335</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -4600,7 +4600,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1785574796</t>
+          <t>1785575708</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -4610,7 +4610,7 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>17.93047</t>
+          <t>14.879479</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4627,7 +4627,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0xf5159a5ea43cd4f5bd5f77236fb23f24714602f00b37c28d1f70bb3786749e16</t>
+          <t>0x087314e5ace3bbb3bbb4f703bfe21af2df9ef3152845f56763bcabd878659d88</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4635,15 +4635,19 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr"/>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.5413</t>
+          <t>1.385</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -4651,7 +4655,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Cheonan City</t>
+        </is>
+      </c>
       <c r="H40" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -4659,27 +4667,27 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Hwaseong FC vs Daegu FC</t>
+          <t>Cheonan City vs Yongin City</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Hwaseong FC</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Daegu FC</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0x3673fddffb9c10163590d13afe39cb241b3c0284138745deddac5c176ba19ebd</t>
+          <t>0x0ae3c1437f52d2b3c8a4d033ef252880ab9d9fee58c4335b560a2a5bdf7ec6bf</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>L19382332</t>
+          <t>L19382335</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -4704,7 +4712,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1785574516</t>
+          <t>1785574808</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -4714,7 +4722,7 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>6.060046</t>
+          <t>8.181818</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -4731,7 +4739,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0x1d3e02f07b5d6a05bde415b055541ce4395cbd9016dfcb7b067173b6ff538c00</t>
+          <t>0x1665cbfdd918d1b313ff8b09985889ba3e20ffef471ed1f77d4454a6d4870eb1</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4746,12 +4754,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>5.76</t>
+          <t>10.96</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.3838</t>
+          <t>1.6113</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -4761,7 +4769,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Suwon Samsung Bluewings</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -4771,27 +4779,27 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Cheonan City vs Yongin City</t>
+          <t>Chungbuk Cheongju FC vs Suwon Samsung Bluewings</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Chungbuk Cheongju FC</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Suwon Samsung Bluewings</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0x0ae3c1437f52d2b3c8a4d033ef252880ab9d9fee58c4335b560a2a5bdf7ec6bf</t>
+          <t>0xb29a7409dfd5ac0b7a29e92e49cc6bab92af282a2f9d95f3eeb630ed33eb7a3a</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>L19382335</t>
+          <t>L19382330</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -4816,7 +4824,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1785573908</t>
+          <t>1785574796</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -4826,7 +4834,7 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>15.009772</t>
+          <t>17.93047</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -4843,7 +4851,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0x43f4e76dc758bd60088f0e19fe831ad6e231cfd3f25713ee2197b0c4c12225c4</t>
+          <t>0xf5159a5ea43cd4f5bd5f77236fb23f24714602f00b37c28d1f70bb3786749e16</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4854,17 +4862,17 @@
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.335</t>
+          <t>1.5413</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G42" t="inlineStr"/>
@@ -4875,27 +4883,27 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Chungbuk Cheongju FC vs Suwon Samsung Bluewings</t>
+          <t>Hwaseong FC vs Daegu FC</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Chungbuk Cheongju FC</t>
+          <t>Hwaseong FC</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Suwon Samsung Bluewings</t>
+          <t>Daegu FC</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0x9e11ba3ce6b4420e4e452b60f302739f1d8467716ba519ebe3f8132832094348</t>
+          <t>0x3673fddffb9c10163590d13afe39cb241b3c0284138745deddac5c176ba19ebd</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>L19382330</t>
+          <t>L19382332</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -4920,7 +4928,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1785573008</t>
+          <t>1785574516</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -4930,7 +4938,7 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>17.164179</t>
+          <t>6.060046</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -4947,7 +4955,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0xcc556a2f534d604ca3147c77e407c4a3caccfb460a650afb93e92f95893a83f3</t>
+          <t>0x1d3e02f07b5d6a05bde415b055541ce4395cbd9016dfcb7b067173b6ff538c00</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4955,23 +4963,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr"/>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>5.74</t>
+          <t>5.76</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.335</t>
+          <t>1.3838</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Cheonan City</t>
+        </is>
+      </c>
       <c r="H43" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -4979,27 +4995,27 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Chungbuk Cheongju FC vs Suwon Samsung Bluewings</t>
+          <t>Cheonan City vs Yongin City</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Chungbuk Cheongju FC</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Suwon Samsung Bluewings</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0x9e11ba3ce6b4420e4e452b60f302739f1d8467716ba519ebe3f8132832094348</t>
+          <t>0x0ae3c1437f52d2b3c8a4d033ef252880ab9d9fee58c4335b560a2a5bdf7ec6bf</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>L19382330</t>
+          <t>L19382335</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -5024,7 +5040,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1785572408</t>
+          <t>1785573908</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -5034,7 +5050,7 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>17.134328</t>
+          <t>15.009772</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -5051,7 +5067,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0xe6b9109907b0068b7b44342bbfe6aa4e4f925a1808a4234ef25d5964c06e8a19</t>
+          <t>0x43f4e76dc758bd60088f0e19fe831ad6e231cfd3f25713ee2197b0c4c12225c4</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5059,31 +5075,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>4.99</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.2913</t>
+          <t>1.335</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -5091,27 +5099,27 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Cheonan City vs Yongin City</t>
+          <t>Chungbuk Cheongju FC vs Suwon Samsung Bluewings</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Chungbuk Cheongju FC</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Suwon Samsung Bluewings</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0x4f0eac96e527e303ba7f731f63206ea5d322051eee61a9087848437cebf10534</t>
+          <t>0x9e11ba3ce6b4420e4e452b60f302739f1d8467716ba519ebe3f8132832094348</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>L19382335</t>
+          <t>L19382330</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -5136,7 +5144,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>1785571129</t>
+          <t>1785573008</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -5146,7 +5154,7 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>17.133047</t>
+          <t>17.164179</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -5163,7 +5171,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0x3adcd675a8ad2ac41cfe2151a15dc0861c045d26ad2b087ec6303e2e6bc75b83</t>
+          <t>0xcc556a2f534d604ca3147c77e407c4a3caccfb460a650afb93e92f95893a83f3</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5171,31 +5179,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>5.74</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1.2412</t>
+          <t>1.335</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -5218,7 +5218,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>0xcbe732f420e35966f1693736f4eff7ac82d6eb79649c462d0b0da88b23389fd7</t>
+          <t>0x9e11ba3ce6b4420e4e452b60f302739f1d8467716ba519ebe3f8132832094348</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -5248,7 +5248,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>1785561333</t>
+          <t>1785572408</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>4.601036</t>
+          <t>17.134328</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -5275,7 +5275,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0x0ba2bf9f0fc74c97ade129a1430bdc4cd89f8fecee54ee5b1f9876c41b38c180</t>
+          <t>0xe6b9109907b0068b7b44342bbfe6aa4e4f925a1808a4234ef25d5964c06e8a19</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5290,12 +5290,12 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>4.99</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.2662</t>
+          <t>1.2913</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -5315,27 +5315,27 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Hwaseong FC vs Daegu FC</t>
+          <t>Cheonan City vs Yongin City</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Hwaseong FC</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Daegu FC</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>0xda1e33e5fc880742964769df06cb9c83769ec80d9cb168728d3a3467d0a0473b</t>
+          <t>0x4f0eac96e527e303ba7f731f63206ea5d322051eee61a9087848437cebf10534</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>L19382332</t>
+          <t>L19382335</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -5360,7 +5360,7 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>1785558588</t>
+          <t>1785571129</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
@@ -5370,7 +5370,7 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>12.995305</t>
+          <t>17.133047</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -5387,7 +5387,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0x59cfeb6eefafd07022cdcaae7869afb45bc60deb8b4c0b4b96ad04ae8bbdb0d3</t>
+          <t>0x3adcd675a8ad2ac41cfe2151a15dc0861c045d26ad2b087ec6303e2e6bc75b83</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5402,52 +5402,52 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>321.53001</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.525</t>
+          <t>1.2412</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
           <t>K2-League</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>Chungnam Asan FC 0</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>K2-League</t>
-        </is>
-      </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Chungnam Asan FC vs Seongnam FC</t>
+          <t>Chungbuk Cheongju FC vs Suwon Samsung Bluewings</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Chungnam Asan FC</t>
+          <t>Chungbuk Cheongju FC</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Seongnam FC</t>
+          <t>Suwon Samsung Bluewings</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>0x5d9fd67211ec6f71728981803ac86abc94216c4e6a398285b5003dabd4e5df0f</t>
+          <t>0xcbe732f420e35966f1693736f4eff7ac82d6eb79649c462d0b0da88b23389fd7</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>L19382328</t>
+          <t>L19382330</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -5472,7 +5472,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>1785534316</t>
+          <t>1785561333</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
@@ -5482,7 +5482,7 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>612.438114</t>
+          <t>4.601036</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -5499,7 +5499,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0x57f84ab38f2e25e292c948ee169e9feff1e8436efac9878d37389052fc7a8ade</t>
+          <t>0x0ba2bf9f0fc74c97ade129a1430bdc4cd89f8fecee54ee5b1f9876c41b38c180</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5514,52 +5514,52 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>9.99999</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.525</t>
+          <t>1.2662</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
           <t>K2-League</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>Chungnam Asan FC 0</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>K2-League</t>
-        </is>
-      </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Chungnam Asan FC vs Seongnam FC</t>
+          <t>Hwaseong FC vs Daegu FC</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Chungnam Asan FC</t>
+          <t>Hwaseong FC</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Seongnam FC</t>
+          <t>Daegu FC</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>0x5d9fd67211ec6f71728981803ac86abc94216c4e6a398285b5003dabd4e5df0f</t>
+          <t>0xda1e33e5fc880742964769df06cb9c83769ec80d9cb168728d3a3467d0a0473b</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>L19382328</t>
+          <t>L19382332</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -5584,7 +5584,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>1785534315</t>
+          <t>1785558588</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
@@ -5594,7 +5594,7 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>19.0476</t>
+          <t>12.995305</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -5611,12 +5611,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0x4da39049a709357f30ef968bfc90b4eec2da9d99090f3b99edf4ea11aeddd708</t>
+          <t>0x59cfeb6eefafd07022cdcaae7869afb45bc60deb8b4c0b4b96ad04ae8bbdb0d3</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -5626,22 +5626,22 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>32.79</t>
+          <t>321.53001</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1.5488</t>
+          <t>1.525</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
+          <t>K2-League</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hwaseong FC +0.5</t>
+          <t>Chungnam Asan FC 0</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -5651,27 +5651,27 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Hwaseong FC vs Daegu FC</t>
+          <t>Chungnam Asan FC vs Seongnam FC</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Hwaseong FC</t>
+          <t>Chungnam Asan FC</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Daegu FC</t>
+          <t>Seongnam FC</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>0xbde5165c3a540b0c6dd64b3df320540fd10ecb173373b087359951e7f790f852</t>
+          <t>0x5d9fd67211ec6f71728981803ac86abc94216c4e6a398285b5003dabd4e5df0f</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>L19382332</t>
+          <t>L19382328</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -5696,7 +5696,7 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>1785527084</t>
+          <t>1785534316</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
@@ -5706,7 +5706,7 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>59.753986</t>
+          <t>612.438114</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -5723,7 +5723,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0x07b844c409deb0bc9c8e8dbda27c7c2b772aec07892356105db79f67ffb0e227</t>
+          <t>0x57f84ab38f2e25e292c948ee169e9feff1e8436efac9878d37389052fc7a8ade</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5731,23 +5731,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr"/>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>6.39</t>
+          <t>9.99999</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1.5675</t>
+          <t>1.525</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr"/>
+          <t>K2-League</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Chungnam Asan FC 0</t>
+        </is>
+      </c>
       <c r="H50" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -5755,27 +5763,27 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC vs Yongin City</t>
+          <t>Chungnam Asan FC vs Seongnam FC</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC</t>
+          <t>Chungnam Asan FC</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Seongnam FC</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>0xf73fcbba4baac94056070f4c2db509913d7317940066a6918ac1f13256f52327</t>
+          <t>0x5d9fd67211ec6f71728981803ac86abc94216c4e6a398285b5003dabd4e5df0f</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>L19306783</t>
+          <t>L19382328</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -5800,17 +5808,17 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>1785064787</t>
+          <t>1785534315</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>1785061800</t>
+          <t>1785580200</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>11.259912</t>
+          <t>19.0476</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -5827,31 +5835,39 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0xf95f88d59f982dc2c9ca6387361b5a066ab48deeb7f9f6071274eb879ddabdd0</t>
+          <t>0x4da39049a709357f30ef968bfc90b4eec2da9d99090f3b99edf4ea11aeddd708</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>126.4351</t>
+          <t>32.79</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1.815</t>
+          <t>1.5488</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr"/>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Hwaseong FC +0.5</t>
+        </is>
+      </c>
       <c r="H51" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -5859,27 +5875,27 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC vs Yongin City</t>
+          <t>Hwaseong FC vs Daegu FC</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC</t>
+          <t>Hwaseong FC</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Daegu FC</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>0x1482cd21984a144c2f6033821f76b4033b1aeaebbab5c85a758b2e86c0553134</t>
+          <t>0xbde5165c3a540b0c6dd64b3df320540fd10ecb173373b087359951e7f790f852</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>L19306783</t>
+          <t>L19382332</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -5904,17 +5920,17 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>1785064732</t>
+          <t>1785527084</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>1785061800</t>
+          <t>1785580200</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>155.135092</t>
+          <t>59.753986</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -5931,7 +5947,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0xe74ba88448233ab30d6e4b230046fe45bf1be0a6f71b8860703364abbbb40afe</t>
+          <t>0x07b844c409deb0bc9c8e8dbda27c7c2b772aec07892356105db79f67ffb0e227</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5939,19 +5955,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t>19.69</t>
+          <t>6.39</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1.5038</t>
+          <t>1.5675</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -5959,11 +5971,7 @@
           <t>Under/Over (1.5)</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>Over 1.5</t>
-        </is>
-      </c>
+      <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -5971,27 +5979,27 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Paju Citizen vs Ansan Greeners</t>
+          <t>Gimpo Citizen FC vs Yongin City</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Gimpo Citizen FC</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>0x6a23b140597c01b1670e03fdb996fc8e94424ec45a5e6e429b292ba1688dff5c</t>
+          <t>0xf73fcbba4baac94056070f4c2db509913d7317940066a6918ac1f13256f52327</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>L19306782</t>
+          <t>L19306783</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -6016,7 +6024,7 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>1785064111</t>
+          <t>1785064787</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
@@ -6026,7 +6034,7 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>39.086849</t>
+          <t>11.259912</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -6043,28 +6051,28 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0x02858e4fe5f076373faa42c17e9058ea19bff69a0b68493520c024b133c2ceed</t>
+          <t>0xf95f88d59f982dc2c9ca6387361b5a066ab48deeb7f9f6071274eb879ddabdd0</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0x0C2DA7fC8702784d6f75c78Da25460783A6709a0</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>126.4351</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1.4975</t>
+          <t>1.815</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G53" t="inlineStr"/>
@@ -6075,27 +6083,27 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Paju Citizen vs Ansan Greeners</t>
+          <t>Gimpo Citizen FC vs Yongin City</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Gimpo Citizen FC</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>0x90106aa6ffeea165b450ea7a1094c65ae9db8d6fdde000ce479b4af5b3fa3072</t>
+          <t>0x1482cd21984a144c2f6033821f76b4033b1aeaebbab5c85a758b2e86c0553134</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>L19306782</t>
+          <t>L19306783</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -6120,7 +6128,7 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>1785063804</t>
+          <t>1785064732</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
@@ -6130,7 +6138,7 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>6.030151</t>
+          <t>155.135092</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -6147,7 +6155,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0xd6b44cd45d93535a9c1b39fad13245ea6ef0e5cbff858b443a9d40a281cf422f</t>
+          <t>0xe74ba88448233ab30d6e4b230046fe45bf1be0a6f71b8860703364abbbb40afe</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -6162,22 +6170,22 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>21.3</t>
+          <t>19.69</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1.2988</t>
+          <t>1.5038</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Over 2.5</t>
+          <t>Over 1.5</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -6202,7 +6210,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>0x2d5eca3e665030fe8c7c2a84772b94d8fc59c9a6991fd216ba914d3b345ffe07</t>
+          <t>0x6a23b140597c01b1670e03fdb996fc8e94424ec45a5e6e429b292ba1688dff5c</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -6232,7 +6240,7 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>1785063590</t>
+          <t>1785064111</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
@@ -6242,7 +6250,7 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>71.297071</t>
+          <t>39.086849</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -6259,27 +6267,23 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0xc41eea20c9aa34da894372c77f23e0a6ee134568f117e95b14c294310b2dc1f7</t>
+          <t>0x02858e4fe5f076373faa42c17e9058ea19bff69a0b68493520c024b133c2ceed</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x0C2DA7fC8702784d6f75c78Da25460783A6709a0</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
-          <t>12.53</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1.2037</t>
+          <t>1.4975</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -6287,11 +6291,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>Yongin City</t>
-        </is>
-      </c>
+      <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -6299,27 +6299,27 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC vs Yongin City</t>
+          <t>Paju Citizen vs Ansan Greeners</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>0x520e073f044523b55003a1d70f752c30f91cd5ebae7e23b2f294ad6679b3ed58</t>
+          <t>0x90106aa6ffeea165b450ea7a1094c65ae9db8d6fdde000ce479b4af5b3fa3072</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>L19306783</t>
+          <t>L19306782</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -6344,7 +6344,7 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>1785063530</t>
+          <t>1785063804</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
@@ -6354,7 +6354,7 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>61.496933</t>
+          <t>6.030151</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -6371,7 +6371,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0xe5a4265d3896fe621f44bfc6c8c9d2efe8a044ac121c6a5ec411dcd8ecbb22c9</t>
+          <t>0xd6b44cd45d93535a9c1b39fad13245ea6ef0e5cbff858b443a9d40a281cf422f</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6386,22 +6386,22 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>21.3</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1.5162</t>
+          <t>1.2988</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC</t>
+          <t>Over 2.5</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -6411,27 +6411,27 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC vs Yongin City</t>
+          <t>Paju Citizen vs Ansan Greeners</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>0x2725ecc350e6d5314ddee250cd3e445f586ab55a992fc73108db0913c5a41f24</t>
+          <t>0x2d5eca3e665030fe8c7c2a84772b94d8fc59c9a6991fd216ba914d3b345ffe07</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>L19306783</t>
+          <t>L19306782</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -6456,7 +6456,7 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>1785063352</t>
+          <t>1785063590</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>1.937046</t>
+          <t>71.297071</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -6483,7 +6483,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0x996289847910ea662fcd868b20c9fa48f68ab4d7334bac4351bc46b6d3f479df</t>
+          <t>0xc41eea20c9aa34da894372c77f23e0a6ee134568f117e95b14c294310b2dc1f7</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6498,12 +6498,12 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12.53</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>1.5162</t>
+          <t>1.2037</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -6513,24 +6513,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
+          <t>Yongin City</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>K2-League</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen FC vs Yongin City</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
           <t>Gimpo Citizen FC</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>K2-League</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>Gimpo Citizen FC vs Yongin City</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>Gimpo Citizen FC</t>
-        </is>
-      </c>
       <c r="K57" t="inlineStr">
         <is>
           <t>Yongin City</t>
@@ -6538,7 +6538,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>0x2725ecc350e6d5314ddee250cd3e445f586ab55a992fc73108db0913c5a41f24</t>
+          <t>0x520e073f044523b55003a1d70f752c30f91cd5ebae7e23b2f294ad6679b3ed58</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -6568,7 +6568,7 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>1785063326</t>
+          <t>1785063530</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
@@ -6578,7 +6578,7 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>1.937046</t>
+          <t>61.496933</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -6595,7 +6595,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0xed44d31e5a5b7071006924700a0078a2f8a3710d9bb8d24217652d198ffae7d7</t>
+          <t>0xe5a4265d3896fe621f44bfc6c8c9d2efe8a044ac121c6a5ec411dcd8ecbb22c9</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6610,7 +6610,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>28.84</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>1785063319</t>
+          <t>1785063352</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
@@ -6690,7 +6690,7 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>55.864407</t>
+          <t>1.937046</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
@@ -6707,7 +6707,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0x2bcba69d716b343c190b4a215a8f323f4abe23b13cd57d716f1b386e77406d71</t>
+          <t>0x996289847910ea662fcd868b20c9fa48f68ab4d7334bac4351bc46b6d3f479df</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6715,23 +6715,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr"/>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>1.3912</t>
+          <t>1.5162</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen FC</t>
+        </is>
+      </c>
       <c r="H59" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -6754,7 +6762,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>0xf73fcbba4baac94056070f4c2db509913d7317940066a6918ac1f13256f52327</t>
+          <t>0x2725ecc350e6d5314ddee250cd3e445f586ab55a992fc73108db0913c5a41f24</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -6784,7 +6792,7 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>1785063319</t>
+          <t>1785063326</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
@@ -6794,7 +6802,7 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>6.696486</t>
+          <t>1.937046</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
@@ -6811,7 +6819,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0x74897816645fe410040b71368723e823f96b8b8ad1a8558a60563ea6a63c17b9</t>
+          <t>0xed44d31e5a5b7071006924700a0078a2f8a3710d9bb8d24217652d198ffae7d7</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6826,12 +6834,12 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>28.84</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>1.5488</t>
+          <t>1.5162</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -6841,7 +6849,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Gimpo Citizen FC</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -6851,27 +6859,27 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Paju Citizen vs Ansan Greeners</t>
+          <t>Gimpo Citizen FC vs Yongin City</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Gimpo Citizen FC</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>0x90106aa6ffeea165b450ea7a1094c65ae9db8d6fdde000ce479b4af5b3fa3072</t>
+          <t>0x2725ecc350e6d5314ddee250cd3e445f586ab55a992fc73108db0913c5a41f24</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>L19306782</t>
+          <t>L19306783</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -6896,7 +6904,7 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>1785063283</t>
+          <t>1785063319</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
@@ -6906,7 +6914,7 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>18.223235</t>
+          <t>55.864407</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
@@ -6923,7 +6931,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0x6c9b96e6ea55e8d6386264e63d154ad9cdf850c8f9c18b5c088abdcfcc710e8d</t>
+          <t>0x2bcba69d716b343c190b4a215a8f323f4abe23b13cd57d716f1b386e77406d71</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6934,17 +6942,17 @@
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr">
         <is>
-          <t>1.74999</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>1.8313</t>
+          <t>1.3912</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G61" t="inlineStr"/>
@@ -6955,27 +6963,27 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Paju Citizen vs Ansan Greeners</t>
+          <t>Gimpo Citizen FC vs Yongin City</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Gimpo Citizen FC</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>0x6de105784818e175bb2cb50f54d4325a684a5693a05f8bd5b7f2b402aeb4bdfa</t>
+          <t>0xf73fcbba4baac94056070f4c2db509913d7317940066a6918ac1f13256f52327</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>L19306782</t>
+          <t>L19306783</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -7000,7 +7008,7 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>1785063278</t>
+          <t>1785063319</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
@@ -7010,7 +7018,7 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>2.105251</t>
+          <t>6.696486</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
@@ -7027,7 +7035,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0x653ed25ca6aba498efe0c95f6d394f607985bf6c4ab830c3599772279631e8b1</t>
+          <t>0x74897816645fe410040b71368723e823f96b8b8ad1a8558a60563ea6a63c17b9</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -7035,15 +7043,19 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr"/>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>201.32998</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>1.8213</t>
+          <t>1.5488</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -7051,7 +7063,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Paju Citizen</t>
+        </is>
+      </c>
       <c r="H62" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -7074,7 +7090,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>0x6de105784818e175bb2cb50f54d4325a684a5693a05f8bd5b7f2b402aeb4bdfa</t>
+          <t>0x90106aa6ffeea165b450ea7a1094c65ae9db8d6fdde000ce479b4af5b3fa3072</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -7104,7 +7120,7 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>1785063071</t>
+          <t>1785063283</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
@@ -7114,7 +7130,7 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>245.150661</t>
+          <t>18.223235</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
@@ -7131,23 +7147,23 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0xd7beeace3688b4d75f908058620cd47f10d9926e086901a2c83333dd169ec720</t>
+          <t>0x6c9b96e6ea55e8d6386264e63d154ad9cdf850c8f9c18b5c088abdcfcc710e8d</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr">
         <is>
-          <t>48.03</t>
+          <t>1.74999</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.8313</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -7163,27 +7179,27 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC vs Yongin City</t>
+          <t>Paju Citizen vs Ansan Greeners</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>0x2725ecc350e6d5314ddee250cd3e445f586ab55a992fc73108db0913c5a41f24</t>
+          <t>0x6de105784818e175bb2cb50f54d4325a684a5693a05f8bd5b7f2b402aeb4bdfa</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>L19306783</t>
+          <t>L19306782</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -7208,7 +7224,7 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>1785062970</t>
+          <t>1785063278</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
@@ -7218,7 +7234,7 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>98.020408</t>
+          <t>2.105251</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
@@ -7235,7 +7251,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0x8940d52e7feb848f5ca44e42ecc2fed94e942961b918122bc87142ffbf346d4c</t>
+          <t>0x653ed25ca6aba498efe0c95f6d394f607985bf6c4ab830c3599772279631e8b1</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -7246,12 +7262,12 @@
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr">
         <is>
-          <t>196.03997</t>
+          <t>201.32998</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>1.8188</t>
+          <t>1.8213</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -7312,7 +7328,7 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>1785062953</t>
+          <t>1785063071</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
@@ -7322,7 +7338,7 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>239.438131</t>
+          <t>245.150661</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
@@ -7339,27 +7355,23 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0x2b9441f7515eb95a00a5708be64644050b069886b2e84d77ecdeea72fe8e3da7</t>
+          <t>0xd7beeace3688b4d75f908058620cd47f10d9926e086901a2c83333dd169ec720</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr">
         <is>
-          <t>12.06</t>
+          <t>48.03</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>1.1975</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -7367,34 +7379,30 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>K2-League</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen FC vs Yongin City</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen FC</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
         <is>
           <t>Yongin City</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>K2-League</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>Gimpo Citizen FC vs Yongin City</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>Gimpo Citizen FC</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>Yongin City</t>
-        </is>
-      </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>0x520e073f044523b55003a1d70f752c30f91cd5ebae7e23b2f294ad6679b3ed58</t>
+          <t>0x2725ecc350e6d5314ddee250cd3e445f586ab55a992fc73108db0913c5a41f24</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -7424,7 +7432,7 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>1785062934</t>
+          <t>1785062970</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
@@ -7434,7 +7442,7 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>61.063291</t>
+          <t>98.020408</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
@@ -7451,7 +7459,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0x17ea9fc34d8d08859197baf8694510eafd385c5cb30d1bccaf4135418710a4ee</t>
+          <t>0x8940d52e7feb848f5ca44e42ecc2fed94e942961b918122bc87142ffbf346d4c</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -7459,31 +7467,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>196.03997</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>1.3862</t>
+          <t>1.8188</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>Over 2.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -7506,7 +7506,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>0x2d5eca3e665030fe8c7c2a84772b94d8fc59c9a6991fd216ba914d3b345ffe07</t>
+          <t>0x6de105784818e175bb2cb50f54d4325a684a5693a05f8bd5b7f2b402aeb4bdfa</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -7536,7 +7536,7 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>1785062748</t>
+          <t>1785062953</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
@@ -7546,7 +7546,7 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>25.889968</t>
+          <t>239.438131</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
@@ -7563,7 +7563,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0xff313e8a80cab759f0306eced2743a83b68017dd8ecc4a5eda49613abd5f72bb</t>
+          <t>0x2b9441f7515eb95a00a5708be64644050b069886b2e84d77ecdeea72fe8e3da7</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -7578,22 +7578,22 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12.06</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>1.2275</t>
+          <t>1.1975</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Over 3.5</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -7603,27 +7603,27 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Paju Citizen vs Ansan Greeners</t>
+          <t>Gimpo Citizen FC vs Yongin City</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Gimpo Citizen FC</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>0x20fab15d1baac82bbe5a9371ad4e1e4f931edb8de76d814e671a0313aa4d8620</t>
+          <t>0x520e073f044523b55003a1d70f752c30f91cd5ebae7e23b2f294ad6679b3ed58</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>L19306782</t>
+          <t>L19306783</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>1785062437</t>
+          <t>1785062934</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
@@ -7658,7 +7658,7 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>43.956044</t>
+          <t>61.063291</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
@@ -7675,7 +7675,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0x5a88256e6b892595ad641ef1ae589c088b32b6034ec557ba72582fa8c93f67e3</t>
+          <t>0x17ea9fc34d8d08859197baf8694510eafd385c5cb30d1bccaf4135418710a4ee</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -7683,23 +7683,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr"/>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>64.98999</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>1.8125</t>
+          <t>1.3862</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr"/>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
       <c r="H68" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -7722,7 +7730,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>0x6de105784818e175bb2cb50f54d4325a684a5693a05f8bd5b7f2b402aeb4bdfa</t>
+          <t>0x2d5eca3e665030fe8c7c2a84772b94d8fc59c9a6991fd216ba914d3b345ffe07</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -7752,7 +7760,7 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>1785062111</t>
+          <t>1785062748</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
@@ -7762,7 +7770,7 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>79.98768</t>
+          <t>25.889968</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
@@ -7779,12 +7787,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0x21aa47ce5d327006a8fdcf609e5990b1ea5499887fd8ccd0ff96d5bbe7df2f89</t>
+          <t>0xff313e8a80cab759f0306eced2743a83b68017dd8ecc4a5eda49613abd5f72bb</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -7794,22 +7802,22 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>23.39</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>1.3887</t>
+          <t>1.2275</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Paju Citizen -1</t>
+          <t>Over 3.5</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -7834,7 +7842,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>0x1398d7baccf6c5154c8090892c6597852ff56e90298e81fb604a8b9bf22c47ce</t>
+          <t>0x20fab15d1baac82bbe5a9371ad4e1e4f931edb8de76d814e671a0313aa4d8620</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -7864,7 +7872,7 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>1785061695</t>
+          <t>1785062437</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
@@ -7874,7 +7882,7 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>60.167203</t>
+          <t>43.956044</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
@@ -7891,39 +7899,31 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0xaa13e9d13e81cd9edae13a80c0e426e52c85c5064c5b0c34d792d027f33fe560</t>
+          <t>0x5a88256e6b892595ad641ef1ae589c088b32b6034ec557ba72582fa8c93f67e3</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr">
         <is>
-          <t>17.04</t>
+          <t>64.98999</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.8125</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>Paju Citizen -1.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -7946,7 +7946,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>0x48cd5a7ee72c95f57110826c0f2e2494d9438250815f7751e5e0fdce91ccbfba</t>
+          <t>0x6de105784818e175bb2cb50f54d4325a684a5693a05f8bd5b7f2b402aeb4bdfa</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -7976,7 +7976,7 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>1785061694</t>
+          <t>1785062111</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>58.758621</t>
+          <t>79.98768</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
@@ -8003,31 +8003,39 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0x9c2da91ae7561670702979941233734bebc22c36fdac867bf5bdb53a8151c6e9</t>
+          <t>0x21aa47ce5d327006a8fdcf609e5990b1ea5499887fd8ccd0ff96d5bbe7df2f89</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>4.99997</t>
+          <t>23.39</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>1.795</t>
+          <t>1.3887</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr"/>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Paju Citizen -1</t>
+        </is>
+      </c>
       <c r="H71" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -8035,27 +8043,27 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC vs Yongin City</t>
+          <t>Paju Citizen vs Ansan Greeners</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>0x520e073f044523b55003a1d70f752c30f91cd5ebae7e23b2f294ad6679b3ed58</t>
+          <t>0x1398d7baccf6c5154c8090892c6597852ff56e90298e81fb604a8b9bf22c47ce</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>L19306783</t>
+          <t>L19306782</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -8080,7 +8088,7 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>1785061651</t>
+          <t>1785061695</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
@@ -8090,7 +8098,7 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>6.28927</t>
+          <t>60.167203</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
@@ -8107,7 +8115,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0x12f98497a1f2dc0a130b32665dfeea9bbd9b744c2732456c77c91801ec687167</t>
+          <t>0xaa13e9d13e81cd9edae13a80c0e426e52c85c5064c5b0c34d792d027f33fe560</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -8122,22 +8130,22 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>21.14</t>
+          <t>17.04</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>1.3513</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC -1</t>
+          <t>Paju Citizen -1.5</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -8147,27 +8155,27 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC vs Yongin City</t>
+          <t>Paju Citizen vs Ansan Greeners</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>0x4a4b2cf0de4356e1be221d31aa0feab4af681e89956037ff111c72307c4d9af6</t>
+          <t>0x48cd5a7ee72c95f57110826c0f2e2494d9438250815f7751e5e0fdce91ccbfba</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>L19306783</t>
+          <t>L19306782</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -8192,7 +8200,7 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>1785061621</t>
+          <t>1785061694</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
@@ -8202,7 +8210,7 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>60.185053</t>
+          <t>58.758621</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
@@ -8219,18 +8227,18 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0x0f90aefde05859a865353743603e3925fef0a390e252c71ca62de94b7f3522d8</t>
+          <t>0x9c2da91ae7561670702979941233734bebc22c36fdac867bf5bdb53a8151c6e9</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr">
         <is>
-          <t>43.51167</t>
+          <t>4.99997</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -8296,7 +8304,7 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>1785061621</t>
+          <t>1785061651</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
@@ -8306,7 +8314,7 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>54.73166</t>
+          <t>6.28927</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
@@ -8323,31 +8331,39 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0x45f1170f51d54ba31ead65b241ce33b618358dd91421e9194877f824ebea4f5d</t>
+          <t>0x12f98497a1f2dc0a130b32665dfeea9bbd9b744c2732456c77c91801ec687167</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0x09b3a190a1e971Dd0B4F82Eb9008287fe43a540C</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>21.14</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.3513</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr"/>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen FC -1</t>
+        </is>
+      </c>
       <c r="H74" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -8370,7 +8386,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>0x7b353104df193f280c01b3e0a75dcbbc5dd4e628b7304c3537dff2339968d702</t>
+          <t>0x4a4b2cf0de4356e1be221d31aa0feab4af681e89956037ff111c72307c4d9af6</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -8400,7 +8416,7 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>1785061583</t>
+          <t>1785061621</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
@@ -8410,7 +8426,7 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>51.020408</t>
+          <t>60.185053</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
@@ -8427,18 +8443,18 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0x8726e3d54f033c4394f3b9a8a297c466f26e8d1814d525163146dc1f9f836029</t>
+          <t>0x0f90aefde05859a865353743603e3925fef0a390e252c71ca62de94b7f3522d8</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr">
         <is>
-          <t>5.70997</t>
+          <t>43.51167</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -8504,7 +8520,7 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>1785061581</t>
+          <t>1785061621</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
@@ -8514,7 +8530,7 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>7.182352</t>
+          <t>54.73166</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
@@ -8531,7 +8547,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0x78b589b7ea305b8a325e286dcbf526301e19f803d90ab77960c290d1d621d34a</t>
+          <t>0x45f1170f51d54ba31ead65b241ce33b618358dd91421e9194877f824ebea4f5d</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -8539,31 +8555,23 @@
           <t>0x09b3a190a1e971Dd0B4F82Eb9008287fe43a540C</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr">
         <is>
-          <t>5.01384</t>
+          <t>25</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>1.2788</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -8586,7 +8594,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>0xf93dab40773f0e01839824957e7cecd4afb676d72a13c45521719f4f5c517a27</t>
+          <t>0x7b353104df193f280c01b3e0a75dcbbc5dd4e628b7304c3537dff2339968d702</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -8616,7 +8624,7 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>1785061533</t>
+          <t>1785061583</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
@@ -8626,7 +8634,7 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>17.98687</t>
+          <t>51.020408</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
@@ -8643,7 +8651,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0x64d493da52ab9f3215f2ee6a066aad2cbaf66597963522c2c53462ae6d466e65</t>
+          <t>0x8726e3d54f033c4394f3b9a8a297c466f26e8d1814d525163146dc1f9f836029</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -8654,12 +8662,12 @@
       <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr">
         <is>
-          <t>43.87998</t>
+          <t>5.70997</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>1.7988</t>
+          <t>1.795</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -8720,7 +8728,7 @@
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>1785061346</t>
+          <t>1785061581</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
@@ -8730,7 +8738,7 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>54.935812</t>
+          <t>7.182352</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
@@ -8747,23 +8755,27 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0xb6a5b0e5cc84223b1b456506ce5bc4a60492c7d715d16ce5ba4bcbbbb205e549</t>
+          <t>0x78b589b7ea305b8a325e286dcbf526301e19f803d90ab77960c290d1d621d34a</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr"/>
+          <t>0x09b3a190a1e971Dd0B4F82Eb9008287fe43a540C</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>10.19999</t>
+          <t>5.01384</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>1.7988</t>
+          <t>1.2788</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -8771,7 +8783,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H78" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -8794,7 +8810,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>0x520e073f044523b55003a1d70f752c30f91cd5ebae7e23b2f294ad6679b3ed58</t>
+          <t>0xf93dab40773f0e01839824957e7cecd4afb676d72a13c45521719f4f5c517a27</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -8824,7 +8840,7 @@
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>1785061261</t>
+          <t>1785061533</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
@@ -8834,7 +8850,7 @@
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>12.769941</t>
+          <t>17.98687</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
@@ -8851,18 +8867,18 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0x932ea4448a5d14be89226effb4bcb8584e5004da981b9fb12e769029a2cd6a34</t>
+          <t>0x64d493da52ab9f3215f2ee6a066aad2cbaf66597963522c2c53462ae6d466e65</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>43.87998</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -8928,7 +8944,7 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>1785061250</t>
+          <t>1785061346</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
@@ -8938,7 +8954,7 @@
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>6.259781</t>
+          <t>54.935812</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
@@ -8955,23 +8971,23 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0x6ba96fe1be95723f4530ab62caaff2817e70e2c1aa504d2f0afe5b7d44447528</t>
+          <t>0xb6a5b0e5cc84223b1b456506ce5bc4a60492c7d715d16ce5ba4bcbbbb205e549</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr">
         <is>
-          <t>43.12404</t>
+          <t>10.19999</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>1.7975</t>
+          <t>1.7988</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -9032,7 +9048,7 @@
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>1785061221</t>
+          <t>1785061261</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
@@ -9042,7 +9058,7 @@
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>54.074031</t>
+          <t>12.769941</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
@@ -9059,27 +9075,23 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0xa4c5cc7d130116507c7f97158d19bded9ace84b90e4089b2386235aca563a109</t>
+          <t>0x932ea4448a5d14be89226effb4bcb8584e5004da981b9fb12e769029a2cd6a34</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr">
         <is>
-          <t>5.54</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>1.2537</t>
+          <t>1.7988</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -9087,11 +9099,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -9099,27 +9107,27 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Paju Citizen vs Ansan Greeners</t>
+          <t>Gimpo Citizen FC vs Yongin City</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Gimpo Citizen FC</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>0xabfa364122222118f5f35af9ee862e2b9587e9c2f656e281725fdca100cf17bf</t>
+          <t>0x520e073f044523b55003a1d70f752c30f91cd5ebae7e23b2f294ad6679b3ed58</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>L19306782</t>
+          <t>L19306783</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -9144,7 +9152,7 @@
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>1785060618</t>
+          <t>1785061250</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">
@@ -9154,7 +9162,7 @@
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>21.832512</t>
+          <t>6.259781</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
@@ -9171,18 +9179,18 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0xed6f77aaa7a7dbe5c2457f000b022f2da0cc5bd1004291d76e71044f4e1faa36</t>
+          <t>0x6ba96fe1be95723f4530ab62caaff2817e70e2c1aa504d2f0afe5b7d44447528</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr">
         <is>
-          <t>4.99999</t>
+          <t>43.12404</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -9248,7 +9256,7 @@
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>1785060105</t>
+          <t>1785061221</t>
         </is>
       </c>
       <c r="S82" t="inlineStr">
@@ -9258,7 +9266,7 @@
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>6.26958</t>
+          <t>54.074031</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
@@ -9275,23 +9283,27 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0xe0d4aa08492162b980b70ecc4ec3e9ae46b9fd85fea771f538c542e4e27f10ca</t>
+          <t>0xa4c5cc7d130116507c7f97158d19bded9ace84b90e4089b2386235aca563a109</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>4.99999</t>
+          <t>5.54</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>1.7975</t>
+          <t>1.2537</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -9299,7 +9311,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H83" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -9307,27 +9323,27 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC vs Yongin City</t>
+          <t>Paju Citizen vs Ansan Greeners</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>0x520e073f044523b55003a1d70f752c30f91cd5ebae7e23b2f294ad6679b3ed58</t>
+          <t>0xabfa364122222118f5f35af9ee862e2b9587e9c2f656e281725fdca100cf17bf</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>L19306783</t>
+          <t>L19306782</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -9352,7 +9368,7 @@
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>1785060103</t>
+          <t>1785060618</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
@@ -9362,7 +9378,7 @@
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>6.26958</t>
+          <t>21.832512</t>
         </is>
       </c>
       <c r="U83" t="inlineStr">
@@ -9379,7 +9395,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0x733bd5ce99f877eba370291936b138251c1bd48cee90480bc876f49523ca7fca</t>
+          <t>0xed6f77aaa7a7dbe5c2457f000b022f2da0cc5bd1004291d76e71044f4e1faa36</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -9456,7 +9472,7 @@
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>1785060101</t>
+          <t>1785060105</t>
         </is>
       </c>
       <c r="S84" t="inlineStr">
@@ -9483,39 +9499,31 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0xcfbe574677265ef97dc3204a001ce1b1e25523c8a98c296a3cf235f97650aace</t>
+          <t>0xe0d4aa08492162b980b70ecc4ec3e9ae46b9fd85fea771f538c542e4e27f10ca</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.99999</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>1.3887</t>
+          <t>1.7975</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>Paju Citizen -1</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr"/>
       <c r="H85" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -9523,27 +9531,27 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Paju Citizen vs Ansan Greeners</t>
+          <t>Gimpo Citizen FC vs Yongin City</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Gimpo Citizen FC</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>0x1398d7baccf6c5154c8090892c6597852ff56e90298e81fb604a8b9bf22c47ce</t>
+          <t>0x520e073f044523b55003a1d70f752c30f91cd5ebae7e23b2f294ad6679b3ed58</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>L19306782</t>
+          <t>L19306783</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -9568,7 +9576,7 @@
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>1785060085</t>
+          <t>1785060103</t>
         </is>
       </c>
       <c r="S85" t="inlineStr">
@@ -9578,7 +9586,7 @@
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>10.289389</t>
+          <t>6.26958</t>
         </is>
       </c>
       <c r="U85" t="inlineStr">
@@ -9595,23 +9603,23 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>0xebd1df0aa7e7f54677bedd84a6c923ca856cf657e0531639938bfb8111becc94</t>
+          <t>0x733bd5ce99f877eba370291936b138251c1bd48cee90480bc876f49523ca7fca</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr">
         <is>
-          <t>22.97198</t>
+          <t>4.99999</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>1.7963</t>
+          <t>1.7975</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -9672,7 +9680,7 @@
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>1785060074</t>
+          <t>1785060101</t>
         </is>
       </c>
       <c r="S86" t="inlineStr">
@@ -9682,7 +9690,7 @@
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>28.85021</t>
+          <t>6.26958</t>
         </is>
       </c>
       <c r="U86" t="inlineStr">
@@ -9699,31 +9707,39 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>0x9137623e3c72596dddeb8dd77deb26f0f80f5d8ad5037c9d9fd9ec11f1d3a62d</t>
+          <t>0xcfbe574677265ef97dc3204a001ce1b1e25523c8a98c296a3cf235f97650aace</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>15.59279</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>1.7963</t>
+          <t>1.3887</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr"/>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Paju Citizen -1</t>
+        </is>
+      </c>
       <c r="H87" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -9731,27 +9747,27 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC vs Yongin City</t>
+          <t>Paju Citizen vs Ansan Greeners</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>0x520e073f044523b55003a1d70f752c30f91cd5ebae7e23b2f294ad6679b3ed58</t>
+          <t>0x1398d7baccf6c5154c8090892c6597852ff56e90298e81fb604a8b9bf22c47ce</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>L19306783</t>
+          <t>L19306782</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -9776,7 +9792,7 @@
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>1785060073</t>
+          <t>1785060085</t>
         </is>
       </c>
       <c r="S87" t="inlineStr">
@@ -9786,7 +9802,7 @@
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>19.582782</t>
+          <t>10.289389</t>
         </is>
       </c>
       <c r="U87" t="inlineStr">
@@ -9803,7 +9819,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>0x47fecae2c93459e7d6a1189dcb95e8bce239b7e2d26ce67db4733b564451a3fd</t>
+          <t>0xebd1df0aa7e7f54677bedd84a6c923ca856cf657e0531639938bfb8111becc94</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -9814,7 +9830,7 @@
       <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr">
         <is>
-          <t>16.1469</t>
+          <t>22.97198</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -9880,7 +9896,7 @@
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>1785060072</t>
+          <t>1785060074</t>
         </is>
       </c>
       <c r="S88" t="inlineStr">
@@ -9890,7 +9906,7 @@
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>20.278681</t>
+          <t>28.85021</t>
         </is>
       </c>
       <c r="U88" t="inlineStr">
@@ -9907,27 +9923,23 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>0x7851323bb653ef81f86e4483a09baec3f52472a947788d079eacebc8ce474280</t>
+          <t>0x9137623e3c72596dddeb8dd77deb26f0f80f5d8ad5037c9d9fd9ec11f1d3a62d</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr"/>
       <c r="D89" t="inlineStr">
         <is>
-          <t>19.02</t>
+          <t>15.59279</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>1.275</t>
+          <t>1.7963</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -9935,11 +9947,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -9962,7 +9970,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>0xf93dab40773f0e01839824957e7cecd4afb676d72a13c45521719f4f5c517a27</t>
+          <t>0x520e073f044523b55003a1d70f752c30f91cd5ebae7e23b2f294ad6679b3ed58</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
@@ -9992,7 +10000,7 @@
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>1785060054</t>
+          <t>1785060073</t>
         </is>
       </c>
       <c r="S89" t="inlineStr">
@@ -10002,7 +10010,7 @@
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t>69.163636</t>
+          <t>19.582782</t>
         </is>
       </c>
       <c r="U89" t="inlineStr">
@@ -10019,27 +10027,23 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>0x5936a0069456d68663344829a3e2e9aa688da6a9e1d38de76848d1bdfb84366a</t>
+          <t>0x47fecae2c93459e7d6a1189dcb95e8bce239b7e2d26ce67db4733b564451a3fd</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr">
         <is>
-          <t>10.56</t>
+          <t>16.1469</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>1.2737</t>
+          <t>1.7963</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -10047,11 +10051,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -10074,7 +10074,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>0xf93dab40773f0e01839824957e7cecd4afb676d72a13c45521719f4f5c517a27</t>
+          <t>0x520e073f044523b55003a1d70f752c30f91cd5ebae7e23b2f294ad6679b3ed58</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -10104,7 +10104,7 @@
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>1785060044</t>
+          <t>1785060072</t>
         </is>
       </c>
       <c r="S90" t="inlineStr">
@@ -10114,7 +10114,7 @@
       </c>
       <c r="T90" t="inlineStr">
         <is>
-          <t>38.575342</t>
+          <t>20.278681</t>
         </is>
       </c>
       <c r="U90" t="inlineStr">
@@ -10131,31 +10131,39 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>0xc27dc932de76aa5047aab63fd483f2351fd3e777a4bebc494353cf3a53c52ba9</t>
+          <t>0x7851323bb653ef81f86e4483a09baec3f52472a947788d079eacebc8ce474280</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>20.61772</t>
+          <t>19.02</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>1.3425</t>
+          <t>1.275</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H91" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -10163,27 +10171,27 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Paju Citizen vs Ansan Greeners</t>
+          <t>Gimpo Citizen FC vs Yongin City</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Gimpo Citizen FC</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>0x386468865ee4fb2d064354b0f4bb50fc57a8f046452fa6667bc56978f4cf3823</t>
+          <t>0xf93dab40773f0e01839824957e7cecd4afb676d72a13c45521719f4f5c517a27</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>L19306782</t>
+          <t>L19306783</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
@@ -10208,7 +10216,7 @@
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>1785059855</t>
+          <t>1785060054</t>
         </is>
       </c>
       <c r="S91" t="inlineStr">
@@ -10218,7 +10226,7 @@
       </c>
       <c r="T91" t="inlineStr">
         <is>
-          <t>60.197723</t>
+          <t>69.163636</t>
         </is>
       </c>
       <c r="U91" t="inlineStr">
@@ -10235,12 +10243,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>0x06cf39065296686830cf556b4943f2a94e035610868690980b237da489f6c32a</t>
+          <t>0x5936a0069456d68663344829a3e2e9aa688da6a9e1d38de76848d1bdfb84366a</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -10250,22 +10258,22 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>4.94155</t>
+          <t>10.56</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>1.355</t>
+          <t>1.2737</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC -1</t>
+          <t>Tie</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -10290,7 +10298,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>0x4a4b2cf0de4356e1be221d31aa0feab4af681e89956037ff111c72307c4d9af6</t>
+          <t>0xf93dab40773f0e01839824957e7cecd4afb676d72a13c45521719f4f5c517a27</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -10320,7 +10328,7 @@
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>1785059821</t>
+          <t>1785060044</t>
         </is>
       </c>
       <c r="S92" t="inlineStr">
@@ -10330,7 +10338,7 @@
       </c>
       <c r="T92" t="inlineStr">
         <is>
-          <t>13.919859</t>
+          <t>38.575342</t>
         </is>
       </c>
       <c r="U92" t="inlineStr">
@@ -10347,7 +10355,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>0x6cad572e295e86d0eff792e6a73f1ecb4b2563c632f3a61d710a79a81bcbefc5</t>
+          <t>0xc27dc932de76aa5047aab63fd483f2351fd3e777a4bebc494353cf3a53c52ba9</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -10355,31 +10363,23 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C93" t="inlineStr"/>
       <c r="D93" t="inlineStr">
         <is>
-          <t>16.43</t>
+          <t>20.61772</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>1.355</t>
+          <t>1.3425</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>Gimpo Citizen FC -1</t>
-        </is>
-      </c>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr"/>
       <c r="H93" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -10387,27 +10387,27 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC vs Yongin City</t>
+          <t>Paju Citizen vs Ansan Greeners</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>0x4a4b2cf0de4356e1be221d31aa0feab4af681e89956037ff111c72307c4d9af6</t>
+          <t>0x386468865ee4fb2d064354b0f4bb50fc57a8f046452fa6667bc56978f4cf3823</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>L19306783</t>
+          <t>L19306782</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
@@ -10432,7 +10432,7 @@
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>1785059820</t>
+          <t>1785059855</t>
         </is>
       </c>
       <c r="S93" t="inlineStr">
@@ -10442,7 +10442,7 @@
       </c>
       <c r="T93" t="inlineStr">
         <is>
-          <t>46.28169</t>
+          <t>60.197723</t>
         </is>
       </c>
       <c r="U93" t="inlineStr">
@@ -10459,31 +10459,39 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>0xd90cf2f29f54991a5ee8c926cce019177b5bb5fd98602218fb9acaaf6a910664</t>
+          <t>0x06cf39065296686830cf556b4943f2a94e035610868690980b237da489f6c32a</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4.94155</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>1.4675</t>
+          <t>1.355</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr"/>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen FC -1</t>
+        </is>
+      </c>
       <c r="H94" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -10491,27 +10499,27 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Paju Citizen vs Ansan Greeners</t>
+          <t>Gimpo Citizen FC vs Yongin City</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Gimpo Citizen FC</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>0x90106aa6ffeea165b450ea7a1094c65ae9db8d6fdde000ce479b4af5b3fa3072</t>
+          <t>0x4a4b2cf0de4356e1be221d31aa0feab4af681e89956037ff111c72307c4d9af6</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>L19306782</t>
+          <t>L19306783</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -10536,7 +10544,7 @@
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>1785058466</t>
+          <t>1785059821</t>
         </is>
       </c>
       <c r="S94" t="inlineStr">
@@ -10546,7 +10554,7 @@
       </c>
       <c r="T94" t="inlineStr">
         <is>
-          <t>23.529412</t>
+          <t>13.919859</t>
         </is>
       </c>
       <c r="U94" t="inlineStr">
@@ -10563,12 +10571,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>0xfaacadf40a626e2b5b306c37ecce7325e0fabbb091c125c037dd14587c31bfe4</t>
+          <t>0x6cad572e295e86d0eff792e6a73f1ecb4b2563c632f3a61d710a79a81bcbefc5</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -10578,39 +10586,39 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>4.53</t>
+          <t>16.43</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>1.5212</t>
+          <t>1.355</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
+          <t>Gimpo Citizen FC -1</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>K2-League</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen FC vs Yongin City</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
           <t>Gimpo Citizen FC</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>K2-League</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>Gimpo Citizen FC vs Yongin City</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>Gimpo Citizen FC</t>
-        </is>
-      </c>
       <c r="K95" t="inlineStr">
         <is>
           <t>Yongin City</t>
@@ -10618,7 +10626,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>0x2725ecc350e6d5314ddee250cd3e445f586ab55a992fc73108db0913c5a41f24</t>
+          <t>0x4a4b2cf0de4356e1be221d31aa0feab4af681e89956037ff111c72307c4d9af6</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -10648,7 +10656,7 @@
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>1785057353</t>
+          <t>1785059820</t>
         </is>
       </c>
       <c r="S95" t="inlineStr">
@@ -10658,7 +10666,7 @@
       </c>
       <c r="T95" t="inlineStr">
         <is>
-          <t>8.690647</t>
+          <t>46.28169</t>
         </is>
       </c>
       <c r="U95" t="inlineStr">
@@ -10675,27 +10683,23 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>0x182964c6008d5b7d29731fd19876092a52fa2068fcb16aaf430dd8e0a6009721</t>
+          <t>0xd90cf2f29f54991a5ee8c926cce019177b5bb5fd98602218fb9acaaf6a910664</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr">
         <is>
-          <t>3.73</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>1.2763</t>
+          <t>1.4675</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -10703,11 +10707,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G96" t="inlineStr"/>
       <c r="H96" t="inlineStr">
         <is>
           <t>K2-League</t>
@@ -10715,27 +10715,27 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC vs Yongin City</t>
+          <t>Paju Citizen vs Ansan Greeners</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>0xf93dab40773f0e01839824957e7cecd4afb676d72a13c45521719f4f5c517a27</t>
+          <t>0x90106aa6ffeea165b450ea7a1094c65ae9db8d6fdde000ce479b4af5b3fa3072</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>L19306783</t>
+          <t>L19306782</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
@@ -10760,7 +10760,7 @@
       </c>
       <c r="R96" t="inlineStr">
         <is>
-          <t>1785057212</t>
+          <t>1785058466</t>
         </is>
       </c>
       <c r="S96" t="inlineStr">
@@ -10770,7 +10770,7 @@
       </c>
       <c r="T96" t="inlineStr">
         <is>
-          <t>13.502262</t>
+          <t>23.529412</t>
         </is>
       </c>
       <c r="U96" t="inlineStr">
@@ -10787,12 +10787,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>0xae029509b64a4e0489363d3aa1a7e18db0cd21b4fb65f5064e49185bb4bfb2f6</t>
+          <t>0xfaacadf40a626e2b5b306c37ecce7325e0fabbb091c125c037dd14587c31bfe4</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -10802,12 +10802,12 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.53</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.5212</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -10872,7 +10872,7 @@
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>1785056897</t>
+          <t>1785057353</t>
         </is>
       </c>
       <c r="S97" t="inlineStr">
@@ -10882,7 +10882,7 @@
       </c>
       <c r="T97" t="inlineStr">
         <is>
-          <t>9.615385</t>
+          <t>8.690647</t>
         </is>
       </c>
       <c r="U97" t="inlineStr">
@@ -10899,7 +10899,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>0xd359a1bde933becdef3ca166f20bbe9291a9b81f961befead4bc72e1713c6447</t>
+          <t>0x182964c6008d5b7d29731fd19876092a52fa2068fcb16aaf430dd8e0a6009721</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -10914,12 +10914,12 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>4.53999</t>
+          <t>3.73</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.2763</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -10929,24 +10929,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>K2-League</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen FC vs Yongin City</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
           <t>Gimpo Citizen FC</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>K2-League</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>Gimpo Citizen FC vs Yongin City</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>Gimpo Citizen FC</t>
-        </is>
-      </c>
       <c r="K98" t="inlineStr">
         <is>
           <t>Yongin City</t>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>0x2725ecc350e6d5314ddee250cd3e445f586ab55a992fc73108db0913c5a41f24</t>
+          <t>0xf93dab40773f0e01839824957e7cecd4afb676d72a13c45521719f4f5c517a27</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -10984,7 +10984,7 @@
       </c>
       <c r="R98" t="inlineStr">
         <is>
-          <t>1785056453</t>
+          <t>1785057212</t>
         </is>
       </c>
       <c r="S98" t="inlineStr">
@@ -10994,7 +10994,7 @@
       </c>
       <c r="T98" t="inlineStr">
         <is>
-          <t>8.73075</t>
+          <t>13.502262</t>
         </is>
       </c>
       <c r="U98" t="inlineStr">
@@ -11011,12 +11011,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>0xe5784e1cc6cec364d74a7267a701924cf5f6543fed6d0c11d5f756f735c714f2</t>
+          <t>0xae029509b64a4e0489363d3aa1a7e18db0cd21b4fb65f5064e49185bb4bfb2f6</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -11026,7 +11026,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -11096,7 +11096,7 @@
       </c>
       <c r="R99" t="inlineStr">
         <is>
-          <t>1785056153</t>
+          <t>1785056897</t>
         </is>
       </c>
       <c r="S99" t="inlineStr">
@@ -11106,7 +11106,7 @@
       </c>
       <c r="T99" t="inlineStr">
         <is>
-          <t>8.75</t>
+          <t>9.615385</t>
         </is>
       </c>
       <c r="U99" t="inlineStr">
@@ -11123,7 +11123,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>0x2fe44b6f9df282a6669198530843764a881fcd8c491dca571eaacc128af126e6</t>
+          <t>0xd359a1bde933becdef3ca166f20bbe9291a9b81f961befead4bc72e1713c6447</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -11138,12 +11138,12 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>9.99999</t>
+          <t>4.53999</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>1.5425</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -11153,7 +11153,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Gimpo Citizen FC</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -11163,27 +11163,27 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Paju Citizen vs Ansan Greeners</t>
+          <t>Gimpo Citizen FC vs Yongin City</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Gimpo Citizen FC</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>0x90106aa6ffeea165b450ea7a1094c65ae9db8d6fdde000ce479b4af5b3fa3072</t>
+          <t>0x2725ecc350e6d5314ddee250cd3e445f586ab55a992fc73108db0913c5a41f24</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>L19306782</t>
+          <t>L19306783</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
@@ -11208,7 +11208,7 @@
       </c>
       <c r="R100" t="inlineStr">
         <is>
-          <t>1785056005</t>
+          <t>1785056453</t>
         </is>
       </c>
       <c r="S100" t="inlineStr">
@@ -11218,7 +11218,7 @@
       </c>
       <c r="T100" t="inlineStr">
         <is>
-          <t>18.433161</t>
+          <t>8.73075</t>
         </is>
       </c>
       <c r="U100" t="inlineStr">
@@ -11235,7 +11235,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>0x318bf0ba1d202676e38a34cf3a263bf2f98d89a54dbf8acb2cccc6beaedcc4e8</t>
+          <t>0xe5784e1cc6cec364d74a7267a701924cf5f6543fed6d0c11d5f756f735c714f2</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>1.2575</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -11265,7 +11265,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Gimpo Citizen FC</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -11275,27 +11275,27 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Paju Citizen vs Ansan Greeners</t>
+          <t>Gimpo Citizen FC vs Yongin City</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Gimpo Citizen FC</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>0xabfa364122222118f5f35af9ee862e2b9587e9c2f656e281725fdca100cf17bf</t>
+          <t>0x2725ecc350e6d5314ddee250cd3e445f586ab55a992fc73108db0913c5a41f24</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>L19306782</t>
+          <t>L19306783</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
@@ -11320,7 +11320,7 @@
       </c>
       <c r="R101" t="inlineStr">
         <is>
-          <t>1785055933</t>
+          <t>1785056153</t>
         </is>
       </c>
       <c r="S101" t="inlineStr">
@@ -11330,7 +11330,7 @@
       </c>
       <c r="T101" t="inlineStr">
         <is>
-          <t>4.970874</t>
+          <t>8.75</t>
         </is>
       </c>
       <c r="U101" t="inlineStr">
@@ -11347,7 +11347,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>0x5dc684f3ea699d27149c867fb82e4e6f97c7382b6d8784e4edd5bf70e604bae2</t>
+          <t>0x2fe44b6f9df282a6669198530843764a881fcd8c491dca571eaacc128af126e6</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -11362,12 +11362,12 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>9.99999</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>1.2575</t>
+          <t>1.5425</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -11377,7 +11377,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -11402,7 +11402,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>0xabfa364122222118f5f35af9ee862e2b9587e9c2f656e281725fdca100cf17bf</t>
+          <t>0x90106aa6ffeea165b450ea7a1094c65ae9db8d6fdde000ce479b4af5b3fa3072</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -11432,7 +11432,7 @@
       </c>
       <c r="R102" t="inlineStr">
         <is>
-          <t>1785055931</t>
+          <t>1785056005</t>
         </is>
       </c>
       <c r="S102" t="inlineStr">
@@ -11442,7 +11442,7 @@
       </c>
       <c r="T102" t="inlineStr">
         <is>
-          <t>9.941748</t>
+          <t>18.433161</t>
         </is>
       </c>
       <c r="U102" t="inlineStr">
@@ -11459,7 +11459,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>0x947b403314498890960e964926f3e25010f3b36a93afc49e309f7a71a57648b0</t>
+          <t>0x318bf0ba1d202676e38a34cf3a263bf2f98d89a54dbf8acb2cccc6beaedcc4e8</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -11474,12 +11474,12 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.2575</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -11489,7 +11489,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC</t>
+          <t>Tie</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -11499,27 +11499,27 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC vs Yongin City</t>
+          <t>Paju Citizen vs Ansan Greeners</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>Gimpo Citizen FC</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>0x2725ecc350e6d5314ddee250cd3e445f586ab55a992fc73108db0913c5a41f24</t>
+          <t>0xabfa364122222118f5f35af9ee862e2b9587e9c2f656e281725fdca100cf17bf</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>L19306783</t>
+          <t>L19306782</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
@@ -11544,7 +11544,7 @@
       </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>1785055853</t>
+          <t>1785055933</t>
         </is>
       </c>
       <c r="S103" t="inlineStr">
@@ -11554,7 +11554,7 @@
       </c>
       <c r="T103" t="inlineStr">
         <is>
-          <t>8.75</t>
+          <t>4.970874</t>
         </is>
       </c>
       <c r="U103" t="inlineStr">
@@ -11571,110 +11571,334 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
+          <t>0x5dc684f3ea699d27149c867fb82e4e6f97c7382b6d8784e4edd5bf70e604bae2</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>2.56</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>1.2575</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>K2-League</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>Paju Citizen vs Ansan Greeners</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>Paju Citizen</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Ansan Greeners</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>0xabfa364122222118f5f35af9ee862e2b9587e9c2f656e281725fdca100cf17bf</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>L19306782</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q104" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R104" t="inlineStr">
+        <is>
+          <t>1785055931</t>
+        </is>
+      </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>1785061800</t>
+        </is>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>9.941748</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>0x947b403314498890960e964926f3e25010f3b36a93afc49e309f7a71a57648b0</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>4.55</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen FC</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>K2-League</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen FC vs Yongin City</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen FC</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Yongin City</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>0x2725ecc350e6d5314ddee250cd3e445f586ab55a992fc73108db0913c5a41f24</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>L19306783</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q105" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R105" t="inlineStr">
+        <is>
+          <t>1785055853</t>
+        </is>
+      </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>1785061800</t>
+        </is>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>8.75</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
           <t>0x4df42281e0de14de14275865cafadfb98d1cc6f76c1873f8fd64bcaa2cae8075</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr">
+      <c r="B106" t="inlineStr">
         <is>
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
         <is>
           <t>4.99</t>
         </is>
       </c>
-      <c r="E104" t="inlineStr">
+      <c r="E106" t="inlineStr">
         <is>
           <t>1.2775</t>
         </is>
       </c>
-      <c r="F104" t="inlineStr">
+      <c r="F106" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr">
+      <c r="G106" t="inlineStr">
         <is>
           <t>Tie</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
+      <c r="H106" t="inlineStr">
         <is>
           <t>K2-League</t>
         </is>
       </c>
-      <c r="I104" t="inlineStr">
+      <c r="I106" t="inlineStr">
         <is>
           <t>Gimpo Citizen FC vs Yongin City</t>
         </is>
       </c>
-      <c r="J104" t="inlineStr">
+      <c r="J106" t="inlineStr">
         <is>
           <t>Gimpo Citizen FC</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr">
+      <c r="K106" t="inlineStr">
         <is>
           <t>Yongin City</t>
         </is>
       </c>
-      <c r="L104" t="inlineStr">
+      <c r="L106" t="inlineStr">
         <is>
           <t>0xf93dab40773f0e01839824957e7cecd4afb676d72a13c45521719f4f5c517a27</t>
         </is>
       </c>
-      <c r="M104" t="inlineStr">
+      <c r="M106" t="inlineStr">
         <is>
           <t>L19306783</t>
         </is>
       </c>
-      <c r="N104" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O104" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P104" t="inlineStr">
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P106" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q104" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R104" t="inlineStr">
+      <c r="Q106" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R106" t="inlineStr">
         <is>
           <t>1785044379</t>
         </is>
       </c>
-      <c r="S104" t="inlineStr">
+      <c r="S106" t="inlineStr">
         <is>
           <t>1785061800</t>
         </is>
       </c>
-      <c r="T104" t="inlineStr">
+      <c r="T106" t="inlineStr">
         <is>
           <t>17.981982</t>
         </is>
       </c>
-      <c r="U104" t="inlineStr">
+      <c r="U106" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V104" t="inlineStr">
+      <c r="V106" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>
